--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathi\Documents\6. DATA PACE\0. Dashboard\Fichiers sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7FCC8D3-854C-4287-B32F-63786C395F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4E1BBA-5F97-423D-A5FC-4268F61649DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10K" sheetId="1" r:id="rId1"/>
@@ -4085,6 +4085,15 @@
       <c r="D19" t="s">
         <v>74</v>
       </c>
+      <c r="K19">
+        <v>17886</v>
+      </c>
+      <c r="M19">
+        <v>18642</v>
+      </c>
+      <c r="N19">
+        <v>21552</v>
+      </c>
       <c r="O19">
         <v>22030</v>
       </c>
@@ -4092,7 +4101,34 @@
         <v>23674</v>
       </c>
       <c r="Q19">
-        <v>24990</v>
+        <v>24980</v>
+      </c>
+      <c r="R19">
+        <v>30371</v>
+      </c>
+      <c r="S19">
+        <v>32913</v>
+      </c>
+      <c r="T19">
+        <v>34879</v>
+      </c>
+      <c r="U19">
+        <v>37108</v>
+      </c>
+      <c r="V19">
+        <v>38326</v>
+      </c>
+      <c r="W19">
+        <v>36510</v>
+      </c>
+      <c r="X19">
+        <v>33868</v>
+      </c>
+      <c r="Y19">
+        <v>18764</v>
+      </c>
+      <c r="Z19">
+        <v>41332</v>
       </c>
       <c r="AA19">
         <v>45387</v>
@@ -4594,16 +4630,19 @@
         <v>165</v>
       </c>
       <c r="V39">
-        <v>43754</v>
+        <v>42412</v>
       </c>
       <c r="W39">
-        <v>42091</v>
+        <v>31956</v>
       </c>
       <c r="X39">
-        <v>48073</v>
+        <v>35181</v>
+      </c>
+      <c r="Y39">
+        <v>27114</v>
       </c>
       <c r="Z39">
-        <v>34357</v>
+        <v>34365</v>
       </c>
       <c r="AA39">
         <v>51234</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -531,28 +531,6 @@
           <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
         <v>9811</v>
       </c>
@@ -582,28 +560,6 @@
           <t>10K Montmartre</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
           <t>-</t>
@@ -639,28 +595,6 @@
           <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>13706</v>
       </c>
@@ -690,28 +624,6 @@
           <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
         <v>11275</v>
       </c>
@@ -741,28 +653,6 @@
           <t>Cooper River Bridge Run</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
         <v>22336</v>
       </c>
@@ -772,7 +662,6 @@
       <c r="AB6" t="n">
         <v>31203</v>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,28 +679,6 @@
           <t>Vancouver Sun Run</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
         <v>25108</v>
       </c>
@@ -821,7 +688,6 @@
       <c r="AB7" t="n">
         <v>39385</v>
       </c>
-      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -839,28 +705,6 @@
           <t>Statesman Capitol 10K</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
         <v>22059</v>
       </c>
@@ -870,7 +714,6 @@
       <c r="AB8" t="n">
         <v>19327</v>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -888,28 +731,6 @@
           <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
         <v>14985</v>
       </c>
@@ -919,7 +740,6 @@
       <c r="AB9" t="n">
         <v>18157</v>
       </c>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -937,28 +757,6 @@
           <t>Bangsaen10</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
         <v>6035</v>
       </c>
@@ -968,7 +766,6 @@
       <c r="AB10" t="n">
         <v>7142</v>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -986,36 +783,12 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
         <v>15291</v>
       </c>
       <c r="AB11" t="n">
         <v>16778</v>
       </c>
-      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1033,28 +806,6 @@
           <t>BOLDERBoulder 10K</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
         <v>35639</v>
       </c>
@@ -1064,7 +815,6 @@
       <c r="AB12" t="n">
         <v>45055</v>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1082,28 +832,6 @@
           <t>Adidas 10K Paris</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
         <v>24629</v>
       </c>
@@ -1113,7 +841,6 @@
       <c r="AB13" t="n">
         <v>34353</v>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1131,28 +858,6 @@
           <t>Royal Run</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
         <v>11329</v>
       </c>
@@ -1162,7 +867,6 @@
       <c r="AB14" t="n">
         <v>13543</v>
       </c>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1180,28 +884,6 @@
           <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
         <v>41806</v>
       </c>
@@ -1211,7 +893,6 @@
       <c r="AB15" t="n">
         <v>43654</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1229,28 +910,6 @@
           <t>Saucony London 10K</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
         <v>13368</v>
       </c>
@@ -1260,7 +919,6 @@
       <c r="AB16" t="n">
         <v>13067</v>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1278,28 +936,6 @@
           <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
         <v>20274</v>
       </c>
@@ -1309,7 +945,6 @@
       <c r="AB17" t="n">
         <v>24703</v>
       </c>
-      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1327,28 +962,6 @@
           <t>Vitality London 10,000</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
         <v>12201</v>
       </c>
@@ -1358,7 +971,6 @@
       <c r="AB18" t="n">
         <v>17154</v>
       </c>
-      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1376,28 +988,6 @@
           <t>Run in Lyon</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
         <v>13566</v>
       </c>
@@ -1407,7 +997,6 @@
       <c r="AB19" t="n">
         <v>11338</v>
       </c>
-      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1425,28 +1014,6 @@
           <t>ASICS LDNX</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
           <t>-</t>
@@ -1460,7 +1027,6 @@
       <c r="AB20" t="n">
         <v>4681</v>
       </c>
-      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1478,28 +1044,6 @@
           <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
         <v>31292</v>
       </c>
@@ -1509,7 +1053,6 @@
       <c r="AB21" t="n">
         <v>36534</v>
       </c>
-      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1527,31 +1070,6 @@
           <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>16283</v>
       </c>
@@ -1681,34 +1199,9 @@
           <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
         <v>22872</v>
       </c>
-      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1726,29 +1219,6 @@
           <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>13715</v>
       </c>
@@ -1775,29 +1245,6 @@
           <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>12135</v>
       </c>
@@ -1824,30 +1271,6 @@
           <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
         <v>13416</v>
       </c>
@@ -1871,30 +1294,6 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
         <v>11453</v>
       </c>
@@ -1918,28 +1317,6 @@
           <t>Riyadh Marathon</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
         <v>288</v>
       </c>
@@ -1969,28 +1346,6 @@
           <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
         <v>17624</v>
       </c>
@@ -2020,28 +1375,6 @@
           <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
         <v>11865</v>
       </c>
@@ -2071,29 +1404,6 @@
           <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>2942</v>
       </c>
@@ -2120,30 +1430,6 @@
           <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
         <v>5732</v>
       </c>
@@ -2167,31 +1453,6 @@
           <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
         <v>9638</v>
       </c>
@@ -2212,16 +1473,6 @@
           <t>HOKA Semi de Paris</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>22030</v>
       </c>
@@ -2231,15 +1482,6 @@
       <c r="P13" t="n">
         <v>24990</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
         <v>45387</v>
       </c>
@@ -2269,28 +1511,6 @@
           <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
         <v>26104</v>
       </c>
@@ -2300,7 +1520,6 @@
       <c r="AB14" t="n">
         <v>34742</v>
       </c>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2318,30 +1537,6 @@
           <t>United Airlines NYC Half</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
         <v>28677</v>
       </c>
@@ -2365,34 +1560,9 @@
           <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="n">
         <v>20918</v>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2410,30 +1580,6 @@
           <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="n">
         <v>19624</v>
       </c>
@@ -2457,29 +1603,6 @@
           <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
         <v>13245</v>
       </c>
@@ -2506,30 +1629,6 @@
           <t>Disney Princess Half Marathon</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="n">
         <v>15879</v>
       </c>
@@ -2553,36 +1652,12 @@
           <t>Warsaw Half Marathon</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
         <v>13422</v>
       </c>
       <c r="AB20" t="n">
         <v>14605</v>
       </c>
-      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2600,28 +1675,6 @@
           <t>Generali Prague Half Marathon</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
         <v>10213</v>
       </c>
@@ -2631,7 +1684,6 @@
       <c r="AB21" t="n">
         <v>14144</v>
       </c>
-      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2649,34 +1701,9 @@
           <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="n">
         <v>12363</v>
       </c>
-      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2694,30 +1721,6 @@
           <t>GetPro Bath Half</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="n">
         <v>11133</v>
       </c>
@@ -2741,28 +1744,6 @@
           <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
         <v>7225</v>
       </c>
@@ -2792,34 +1773,9 @@
           <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="n">
         <v>24590</v>
       </c>
-      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2837,36 +1793,12 @@
           <t>London Landmarks Half Marathon</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="n">
         <v>18869</v>
       </c>
       <c r="AB26" t="n">
         <v>19968</v>
       </c>
-      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2884,28 +1816,6 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
         <v>15306</v>
       </c>
@@ -2915,7 +1825,6 @@
       <c r="AB27" t="n">
         <v>19356</v>
       </c>
-      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2933,34 +1842,9 @@
           <t>Vienna City Half Marathon</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="n">
         <v>12788</v>
       </c>
-      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2978,34 +1862,9 @@
           <t>21K de Montréal</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="n">
         <v>11795</v>
       </c>
-      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3023,34 +1882,9 @@
           <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="n">
         <v>10776</v>
       </c>
-      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3068,40 +1902,18 @@
           <t xml:space="preserve">Göteborgsvarvet </t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>44099</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>45015</v>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
         <v>40765</v>
       </c>
       <c r="AB31" t="n">
         <v>46706</v>
       </c>
-      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3119,34 +1931,9 @@
           <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="n">
         <v>28474</v>
       </c>
-      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3164,34 +1951,9 @@
           <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
         <v>20531</v>
       </c>
-      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3209,34 +1971,9 @@
           <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="n">
         <v>17697</v>
       </c>
-      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3254,34 +1991,9 @@
           <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="n">
         <v>17222</v>
       </c>
-      <c r="AC35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3299,34 +2011,9 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="n">
         <v>12300</v>
       </c>
-      <c r="AC36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3344,34 +2031,9 @@
           <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="n">
         <v>10768</v>
       </c>
-      <c r="AC37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3389,34 +2051,9 @@
           <t>Broløbet - The Bridge Run</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="n">
         <v>40241</v>
       </c>
-      <c r="AC38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3434,34 +2071,9 @@
           <t>Media Maraton de Bogota</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="n">
         <v>21011</v>
       </c>
-      <c r="AC39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3479,34 +2091,9 @@
           <t>Asics Run Melbourne</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="n">
         <v>11218</v>
       </c>
-      <c r="AC40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3524,42 +2111,21 @@
           <t>AJ Bell Great North Run</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>35777</v>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
         <v>39459</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>41615</v>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="n">
         <v>43768</v>
       </c>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="n">
         <v>46258</v>
       </c>
-      <c r="AC41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3577,28 +2143,6 @@
           <t>Copenhagen Half Marathon</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="n">
         <v>24381</v>
       </c>
@@ -3608,7 +2152,6 @@
       <c r="AB42" t="n">
         <v>31440</v>
       </c>
-      <c r="AC42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3626,34 +2169,9 @@
           <t>The Big Half</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="n">
         <v>17223</v>
       </c>
-      <c r="AC43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3671,36 +2189,12 @@
           <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="n">
         <v>7392</v>
       </c>
       <c r="AB44" t="n">
         <v>8918</v>
       </c>
-      <c r="AC44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3718,34 +2212,9 @@
           <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="n">
         <v>26060</v>
       </c>
-      <c r="AC45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3763,34 +2232,9 @@
           <t>Cardiff Half Marathon</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="n">
         <v>24634</v>
       </c>
-      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3808,34 +2252,9 @@
           <t>Manchester Half Marathon</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="n">
         <v>22354</v>
       </c>
-      <c r="AC47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3853,34 +2272,9 @@
           <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="n">
         <v>18564</v>
       </c>
-      <c r="AC48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3898,28 +2292,6 @@
           <t>Run in Lyon</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
         <v>11065</v>
       </c>
@@ -3929,7 +2301,6 @@
       <c r="AB49" t="n">
         <v>16280</v>
       </c>
-      <c r="AC49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3947,34 +2318,9 @@
           <t>Royal Parks Half Marathon</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="n">
         <v>16201</v>
       </c>
-      <c r="AC50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3992,34 +2338,9 @@
           <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="n">
         <v>14635</v>
       </c>
-      <c r="AC51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4037,34 +2358,9 @@
           <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="n">
         <v>13341</v>
       </c>
-      <c r="AC52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4082,34 +2378,9 @@
           <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="n">
         <v>12156</v>
       </c>
-      <c r="AC53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4127,34 +2398,9 @@
           <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="n">
         <v>11471</v>
       </c>
-      <c r="AC54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4172,28 +2418,6 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="n">
         <v>10690</v>
       </c>
@@ -4203,7 +2427,6 @@
       <c r="AB55" t="n">
         <v>11416</v>
       </c>
-      <c r="AC55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4221,34 +2444,9 @@
           <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="n">
         <v>10752</v>
       </c>
-      <c r="AC56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4266,28 +2464,6 @@
           <t xml:space="preserve">Hyundai Meia Maratona </t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
         <v>6567</v>
       </c>
@@ -4297,7 +2473,6 @@
       <c r="AB57" t="n">
         <v>7635</v>
       </c>
-      <c r="AC57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4315,34 +2490,9 @@
           <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="n">
         <v>10896</v>
       </c>
-      <c r="AC58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4360,28 +2510,6 @@
           <t>Taipei Half Marathon</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="n">
         <v>16689</v>
       </c>
@@ -4391,7 +2519,6 @@
       <c r="AB59" t="n">
         <v>16954</v>
       </c>
-      <c r="AC59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4409,34 +2536,9 @@
           <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="n">
         <v>14747</v>
       </c>
-      <c r="AC60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4454,28 +2556,6 @@
           <t>Bangsaen21</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="n">
         <v>9126</v>
       </c>
@@ -4485,7 +2565,6 @@
       <c r="AB61" t="n">
         <v>10364</v>
       </c>
-      <c r="AC61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4503,34 +2582,9 @@
           <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="n">
         <v>10178</v>
       </c>
-      <c r="AC62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4657,28 +2711,6 @@
           <t>Chevron Houston Marathon</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
         <v>6104</v>
       </c>
@@ -4708,28 +2740,6 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
         <v>7238</v>
       </c>
@@ -4759,28 +2769,6 @@
           <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
         <v>8228</v>
       </c>
@@ -4810,28 +2798,6 @@
           <t>Seoul Marathon</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
         <v>25905</v>
       </c>
@@ -4841,7 +2807,6 @@
       <c r="AB5" t="n">
         <v>19112</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4859,13 +2824,6 @@
           <t>Tokyo Marathon</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>25102</v>
       </c>
@@ -4908,7 +2866,6 @@
       <c r="X6" t="n">
         <v>18272</v>
       </c>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
         <v>36560</v>
       </c>
@@ -4938,28 +2895,6 @@
           <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
         <v>10853</v>
       </c>
@@ -4989,28 +2924,6 @@
           <t>Acea Run Rome The Marathon</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
         <v>11235</v>
       </c>
@@ -5020,7 +2933,6 @@
       <c r="AB8" t="n">
         <v>21930</v>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5038,28 +2950,6 @@
           <t>ASICS Los Angeles Marathon</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
         <v>17036</v>
       </c>
@@ -5089,30 +2979,9 @@
           <t>Boston Marathon</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>17584</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
         <v>26715</v>
       </c>
@@ -5122,7 +2991,6 @@
       <c r="AB10" t="n">
         <v>28506</v>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5140,32 +3008,12 @@
           <t>TCS London Marathon</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>36549</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
         <v>40179</v>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
         <v>48832</v>
       </c>
@@ -5175,7 +3023,6 @@
       <c r="AB11" t="n">
         <v>56640</v>
       </c>
-      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5193,28 +3040,6 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
         <v>7661</v>
       </c>
@@ -5224,7 +3049,6 @@
       <c r="AB12" t="n">
         <v>11464</v>
       </c>
-      <c r="AC12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5242,28 +3066,6 @@
           <t>Adidas Manchester Marathon</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="n">
         <v>18221</v>
       </c>
@@ -5273,7 +3075,6 @@
       <c r="AB13" t="n">
         <v>23828</v>
       </c>
-      <c r="AC13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5291,23 +3092,6 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
         <v>43754</v>
       </c>
@@ -5317,8 +3101,6 @@
       <c r="W14" t="n">
         <v>48073</v>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="n">
         <v>51234</v>
       </c>
@@ -5328,7 +3110,6 @@
       <c r="AB14" t="n">
         <v>55499</v>
       </c>
-      <c r="AC14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5346,28 +3127,6 @@
           <t>NN Marathon Rotterdam</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
         <v>16848</v>
       </c>
@@ -5377,7 +3136,6 @@
       <c r="AB15" t="n">
         <v>17867</v>
       </c>
-      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5395,28 +3153,6 @@
           <t>Vienna City Marathon</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="n">
         <v>6650</v>
       </c>
@@ -5426,7 +3162,6 @@
       <c r="AB16" t="n">
         <v>9300</v>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5444,28 +3179,6 @@
           <t>Copenhagen Marathon</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="n">
         <v>10164</v>
       </c>
@@ -5475,7 +3188,6 @@
       <c r="AB17" t="n">
         <v>18508</v>
       </c>
-      <c r="AC17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5493,28 +3205,6 @@
           <t>Prague International Marathon</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="n">
         <v>5467</v>
       </c>
@@ -5524,7 +3214,6 @@
       <c r="AB18" t="n">
         <v>7636</v>
       </c>
-      <c r="AC18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5542,28 +3231,6 @@
           <t>Sanlam Cape Town Marathon</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
         <v>13336</v>
       </c>
@@ -5575,7 +3242,6 @@
           <t>Canceled</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5593,28 +3259,6 @@
           <t>Maratón de la Ciudad de México Telcel</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
         <v>28364</v>
       </c>
@@ -5624,7 +3268,6 @@
       <c r="AB20" t="n">
         <v>29363</v>
       </c>
-      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5642,28 +3285,6 @@
           <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
         <v>13297</v>
       </c>
@@ -5673,7 +3294,6 @@
       <c r="AB21" t="n">
         <v>32963</v>
       </c>
-      <c r="AC21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5691,23 +3311,9 @@
           <t>BMW Berlin Marathon</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>35783</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
         <v>36768</v>
       </c>
@@ -5738,7 +3344,6 @@
       <c r="AB22" t="n">
         <v>48361</v>
       </c>
-      <c r="AC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5756,28 +3361,6 @@
           <t>NN Maraton Warszawski</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
         <v>5557</v>
       </c>
@@ -5787,7 +3370,6 @@
       <c r="AB23" t="n">
         <v>9544</v>
       </c>
-      <c r="AC23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5805,28 +3387,6 @@
           <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
         <v>16069</v>
       </c>
@@ -5836,7 +3396,6 @@
       <c r="AB24" t="n">
         <v>23328</v>
       </c>
-      <c r="AC24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5854,28 +3413,6 @@
           <t>Bank of America Chicago Marathon</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
         <v>48155</v>
       </c>
@@ -5885,7 +3422,6 @@
       <c r="AB25" t="n">
         <v>54187</v>
       </c>
-      <c r="AC25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5903,28 +3439,6 @@
           <t>EDP Maratona de Lisboa</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
         <v>4847</v>
       </c>
@@ -5934,7 +3448,6 @@
       <c r="AB26" t="n">
         <v>9600</v>
       </c>
-      <c r="AC26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5952,28 +3465,6 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
         <v>4563</v>
       </c>
@@ -5983,7 +3474,6 @@
       <c r="AB27" t="n">
         <v>7312</v>
       </c>
-      <c r="AC27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6001,28 +3491,6 @@
           <t xml:space="preserve">	Irish Life Dublin Marathon</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
         <v>16495</v>
       </c>
@@ -6032,7 +3500,6 @@
       <c r="AB28" t="n">
         <v>18503</v>
       </c>
-      <c r="AC28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6050,28 +3517,6 @@
           <t>Marine Corps Marathon</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
         <v>13819</v>
       </c>
@@ -6081,7 +3526,6 @@
       <c r="AB29" t="n">
         <v>30085</v>
       </c>
-      <c r="AC29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6099,28 +3543,6 @@
           <t>Bangsaen42 Chonburi Marathon</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
         <v>9758</v>
       </c>
@@ -6130,7 +3552,6 @@
       <c r="AB30" t="n">
         <v>9733</v>
       </c>
-      <c r="AC30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6184,7 +3605,6 @@
       <c r="O31" t="n">
         <v>46795</v>
       </c>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
         <v>50062</v>
       </c>
@@ -6206,8 +3626,6 @@
       <c r="W31" t="n">
         <v>53627</v>
       </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
         <v>51349</v>
       </c>
@@ -6217,7 +3635,6 @@
       <c r="AB31" t="n">
         <v>59124</v>
       </c>
-      <c r="AC31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6235,36 +3652,12 @@
           <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
         <v>8660</v>
       </c>
       <c r="AB32" t="n">
         <v>8933</v>
       </c>
-      <c r="AC32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6282,28 +3675,6 @@
           <t>Taipei Marathon</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="n">
         <v>8117</v>
       </c>
@@ -6313,7 +3684,6 @@
       <c r="AB33" t="n">
         <v>8278</v>
       </c>
-      <c r="AC33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6331,28 +3701,6 @@
           <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
         <v>25905</v>
       </c>
@@ -6362,7 +3710,6 @@
       <c r="AB34" t="n">
         <v>30772</v>
       </c>
-      <c r="AC34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6380,28 +3727,6 @@
           <t>Honolulu Marathon</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
         <v>15151</v>
       </c>
@@ -6411,7 +3736,6 @@
       <c r="AB35" t="n">
         <v>22772</v>
       </c>
-      <c r="AC35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6548,29 +3872,6 @@
           <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
         <v>12135</v>
       </c>
@@ -6602,30 +3903,6 @@
           <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>13416</v>
       </c>
@@ -6654,29 +3931,6 @@
           <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
         <v>13715</v>
       </c>
@@ -6708,28 +3962,6 @@
           <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>9811</v>
       </c>
@@ -6764,30 +3996,6 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
         <v>11453</v>
       </c>
@@ -6816,28 +4024,6 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>7238</v>
       </c>
@@ -6872,28 +4058,6 @@
           <t>10K Montmartre</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>-</t>
@@ -6934,28 +4098,6 @@
           <t>Chevron Houston Marathon</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
         <v>6104</v>
       </c>
@@ -6990,28 +4132,6 @@
           <t>Riyadh Marathon</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>288</v>
       </c>
@@ -7046,34 +4166,9 @@
           <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>22872</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7096,28 +4191,6 @@
           <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
         <v>17624</v>
       </c>
@@ -7152,28 +4225,6 @@
           <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
         <v>13706</v>
       </c>
@@ -7208,28 +4259,6 @@
           <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
         <v>8228</v>
       </c>
@@ -7264,28 +4293,6 @@
           <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>11865</v>
       </c>
@@ -7320,29 +4327,6 @@
           <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="n">
         <v>2942</v>
       </c>
@@ -7374,31 +4358,6 @@
           <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
         <v>9638</v>
       </c>
@@ -7424,30 +4383,6 @@
           <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>5732</v>
       </c>
@@ -7476,16 +4411,6 @@
           <t>HOKA Semi de Paris</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>22030</v>
       </c>
@@ -7495,15 +4420,6 @@
       <c r="Q19" t="n">
         <v>24990</v>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
         <v>45387</v>
       </c>
@@ -7538,13 +4454,6 @@
           <t>Tokyo Marathon</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>25102</v>
       </c>
@@ -7587,7 +4496,6 @@
       <c r="Y20" t="n">
         <v>18272</v>
       </c>
-      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
         <v>36560</v>
       </c>
@@ -7622,28 +4530,6 @@
           <t>ASICS Los Angeles Marathon</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
         <v>17036</v>
       </c>
@@ -7678,29 +4564,6 @@
           <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="n">
         <v>13245</v>
       </c>
@@ -7732,28 +4595,6 @@
           <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
         <v>7225</v>
       </c>
@@ -7788,28 +4629,6 @@
           <t>Generali Berlin Half Marathon</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
         <v>26104</v>
       </c>
@@ -7819,7 +4638,6 @@
       <c r="AC24" t="n">
         <v>34742</v>
       </c>
-      <c r="AD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7842,28 +4660,6 @@
           <t>Cooper River Bridge Run</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
         <v>22336</v>
       </c>
@@ -7873,7 +4669,6 @@
       <c r="AC25" t="n">
         <v>31203</v>
       </c>
-      <c r="AD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7896,30 +4691,6 @@
           <t>United Airlines NYC Half</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>28677</v>
       </c>
@@ -7948,28 +4719,6 @@
           <t>Acea Run Rome The Marathon</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
         <v>11235</v>
       </c>
@@ -7979,7 +4728,6 @@
       <c r="AC27" t="n">
         <v>21930</v>
       </c>
-      <c r="AD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8002,28 +4750,6 @@
           <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="n">
         <v>10853</v>
       </c>
@@ -8058,34 +4784,9 @@
           <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>20918</v>
       </c>
-      <c r="AD29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8108,30 +4809,6 @@
           <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>19624</v>
       </c>
@@ -8160,28 +4837,6 @@
           <t>Seoul Marathon</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="n">
         <v>25905</v>
       </c>
@@ -8191,7 +4846,6 @@
       <c r="AC31" t="n">
         <v>19112</v>
       </c>
-      <c r="AD31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8214,30 +4868,6 @@
           <t>Disney Princess Half Marathon</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>15879</v>
       </c>
@@ -8266,36 +4896,12 @@
           <t>Warsaw Half Marathon</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
         <v>13422</v>
       </c>
       <c r="AC33" t="n">
         <v>14605</v>
       </c>
-      <c r="AD33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8318,28 +4924,6 @@
           <t>Generali Prague Half Marathon</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="n">
         <v>10213</v>
       </c>
@@ -8349,7 +4933,6 @@
       <c r="AC34" t="n">
         <v>14144</v>
       </c>
-      <c r="AD34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8372,34 +4955,9 @@
           <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>12363</v>
       </c>
-      <c r="AD35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8422,30 +4980,6 @@
           <t>GetPro Bath Half</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>11133</v>
       </c>
@@ -8474,28 +5008,6 @@
           <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="n">
         <v>11275</v>
       </c>
@@ -8530,32 +5042,42 @@
           <t>TCS London Marathon</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
         <v>36549</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>34688</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>36699</v>
+      </c>
+      <c r="R38" t="n">
+        <v>34202</v>
+      </c>
+      <c r="S38" t="n">
+        <v>35817</v>
+      </c>
+      <c r="T38" t="n">
+        <v>37581</v>
+      </c>
+      <c r="U38" t="n">
+        <v>39091</v>
+      </c>
+      <c r="V38" t="n">
+        <v>39406</v>
+      </c>
       <c r="W38" t="n">
         <v>40179</v>
       </c>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+      <c r="X38" t="n">
+        <v>42549</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>35321</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>40651</v>
+      </c>
       <c r="AA38" t="n">
         <v>48832</v>
       </c>
@@ -8565,7 +5087,6 @@
       <c r="AC38" t="n">
         <v>56640</v>
       </c>
-      <c r="AD38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8588,23 +5109,6 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
         <v>43754</v>
       </c>
@@ -8614,8 +5118,6 @@
       <c r="X39" t="n">
         <v>48073</v>
       </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="n">
         <v>51234</v>
       </c>
@@ -8625,7 +5127,6 @@
       <c r="AC39" t="n">
         <v>55499</v>
       </c>
-      <c r="AD39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8648,28 +5149,6 @@
           <t>Vancouver Sun Run</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="n">
         <v>25108</v>
       </c>
@@ -8679,7 +5158,6 @@
       <c r="AC40" t="n">
         <v>39385</v>
       </c>
-      <c r="AD40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8702,30 +5180,33 @@
           <t>Boston Marathon</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>17584</v>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>31805</v>
+      </c>
+      <c r="T41" t="n">
+        <v>26610</v>
+      </c>
+      <c r="U41" t="n">
+        <v>26639</v>
+      </c>
+      <c r="V41" t="n">
+        <v>26411</v>
+      </c>
+      <c r="W41" t="n">
+        <v>25746</v>
+      </c>
+      <c r="X41" t="n">
+        <v>26632</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>15416</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>25025</v>
+      </c>
       <c r="AA41" t="n">
         <v>26715</v>
       </c>
@@ -8735,7 +5216,6 @@
       <c r="AC41" t="n">
         <v>28506</v>
       </c>
-      <c r="AD41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8758,34 +5238,9 @@
           <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>24590</v>
       </c>
-      <c r="AD42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8808,28 +5263,6 @@
           <t>Adidas Manchester Marathon</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="n">
         <v>18221</v>
       </c>
@@ -8839,7 +5272,6 @@
       <c r="AC43" t="n">
         <v>23828</v>
       </c>
-      <c r="AD43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8862,36 +5294,12 @@
           <t>London Landmarks Half Marathon</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="n">
         <v>18869</v>
       </c>
       <c r="AC44" t="n">
         <v>19968</v>
       </c>
-      <c r="AD44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8914,28 +5322,6 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="n">
         <v>15306</v>
       </c>
@@ -8945,7 +5331,6 @@
       <c r="AC45" t="n">
         <v>19356</v>
       </c>
-      <c r="AD45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8968,28 +5353,6 @@
           <t>Statesman Capitol 10K</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="n">
         <v>22059</v>
       </c>
@@ -8999,7 +5362,6 @@
       <c r="AC46" t="n">
         <v>19327</v>
       </c>
-      <c r="AD46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9022,28 +5384,6 @@
           <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="n">
         <v>14985</v>
       </c>
@@ -9053,7 +5393,6 @@
       <c r="AC47" t="n">
         <v>18157</v>
       </c>
-      <c r="AD47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9076,28 +5415,6 @@
           <t>NN Marathon Rotterdam</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="n">
         <v>16848</v>
       </c>
@@ -9107,7 +5424,6 @@
       <c r="AC48" t="n">
         <v>17867</v>
       </c>
-      <c r="AD48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9130,34 +5446,9 @@
           <t>Vienna City Half Marathon</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>12788</v>
       </c>
-      <c r="AD49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9180,34 +5471,9 @@
           <t>21K de Montréal</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>11795</v>
       </c>
-      <c r="AD50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9230,28 +5496,6 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="n">
         <v>7661</v>
       </c>
@@ -9261,7 +5505,6 @@
       <c r="AC51" t="n">
         <v>11464</v>
       </c>
-      <c r="AD51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9284,34 +5527,9 @@
           <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>10776</v>
       </c>
-      <c r="AD52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9334,28 +5552,6 @@
           <t>Vienna City Marathon</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="n">
         <v>6650</v>
       </c>
@@ -9365,7 +5561,6 @@
       <c r="AC53" t="n">
         <v>9300</v>
       </c>
-      <c r="AD53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9388,28 +5583,6 @@
           <t>Sanlam Cape Town Marathon</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="n">
         <v>13336</v>
       </c>
@@ -9421,7 +5594,6 @@
           <t>Canceled</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9444,40 +5616,18 @@
           <t xml:space="preserve">Göteborgsvarvet </t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>44099</v>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
         <v>45015</v>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="n">
         <v>40765</v>
       </c>
       <c r="AC55" t="n">
         <v>46706</v>
       </c>
-      <c r="AD55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9500,28 +5650,6 @@
           <t>BOLDERBoulder 10K</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="n">
         <v>35639</v>
       </c>
@@ -9531,7 +5659,6 @@
       <c r="AC56" t="n">
         <v>45055</v>
       </c>
-      <c r="AD56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9554,34 +5681,9 @@
           <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>28474</v>
       </c>
-      <c r="AD57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9604,34 +5706,9 @@
           <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>20531</v>
       </c>
-      <c r="AD58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9654,28 +5731,6 @@
           <t>Copenhagen Marathon</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="n">
         <v>10164</v>
       </c>
@@ -9685,7 +5740,6 @@
       <c r="AC59" t="n">
         <v>18508</v>
       </c>
-      <c r="AD59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9708,34 +5762,9 @@
           <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
         <v>17697</v>
       </c>
-      <c r="AD60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9758,34 +5787,9 @@
           <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>17222</v>
       </c>
-      <c r="AD61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9808,36 +5812,12 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="n">
         <v>15291</v>
       </c>
       <c r="AC62" t="n">
         <v>16778</v>
       </c>
-      <c r="AD62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9860,34 +5840,9 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>12300</v>
       </c>
-      <c r="AD63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9910,34 +5865,9 @@
           <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
         <v>10768</v>
       </c>
-      <c r="AD64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9960,28 +5890,6 @@
           <t>Prague International Marathon</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="n">
         <v>5467</v>
       </c>
@@ -9991,7 +5899,6 @@
       <c r="AC65" t="n">
         <v>7636</v>
       </c>
-      <c r="AD65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10014,28 +5921,6 @@
           <t>Bangsaen10</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="n">
         <v>6035</v>
       </c>
@@ -10045,7 +5930,6 @@
       <c r="AC66" t="n">
         <v>7142</v>
       </c>
-      <c r="AD66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10068,34 +5952,9 @@
           <t>Broløbet - The Bridge Run</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
         <v>40241</v>
       </c>
-      <c r="AD67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10118,28 +5977,6 @@
           <t>Adidas 10K Paris</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="n">
         <v>24629</v>
       </c>
@@ -10149,7 +5986,6 @@
       <c r="AC68" t="n">
         <v>34353</v>
       </c>
-      <c r="AD68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10172,28 +6008,6 @@
           <t>Royal Run</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="n">
         <v>11329</v>
       </c>
@@ -10203,7 +6017,6 @@
       <c r="AC69" t="n">
         <v>13543</v>
       </c>
-      <c r="AD69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10226,28 +6039,6 @@
           <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="n">
         <v>41806</v>
       </c>
@@ -10257,7 +6048,6 @@
       <c r="AC70" t="n">
         <v>43654</v>
       </c>
-      <c r="AD70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10280,34 +6070,9 @@
           <t>Media Maraton de Bogota</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
         <v>21011</v>
       </c>
-      <c r="AD71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10330,28 +6095,6 @@
           <t>Saucony London 10K</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="n">
         <v>13368</v>
       </c>
@@ -10361,7 +6104,6 @@
       <c r="AC72" t="n">
         <v>13067</v>
       </c>
-      <c r="AD72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10384,34 +6126,9 @@
           <t>Asics Run Melbourne</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
         <v>11218</v>
       </c>
-      <c r="AD73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10434,28 +6151,6 @@
           <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="n">
         <v>13297</v>
       </c>
@@ -10465,7 +6160,6 @@
       <c r="AC74" t="n">
         <v>32963</v>
       </c>
-      <c r="AD74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10488,28 +6182,6 @@
           <t>Maratón de la Ciudad de México Telcel</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="n">
         <v>28364</v>
       </c>
@@ -10519,7 +6191,6 @@
       <c r="AC75" t="n">
         <v>29363</v>
       </c>
-      <c r="AD75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10542,23 +6213,27 @@
           <t>BMW Berlin Marathon</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
         <v>35783</v>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+      <c r="N76" t="n">
+        <v>35015</v>
+      </c>
+      <c r="O76" t="n">
+        <v>34225</v>
+      </c>
+      <c r="P76" t="n">
+        <v>32991</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>34377</v>
+      </c>
+      <c r="R76" t="n">
+        <v>30837</v>
+      </c>
+      <c r="S76" t="n">
+        <v>28946</v>
+      </c>
       <c r="T76" t="n">
         <v>36768</v>
       </c>
@@ -10589,7 +6264,6 @@
       <c r="AC76" t="n">
         <v>48361</v>
       </c>
-      <c r="AD76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10612,42 +6286,24 @@
           <t>AJ Bell Great North Run</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
         <v>35777</v>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
         <v>39459</v>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="n">
         <v>41615</v>
       </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="W77" t="n">
+        <v>43656</v>
+      </c>
       <c r="X77" t="n">
         <v>43768</v>
       </c>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
         <v>46258</v>
       </c>
-      <c r="AD77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10670,28 +6326,6 @@
           <t>Copenhagen Half Marathon</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="n">
         <v>24381</v>
       </c>
@@ -10701,7 +6335,6 @@
       <c r="AC78" t="n">
         <v>31440</v>
       </c>
-      <c r="AD78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10724,28 +6357,6 @@
           <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="n">
         <v>20274</v>
       </c>
@@ -10755,7 +6366,6 @@
       <c r="AC79" t="n">
         <v>24703</v>
       </c>
-      <c r="AD79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10778,34 +6388,9 @@
           <t>The Big Half</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
         <v>17223</v>
       </c>
-      <c r="AD80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10828,28 +6413,6 @@
           <t>Vitality London 10,000</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="n">
         <v>12201</v>
       </c>
@@ -10859,7 +6422,6 @@
       <c r="AC81" t="n">
         <v>17154</v>
       </c>
-      <c r="AD81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10882,28 +6444,6 @@
           <t>NN Maraton Warszawski</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-      <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="n">
         <v>5557</v>
       </c>
@@ -10913,7 +6453,6 @@
       <c r="AC82" t="n">
         <v>9544</v>
       </c>
-      <c r="AD82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10936,36 +6475,12 @@
           <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="n">
         <v>7392</v>
       </c>
       <c r="AC83" t="n">
         <v>8918</v>
       </c>
-      <c r="AD83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10988,28 +6503,30 @@
           <t>Bank of America Chicago Marathon</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-      <c r="Z84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>39122</v>
+      </c>
+      <c r="S84" t="n">
+        <v>40659</v>
+      </c>
+      <c r="U84" t="n">
+        <v>39313</v>
+      </c>
+      <c r="V84" t="n">
+        <v>44341</v>
+      </c>
+      <c r="W84" t="n">
+        <v>44584</v>
+      </c>
+      <c r="X84" t="n">
+        <v>45932</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>26265</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>40802</v>
+      </c>
       <c r="AA84" t="n">
         <v>48155</v>
       </c>
@@ -11019,7 +6536,6 @@
       <c r="AC84" t="n">
         <v>54187</v>
       </c>
-      <c r="AD84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11042,28 +6558,6 @@
           <t>Marine Corps Marathon</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="n">
         <v>13819</v>
       </c>
@@ -11073,7 +6567,6 @@
       <c r="AC85" t="n">
         <v>30085</v>
       </c>
-      <c r="AD85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11096,34 +6589,9 @@
           <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-      <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
         <v>26060</v>
       </c>
-      <c r="AD86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11146,34 +6614,9 @@
           <t>Cardiff Half Marathon</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
         <v>24634</v>
       </c>
-      <c r="AD87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11196,28 +6639,6 @@
           <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-      <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="n">
         <v>16069</v>
       </c>
@@ -11227,7 +6648,6 @@
       <c r="AC88" t="n">
         <v>23328</v>
       </c>
-      <c r="AD88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11250,34 +6670,9 @@
           <t>Manchester Half Marathon</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
         <v>22354</v>
       </c>
-      <c r="AD89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11300,34 +6695,9 @@
           <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
         <v>18564</v>
       </c>
-      <c r="AD90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11350,28 +6720,6 @@
           <t xml:space="preserve">	Irish Life Dublin Marathon</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="n">
         <v>16495</v>
       </c>
@@ -11381,7 +6729,6 @@
       <c r="AC91" t="n">
         <v>18503</v>
       </c>
-      <c r="AD91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11404,28 +6751,6 @@
           <t>Run in Lyon</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="n">
         <v>11065</v>
       </c>
@@ -11435,7 +6760,6 @@
       <c r="AC92" t="n">
         <v>16280</v>
       </c>
-      <c r="AD92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11458,34 +6782,9 @@
           <t>Royal Parks Half Marathon</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
         <v>16201</v>
       </c>
-      <c r="AD93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11508,34 +6807,9 @@
           <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
         <v>14635</v>
       </c>
-      <c r="AD94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11558,34 +6832,9 @@
           <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="n">
         <v>13341</v>
       </c>
-      <c r="AD95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11608,34 +6857,9 @@
           <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
         <v>12156</v>
       </c>
-      <c r="AD96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11658,34 +6882,9 @@
           <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
         <v>11471</v>
       </c>
-      <c r="AD97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11708,28 +6907,6 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="n">
         <v>10690</v>
       </c>
@@ -11739,7 +6916,6 @@
       <c r="AC98" t="n">
         <v>11416</v>
       </c>
-      <c r="AD98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11762,28 +6938,6 @@
           <t>Run in Lyon</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="n">
         <v>13566</v>
       </c>
@@ -11793,7 +6947,6 @@
       <c r="AC99" t="n">
         <v>11338</v>
       </c>
-      <c r="AD99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11816,34 +6969,9 @@
           <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="n">
         <v>10752</v>
       </c>
-      <c r="AD100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11866,28 +6994,6 @@
           <t>EDP Maratona de Lisboa</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="n">
         <v>4847</v>
       </c>
@@ -11897,7 +7003,6 @@
       <c r="AC101" t="n">
         <v>9600</v>
       </c>
-      <c r="AD101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -11920,28 +7025,6 @@
           <t xml:space="preserve">Hyundai Meia Maratona </t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="n">
         <v>6567</v>
       </c>
@@ -11951,7 +7034,6 @@
       <c r="AC102" t="n">
         <v>7635</v>
       </c>
-      <c r="AD102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -11974,28 +7056,6 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="n">
         <v>4563</v>
       </c>
@@ -12005,7 +7065,6 @@
       <c r="AC103" t="n">
         <v>7312</v>
       </c>
-      <c r="AD103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12028,28 +7087,6 @@
           <t>ASICS LDNX</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr">
         <is>
           <t>-</t>
@@ -12063,7 +7100,6 @@
       <c r="AC104" t="n">
         <v>4681</v>
       </c>
-      <c r="AD104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12122,7 +7158,6 @@
       <c r="P105" t="n">
         <v>46795</v>
       </c>
-      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="n">
         <v>50062</v>
       </c>
@@ -12144,8 +7179,12 @@
       <c r="X105" t="n">
         <v>53627</v>
       </c>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
+      <c r="Y105" t="n">
+        <v>25018</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>47838</v>
+      </c>
       <c r="AA105" t="n">
         <v>51349</v>
       </c>
@@ -12155,7 +7194,6 @@
       <c r="AC105" t="n">
         <v>59124</v>
       </c>
-      <c r="AD105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12178,34 +7216,9 @@
           <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
-      <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="n">
         <v>10896</v>
       </c>
-      <c r="AD106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12228,28 +7241,6 @@
           <t>Bangsaen42 Chonburi Marathon</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
-      <c r="Y107" t="inlineStr"/>
-      <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="n">
         <v>9758</v>
       </c>
@@ -12259,7 +7250,6 @@
       <c r="AC107" t="n">
         <v>9733</v>
       </c>
-      <c r="AD107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12282,28 +7272,6 @@
           <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
-      <c r="Y108" t="inlineStr"/>
-      <c r="Z108" t="inlineStr"/>
       <c r="AA108" t="n">
         <v>31292</v>
       </c>
@@ -12313,7 +7281,6 @@
       <c r="AC108" t="n">
         <v>36534</v>
       </c>
-      <c r="AD108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12336,28 +7303,6 @@
           <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
-      <c r="Y109" t="inlineStr"/>
-      <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="n">
         <v>25905</v>
       </c>
@@ -12367,7 +7312,6 @@
       <c r="AC109" t="n">
         <v>30772</v>
       </c>
-      <c r="AD109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12390,28 +7334,6 @@
           <t>Honolulu Marathon</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
-      <c r="Y110" t="inlineStr"/>
-      <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="n">
         <v>15151</v>
       </c>
@@ -12421,7 +7343,6 @@
       <c r="AC110" t="n">
         <v>22772</v>
       </c>
-      <c r="AD110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -12444,28 +7365,6 @@
           <t>Taipei Half Marathon</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
-      <c r="Y111" t="inlineStr"/>
-      <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="n">
         <v>16689</v>
       </c>
@@ -12475,7 +7374,6 @@
       <c r="AC111" t="n">
         <v>16954</v>
       </c>
-      <c r="AD111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -12498,34 +7396,9 @@
           <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
-      <c r="Y112" t="inlineStr"/>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="n">
         <v>14747</v>
       </c>
-      <c r="AD112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -12548,28 +7421,6 @@
           <t>Bangsaen21</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
-      <c r="Y113" t="inlineStr"/>
-      <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="n">
         <v>9126</v>
       </c>
@@ -12579,7 +7430,6 @@
       <c r="AC113" t="n">
         <v>10364</v>
       </c>
-      <c r="AD113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -12602,34 +7452,9 @@
           <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
-      <c r="Y114" t="inlineStr"/>
-      <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
-      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="n">
         <v>10178</v>
       </c>
-      <c r="AD114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12652,36 +7477,12 @@
           <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
-      <c r="Y115" t="inlineStr"/>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="n">
         <v>8660</v>
       </c>
       <c r="AC115" t="n">
         <v>8933</v>
       </c>
-      <c r="AD115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12704,28 +7505,6 @@
           <t>Taipei Marathon</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
-      <c r="Y116" t="inlineStr"/>
-      <c r="Z116" t="inlineStr"/>
       <c r="AA116" t="n">
         <v>8117</v>
       </c>
@@ -12735,7 +7514,6 @@
       <c r="AC116" t="n">
         <v>8278</v>
       </c>
-      <c r="AD116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12758,31 +7536,6 @@
           <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
-      <c r="Y117" t="inlineStr"/>
-      <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
-      <c r="AB117" t="inlineStr"/>
-      <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="n">
         <v>16283</v>
       </c>
@@ -12958,7 +7711,6 @@
       <c r="P2" t="n">
         <v>46795</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>50062</v>
       </c>
@@ -12980,8 +7732,6 @@
       <c r="X2" t="n">
         <v>53627</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>51349</v>
       </c>
@@ -12991,7 +7741,6 @@
       <c r="AC2" t="n">
         <v>59124</v>
       </c>
-      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13014,32 +7763,12 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>36549</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
         <v>40179</v>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>48832</v>
       </c>
@@ -13049,7 +7778,6 @@
       <c r="AC3" t="n">
         <v>56640</v>
       </c>
-      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13072,23 +7800,6 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
         <v>43754</v>
       </c>
@@ -13098,8 +7809,6 @@
       <c r="X4" t="n">
         <v>48073</v>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>51234</v>
       </c>
@@ -13109,7 +7818,6 @@
       <c r="AC4" t="n">
         <v>55499</v>
       </c>
-      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13132,28 +7840,6 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>48155</v>
       </c>
@@ -13163,7 +7849,6 @@
       <c r="AC5" t="n">
         <v>54187</v>
       </c>
-      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13186,23 +7871,9 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>35783</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>36768</v>
       </c>
@@ -13233,7 +7904,6 @@
       <c r="AC6" t="n">
         <v>48361</v>
       </c>
-      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13256,16 +7926,6 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>22030</v>
       </c>
@@ -13275,15 +7935,6 @@
       <c r="Q7" t="n">
         <v>24990</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>45387</v>
       </c>
@@ -13318,40 +7969,18 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>44099</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>45015</v>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="n">
         <v>40765</v>
       </c>
       <c r="AC8" t="n">
         <v>46706</v>
       </c>
-      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13374,42 +8003,21 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>35777</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>39459</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>41615</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>43768</v>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>46258</v>
       </c>
-      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13432,28 +8040,6 @@
           <t>10km</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>35639</v>
       </c>
@@ -13463,7 +8049,6 @@
       <c r="AC10" t="n">
         <v>45055</v>
       </c>
-      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13486,34 +8071,9 @@
           <t>Marathon / Semi / 7,5km</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>44578</v>
       </c>
-      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -13536,28 +8096,6 @@
           <t>10km</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
         <v>41806</v>
       </c>
@@ -13567,7 +8105,6 @@
       <c r="AC12" t="n">
         <v>43654</v>
       </c>
-      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13590,28 +8127,6 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
           <t>-</t>
@@ -13625,7 +8140,6 @@
       <c r="AC13" t="n">
         <v>40241</v>
       </c>
-      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -13648,28 +8162,6 @@
           <t>10km</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
         <v>25108</v>
       </c>
@@ -13679,7 +8171,6 @@
       <c r="AC14" t="n">
         <v>39385</v>
       </c>
-      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13702,28 +8193,6 @@
           <t>10km</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>31292</v>
       </c>
@@ -13733,7 +8202,6 @@
       <c r="AC15" t="n">
         <v>36534</v>
       </c>
-      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13756,13 +8224,6 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>25102</v>
       </c>
@@ -13805,7 +8266,6 @@
       <c r="Y16" t="n">
         <v>18272</v>
       </c>
-      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
         <v>36560</v>
       </c>
@@ -13840,28 +8300,6 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="n">
         <v>26104</v>
       </c>
@@ -13871,7 +8309,6 @@
       <c r="AC17" t="n">
         <v>34742</v>
       </c>
-      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -13894,28 +8331,6 @@
           <t>10km</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
         <v>24629</v>
       </c>
@@ -13925,7 +8340,6 @@
       <c r="AC18" t="n">
         <v>34353</v>
       </c>
-      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -13948,28 +8362,6 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
         <v>13297</v>
       </c>
@@ -13979,7 +8371,6 @@
       <c r="AC19" t="n">
         <v>32963</v>
       </c>
-      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14002,34 +8393,9 @@
           <t>Marathon / Semi / 10km</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
         <v>32767</v>
       </c>
-      <c r="AD20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14052,28 +8418,6 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
         <v>24381</v>
       </c>
@@ -14083,7 +8427,6 @@
       <c r="AC21" t="n">
         <v>31440</v>
       </c>
-      <c r="AD21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14106,28 +8449,6 @@
           <t>10km</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
         <v>22336</v>
       </c>
@@ -14137,7 +8458,6 @@
       <c r="AC22" t="n">
         <v>31203</v>
       </c>
-      <c r="AD22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14160,28 +8480,6 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
         <v>25905</v>
       </c>
@@ -14191,7 +8489,6 @@
       <c r="AC23" t="n">
         <v>30772</v>
       </c>
-      <c r="AD23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -14214,28 +8511,6 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="n">
         <v>13819</v>
       </c>
@@ -14245,7 +8520,6 @@
       <c r="AC24" t="n">
         <v>30085</v>
       </c>
-      <c r="AD24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -14268,34 +8542,9 @@
           <t>Semi / 10km</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>29078</v>
       </c>
-      <c r="AD25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -14318,30 +8567,6 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>28677</v>
       </c>
@@ -14370,30 +8595,9 @@
           <t>Marathon</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>17584</v>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
         <v>26715</v>
       </c>
@@ -14403,7 +8607,6 @@
       <c r="AC27" t="n">
         <v>28506</v>
       </c>
-      <c r="AD27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14426,34 +8629,9 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>28474</v>
       </c>
-      <c r="AD28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14476,28 +8654,6 @@
           <t>Semi</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="n">
         <v>17624</v>
       </c>
@@ -14532,31 +8688,6 @@
           <t>Semi / 10km / 5km</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="n">
         <v>47641</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4420,6 +4420,33 @@
       <c r="Q19" t="n">
         <v>24990</v>
       </c>
+      <c r="R19" t="n">
+        <v>30371</v>
+      </c>
+      <c r="S19" t="n">
+        <v>32913</v>
+      </c>
+      <c r="T19" t="n">
+        <v>34879</v>
+      </c>
+      <c r="U19" t="n">
+        <v>37108</v>
+      </c>
+      <c r="V19" t="n">
+        <v>38326</v>
+      </c>
+      <c r="W19" t="n">
+        <v>36510</v>
+      </c>
+      <c r="X19" t="n">
+        <v>33348</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>41351</v>
+      </c>
       <c r="AA19" t="n">
         <v>45387</v>
       </c>
@@ -5619,6 +5646,9 @@
       <c r="O55" t="n">
         <v>44099</v>
       </c>
+      <c r="Q55" t="n">
+        <v>44099</v>
+      </c>
       <c r="R55" t="n">
         <v>45015</v>
       </c>
@@ -6558,6 +6588,12 @@
           <t>Marine Corps Marathon</t>
         </is>
       </c>
+      <c r="V85" t="n">
+        <v>20122</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>11185</v>
+      </c>
       <c r="AA85" t="n">
         <v>13819</v>
       </c>
@@ -6720,6 +6756,12 @@
           <t xml:space="preserve">	Irish Life Dublin Marathon</t>
         </is>
       </c>
+      <c r="X91" t="n">
+        <v>17724</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>14773</v>
+      </c>
       <c r="AA91" t="n">
         <v>16495</v>
       </c>
@@ -7333,6 +7375,42 @@
         <is>
           <t>Honolulu Marathon</t>
         </is>
+      </c>
+      <c r="O110" t="n">
+        <v>20181</v>
+      </c>
+      <c r="P110" t="n">
+        <v>19078</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>24156</v>
+      </c>
+      <c r="R110" t="n">
+        <v>22077</v>
+      </c>
+      <c r="S110" t="n">
+        <v>21827</v>
+      </c>
+      <c r="T110" t="n">
+        <v>21563</v>
+      </c>
+      <c r="U110" t="n">
+        <v>20235</v>
+      </c>
+      <c r="V110" t="n">
+        <v>20390</v>
+      </c>
+      <c r="W110" t="n">
+        <v>19773</v>
+      </c>
+      <c r="X110" t="n">
+        <v>18805</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>6241</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>14276</v>
       </c>
       <c r="AA110" t="n">
         <v>15151</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4557,6 +4557,33 @@
           <t>ASICS Los Angeles Marathon</t>
         </is>
       </c>
+      <c r="R21" t="n">
+        <v>19955</v>
+      </c>
+      <c r="S21" t="n">
+        <v>21516</v>
+      </c>
+      <c r="T21" t="n">
+        <v>21924</v>
+      </c>
+      <c r="U21" t="n">
+        <v>20623</v>
+      </c>
+      <c r="V21" t="n">
+        <v>18990</v>
+      </c>
+      <c r="W21" t="n">
+        <v>19547</v>
+      </c>
+      <c r="X21" t="n">
+        <v>19992</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>5590</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11616</v>
+      </c>
       <c r="AA21" t="n">
         <v>17036</v>
       </c>
@@ -5136,6 +5163,21 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="Q39" t="n">
+        <v>32981</v>
+      </c>
+      <c r="R39" t="n">
+        <v>32916</v>
+      </c>
+      <c r="S39" t="n">
+        <v>39135</v>
+      </c>
+      <c r="T39" t="n">
+        <v>40242</v>
+      </c>
+      <c r="U39" t="n">
+        <v>41736</v>
+      </c>
       <c r="V39" t="n">
         <v>43754</v>
       </c>
@@ -5442,6 +5484,36 @@
           <t>NN Marathon Rotterdam</t>
         </is>
       </c>
+      <c r="O48" t="n">
+        <v>7877</v>
+      </c>
+      <c r="P48" t="n">
+        <v>7325</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>7525</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7798</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10658</v>
+      </c>
+      <c r="T48" t="n">
+        <v>11879</v>
+      </c>
+      <c r="U48" t="n">
+        <v>12978</v>
+      </c>
+      <c r="V48" t="n">
+        <v>13065</v>
+      </c>
+      <c r="W48" t="n">
+        <v>13978</v>
+      </c>
+      <c r="X48" t="n">
+        <v>14535</v>
+      </c>
       <c r="AA48" t="n">
         <v>16848</v>
       </c>
@@ -6674,6 +6746,9 @@
         <is>
           <t>TCS Amsterdam Marathon</t>
         </is>
+      </c>
+      <c r="X88" t="n">
+        <v>13469</v>
       </c>
       <c r="AA88" t="n">
         <v>16069</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6605,11 +6605,26 @@
           <t>Bank of America Chicago Marathon</t>
         </is>
       </c>
+      <c r="N84" t="n">
+        <v>33697</v>
+      </c>
+      <c r="O84" t="n">
+        <v>36159</v>
+      </c>
+      <c r="P84" t="n">
+        <v>35670</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>37455</v>
+      </c>
       <c r="R84" t="n">
         <v>39122</v>
       </c>
       <c r="S84" t="n">
         <v>40659</v>
+      </c>
+      <c r="T84" t="n">
+        <v>37182</v>
       </c>
       <c r="U84" t="n">
         <v>39313</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5187,6 +5187,9 @@
       <c r="X39" t="n">
         <v>48073</v>
       </c>
+      <c r="Z39" t="n">
+        <v>35757</v>
+      </c>
       <c r="AA39" t="n">
         <v>51234</v>
       </c>
@@ -6605,6 +6608,9 @@
           <t>Bank of America Chicago Marathon</t>
         </is>
       </c>
+      <c r="M84" t="n">
+        <v>31345</v>
+      </c>
       <c r="N84" t="n">
         <v>33697</v>
       </c>
@@ -6675,9 +6681,18 @@
           <t>Marine Corps Marathon</t>
         </is>
       </c>
+      <c r="U85" t="n">
+        <v>19678</v>
+      </c>
       <c r="V85" t="n">
         <v>20122</v>
       </c>
+      <c r="W85" t="n">
+        <v>20699</v>
+      </c>
+      <c r="X85" t="n">
+        <v>18500</v>
+      </c>
       <c r="Z85" t="n">
         <v>11185</v>
       </c>
@@ -7466,6 +7481,36 @@
           <t>Honolulu Marathon</t>
         </is>
       </c>
+      <c r="E110" t="n">
+        <v>22636</v>
+      </c>
+      <c r="F110" t="n">
+        <v>19236</v>
+      </c>
+      <c r="G110" t="n">
+        <v>26477</v>
+      </c>
+      <c r="H110" t="n">
+        <v>22161</v>
+      </c>
+      <c r="I110" t="n">
+        <v>22407</v>
+      </c>
+      <c r="J110" t="n">
+        <v>24295</v>
+      </c>
+      <c r="K110" t="n">
+        <v>24575</v>
+      </c>
+      <c r="L110" t="n">
+        <v>23299</v>
+      </c>
+      <c r="M110" t="n">
+        <v>20062</v>
+      </c>
+      <c r="N110" t="n">
+        <v>20323</v>
+      </c>
       <c r="O110" t="n">
         <v>20181</v>
       </c>
@@ -7506,7 +7551,7 @@
         <v>15151</v>
       </c>
       <c r="AB110" t="n">
-        <v>18432</v>
+        <v>18379</v>
       </c>
       <c r="AC110" t="n">
         <v>22772</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5187,6 +5187,9 @@
       <c r="X39" t="n">
         <v>48073</v>
       </c>
+      <c r="Y39" t="n">
+        <v>35000</v>
+      </c>
       <c r="Z39" t="n">
         <v>35757</v>
       </c>
@@ -5995,6 +5998,18 @@
           <t>Prague International Marathon</t>
         </is>
       </c>
+      <c r="O65" t="n">
+        <v>4860</v>
+      </c>
+      <c r="P65" t="n">
+        <v>5296</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>5619</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5874</v>
+      </c>
       <c r="AA65" t="n">
         <v>5467</v>
       </c>
@@ -6608,6 +6623,21 @@
           <t>Bank of America Chicago Marathon</t>
         </is>
       </c>
+      <c r="E84" t="n">
+        <v>27956</v>
+      </c>
+      <c r="F84" t="n">
+        <v>37500</v>
+      </c>
+      <c r="I84" t="n">
+        <v>33125</v>
+      </c>
+      <c r="J84" t="n">
+        <v>33125</v>
+      </c>
+      <c r="L84" t="n">
+        <v>25534</v>
+      </c>
       <c r="M84" t="n">
         <v>31345</v>
       </c>
@@ -6681,6 +6711,9 @@
           <t>Marine Corps Marathon</t>
         </is>
       </c>
+      <c r="T85" t="n">
+        <v>23197</v>
+      </c>
       <c r="U85" t="n">
         <v>19678</v>
       </c>
@@ -6860,6 +6893,12 @@
         <is>
           <t xml:space="preserve">	Irish Life Dublin Marathon</t>
         </is>
+      </c>
+      <c r="U91" t="n">
+        <v>19500</v>
+      </c>
+      <c r="V91" t="n">
+        <v>17732</v>
       </c>
       <c r="X91" t="n">
         <v>17724</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4024,6 +4024,9 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>7803</v>
+      </c>
       <c r="AA7" t="n">
         <v>7238</v>
       </c>
@@ -5721,15 +5724,39 @@
           <t xml:space="preserve">Göteborgsvarvet </t>
         </is>
       </c>
+      <c r="M55" t="n">
+        <v>45075</v>
+      </c>
+      <c r="N55" t="n">
+        <v>40000</v>
+      </c>
       <c r="O55" t="n">
         <v>44099</v>
       </c>
+      <c r="P55" t="n">
+        <v>43000</v>
+      </c>
       <c r="Q55" t="n">
         <v>44099</v>
       </c>
       <c r="R55" t="n">
         <v>45015</v>
       </c>
+      <c r="T55" t="n">
+        <v>43000</v>
+      </c>
+      <c r="U55" t="n">
+        <v>44000</v>
+      </c>
+      <c r="V55" t="n">
+        <v>43500</v>
+      </c>
+      <c r="W55" t="n">
+        <v>43500</v>
+      </c>
+      <c r="X55" t="n">
+        <v>42000</v>
+      </c>
       <c r="AB55" t="n">
         <v>40765</v>
       </c>
@@ -6415,6 +6442,9 @@
       <c r="S77" t="n">
         <v>41615</v>
       </c>
+      <c r="U77" t="n">
+        <v>41615</v>
+      </c>
       <c r="W77" t="n">
         <v>43656</v>
       </c>
@@ -7488,6 +7518,15 @@
         <is>
           <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
+      </c>
+      <c r="X109" t="n">
+        <v>25000</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>17000</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>30000</v>
       </c>
       <c r="AA109" t="n">
         <v>25905</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3748,7 +3748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD117"/>
+  <dimension ref="A1:AD171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7829,6 +7829,1356 @@
       </c>
       <c r="AD117" t="n">
         <v>16283</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Broad Street Run</t>
+        </is>
+      </c>
+      <c r="AC118" t="n">
+        <v>33050</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Flying Pig Marathon</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>30908</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Spokane</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lilac Bloomsday Run</t>
+        </is>
+      </c>
+      <c r="AC120" t="n">
+        <v>30049</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Credit Union Cherry Blossom</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>26868</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>San Francisco Marathon</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>24698</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Bank of America Shamrock Shuffle</t>
+        </is>
+      </c>
+      <c r="AC123" t="n">
+        <v>23733</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pittsburgh</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Dick's Pittsburgh Marathon</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>21899</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Minneapolis</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Medtronic Twin Cities Marathon</t>
+        </is>
+      </c>
+      <c r="AC125" t="n">
+        <v>21658</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Fort Worth</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Cowtown Marathon</t>
+        </is>
+      </c>
+      <c r="AC126" t="n">
+        <v>20995</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Long Beach</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Long Beach Marathon</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>20332</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Bay to Breakers</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>20007</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Silicon Valley Turkey Trot</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>20019</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Austin Marathon</t>
+        </is>
+      </c>
+      <c r="AC130" t="n">
+        <v>19206</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Miami</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Miami Marathon</t>
+        </is>
+      </c>
+      <c r="AC131" t="n">
+        <v>19119</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Washington DC</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Army Ten Miler</t>
+        </is>
+      </c>
+      <c r="AC132" t="n">
+        <v>18975</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Duluth</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Grandma's Marathon</t>
+        </is>
+      </c>
+      <c r="AC133" t="n">
+        <v>18354</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Detroit</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Detroit Marathon</t>
+        </is>
+      </c>
+      <c r="AC134" t="n">
+        <v>17918</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Gasparilla Distance Classic</t>
+        </is>
+      </c>
+      <c r="AC135" t="n">
+        <v>17790</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Memphis</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>St. Jude Memphis Marathon</t>
+        </is>
+      </c>
+      <c r="AC136" t="n">
+        <v>17497</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Oklahoma City</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Oklahoma City Memorial Marathon</t>
+        </is>
+      </c>
+      <c r="AC137" t="n">
+        <v>17278</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Richmond Marathon</t>
+        </is>
+      </c>
+      <c r="AC138" t="n">
+        <v>17220</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Crescent City Classic</t>
+        </is>
+      </c>
+      <c r="AC139" t="n">
+        <v>16486</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>San Antonio Marathon</t>
+        </is>
+      </c>
+      <c r="AC140" t="n">
+        <v>15615</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Newport Beach</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Hoag OC Marathon</t>
+        </is>
+      </c>
+      <c r="AC141" t="n">
+        <v>15569</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Jacksonville</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Gate River Run</t>
+        </is>
+      </c>
+      <c r="AC142" t="n">
+        <v>15415</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Denver Colfax Marathon</t>
+        </is>
+      </c>
+      <c r="AC143" t="n">
+        <v>14892</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Shamrock Marathon</t>
+        </is>
+      </c>
+      <c r="AC144" t="n">
+        <v>14301</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Indianapolis Monumental Marathon</t>
+        </is>
+      </c>
+      <c r="AC145" t="n">
+        <v>13827</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Columbus</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Columbus Marathon</t>
+        </is>
+      </c>
+      <c r="AC146" t="n">
+        <v>13101</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Utica</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Boilermaker Road Race</t>
+        </is>
+      </c>
+      <c r="AC147" t="n">
+        <v>12471</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Baltimore</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Baltimore Running Festival</t>
+        </is>
+      </c>
+      <c r="AC148" t="n">
+        <v>11475</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Manchester Road Race</t>
+        </is>
+      </c>
+      <c r="AC149" t="n">
+        <v>11003</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Shamrock Run Portland</t>
+        </is>
+      </c>
+      <c r="AC150" t="n">
+        <v>10929</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Falmouth</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Falmouth Road Race</t>
+        </is>
+      </c>
+      <c r="AC151" t="n">
+        <v>10783</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Eugene</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Eugene Marathon</t>
+        </is>
+      </c>
+      <c r="AC152" t="n">
+        <v>10771</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>BMW Dallas Marathon</t>
+        </is>
+      </c>
+      <c r="AC153" t="n">
+        <v>19966</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>California International Marathon</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>9083</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Fargo</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Fargo Marathon</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>9038</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Rock 'n' Roll Arizona Marathon</t>
+        </is>
+      </c>
+      <c r="AC156" t="n">
+        <v>8965</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Portland Marathon</t>
+        </is>
+      </c>
+      <c r="AC157" t="n">
+        <v>9838</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Haspa Marathon Hamburg</t>
+        </is>
+      </c>
+      <c r="AC158" t="n">
+        <v>12923</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Mainova Frankfurt Marathon</t>
+        </is>
+      </c>
+      <c r="AC159" t="n">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Stockholm Marathon</t>
+        </is>
+      </c>
+      <c r="AC160" t="n">
+        <v>18839</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Milano Marathon</t>
+        </is>
+      </c>
+      <c r="AC161" t="n">
+        <v>10250</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Brighton Marathon</t>
+        </is>
+      </c>
+      <c r="AC162" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Shanghai Marathon</t>
+        </is>
+      </c>
+      <c r="AC163" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Beijing Marathon</t>
+        </is>
+      </c>
+      <c r="AC164" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Osaka</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Osaka Marathon</t>
+        </is>
+      </c>
+      <c r="AC165" t="n">
+        <v>26175</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Gold Coast</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Gold Coast Marathon</t>
+        </is>
+      </c>
+      <c r="AC166" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Dam tot Damloop</t>
+        </is>
+      </c>
+      <c r="AC167" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Août</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>City2Surf</t>
+        </is>
+      </c>
+      <c r="AC168" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Great Scottish Run</t>
+        </is>
+      </c>
+      <c r="AC169" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Istanbul Marathon</t>
+        </is>
+      </c>
+      <c r="AC170" t="n">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Athènes</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Athens Marathon</t>
+        </is>
+      </c>
+      <c r="AC171" t="n">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4444,9 +4444,6 @@
       <c r="X19" t="n">
         <v>33348</v>
       </c>
-      <c r="Y19" t="n">
-        <v>25000</v>
-      </c>
       <c r="Z19" t="n">
         <v>41351</v>
       </c>
@@ -5190,9 +5187,6 @@
       <c r="X39" t="n">
         <v>48073</v>
       </c>
-      <c r="Y39" t="n">
-        <v>35000</v>
-      </c>
       <c r="Z39" t="n">
         <v>35757</v>
       </c>
@@ -5727,36 +5721,15 @@
       <c r="M55" t="n">
         <v>45075</v>
       </c>
-      <c r="N55" t="n">
-        <v>40000</v>
-      </c>
       <c r="O55" t="n">
         <v>44099</v>
       </c>
-      <c r="P55" t="n">
-        <v>43000</v>
-      </c>
       <c r="Q55" t="n">
         <v>44099</v>
       </c>
       <c r="R55" t="n">
         <v>45015</v>
       </c>
-      <c r="T55" t="n">
-        <v>43000</v>
-      </c>
-      <c r="U55" t="n">
-        <v>44000</v>
-      </c>
-      <c r="V55" t="n">
-        <v>43500</v>
-      </c>
-      <c r="W55" t="n">
-        <v>43500</v>
-      </c>
-      <c r="X55" t="n">
-        <v>42000</v>
-      </c>
       <c r="AB55" t="n">
         <v>40765</v>
       </c>
@@ -6656,9 +6629,6 @@
       <c r="E84" t="n">
         <v>27956</v>
       </c>
-      <c r="F84" t="n">
-        <v>37500</v>
-      </c>
       <c r="I84" t="n">
         <v>33125</v>
       </c>
@@ -6753,9 +6723,6 @@
       <c r="W85" t="n">
         <v>20699</v>
       </c>
-      <c r="X85" t="n">
-        <v>18500</v>
-      </c>
       <c r="Z85" t="n">
         <v>11185</v>
       </c>
@@ -6925,7 +6892,7 @@
         </is>
       </c>
       <c r="U91" t="n">
-        <v>19500</v>
+        <v>16312</v>
       </c>
       <c r="V91" t="n">
         <v>17732</v>
@@ -7520,19 +7487,16 @@
         </is>
       </c>
       <c r="X109" t="n">
-        <v>25000</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>17000</v>
+        <v>21230</v>
       </c>
       <c r="Z109" t="n">
-        <v>30000</v>
+        <v>28176</v>
       </c>
       <c r="AA109" t="n">
         <v>25905</v>
       </c>
       <c r="AB109" t="n">
-        <v>28182</v>
+        <v>28176</v>
       </c>
       <c r="AC109" t="n">
         <v>30772</v>
@@ -8877,9 +8841,6 @@
           <t>Mainova Frankfurt Marathon</t>
         </is>
       </c>
-      <c r="AC159" t="n">
-        <v>17000</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8952,9 +8913,6 @@
           <t>Brighton Marathon</t>
         </is>
       </c>
-      <c r="AC162" t="n">
-        <v>12500</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8977,9 +8935,6 @@
           <t>Shanghai Marathon</t>
         </is>
       </c>
-      <c r="AC163" t="n">
-        <v>23000</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9002,9 +8957,6 @@
           <t>Beijing Marathon</t>
         </is>
       </c>
-      <c r="AC164" t="n">
-        <v>32000</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9052,9 +9004,6 @@
           <t>Gold Coast Marathon</t>
         </is>
       </c>
-      <c r="AC166" t="n">
-        <v>15000</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9077,9 +9026,6 @@
           <t>Dam tot Damloop</t>
         </is>
       </c>
-      <c r="AC167" t="n">
-        <v>50000</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9103,7 +9049,7 @@
         </is>
       </c>
       <c r="AC168" t="n">
-        <v>90000</v>
+        <v>73253</v>
       </c>
     </row>
     <row r="169">
@@ -9127,9 +9073,6 @@
           <t>Great Scottish Run</t>
         </is>
       </c>
-      <c r="AC169" t="n">
-        <v>32000</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9178,7 +9121,7 @@
         </is>
       </c>
       <c r="AC171" t="n">
-        <v>20000</v>
+        <v>19105</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="10K" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +13,7 @@
     <sheet name="BIGGEST EVENTS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -54,7 +53,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -418,7 +417,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1086,7 +1085,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2598,7 +2597,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AC35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3749,7 +3748,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AD171"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4414,6 +4413,12 @@
           <t>HOKA Semi de Paris</t>
         </is>
       </c>
+      <c r="M19" t="n">
+        <v>18642</v>
+      </c>
+      <c r="N19" t="n">
+        <v>21552</v>
+      </c>
       <c r="O19" t="n">
         <v>22030</v>
       </c>
@@ -4444,6 +4449,9 @@
       <c r="X19" t="n">
         <v>33348</v>
       </c>
+      <c r="Y19" t="n">
+        <v>18764</v>
+      </c>
       <c r="Z19" t="n">
         <v>41351</v>
       </c>
@@ -4682,6 +4690,42 @@
         <is>
           <t>Generali Berlin Half Marathon</t>
         </is>
+      </c>
+      <c r="L24" t="n">
+        <v>16050</v>
+      </c>
+      <c r="N24" t="n">
+        <v>17888</v>
+      </c>
+      <c r="O24" t="n">
+        <v>19670</v>
+      </c>
+      <c r="R24" t="n">
+        <v>22254</v>
+      </c>
+      <c r="S24" t="n">
+        <v>22224</v>
+      </c>
+      <c r="T24" t="n">
+        <v>23536</v>
+      </c>
+      <c r="U24" t="n">
+        <v>23957</v>
+      </c>
+      <c r="V24" t="n">
+        <v>25595</v>
+      </c>
+      <c r="W24" t="n">
+        <v>25001</v>
+      </c>
+      <c r="X24" t="n">
+        <v>28471</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13290</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>22001</v>
       </c>
       <c r="AA24" t="n">
         <v>26104</v>
@@ -9136,7 +9180,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AD30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4724,9 +4724,6 @@
       <c r="Y24" t="n">
         <v>13290</v>
       </c>
-      <c r="Z24" t="n">
-        <v>22001</v>
-      </c>
       <c r="AA24" t="n">
         <v>26104</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3871,6 +3871,9 @@
           <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
+      <c r="AA2" t="n">
+        <v>10234</v>
+      </c>
       <c r="AB2" t="n">
         <v>12135</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7852,7 +7852,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3913,6 +3913,11 @@
           <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD3" t="n">
         <v>13416</v>
       </c>
@@ -3972,6 +3977,11 @@
           <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB5" t="n">
         <v>9811</v>
       </c>
@@ -4164,6 +4174,11 @@
           <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD11" t="n">
         <v>22872</v>
       </c>
@@ -4238,6 +4253,11 @@
           <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB13" t="n">
         <v>13706</v>
       </c>
@@ -4306,6 +4326,11 @@
           <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB15" t="n">
         <v>11865</v>
       </c>
@@ -4460,6 +4485,11 @@
       <c r="X19" t="n">
         <v>33348</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z19" t="n">
         <v>18764</v>
       </c>
@@ -4637,6 +4667,11 @@
           <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC22" t="n">
         <v>13245</v>
       </c>
@@ -4668,6 +4703,11 @@
           <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB23" t="n">
         <v>7225</v>
       </c>
@@ -4732,6 +4772,11 @@
       <c r="X24" t="n">
         <v>28471</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z24" t="n">
         <v>13290</v>
       </c>
@@ -4766,6 +4811,11 @@
           <t>Cooper River Bridge Run</t>
         </is>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB25" t="n">
         <v>22336</v>
       </c>
@@ -4883,6 +4933,11 @@
           <t>Acea Run Rome The Marathon</t>
         </is>
       </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB27" t="n">
         <v>11235</v>
       </c>
@@ -4914,6 +4969,11 @@
           <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB28" t="n">
         <v>10853</v>
       </c>
@@ -4948,6 +5008,11 @@
           <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD29" t="n">
         <v>20918</v>
       </c>
@@ -4973,6 +5038,11 @@
           <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD30" t="n">
         <v>19624</v>
       </c>
@@ -5001,6 +5071,11 @@
           <t>Seoul Marathon</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB31" t="n">
         <v>25905</v>
       </c>
@@ -5032,6 +5107,11 @@
           <t>Disney Princess Half Marathon</t>
         </is>
       </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD32" t="n">
         <v>15879</v>
       </c>
@@ -5060,6 +5140,11 @@
           <t>Warsaw Half Marathon</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC33" t="n">
         <v>13422</v>
       </c>
@@ -5088,6 +5173,11 @@
           <t>Generali Prague Half Marathon</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB34" t="n">
         <v>10213</v>
       </c>
@@ -5119,6 +5209,11 @@
           <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD35" t="n">
         <v>12363</v>
       </c>
@@ -5144,6 +5239,11 @@
           <t>GetPro Bath Half</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD36" t="n">
         <v>11133</v>
       </c>
@@ -5172,6 +5272,11 @@
           <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB37" t="n">
         <v>11275</v>
       </c>
@@ -5236,6 +5341,11 @@
       <c r="X38" t="n">
         <v>42549</v>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z38" t="n">
         <v>35321</v>
       </c>
@@ -5297,6 +5407,11 @@
       <c r="X39" t="n">
         <v>48073</v>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA39" t="n">
         <v>35757</v>
       </c>
@@ -5331,6 +5446,11 @@
           <t>Vancouver Sun Run</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB40" t="n">
         <v>25108</v>
       </c>
@@ -5383,6 +5503,11 @@
       <c r="X41" t="n">
         <v>26632</v>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z41" t="n">
         <v>15416</v>
       </c>
@@ -5420,6 +5545,11 @@
           <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD42" t="n">
         <v>24590</v>
       </c>
@@ -5445,6 +5575,11 @@
           <t>Adidas Manchester Marathon</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB43" t="n">
         <v>18221</v>
       </c>
@@ -5476,6 +5611,11 @@
           <t>London Landmarks Half Marathon</t>
         </is>
       </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC44" t="n">
         <v>18869</v>
       </c>
@@ -5504,6 +5644,11 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB45" t="n">
         <v>15306</v>
       </c>
@@ -5535,6 +5680,11 @@
           <t>Statesman Capitol 10K</t>
         </is>
       </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB46" t="n">
         <v>22059</v>
       </c>
@@ -5566,6 +5716,11 @@
           <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB47" t="n">
         <v>14985</v>
       </c>
@@ -5627,6 +5782,11 @@
       <c r="X48" t="n">
         <v>14535</v>
       </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB48" t="n">
         <v>16848</v>
       </c>
@@ -5658,6 +5818,11 @@
           <t>Vienna City Half Marathon</t>
         </is>
       </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD49" t="n">
         <v>12788</v>
       </c>
@@ -5683,6 +5848,11 @@
           <t>21K de Montréal</t>
         </is>
       </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD50" t="n">
         <v>11795</v>
       </c>
@@ -5708,6 +5878,11 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB51" t="n">
         <v>7661</v>
       </c>
@@ -5739,6 +5914,11 @@
           <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD52" t="n">
         <v>10776</v>
       </c>
@@ -5764,6 +5944,11 @@
           <t>Vienna City Marathon</t>
         </is>
       </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB53" t="n">
         <v>6650</v>
       </c>
@@ -5795,6 +5980,11 @@
           <t>Sanlam Cape Town Marathon</t>
         </is>
       </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB54" t="n">
         <v>13336</v>
       </c>
@@ -5840,6 +6030,11 @@
       <c r="R55" t="n">
         <v>45015</v>
       </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC55" t="n">
         <v>40765</v>
       </c>
@@ -5868,6 +6063,11 @@
           <t>BOLDERBoulder 10K</t>
         </is>
       </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB56" t="n">
         <v>35639</v>
       </c>
@@ -5899,6 +6099,11 @@
           <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD57" t="n">
         <v>28474</v>
       </c>
@@ -5924,6 +6129,11 @@
           <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD58" t="n">
         <v>20531</v>
       </c>
@@ -5949,6 +6159,11 @@
           <t>Copenhagen Marathon</t>
         </is>
       </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB59" t="n">
         <v>10164</v>
       </c>
@@ -5980,6 +6195,11 @@
           <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD60" t="n">
         <v>17697</v>
       </c>
@@ -6005,6 +6225,11 @@
           <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD61" t="n">
         <v>17222</v>
       </c>
@@ -6030,6 +6255,11 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC62" t="n">
         <v>15291</v>
       </c>
@@ -6058,6 +6288,11 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD63" t="n">
         <v>12300</v>
       </c>
@@ -6083,6 +6318,11 @@
           <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD64" t="n">
         <v>10768</v>
       </c>
@@ -6120,6 +6360,11 @@
       <c r="T65" t="n">
         <v>5874</v>
       </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB65" t="n">
         <v>5467</v>
       </c>
@@ -6151,6 +6396,11 @@
           <t>Bangsaen10</t>
         </is>
       </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB66" t="n">
         <v>6035</v>
       </c>
@@ -6182,6 +6432,11 @@
           <t>Broløbet - The Bridge Run</t>
         </is>
       </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD67" t="n">
         <v>40241</v>
       </c>
@@ -6207,6 +6462,11 @@
           <t>Adidas 10K Paris</t>
         </is>
       </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB68" t="n">
         <v>24629</v>
       </c>
@@ -6238,6 +6498,11 @@
           <t>Royal Run</t>
         </is>
       </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB69" t="n">
         <v>11329</v>
       </c>
@@ -6269,6 +6534,11 @@
           <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB70" t="n">
         <v>41806</v>
       </c>
@@ -6300,6 +6570,11 @@
           <t>Media Maraton de Bogota</t>
         </is>
       </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD71" t="n">
         <v>21011</v>
       </c>
@@ -6325,6 +6600,11 @@
           <t>Saucony London 10K</t>
         </is>
       </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB72" t="n">
         <v>13368</v>
       </c>
@@ -6356,6 +6636,11 @@
           <t>Asics Run Melbourne</t>
         </is>
       </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD73" t="n">
         <v>11218</v>
       </c>
@@ -6381,6 +6666,11 @@
           <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB74" t="n">
         <v>13297</v>
       </c>
@@ -6412,6 +6702,11 @@
           <t>Maratón de la Ciudad de México Telcel</t>
         </is>
       </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB75" t="n">
         <v>28364</v>
       </c>
@@ -6479,6 +6774,11 @@
       <c r="X76" t="n">
         <v>44065</v>
       </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z76" t="n">
         <v>23097</v>
       </c>
@@ -6534,6 +6834,11 @@
       <c r="X77" t="n">
         <v>43768</v>
       </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD77" t="n">
         <v>46258</v>
       </c>
@@ -6559,6 +6864,11 @@
           <t>Copenhagen Half Marathon</t>
         </is>
       </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB78" t="n">
         <v>24381</v>
       </c>
@@ -6590,6 +6900,11 @@
           <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB79" t="n">
         <v>20274</v>
       </c>
@@ -6621,6 +6936,11 @@
           <t>The Big Half</t>
         </is>
       </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD80" t="n">
         <v>17223</v>
       </c>
@@ -6646,6 +6966,11 @@
           <t>Vitality London 10,000</t>
         </is>
       </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB81" t="n">
         <v>12201</v>
       </c>
@@ -6677,6 +7002,11 @@
           <t>NN Maraton Warszawski</t>
         </is>
       </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB82" t="n">
         <v>5557</v>
       </c>
@@ -6708,6 +7038,11 @@
           <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC83" t="n">
         <v>7392</v>
       </c>
@@ -6784,6 +7119,11 @@
       <c r="X84" t="n">
         <v>45932</v>
       </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z84" t="n">
         <v>26265</v>
       </c>
@@ -6833,6 +7173,11 @@
       <c r="W85" t="n">
         <v>20699</v>
       </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA85" t="n">
         <v>11185</v>
       </c>
@@ -6867,6 +7212,11 @@
           <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD86" t="n">
         <v>26060</v>
       </c>
@@ -6892,6 +7242,11 @@
           <t>Cardiff Half Marathon</t>
         </is>
       </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD87" t="n">
         <v>24634</v>
       </c>
@@ -6920,6 +7275,11 @@
       <c r="X88" t="n">
         <v>13469</v>
       </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB88" t="n">
         <v>16069</v>
       </c>
@@ -6951,6 +7311,11 @@
           <t>Manchester Half Marathon</t>
         </is>
       </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD89" t="n">
         <v>22354</v>
       </c>
@@ -6976,6 +7341,11 @@
           <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD90" t="n">
         <v>18564</v>
       </c>
@@ -7010,6 +7380,11 @@
       <c r="X91" t="n">
         <v>17724</v>
       </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA91" t="n">
         <v>14773</v>
       </c>
@@ -7044,6 +7419,11 @@
           <t>Run in Lyon</t>
         </is>
       </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB92" t="n">
         <v>11065</v>
       </c>
@@ -7075,6 +7455,11 @@
           <t>Royal Parks Half Marathon</t>
         </is>
       </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD93" t="n">
         <v>16201</v>
       </c>
@@ -7100,6 +7485,11 @@
           <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD94" t="n">
         <v>14635</v>
       </c>
@@ -7125,6 +7515,11 @@
           <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD95" t="n">
         <v>13341</v>
       </c>
@@ -7150,6 +7545,11 @@
           <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD96" t="n">
         <v>12156</v>
       </c>
@@ -7175,6 +7575,11 @@
           <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD97" t="n">
         <v>11471</v>
       </c>
@@ -7200,6 +7605,11 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB98" t="n">
         <v>10690</v>
       </c>
@@ -7231,6 +7641,11 @@
           <t>Run in Lyon</t>
         </is>
       </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB99" t="n">
         <v>13566</v>
       </c>
@@ -7262,6 +7677,11 @@
           <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD100" t="n">
         <v>10752</v>
       </c>
@@ -7287,6 +7707,11 @@
           <t>EDP Maratona de Lisboa</t>
         </is>
       </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB101" t="n">
         <v>4847</v>
       </c>
@@ -7318,6 +7743,11 @@
           <t xml:space="preserve">Hyundai Meia Maratona </t>
         </is>
       </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB102" t="n">
         <v>6567</v>
       </c>
@@ -7349,6 +7779,11 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB103" t="n">
         <v>4563</v>
       </c>
@@ -7509,6 +7944,11 @@
           <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD106" t="n">
         <v>10896</v>
       </c>
@@ -7534,6 +7974,11 @@
           <t>Bangsaen42 Chonburi Marathon</t>
         </is>
       </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB107" t="n">
         <v>9758</v>
       </c>
@@ -7565,6 +8010,11 @@
           <t>NN San Silvestre Vallecana</t>
         </is>
       </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB108" t="n">
         <v>31292</v>
       </c>
@@ -7599,6 +8049,11 @@
       <c r="X109" t="n">
         <v>21230</v>
       </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA109" t="n">
         <v>28176</v>
       </c>
@@ -7693,6 +8148,11 @@
       <c r="X110" t="n">
         <v>18805</v>
       </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z110" t="n">
         <v>6241</v>
       </c>
@@ -7730,6 +8190,11 @@
           <t>Taipei Half Marathon</t>
         </is>
       </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB111" t="n">
         <v>16689</v>
       </c>
@@ -7761,6 +8226,11 @@
           <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD112" t="n">
         <v>14747</v>
       </c>
@@ -7786,6 +8256,11 @@
           <t>Bangsaen21</t>
         </is>
       </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB113" t="n">
         <v>9126</v>
       </c>
@@ -7817,6 +8292,11 @@
           <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD114" t="n">
         <v>10178</v>
       </c>
@@ -7842,6 +8322,11 @@
           <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC115" t="n">
         <v>8660</v>
       </c>
@@ -7870,6 +8355,11 @@
           <t>Taipei Marathon</t>
         </is>
       </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB116" t="n">
         <v>8117</v>
       </c>
@@ -7926,6 +8416,11 @@
           <t>Broad Street Run</t>
         </is>
       </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD118" t="n">
         <v>33050</v>
       </c>
@@ -7951,6 +8446,11 @@
           <t>Flying Pig Marathon</t>
         </is>
       </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD119" t="n">
         <v>30908</v>
       </c>
@@ -7976,6 +8476,11 @@
           <t>Lilac Bloomsday Run</t>
         </is>
       </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD120" t="n">
         <v>30049</v>
       </c>
@@ -8001,6 +8506,11 @@
           <t>Credit Union Cherry Blossom</t>
         </is>
       </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD121" t="n">
         <v>26868</v>
       </c>
@@ -8026,6 +8536,11 @@
           <t>San Francisco Marathon</t>
         </is>
       </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD122" t="n">
         <v>24698</v>
       </c>
@@ -8051,6 +8566,11 @@
           <t>Bank of America Shamrock Shuffle</t>
         </is>
       </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD123" t="n">
         <v>23733</v>
       </c>
@@ -8076,6 +8596,11 @@
           <t>Dick's Pittsburgh Marathon</t>
         </is>
       </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD124" t="n">
         <v>21899</v>
       </c>
@@ -8101,6 +8626,11 @@
           <t>Medtronic Twin Cities Marathon</t>
         </is>
       </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD125" t="n">
         <v>21658</v>
       </c>
@@ -8151,6 +8681,11 @@
           <t>Long Beach Marathon</t>
         </is>
       </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD127" t="n">
         <v>20332</v>
       </c>
@@ -8176,6 +8711,11 @@
           <t>Bay to Breakers</t>
         </is>
       </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD128" t="n">
         <v>20007</v>
       </c>
@@ -8201,6 +8741,11 @@
           <t>Silicon Valley Turkey Trot</t>
         </is>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD129" t="n">
         <v>20019</v>
       </c>
@@ -8276,6 +8821,11 @@
           <t>Army Ten Miler</t>
         </is>
       </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD132" t="n">
         <v>18975</v>
       </c>
@@ -8301,6 +8851,11 @@
           <t>Grandma's Marathon</t>
         </is>
       </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD133" t="n">
         <v>18354</v>
       </c>
@@ -8326,6 +8881,11 @@
           <t>Detroit Marathon</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD134" t="n">
         <v>17918</v>
       </c>
@@ -8376,6 +8936,11 @@
           <t>St. Jude Memphis Marathon</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD136" t="n">
         <v>17497</v>
       </c>
@@ -8401,6 +8966,11 @@
           <t>Oklahoma City Memorial Marathon</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD137" t="n">
         <v>17278</v>
       </c>
@@ -8426,6 +8996,11 @@
           <t>Richmond Marathon</t>
         </is>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD138" t="n">
         <v>17220</v>
       </c>
@@ -8451,6 +9026,11 @@
           <t>Crescent City Classic</t>
         </is>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD139" t="n">
         <v>16486</v>
       </c>
@@ -8476,6 +9056,11 @@
           <t>San Antonio Marathon</t>
         </is>
       </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD140" t="n">
         <v>15615</v>
       </c>
@@ -8501,6 +9086,11 @@
           <t>Hoag OC Marathon</t>
         </is>
       </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD141" t="n">
         <v>15569</v>
       </c>
@@ -8526,6 +9116,11 @@
           <t>Gate River Run</t>
         </is>
       </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD142" t="n">
         <v>15415</v>
       </c>
@@ -8551,6 +9146,11 @@
           <t>Denver Colfax Marathon</t>
         </is>
       </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD143" t="n">
         <v>14892</v>
       </c>
@@ -8601,6 +9201,11 @@
           <t>Indianapolis Monumental Marathon</t>
         </is>
       </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD145" t="n">
         <v>13827</v>
       </c>
@@ -8626,6 +9231,11 @@
           <t>Columbus Marathon</t>
         </is>
       </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD146" t="n">
         <v>13101</v>
       </c>
@@ -8651,6 +9261,11 @@
           <t>Boilermaker Road Race</t>
         </is>
       </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD147" t="n">
         <v>12471</v>
       </c>
@@ -8676,6 +9291,11 @@
           <t>Baltimore Running Festival</t>
         </is>
       </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD148" t="n">
         <v>11475</v>
       </c>
@@ -8701,6 +9321,11 @@
           <t>Manchester Road Race</t>
         </is>
       </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD149" t="n">
         <v>11003</v>
       </c>
@@ -8726,6 +9351,11 @@
           <t>Shamrock Run Portland</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD150" t="n">
         <v>10929</v>
       </c>
@@ -8751,6 +9381,11 @@
           <t>Falmouth Road Race</t>
         </is>
       </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD151" t="n">
         <v>10783</v>
       </c>
@@ -8776,6 +9411,11 @@
           <t>Eugene Marathon</t>
         </is>
       </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD152" t="n">
         <v>10771</v>
       </c>
@@ -8801,6 +9441,11 @@
           <t>BMW Dallas Marathon</t>
         </is>
       </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD153" t="n">
         <v>19966</v>
       </c>
@@ -8826,6 +9471,11 @@
           <t>California International Marathon</t>
         </is>
       </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD154" t="n">
         <v>9083</v>
       </c>
@@ -8851,6 +9501,11 @@
           <t>Fargo Marathon</t>
         </is>
       </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD155" t="n">
         <v>9038</v>
       </c>
@@ -8876,6 +9531,11 @@
           <t>Rock 'n' Roll Arizona Marathon</t>
         </is>
       </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD156" t="n">
         <v>8965</v>
       </c>
@@ -8901,6 +9561,11 @@
           <t>Portland Marathon</t>
         </is>
       </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD157" t="n">
         <v>9838</v>
       </c>
@@ -8926,6 +9591,11 @@
           <t>Haspa Marathon Hamburg</t>
         </is>
       </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD158" t="n">
         <v>12923</v>
       </c>
@@ -8951,6 +9621,11 @@
           <t>Mainova Frankfurt Marathon</t>
         </is>
       </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8973,6 +9648,11 @@
           <t>Stockholm Marathon</t>
         </is>
       </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD160" t="n">
         <v>18839</v>
       </c>
@@ -8998,6 +9678,11 @@
           <t>Milano Marathon</t>
         </is>
       </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD161" t="n">
         <v>10250</v>
       </c>
@@ -9023,6 +9708,11 @@
           <t>Brighton Marathon</t>
         </is>
       </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9067,6 +9757,11 @@
           <t>Beijing Marathon</t>
         </is>
       </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9114,6 +9809,11 @@
           <t>Gold Coast Marathon</t>
         </is>
       </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9136,6 +9836,11 @@
           <t>Dam tot Damloop</t>
         </is>
       </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9218,6 +9923,11 @@
       <c r="X168" t="n">
         <v>70517</v>
       </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z168" t="inlineStr">
         <is>
           <t>-</t>
@@ -9259,6 +9969,11 @@
           <t>Great Scottish Run</t>
         </is>
       </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9304,6 +10019,11 @@
       <c r="D171" t="inlineStr">
         <is>
           <t>Athens Marathon</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="AD171" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4569,6 +4569,11 @@
       <c r="X20" t="n">
         <v>35460</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
       <c r="Z20" t="n">
         <v>18272</v>
       </c>
@@ -5343,7 +5348,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="Z38" t="n">
@@ -8051,7 +8056,7 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="AA109" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3879,6 +3879,11 @@
           <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB2" t="n">
         <v>10234</v>
       </c>
@@ -4292,6 +4297,11 @@
           <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB14" t="n">
         <v>8228</v>
       </c>
@@ -4677,6 +4687,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC22" t="n">
         <v>13245</v>
       </c>
@@ -4713,6 +4728,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB23" t="n">
         <v>7225</v>
       </c>
@@ -4943,6 +4963,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB27" t="n">
         <v>11235</v>
       </c>
@@ -5081,6 +5106,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB31" t="n">
         <v>25905</v>
       </c>
@@ -5183,6 +5213,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB34" t="n">
         <v>10213</v>
       </c>
@@ -5456,6 +5491,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB40" t="n">
         <v>25108</v>
       </c>
@@ -5990,6 +6030,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB54" t="n">
         <v>13336</v>
       </c>
@@ -6040,6 +6085,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC55" t="n">
         <v>40765</v>
       </c>
@@ -6073,6 +6123,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB56" t="n">
         <v>35639</v>
       </c>
@@ -6139,6 +6194,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD58" t="n">
         <v>20531</v>
       </c>
@@ -6169,6 +6229,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB59" t="n">
         <v>10164</v>
       </c>
@@ -6370,6 +6435,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB65" t="n">
         <v>5467</v>
       </c>
@@ -6472,6 +6542,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB68" t="n">
         <v>24629</v>
       </c>
@@ -6910,6 +6985,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB79" t="n">
         <v>20274</v>
       </c>
@@ -7390,6 +7470,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA91" t="n">
         <v>14773</v>
       </c>
@@ -7717,6 +7802,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB101" t="n">
         <v>4847</v>
       </c>
@@ -7753,6 +7843,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB102" t="n">
         <v>6567</v>
       </c>
@@ -7984,6 +8079,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB107" t="n">
         <v>9758</v>
       </c>
@@ -9658,6 +9758,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD160" t="n">
         <v>18839</v>
       </c>
@@ -9718,6 +9823,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9740,6 +9850,11 @@
           <t>Shanghai Marathon</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9767,6 +9882,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9789,6 +9909,11 @@
           <t>Osaka Marathon</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD165" t="n">
         <v>26175</v>
       </c>
@@ -9819,6 +9944,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9842,6 +9972,11 @@
         </is>
       </c>
       <c r="Y167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5632,7 +5632,7 @@
         <v>21847</v>
       </c>
       <c r="AD43" t="n">
-        <v>23828</v>
+        <v>23949</v>
       </c>
     </row>
     <row r="44">
@@ -7811,7 +7811,7 @@
         <v>4847</v>
       </c>
       <c r="AC101" t="n">
-        <v>5720</v>
+        <v>9600</v>
       </c>
       <c r="AD101" t="n">
         <v>9600</v>
@@ -7852,7 +7852,7 @@
         <v>6567</v>
       </c>
       <c r="AC102" t="n">
-        <v>7255</v>
+        <v>7635</v>
       </c>
       <c r="AD102" t="n">
         <v>7635</v>
@@ -9980,6 +9980,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AD167" t="n">
+        <v>37233</v>
       </c>
     </row>
     <row r="168">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4692,8 +4692,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AB22" t="n">
+        <v>11177</v>
+      </c>
       <c r="AC22" t="n">
-        <v>13245</v>
+        <v>13346</v>
       </c>
       <c r="AD22" t="n">
         <v>17675</v>
@@ -5626,10 +5629,10 @@
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>18221</v>
+        <v>18576</v>
       </c>
       <c r="AC43" t="n">
-        <v>21847</v>
+        <v>21893</v>
       </c>
       <c r="AD43" t="n">
         <v>23949</v>
@@ -5701,7 +5704,7 @@
         <v>17350</v>
       </c>
       <c r="AD45" t="n">
-        <v>19356</v>
+        <v>19850</v>
       </c>
     </row>
     <row r="46">
@@ -5831,6 +5834,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>11722</v>
       </c>
       <c r="AB48" t="n">
         <v>16848</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8532,6 +8532,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC118" t="n">
+        <v>31455</v>
+      </c>
       <c r="AD118" t="n">
         <v>33050</v>
       </c>
@@ -8562,6 +8565,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC119" t="n">
+        <v>25027</v>
+      </c>
       <c r="AD119" t="n">
         <v>30908</v>
       </c>
@@ -8592,6 +8598,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC120" t="n">
+        <v>27897</v>
+      </c>
       <c r="AD120" t="n">
         <v>30049</v>
       </c>
@@ -8622,6 +8631,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC121" t="n">
+        <v>24520</v>
+      </c>
       <c r="AD121" t="n">
         <v>26868</v>
       </c>
@@ -8652,6 +8664,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC122" t="n">
+        <v>22491</v>
+      </c>
       <c r="AD122" t="n">
         <v>24698</v>
       </c>
@@ -8682,6 +8697,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC123" t="n">
+        <v>21391</v>
+      </c>
       <c r="AD123" t="n">
         <v>23733</v>
       </c>
@@ -8712,6 +8730,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC124" t="n">
+        <v>19748</v>
+      </c>
       <c r="AD124" t="n">
         <v>21899</v>
       </c>
@@ -8742,6 +8763,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC125" t="n">
+        <v>20523</v>
+      </c>
       <c r="AD125" t="n">
         <v>21658</v>
       </c>
@@ -8767,6 +8791,9 @@
           <t>Cowtown Marathon</t>
         </is>
       </c>
+      <c r="AC126" t="n">
+        <v>19119</v>
+      </c>
       <c r="AD126" t="n">
         <v>20995</v>
       </c>
@@ -8797,6 +8824,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC127" t="n">
+        <v>17187</v>
+      </c>
       <c r="AD127" t="n">
         <v>20332</v>
       </c>
@@ -8827,6 +8857,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC128" t="n">
+        <v>16010</v>
+      </c>
       <c r="AD128" t="n">
         <v>20007</v>
       </c>
@@ -8857,6 +8890,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC129" t="n">
+        <v>17059</v>
+      </c>
       <c r="AD129" t="n">
         <v>20019</v>
       </c>
@@ -8882,6 +8918,9 @@
           <t>Austin Marathon</t>
         </is>
       </c>
+      <c r="AC130" t="n">
+        <v>16234</v>
+      </c>
       <c r="AD130" t="n">
         <v>19206</v>
       </c>
@@ -8907,6 +8946,9 @@
           <t>Miami Marathon</t>
         </is>
       </c>
+      <c r="AC131" t="n">
+        <v>17827</v>
+      </c>
       <c r="AD131" t="n">
         <v>19119</v>
       </c>
@@ -8937,6 +8979,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC132" t="n">
+        <v>19225</v>
+      </c>
       <c r="AD132" t="n">
         <v>18975</v>
       </c>
@@ -8967,6 +9012,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC133" t="n">
+        <v>17556</v>
+      </c>
       <c r="AD133" t="n">
         <v>18354</v>
       </c>
@@ -8997,6 +9045,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC134" t="n">
+        <v>16526</v>
+      </c>
       <c r="AD134" t="n">
         <v>17918</v>
       </c>
@@ -9022,6 +9073,9 @@
           <t>Gasparilla Distance Classic</t>
         </is>
       </c>
+      <c r="AC135" t="n">
+        <v>15499</v>
+      </c>
       <c r="AD135" t="n">
         <v>17790</v>
       </c>
@@ -9052,6 +9106,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC136" t="n">
+        <v>18030</v>
+      </c>
       <c r="AD136" t="n">
         <v>17497</v>
       </c>
@@ -9082,6 +9139,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC137" t="n">
+        <v>13767</v>
+      </c>
       <c r="AD137" t="n">
         <v>17278</v>
       </c>
@@ -9112,6 +9172,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC138" t="n">
+        <v>17495</v>
+      </c>
       <c r="AD138" t="n">
         <v>17220</v>
       </c>
@@ -9142,6 +9205,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC139" t="n">
+        <v>13063</v>
+      </c>
       <c r="AD139" t="n">
         <v>16486</v>
       </c>
@@ -9172,6 +9238,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC140" t="n">
+        <v>15456</v>
+      </c>
       <c r="AD140" t="n">
         <v>15615</v>
       </c>
@@ -9202,6 +9271,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC141" t="n">
+        <v>16080</v>
+      </c>
       <c r="AD141" t="n">
         <v>15569</v>
       </c>
@@ -9232,6 +9304,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC142" t="n">
+        <v>13246</v>
+      </c>
       <c r="AD142" t="n">
         <v>15415</v>
       </c>
@@ -9262,6 +9337,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC143" t="n">
+        <v>14225</v>
+      </c>
       <c r="AD143" t="n">
         <v>14892</v>
       </c>
@@ -9287,6 +9365,9 @@
           <t>Shamrock Marathon</t>
         </is>
       </c>
+      <c r="AC144" t="n">
+        <v>13868</v>
+      </c>
       <c r="AD144" t="n">
         <v>14301</v>
       </c>
@@ -9317,6 +9398,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC145" t="n">
+        <v>13548</v>
+      </c>
       <c r="AD145" t="n">
         <v>13827</v>
       </c>
@@ -9347,6 +9431,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC146" t="n">
+        <v>11681</v>
+      </c>
       <c r="AD146" t="n">
         <v>13101</v>
       </c>
@@ -9377,6 +9464,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC147" t="n">
+        <v>11630</v>
+      </c>
       <c r="AD147" t="n">
         <v>12471</v>
       </c>
@@ -9407,6 +9497,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC148" t="n">
+        <v>10336</v>
+      </c>
       <c r="AD148" t="n">
         <v>11475</v>
       </c>
@@ -9467,6 +9560,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC150" t="n">
+        <v>12539</v>
+      </c>
       <c r="AD150" t="n">
         <v>10929</v>
       </c>
@@ -9497,6 +9593,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC151" t="n">
+        <v>11070</v>
+      </c>
       <c r="AD151" t="n">
         <v>10783</v>
       </c>
@@ -9527,6 +9626,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC152" t="n">
+        <v>8915</v>
+      </c>
       <c r="AD152" t="n">
         <v>10771</v>
       </c>
@@ -9557,6 +9659,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC153" t="n">
+        <v>18344</v>
+      </c>
       <c r="AD153" t="n">
         <v>19966</v>
       </c>
@@ -9587,6 +9692,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC154" t="n">
+        <v>9125</v>
+      </c>
       <c r="AD154" t="n">
         <v>9083</v>
       </c>
@@ -9617,6 +9725,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC155" t="n">
+        <v>9543</v>
+      </c>
       <c r="AD155" t="n">
         <v>9038</v>
       </c>
@@ -9646,6 +9757,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AC156" t="n">
+        <v>9965</v>
       </c>
       <c r="AD156" t="n">
         <v>8965</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7134,6 +7134,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA83" t="n">
+        <v>8329</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>8475</v>
+      </c>
       <c r="AC83" t="n">
         <v>7392</v>
       </c>
@@ -8532,6 +8538,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA118" t="n">
+        <v>20474</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>28025</v>
+      </c>
       <c r="AC118" t="n">
         <v>31455</v>
       </c>
@@ -8565,6 +8577,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA119" t="n">
+        <v>19860</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>29946</v>
+      </c>
       <c r="AC119" t="n">
         <v>25027</v>
       </c>
@@ -8598,6 +8616,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA120" t="n">
+        <v>21018</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>25773</v>
+      </c>
       <c r="AC120" t="n">
         <v>27897</v>
       </c>
@@ -8631,6 +8655,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA121" t="n">
+        <v>16716</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>22612</v>
+      </c>
       <c r="AC121" t="n">
         <v>24520</v>
       </c>
@@ -8664,6 +8694,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA122" t="n">
+        <v>13362</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>20918</v>
+      </c>
       <c r="AC122" t="n">
         <v>22491</v>
       </c>
@@ -8697,6 +8733,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA123" t="n">
+        <v>16772</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>19521</v>
+      </c>
       <c r="AC123" t="n">
         <v>21391</v>
       </c>
@@ -8730,6 +8772,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA124" t="n">
+        <v>16750</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>23636</v>
+      </c>
       <c r="AC124" t="n">
         <v>19748</v>
       </c>
@@ -8763,6 +8811,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA125" t="n">
+        <v>18466</v>
+      </c>
       <c r="AC125" t="n">
         <v>20523</v>
       </c>
@@ -8791,6 +8842,12 @@
           <t>Cowtown Marathon</t>
         </is>
       </c>
+      <c r="AA126" t="n">
+        <v>9830</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>16661</v>
+      </c>
       <c r="AC126" t="n">
         <v>19119</v>
       </c>
@@ -8824,6 +8881,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA127" t="n">
+        <v>8874</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>11560</v>
+      </c>
       <c r="AC127" t="n">
         <v>17187</v>
       </c>
@@ -8857,6 +8920,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA128" t="n">
+        <v>16782</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>11858</v>
+      </c>
       <c r="AC128" t="n">
         <v>16010</v>
       </c>
@@ -8890,6 +8959,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA129" t="n">
+        <v>15076</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>15388</v>
+      </c>
       <c r="AC129" t="n">
         <v>17059</v>
       </c>
@@ -8918,6 +8993,12 @@
           <t>Austin Marathon</t>
         </is>
       </c>
+      <c r="AA130" t="n">
+        <v>10154</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>13379</v>
+      </c>
       <c r="AC130" t="n">
         <v>16234</v>
       </c>
@@ -8946,6 +9027,12 @@
           <t>Miami Marathon</t>
         </is>
       </c>
+      <c r="AA131" t="n">
+        <v>14696</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>17704</v>
+      </c>
       <c r="AC131" t="n">
         <v>17827</v>
       </c>
@@ -8979,6 +9066,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA132" t="n">
+        <v>12008</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>17583</v>
+      </c>
       <c r="AC132" t="n">
         <v>19225</v>
       </c>
@@ -9012,6 +9105,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA133" t="n">
+        <v>7006</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>16358</v>
+      </c>
       <c r="AC133" t="n">
         <v>17556</v>
       </c>
@@ -9045,6 +9144,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA134" t="n">
+        <v>12659</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>16554</v>
+      </c>
       <c r="AC134" t="n">
         <v>16526</v>
       </c>
@@ -9073,6 +9178,12 @@
           <t>Gasparilla Distance Classic</t>
         </is>
       </c>
+      <c r="AA135" t="n">
+        <v>12474</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>15415</v>
+      </c>
       <c r="AC135" t="n">
         <v>15499</v>
       </c>
@@ -9106,6 +9217,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA136" t="n">
+        <v>18944</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>20201</v>
+      </c>
       <c r="AC136" t="n">
         <v>18030</v>
       </c>
@@ -9139,6 +9256,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA137" t="n">
+        <v>8470</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>12418</v>
+      </c>
       <c r="AC137" t="n">
         <v>13767</v>
       </c>
@@ -9172,6 +9295,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA138" t="n">
+        <v>12358</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>14560</v>
+      </c>
       <c r="AC138" t="n">
         <v>17495</v>
       </c>
@@ -9205,6 +9334,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA139" t="n">
+        <v>8416</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>10242</v>
+      </c>
       <c r="AC139" t="n">
         <v>13063</v>
       </c>
@@ -9238,6 +9373,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA140" t="n">
+        <v>17260</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>13382</v>
+      </c>
       <c r="AC140" t="n">
         <v>15456</v>
       </c>
@@ -9271,6 +9412,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA141" t="n">
+        <v>8425</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>16379</v>
+      </c>
       <c r="AC141" t="n">
         <v>16080</v>
       </c>
@@ -9304,6 +9451,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA142" t="n">
+        <v>11413</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>13009</v>
+      </c>
       <c r="AC142" t="n">
         <v>13246</v>
       </c>
@@ -9337,6 +9490,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA143" t="n">
+        <v>9851</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>11439</v>
+      </c>
       <c r="AC143" t="n">
         <v>14225</v>
       </c>
@@ -9365,6 +9524,12 @@
           <t>Shamrock Marathon</t>
         </is>
       </c>
+      <c r="AA144" t="n">
+        <v>17702</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>16305</v>
+      </c>
       <c r="AC144" t="n">
         <v>13868</v>
       </c>
@@ -9398,6 +9563,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA145" t="n">
+        <v>11520</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>10712</v>
+      </c>
       <c r="AC145" t="n">
         <v>13548</v>
       </c>
@@ -9431,6 +9602,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA146" t="n">
+        <v>9124</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>10863</v>
+      </c>
       <c r="AC146" t="n">
         <v>11681</v>
       </c>
@@ -9464,6 +9641,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA147" t="n">
+        <v>8348</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>10137</v>
+      </c>
       <c r="AC147" t="n">
         <v>11630</v>
       </c>
@@ -9497,6 +9680,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA148" t="n">
+        <v>10060</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>9984</v>
+      </c>
       <c r="AC148" t="n">
         <v>10336</v>
       </c>
@@ -9530,6 +9719,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA149" t="n">
+        <v>8360</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>9590</v>
+      </c>
       <c r="AD149" t="n">
         <v>11003</v>
       </c>
@@ -9560,6 +9755,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA150" t="n">
+        <v>8758</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>9906</v>
+      </c>
       <c r="AC150" t="n">
         <v>12539</v>
       </c>
@@ -9593,6 +9794,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA151" t="n">
+        <v>8609</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>9198</v>
+      </c>
       <c r="AC151" t="n">
         <v>11070</v>
       </c>
@@ -9659,6 +9866,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA153" t="n">
+        <v>13343</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>16803</v>
+      </c>
       <c r="AC153" t="n">
         <v>18344</v>
       </c>
@@ -9692,6 +9905,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA154" t="n">
+        <v>8372</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>10165</v>
+      </c>
       <c r="AC154" t="n">
         <v>9125</v>
       </c>
@@ -9757,6 +9976,12 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA156" t="n">
+        <v>18272</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>10950</v>
       </c>
       <c r="AC156" t="n">
         <v>9965</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7129,6 +7129,12 @@
           <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
+      <c r="W83" t="n">
+        <v>13224</v>
+      </c>
+      <c r="X83" t="n">
+        <v>13823</v>
+      </c>
       <c r="Y83" t="inlineStr">
         <is>
           <t>-</t>
@@ -8533,6 +8539,12 @@
           <t>Broad Street Run</t>
         </is>
       </c>
+      <c r="W118" t="n">
+        <v>36222</v>
+      </c>
+      <c r="X118" t="n">
+        <v>34565</v>
+      </c>
       <c r="Y118" t="inlineStr">
         <is>
           <t>-</t>
@@ -8572,6 +8584,12 @@
           <t>Flying Pig Marathon</t>
         </is>
       </c>
+      <c r="W119" t="n">
+        <v>36726</v>
+      </c>
+      <c r="X119" t="n">
+        <v>31325</v>
+      </c>
       <c r="Y119" t="inlineStr">
         <is>
           <t>-</t>
@@ -8611,6 +8629,12 @@
           <t>Lilac Bloomsday Run</t>
         </is>
       </c>
+      <c r="W120" t="n">
+        <v>38068</v>
+      </c>
+      <c r="X120" t="n">
+        <v>34832</v>
+      </c>
       <c r="Y120" t="inlineStr">
         <is>
           <t>-</t>
@@ -8650,6 +8674,12 @@
           <t>Credit Union Cherry Blossom</t>
         </is>
       </c>
+      <c r="W121" t="n">
+        <v>19188</v>
+      </c>
+      <c r="X121" t="n">
+        <v>20358</v>
+      </c>
       <c r="Y121" t="inlineStr">
         <is>
           <t>-</t>
@@ -8689,6 +8719,12 @@
           <t>San Francisco Marathon</t>
         </is>
       </c>
+      <c r="W122" t="n">
+        <v>17621</v>
+      </c>
+      <c r="X122" t="n">
+        <v>17587</v>
+      </c>
       <c r="Y122" t="inlineStr">
         <is>
           <t>-</t>
@@ -8728,6 +8764,12 @@
           <t>Bank of America Shamrock Shuffle</t>
         </is>
       </c>
+      <c r="W123" t="n">
+        <v>20892</v>
+      </c>
+      <c r="X123" t="n">
+        <v>20781</v>
+      </c>
       <c r="Y123" t="inlineStr">
         <is>
           <t>-</t>
@@ -8767,6 +8809,12 @@
           <t>Dick's Pittsburgh Marathon</t>
         </is>
       </c>
+      <c r="W124" t="n">
+        <v>21135</v>
+      </c>
+      <c r="X124" t="n">
+        <v>20140</v>
+      </c>
       <c r="Y124" t="inlineStr">
         <is>
           <t>-</t>
@@ -8806,6 +8854,12 @@
           <t>Medtronic Twin Cities Marathon</t>
         </is>
       </c>
+      <c r="W125" t="n">
+        <v>22923</v>
+      </c>
+      <c r="X125" t="n">
+        <v>17796</v>
+      </c>
       <c r="Y125" t="inlineStr">
         <is>
           <t>-</t>
@@ -8842,6 +8896,12 @@
           <t>Cowtown Marathon</t>
         </is>
       </c>
+      <c r="W126" t="n">
+        <v>14874</v>
+      </c>
+      <c r="X126" t="n">
+        <v>18852</v>
+      </c>
       <c r="AA126" t="n">
         <v>9830</v>
       </c>
@@ -8876,6 +8936,12 @@
           <t>Long Beach Marathon</t>
         </is>
       </c>
+      <c r="W127" t="n">
+        <v>10323</v>
+      </c>
+      <c r="X127" t="n">
+        <v>9456</v>
+      </c>
       <c r="Y127" t="inlineStr">
         <is>
           <t>-</t>
@@ -8915,6 +8981,12 @@
           <t>Bay to Breakers</t>
         </is>
       </c>
+      <c r="W128" t="n">
+        <v>24572</v>
+      </c>
+      <c r="X128" t="n">
+        <v>18336</v>
+      </c>
       <c r="Y128" t="inlineStr">
         <is>
           <t>-</t>
@@ -8954,6 +9026,12 @@
           <t>Silicon Valley Turkey Trot</t>
         </is>
       </c>
+      <c r="W129" t="n">
+        <v>15878</v>
+      </c>
+      <c r="X129" t="n">
+        <v>16864</v>
+      </c>
       <c r="Y129" t="inlineStr">
         <is>
           <t>-</t>
@@ -8993,6 +9071,12 @@
           <t>Austin Marathon</t>
         </is>
       </c>
+      <c r="W130" t="n">
+        <v>11669</v>
+      </c>
+      <c r="X130" t="n">
+        <v>13914</v>
+      </c>
       <c r="AA130" t="n">
         <v>10154</v>
       </c>
@@ -9027,6 +9111,12 @@
           <t>Miami Marathon</t>
         </is>
       </c>
+      <c r="W131" t="n">
+        <v>18906</v>
+      </c>
+      <c r="X131" t="n">
+        <v>19535</v>
+      </c>
       <c r="AA131" t="n">
         <v>14696</v>
       </c>
@@ -9061,6 +9151,12 @@
           <t>Army Ten Miler</t>
         </is>
       </c>
+      <c r="W132" t="n">
+        <v>24808</v>
+      </c>
+      <c r="X132" t="n">
+        <v>25107</v>
+      </c>
       <c r="Y132" t="inlineStr">
         <is>
           <t>-</t>
@@ -9100,6 +9196,12 @@
           <t>Grandma's Marathon</t>
         </is>
       </c>
+      <c r="W133" t="n">
+        <v>15483</v>
+      </c>
+      <c r="X133" t="n">
+        <v>18957</v>
+      </c>
       <c r="Y133" t="inlineStr">
         <is>
           <t>-</t>
@@ -9139,6 +9241,12 @@
           <t>Detroit Marathon</t>
         </is>
       </c>
+      <c r="W134" t="n">
+        <v>17568</v>
+      </c>
+      <c r="X134" t="n">
+        <v>18806</v>
+      </c>
       <c r="Y134" t="inlineStr">
         <is>
           <t>-</t>
@@ -9178,6 +9286,12 @@
           <t>Gasparilla Distance Classic</t>
         </is>
       </c>
+      <c r="W135" t="n">
+        <v>26682</v>
+      </c>
+      <c r="X135" t="n">
+        <v>26476</v>
+      </c>
       <c r="AA135" t="n">
         <v>12474</v>
       </c>
@@ -9212,6 +9326,12 @@
           <t>St. Jude Memphis Marathon</t>
         </is>
       </c>
+      <c r="W136" t="n">
+        <v>19406</v>
+      </c>
+      <c r="X136" t="n">
+        <v>19702</v>
+      </c>
       <c r="Y136" t="inlineStr">
         <is>
           <t>-</t>
@@ -9251,6 +9371,12 @@
           <t>Oklahoma City Memorial Marathon</t>
         </is>
       </c>
+      <c r="W137" t="n">
+        <v>15162</v>
+      </c>
+      <c r="X137" t="n">
+        <v>14348</v>
+      </c>
       <c r="Y137" t="inlineStr">
         <is>
           <t>-</t>
@@ -9290,6 +9416,12 @@
           <t>Richmond Marathon</t>
         </is>
       </c>
+      <c r="W138" t="n">
+        <v>14545</v>
+      </c>
+      <c r="X138" t="n">
+        <v>15382</v>
+      </c>
       <c r="Y138" t="inlineStr">
         <is>
           <t>-</t>
@@ -9329,6 +9461,12 @@
           <t>Crescent City Classic</t>
         </is>
       </c>
+      <c r="W139" t="n">
+        <v>13729</v>
+      </c>
+      <c r="X139" t="n">
+        <v>13942</v>
+      </c>
       <c r="Y139" t="inlineStr">
         <is>
           <t>-</t>
@@ -9368,6 +9506,12 @@
           <t>San Antonio Marathon</t>
         </is>
       </c>
+      <c r="W140" t="n">
+        <v>18639</v>
+      </c>
+      <c r="X140" t="n">
+        <v>16649</v>
+      </c>
       <c r="Y140" t="inlineStr">
         <is>
           <t>-</t>
@@ -9407,6 +9551,12 @@
           <t>Hoag OC Marathon</t>
         </is>
       </c>
+      <c r="W141" t="n">
+        <v>10707</v>
+      </c>
+      <c r="X141" t="n">
+        <v>10750</v>
+      </c>
       <c r="Y141" t="inlineStr">
         <is>
           <t>-</t>
@@ -9446,6 +9596,12 @@
           <t>Gate River Run</t>
         </is>
       </c>
+      <c r="W142" t="n">
+        <v>14113</v>
+      </c>
+      <c r="X142" t="n">
+        <v>12616</v>
+      </c>
       <c r="Y142" t="inlineStr">
         <is>
           <t>-</t>
@@ -9524,6 +9680,12 @@
           <t>Shamrock Marathon</t>
         </is>
       </c>
+      <c r="W144" t="n">
+        <v>18116</v>
+      </c>
+      <c r="X144" t="n">
+        <v>19965</v>
+      </c>
       <c r="AA144" t="n">
         <v>17702</v>
       </c>
@@ -9558,6 +9720,12 @@
           <t>Indianapolis Monumental Marathon</t>
         </is>
       </c>
+      <c r="W145" t="n">
+        <v>14992</v>
+      </c>
+      <c r="X145" t="n">
+        <v>16182</v>
+      </c>
       <c r="Y145" t="inlineStr">
         <is>
           <t>-</t>
@@ -9597,6 +9765,12 @@
           <t>Columbus Marathon</t>
         </is>
       </c>
+      <c r="W146" t="n">
+        <v>12335</v>
+      </c>
+      <c r="X146" t="n">
+        <v>12530</v>
+      </c>
       <c r="Y146" t="inlineStr">
         <is>
           <t>-</t>
@@ -9636,6 +9810,12 @@
           <t>Boilermaker Road Race</t>
         </is>
       </c>
+      <c r="W147" t="n">
+        <v>15752</v>
+      </c>
+      <c r="X147" t="n">
+        <v>15569</v>
+      </c>
       <c r="Y147" t="inlineStr">
         <is>
           <t>-</t>
@@ -9675,6 +9855,12 @@
           <t>Baltimore Running Festival</t>
         </is>
       </c>
+      <c r="W148" t="n">
+        <v>17752</v>
+      </c>
+      <c r="X148" t="n">
+        <v>17020</v>
+      </c>
       <c r="Y148" t="inlineStr">
         <is>
           <t>-</t>
@@ -9714,6 +9900,12 @@
           <t>Manchester Road Race</t>
         </is>
       </c>
+      <c r="W149" t="n">
+        <v>9244</v>
+      </c>
+      <c r="X149" t="n">
+        <v>9956</v>
+      </c>
       <c r="Y149" t="inlineStr">
         <is>
           <t>-</t>
@@ -9750,6 +9942,12 @@
           <t>Shamrock Run Portland</t>
         </is>
       </c>
+      <c r="W150" t="n">
+        <v>15399</v>
+      </c>
+      <c r="X150" t="n">
+        <v>12604</v>
+      </c>
       <c r="Y150" t="inlineStr">
         <is>
           <t>-</t>
@@ -9789,6 +9987,12 @@
           <t>Falmouth Road Race</t>
         </is>
       </c>
+      <c r="W151" t="n">
+        <v>11063</v>
+      </c>
+      <c r="X151" t="n">
+        <v>11544</v>
+      </c>
       <c r="Y151" t="inlineStr">
         <is>
           <t>-</t>
@@ -9861,6 +10065,12 @@
           <t>BMW Dallas Marathon</t>
         </is>
       </c>
+      <c r="W153" t="n">
+        <v>10335</v>
+      </c>
+      <c r="X153" t="n">
+        <v>9518</v>
+      </c>
       <c r="Y153" t="inlineStr">
         <is>
           <t>-</t>
@@ -9900,6 +10110,9 @@
           <t>California International Marathon</t>
         </is>
       </c>
+      <c r="X154" t="n">
+        <v>11840</v>
+      </c>
       <c r="Y154" t="inlineStr">
         <is>
           <t>-</t>
@@ -9939,6 +10152,12 @@
           <t>Fargo Marathon</t>
         </is>
       </c>
+      <c r="W155" t="n">
+        <v>13981</v>
+      </c>
+      <c r="X155" t="n">
+        <v>12399</v>
+      </c>
       <c r="Y155" t="inlineStr">
         <is>
           <t>-</t>
@@ -9971,6 +10190,12 @@
         <is>
           <t>Rock 'n' Roll Arizona Marathon</t>
         </is>
+      </c>
+      <c r="W156" t="n">
+        <v>15908</v>
+      </c>
+      <c r="X156" t="n">
+        <v>15990</v>
       </c>
       <c r="Y156" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10323,15 +10323,16 @@
           <t>Stockholm Marathon</t>
         </is>
       </c>
+      <c r="X160" t="n">
+        <v>12349</v>
+      </c>
       <c r="Y160" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z160" t="n">
+        <v>6958</v>
       </c>
       <c r="AD160" t="n">
         <v>18839</v>
@@ -10363,6 +10364,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AB161" t="n">
+        <v>5123</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>8545</v>
+      </c>
       <c r="AD161" t="n">
         <v>10250</v>
       </c>
@@ -10709,6 +10716,15 @@
           <t>Istanbul Marathon</t>
         </is>
       </c>
+      <c r="AA170" t="n">
+        <v>3039</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>3468</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>4097</v>
+      </c>
       <c r="AD170" t="n">
         <v>4456</v>
       </c>
@@ -10738,6 +10754,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AC171" t="n">
+        <v>19105</v>
       </c>
       <c r="AD171" t="n">
         <v>19105</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7276,7 +7276,15 @@
       <c r="W85" t="n">
         <v>20699</v>
       </c>
+      <c r="X85" t="n">
+        <v>26502</v>
+      </c>
       <c r="Y85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7480,6 +7488,9 @@
       <c r="V91" t="n">
         <v>17732</v>
       </c>
+      <c r="W91" t="n">
+        <v>16237</v>
+      </c>
       <c r="X91" t="n">
         <v>17724</v>
       </c>
@@ -8550,6 +8561,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA118" t="n">
         <v>20474</v>
       </c>
@@ -8685,6 +8701,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA121" t="n">
         <v>16716</v>
       </c>
@@ -8775,6 +8796,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA123" t="n">
         <v>16772</v>
       </c>
@@ -8992,6 +9018,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA128" t="n">
         <v>16782</v>
       </c>
@@ -9472,6 +9503,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA139" t="n">
         <v>8416</v>
       </c>
@@ -9607,6 +9643,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA142" t="n">
         <v>11413</v>
       </c>
@@ -9821,6 +9862,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA147" t="n">
         <v>8348</v>
       </c>
@@ -9911,6 +9957,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA149" t="n">
         <v>8360</v>
       </c>
@@ -9953,6 +10004,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA150" t="n">
         <v>8758</v>
       </c>
@@ -9994,6 +10050,11 @@
         <v>11544</v>
       </c>
       <c r="Y151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4111,17 +4111,77 @@
           <t>Chevron Houston Marathon</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>4794</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4016</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4395</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4740</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5386</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5712</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5414</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5331</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5567</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5349</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6287</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6850</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7606</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6524</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6945</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7003</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7791</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7129</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6997</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>6258</v>
+      </c>
       <c r="AB9" t="n">
-        <v>6104</v>
+        <v>6416</v>
       </c>
       <c r="AC9" t="n">
-        <v>7181</v>
+        <v>7377</v>
       </c>
       <c r="AD9" t="n">
-        <v>7568</v>
+        <v>7325</v>
       </c>
       <c r="AE9" t="n">
-        <v>8869</v>
+        <v>8867</v>
       </c>
     </row>
     <row r="10">
@@ -4297,22 +4357,55 @@
           <t>Zurich Maratón de Sevilla</t>
         </is>
       </c>
+      <c r="N14" t="n">
+        <v>2828</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3124</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3899</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4353</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5963</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7996</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8588</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10355</v>
+      </c>
+      <c r="V14" t="n">
+        <v>10145</v>
+      </c>
+      <c r="W14" t="n">
+        <v>9493</v>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="AA14" t="n">
+        <v>7561</v>
+      </c>
       <c r="AB14" t="n">
-        <v>8228</v>
+        <v>8280</v>
       </c>
       <c r="AC14" t="n">
-        <v>9411</v>
+        <v>9403</v>
       </c>
       <c r="AD14" t="n">
-        <v>10722</v>
+        <v>10689</v>
       </c>
       <c r="AE14" t="n">
-        <v>12448</v>
+        <v>12430</v>
       </c>
     </row>
     <row r="15">
@@ -4621,44 +4714,56 @@
           <t>ASICS Los Angeles Marathon</t>
         </is>
       </c>
+      <c r="N21" t="n">
+        <v>14061</v>
+      </c>
+      <c r="O21" t="n">
+        <v>22403</v>
+      </c>
+      <c r="P21" t="n">
+        <v>19626</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18729</v>
+      </c>
       <c r="R21" t="n">
-        <v>19955</v>
+        <v>19545</v>
       </c>
       <c r="S21" t="n">
-        <v>21516</v>
+        <v>21505</v>
       </c>
       <c r="T21" t="n">
         <v>21924</v>
       </c>
       <c r="U21" t="n">
-        <v>20623</v>
+        <v>20648</v>
       </c>
       <c r="V21" t="n">
-        <v>18990</v>
+        <v>18941</v>
       </c>
       <c r="W21" t="n">
-        <v>19547</v>
+        <v>19573</v>
       </c>
       <c r="X21" t="n">
         <v>19992</v>
       </c>
       <c r="Z21" t="n">
-        <v>5590</v>
+        <v>8643</v>
       </c>
       <c r="AA21" t="n">
-        <v>11616</v>
+        <v>11656</v>
       </c>
       <c r="AB21" t="n">
-        <v>17036</v>
+        <v>16973</v>
       </c>
       <c r="AC21" t="n">
-        <v>20518</v>
+        <v>20453</v>
       </c>
       <c r="AD21" t="n">
-        <v>21476</v>
+        <v>21236</v>
       </c>
       <c r="AE21" t="n">
-        <v>21881</v>
+        <v>21944</v>
       </c>
     </row>
     <row r="22">
@@ -4961,24 +5066,70 @@
           <t>Acea Run Rome The Marathon</t>
         </is>
       </c>
+      <c r="I27" t="n">
+        <v>7587</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7939</v>
+      </c>
+      <c r="K27" t="n">
+        <v>9956</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12014</v>
+      </c>
+      <c r="M27" t="n">
+        <v>10248</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11007</v>
+      </c>
+      <c r="O27" t="n">
+        <v>10995</v>
+      </c>
+      <c r="P27" t="n">
+        <v>12614</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>12499</v>
+      </c>
+      <c r="R27" t="n">
+        <v>10667</v>
+      </c>
+      <c r="S27" t="n">
+        <v>14875</v>
+      </c>
+      <c r="T27" t="n">
+        <v>11487</v>
+      </c>
+      <c r="U27" t="n">
+        <v>13881</v>
+      </c>
+      <c r="V27" t="n">
+        <v>13318</v>
+      </c>
+      <c r="W27" t="n">
+        <v>11743</v>
+      </c>
       <c r="Y27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z27" t="n">
+        <v>5265</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8396</v>
       </c>
       <c r="AB27" t="n">
-        <v>11235</v>
+        <v>11234</v>
       </c>
       <c r="AC27" t="n">
-        <v>15196</v>
+        <v>15166</v>
       </c>
       <c r="AD27" t="n">
-        <v>21930</v>
+        <v>21893</v>
       </c>
     </row>
     <row r="28">
@@ -5002,19 +5153,64 @@
           <t>Zurich Marató de Barcelona</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>4183</v>
+      </c>
+      <c r="L28" t="n">
+        <v>6166</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7589</v>
+      </c>
+      <c r="N28" t="n">
+        <v>8132</v>
+      </c>
+      <c r="O28" t="n">
+        <v>10115</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12468</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>16012</v>
+      </c>
+      <c r="R28" t="n">
+        <v>14777</v>
+      </c>
+      <c r="S28" t="n">
+        <v>14225</v>
+      </c>
+      <c r="T28" t="n">
+        <v>15430</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16495</v>
+      </c>
+      <c r="V28" t="n">
+        <v>16262</v>
+      </c>
+      <c r="W28" t="n">
+        <v>13566</v>
+      </c>
       <c r="Y28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="Z28" t="n">
+        <v>9126</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>5407</v>
+      </c>
       <c r="AB28" t="n">
-        <v>10853</v>
+        <v>10875</v>
       </c>
       <c r="AC28" t="n">
-        <v>16130</v>
+        <v>16127</v>
       </c>
       <c r="AD28" t="n">
-        <v>21695</v>
+        <v>21715</v>
       </c>
       <c r="AE28" t="n">
         <v>25115</v>
@@ -5995,19 +6191,82 @@
           <t>Vienna City Marathon</t>
         </is>
       </c>
+      <c r="E53" t="n">
+        <v>6729</v>
+      </c>
+      <c r="F53" t="n">
+        <v>9198</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8817</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7735</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5942</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5233</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5580</v>
+      </c>
+      <c r="L53" t="n">
+        <v>5880</v>
+      </c>
+      <c r="M53" t="n">
+        <v>6251</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5021</v>
+      </c>
+      <c r="O53" t="n">
+        <v>5052</v>
+      </c>
+      <c r="P53" t="n">
+        <v>5942</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>5892</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6878</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6343</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5970</v>
+      </c>
+      <c r="U53" t="n">
+        <v>6498</v>
+      </c>
+      <c r="V53" t="n">
+        <v>6340</v>
+      </c>
+      <c r="W53" t="n">
+        <v>5432</v>
+      </c>
       <c r="Y53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="Z53" t="n">
+        <v>3054</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4801</v>
+      </c>
       <c r="AB53" t="n">
-        <v>6650</v>
+        <v>6648</v>
       </c>
       <c r="AC53" t="n">
-        <v>7490</v>
+        <v>7434</v>
       </c>
       <c r="AD53" t="n">
-        <v>9300</v>
+        <v>9286</v>
       </c>
     </row>
     <row r="54">
@@ -6230,6 +6489,51 @@
           <t>Copenhagen Marathon</t>
         </is>
       </c>
+      <c r="F59" t="n">
+        <v>4720</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4622</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5570</v>
+      </c>
+      <c r="K59" t="n">
+        <v>4598</v>
+      </c>
+      <c r="M59" t="n">
+        <v>6448</v>
+      </c>
+      <c r="N59" t="n">
+        <v>8170</v>
+      </c>
+      <c r="O59" t="n">
+        <v>9077</v>
+      </c>
+      <c r="P59" t="n">
+        <v>9210</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>9498</v>
+      </c>
+      <c r="R59" t="n">
+        <v>9196</v>
+      </c>
+      <c r="S59" t="n">
+        <v>9624</v>
+      </c>
+      <c r="T59" t="n">
+        <v>9226</v>
+      </c>
+      <c r="U59" t="n">
+        <v>8478</v>
+      </c>
+      <c r="V59" t="n">
+        <v>8154</v>
+      </c>
+      <c r="W59" t="n">
+        <v>7413</v>
+      </c>
       <c r="Y59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6240,14 +6544,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA59" t="n">
+        <v>8492</v>
+      </c>
       <c r="AB59" t="n">
-        <v>10164</v>
+        <v>10159</v>
       </c>
       <c r="AC59" t="n">
-        <v>14585</v>
+        <v>14562</v>
       </c>
       <c r="AD59" t="n">
-        <v>18508</v>
+        <v>18549</v>
       </c>
     </row>
     <row r="60">
@@ -6424,6 +6731,36 @@
           <t>Prague International Marathon</t>
         </is>
       </c>
+      <c r="E65" t="n">
+        <v>2776</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2641</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2808</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2594</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3433</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3402</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2991</v>
+      </c>
+      <c r="L65" t="n">
+        <v>3190</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3691</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3980</v>
+      </c>
       <c r="O65" t="n">
         <v>4860</v>
       </c>
@@ -6433,9 +6770,24 @@
       <c r="Q65" t="n">
         <v>5619</v>
       </c>
+      <c r="R65" t="n">
+        <v>5768</v>
+      </c>
+      <c r="S65" t="n">
+        <v>6038</v>
+      </c>
       <c r="T65" t="n">
         <v>5874</v>
       </c>
+      <c r="U65" t="n">
+        <v>5778</v>
+      </c>
+      <c r="V65" t="n">
+        <v>6499</v>
+      </c>
+      <c r="W65" t="n">
+        <v>6951</v>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
           <t>-</t>
@@ -6446,14 +6798,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA65" t="n">
+        <v>4603</v>
+      </c>
       <c r="AB65" t="n">
-        <v>5467</v>
+        <v>5381</v>
       </c>
       <c r="AC65" t="n">
-        <v>6018</v>
+        <v>6023</v>
       </c>
       <c r="AD65" t="n">
-        <v>7636</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="66">
@@ -7264,17 +7619,62 @@
           <t>Marine Corps Marathon</t>
         </is>
       </c>
+      <c r="E85" t="n">
+        <v>17016</v>
+      </c>
+      <c r="F85" t="n">
+        <v>13818</v>
+      </c>
+      <c r="G85" t="n">
+        <v>14044</v>
+      </c>
+      <c r="H85" t="n">
+        <v>15531</v>
+      </c>
+      <c r="I85" t="n">
+        <v>16428</v>
+      </c>
+      <c r="J85" t="n">
+        <v>19165</v>
+      </c>
+      <c r="K85" t="n">
+        <v>20905</v>
+      </c>
+      <c r="L85" t="n">
+        <v>20626</v>
+      </c>
+      <c r="M85" t="n">
+        <v>18237</v>
+      </c>
+      <c r="N85" t="n">
+        <v>21405</v>
+      </c>
+      <c r="O85" t="n">
+        <v>21947</v>
+      </c>
+      <c r="P85" t="n">
+        <v>21024</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>23518</v>
+      </c>
+      <c r="R85" t="n">
+        <v>23386</v>
+      </c>
+      <c r="S85" t="n">
+        <v>19688</v>
+      </c>
       <c r="T85" t="n">
-        <v>23197</v>
+        <v>23183</v>
       </c>
       <c r="U85" t="n">
         <v>19678</v>
       </c>
       <c r="V85" t="n">
-        <v>20122</v>
+        <v>20040</v>
       </c>
       <c r="W85" t="n">
-        <v>20699</v>
+        <v>20614</v>
       </c>
       <c r="X85" t="n">
         <v>26502</v>
@@ -7290,16 +7690,16 @@
         </is>
       </c>
       <c r="AA85" t="n">
-        <v>11185</v>
+        <v>11256</v>
       </c>
       <c r="AB85" t="n">
-        <v>13819</v>
+        <v>13670</v>
       </c>
       <c r="AC85" t="n">
-        <v>16167</v>
+        <v>15632</v>
       </c>
       <c r="AD85" t="n">
-        <v>30085</v>
+        <v>28990</v>
       </c>
     </row>
     <row r="86">
@@ -7383,6 +7783,54 @@
           <t>TCS Amsterdam Marathon</t>
         </is>
       </c>
+      <c r="H88" t="n">
+        <v>3537</v>
+      </c>
+      <c r="I88" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5335</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5851</v>
+      </c>
+      <c r="L88" t="n">
+        <v>6530</v>
+      </c>
+      <c r="M88" t="n">
+        <v>5983</v>
+      </c>
+      <c r="N88" t="n">
+        <v>6909</v>
+      </c>
+      <c r="O88" t="n">
+        <v>7879</v>
+      </c>
+      <c r="P88" t="n">
+        <v>9634</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>10145</v>
+      </c>
+      <c r="R88" t="n">
+        <v>11309</v>
+      </c>
+      <c r="S88" t="n">
+        <v>12217</v>
+      </c>
+      <c r="T88" t="n">
+        <v>12367</v>
+      </c>
+      <c r="U88" t="n">
+        <v>12194</v>
+      </c>
+      <c r="V88" t="n">
+        <v>11435</v>
+      </c>
+      <c r="W88" t="n">
+        <v>12113</v>
+      </c>
       <c r="X88" t="n">
         <v>13469</v>
       </c>
@@ -7391,14 +7839,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z88" t="n">
+        <v>6640</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>12733</v>
+      </c>
       <c r="AB88" t="n">
-        <v>16069</v>
+        <v>16160</v>
       </c>
       <c r="AC88" t="n">
-        <v>16815</v>
+        <v>16931</v>
       </c>
       <c r="AD88" t="n">
-        <v>23328</v>
+        <v>23326</v>
       </c>
     </row>
     <row r="89">
@@ -7482,6 +7936,54 @@
           <t xml:space="preserve">	Irish Life Dublin Marathon</t>
         </is>
       </c>
+      <c r="E91" t="n">
+        <v>7169</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6150</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6491</v>
+      </c>
+      <c r="H91" t="n">
+        <v>6258</v>
+      </c>
+      <c r="I91" t="n">
+        <v>8511</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7888</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8171</v>
+      </c>
+      <c r="L91" t="n">
+        <v>8442</v>
+      </c>
+      <c r="M91" t="n">
+        <v>9362</v>
+      </c>
+      <c r="N91" t="n">
+        <v>10459</v>
+      </c>
+      <c r="O91" t="n">
+        <v>10747</v>
+      </c>
+      <c r="P91" t="n">
+        <v>11670</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>12208</v>
+      </c>
+      <c r="R91" t="n">
+        <v>12347</v>
+      </c>
+      <c r="S91" t="n">
+        <v>12288</v>
+      </c>
+      <c r="T91" t="n">
+        <v>12924</v>
+      </c>
       <c r="U91" t="n">
         <v>16312</v>
       </c>
@@ -8180,6 +8682,39 @@
           <t>Valencia Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
+      <c r="M109" t="n">
+        <v>2761</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2744</v>
+      </c>
+      <c r="O109" t="n">
+        <v>2968</v>
+      </c>
+      <c r="P109" t="n">
+        <v>5676</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>7777</v>
+      </c>
+      <c r="R109" t="n">
+        <v>9645</v>
+      </c>
+      <c r="S109" t="n">
+        <v>11318</v>
+      </c>
+      <c r="T109" t="n">
+        <v>14066</v>
+      </c>
+      <c r="U109" t="n">
+        <v>15828</v>
+      </c>
+      <c r="V109" t="n">
+        <v>16170</v>
+      </c>
+      <c r="W109" t="n">
+        <v>19495</v>
+      </c>
       <c r="X109" t="n">
         <v>21230</v>
       </c>
@@ -8188,14 +8723,17 @@
           <t>Elite</t>
         </is>
       </c>
+      <c r="Z109" t="n">
+        <v>12662</v>
+      </c>
       <c r="AA109" t="n">
-        <v>28176</v>
+        <v>21563</v>
       </c>
       <c r="AB109" t="n">
-        <v>25905</v>
+        <v>25713</v>
       </c>
       <c r="AC109" t="n">
-        <v>28176</v>
+        <v>28247</v>
       </c>
       <c r="AD109" t="n">
         <v>30772</v>
@@ -8550,6 +9088,9 @@
           <t>Broad Street Run</t>
         </is>
       </c>
+      <c r="U118" t="n">
+        <v>34237</v>
+      </c>
       <c r="W118" t="n">
         <v>36222</v>
       </c>
@@ -8600,8 +9141,62 @@
           <t>Flying Pig Marathon</t>
         </is>
       </c>
+      <c r="E119" t="n">
+        <v>3632</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4131</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4097</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3893</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3947</v>
+      </c>
+      <c r="J119" t="n">
+        <v>3757</v>
+      </c>
+      <c r="K119" t="n">
+        <v>4523</v>
+      </c>
+      <c r="L119" t="n">
+        <v>3973</v>
+      </c>
+      <c r="M119" t="n">
+        <v>4735</v>
+      </c>
+      <c r="N119" t="n">
+        <v>4071</v>
+      </c>
+      <c r="O119" t="n">
+        <v>4113</v>
+      </c>
+      <c r="P119" t="n">
+        <v>4299</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>4094</v>
+      </c>
+      <c r="R119" t="n">
+        <v>4135</v>
+      </c>
+      <c r="S119" t="n">
+        <v>3978</v>
+      </c>
+      <c r="T119" t="n">
+        <v>3820</v>
+      </c>
+      <c r="U119" t="n">
+        <v>3795</v>
+      </c>
+      <c r="V119" t="n">
+        <v>3356</v>
+      </c>
       <c r="W119" t="n">
-        <v>36726</v>
+        <v>5829</v>
       </c>
       <c r="X119" t="n">
         <v>31325</v>
@@ -8611,17 +9206,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z119" t="n">
+        <v>1689</v>
+      </c>
       <c r="AA119" t="n">
-        <v>19860</v>
+        <v>2578</v>
       </c>
       <c r="AB119" t="n">
-        <v>29946</v>
+        <v>4489</v>
       </c>
       <c r="AC119" t="n">
-        <v>25027</v>
+        <v>4057</v>
       </c>
       <c r="AD119" t="n">
-        <v>30908</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="120">
@@ -8645,6 +9243,9 @@
           <t>Lilac Bloomsday Run</t>
         </is>
       </c>
+      <c r="U120" t="n">
+        <v>42206</v>
+      </c>
       <c r="W120" t="n">
         <v>38068</v>
       </c>
@@ -8690,6 +9291,9 @@
           <t>Credit Union Cherry Blossom</t>
         </is>
       </c>
+      <c r="U121" t="n">
+        <v>16009</v>
+      </c>
       <c r="W121" t="n">
         <v>19188</v>
       </c>
@@ -8740,8 +9344,62 @@
           <t>San Francisco Marathon</t>
         </is>
       </c>
+      <c r="E122" t="n">
+        <v>2345</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2249</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1920</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1891</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2665</v>
+      </c>
+      <c r="J122" t="n">
+        <v>4873</v>
+      </c>
+      <c r="K122" t="n">
+        <v>4021</v>
+      </c>
+      <c r="L122" t="n">
+        <v>4287</v>
+      </c>
+      <c r="M122" t="n">
+        <v>4450</v>
+      </c>
+      <c r="N122" t="n">
+        <v>5101</v>
+      </c>
+      <c r="O122" t="n">
+        <v>5992</v>
+      </c>
+      <c r="P122" t="n">
+        <v>6040</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>6494</v>
+      </c>
+      <c r="R122" t="n">
+        <v>5827</v>
+      </c>
+      <c r="S122" t="n">
+        <v>6624</v>
+      </c>
+      <c r="T122" t="n">
+        <v>6071</v>
+      </c>
+      <c r="U122" t="n">
+        <v>6335</v>
+      </c>
+      <c r="V122" t="n">
+        <v>6586</v>
+      </c>
       <c r="W122" t="n">
-        <v>17621</v>
+        <v>5264</v>
       </c>
       <c r="X122" t="n">
         <v>17587</v>
@@ -8751,17 +9409,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z122" t="n">
+        <v>3184</v>
+      </c>
       <c r="AA122" t="n">
-        <v>13362</v>
+        <v>4091</v>
       </c>
       <c r="AB122" t="n">
-        <v>20918</v>
+        <v>4883</v>
       </c>
       <c r="AC122" t="n">
-        <v>22491</v>
+        <v>5868</v>
       </c>
       <c r="AD122" t="n">
-        <v>24698</v>
+        <v>6536</v>
       </c>
     </row>
     <row r="123">
@@ -8835,6 +9496,9 @@
           <t>Dick's Pittsburgh Marathon</t>
         </is>
       </c>
+      <c r="U124" t="n">
+        <v>14132</v>
+      </c>
       <c r="W124" t="n">
         <v>21135</v>
       </c>
@@ -8880,8 +9544,59 @@
           <t>Medtronic Twin Cities Marathon</t>
         </is>
       </c>
+      <c r="F125" t="n">
+        <v>6360</v>
+      </c>
+      <c r="G125" t="n">
+        <v>6657</v>
+      </c>
+      <c r="H125" t="n">
+        <v>7089</v>
+      </c>
+      <c r="I125" t="n">
+        <v>7302</v>
+      </c>
+      <c r="J125" t="n">
+        <v>7752</v>
+      </c>
+      <c r="K125" t="n">
+        <v>8196</v>
+      </c>
+      <c r="L125" t="n">
+        <v>7154</v>
+      </c>
+      <c r="M125" t="n">
+        <v>7978</v>
+      </c>
+      <c r="N125" t="n">
+        <v>8473</v>
+      </c>
+      <c r="O125" t="n">
+        <v>8197</v>
+      </c>
+      <c r="P125" t="n">
+        <v>8534</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>8783</v>
+      </c>
+      <c r="R125" t="n">
+        <v>8855</v>
+      </c>
+      <c r="S125" t="n">
+        <v>8853</v>
+      </c>
+      <c r="T125" t="n">
+        <v>8546</v>
+      </c>
+      <c r="U125" t="n">
+        <v>8561</v>
+      </c>
+      <c r="V125" t="n">
+        <v>7490</v>
+      </c>
       <c r="W125" t="n">
-        <v>22923</v>
+        <v>7162</v>
       </c>
       <c r="X125" t="n">
         <v>17796</v>
@@ -8891,14 +9606,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z125" t="n">
+        <v>3204</v>
+      </c>
       <c r="AA125" t="n">
-        <v>18466</v>
+        <v>6495</v>
       </c>
       <c r="AC125" t="n">
-        <v>20523</v>
+        <v>6787</v>
       </c>
       <c r="AD125" t="n">
-        <v>21658</v>
+        <v>7006</v>
       </c>
     </row>
     <row r="126">
@@ -8922,23 +9640,77 @@
           <t>Cowtown Marathon</t>
         </is>
       </c>
+      <c r="E126" t="n">
+        <v>888</v>
+      </c>
+      <c r="F126" t="n">
+        <v>614</v>
+      </c>
+      <c r="G126" t="n">
+        <v>670</v>
+      </c>
+      <c r="H126" t="n">
+        <v>662</v>
+      </c>
+      <c r="I126" t="n">
+        <v>780</v>
+      </c>
+      <c r="J126" t="n">
+        <v>637</v>
+      </c>
+      <c r="K126" t="n">
+        <v>566</v>
+      </c>
+      <c r="L126" t="n">
+        <v>599</v>
+      </c>
+      <c r="M126" t="n">
+        <v>640</v>
+      </c>
+      <c r="N126" t="n">
+        <v>905</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1193</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1244</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>1424</v>
+      </c>
+      <c r="R126" t="n">
+        <v>1486</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1263</v>
+      </c>
+      <c r="V126" t="n">
+        <v>1242</v>
+      </c>
       <c r="W126" t="n">
-        <v>14874</v>
+        <v>1179</v>
       </c>
       <c r="X126" t="n">
         <v>18852</v>
       </c>
       <c r="AA126" t="n">
-        <v>9830</v>
+        <v>939</v>
       </c>
       <c r="AB126" t="n">
-        <v>16661</v>
+        <v>1262</v>
       </c>
       <c r="AC126" t="n">
-        <v>19119</v>
+        <v>1441</v>
       </c>
       <c r="AD126" t="n">
-        <v>20995</v>
+        <v>1753</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2415</v>
       </c>
     </row>
     <row r="127">
@@ -9007,6 +9779,9 @@
           <t>Bay to Breakers</t>
         </is>
       </c>
+      <c r="U128" t="n">
+        <v>28009</v>
+      </c>
       <c r="W128" t="n">
         <v>24572</v>
       </c>
@@ -9102,23 +9877,80 @@
           <t>Austin Marathon</t>
         </is>
       </c>
+      <c r="E130" t="n">
+        <v>4054</v>
+      </c>
+      <c r="F130" t="n">
+        <v>4189</v>
+      </c>
+      <c r="G130" t="n">
+        <v>4424</v>
+      </c>
+      <c r="H130" t="n">
+        <v>5360</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5238</v>
+      </c>
+      <c r="J130" t="n">
+        <v>4967</v>
+      </c>
+      <c r="K130" t="n">
+        <v>4788</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4549</v>
+      </c>
+      <c r="M130" t="n">
+        <v>4646</v>
+      </c>
+      <c r="N130" t="n">
+        <v>4141</v>
+      </c>
+      <c r="O130" t="n">
+        <v>4048</v>
+      </c>
+      <c r="P130" t="n">
+        <v>5027</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>3898</v>
+      </c>
+      <c r="R130" t="n">
+        <v>3548</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3628</v>
+      </c>
+      <c r="T130" t="n">
+        <v>3137</v>
+      </c>
+      <c r="U130" t="n">
+        <v>3225</v>
+      </c>
+      <c r="V130" t="n">
+        <v>2664</v>
+      </c>
       <c r="W130" t="n">
-        <v>11669</v>
+        <v>2549</v>
       </c>
       <c r="X130" t="n">
         <v>13914</v>
       </c>
       <c r="AA130" t="n">
-        <v>10154</v>
+        <v>2766</v>
       </c>
       <c r="AB130" t="n">
-        <v>13379</v>
+        <v>3157</v>
       </c>
       <c r="AC130" t="n">
-        <v>16234</v>
+        <v>4022</v>
       </c>
       <c r="AD130" t="n">
-        <v>19206</v>
+        <v>5728</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>7250</v>
       </c>
     </row>
     <row r="131">
@@ -9142,6 +9974,9 @@
           <t>Miami Marathon</t>
         </is>
       </c>
+      <c r="U131" t="n">
+        <v>14205</v>
+      </c>
       <c r="W131" t="n">
         <v>18906</v>
       </c>
@@ -9182,6 +10017,9 @@
           <t>Army Ten Miler</t>
         </is>
       </c>
+      <c r="U132" t="n">
+        <v>24008</v>
+      </c>
       <c r="W132" t="n">
         <v>24808</v>
       </c>
@@ -9227,8 +10065,62 @@
           <t>Grandma's Marathon</t>
         </is>
       </c>
+      <c r="E133" t="n">
+        <v>4794</v>
+      </c>
+      <c r="F133" t="n">
+        <v>4016</v>
+      </c>
+      <c r="G133" t="n">
+        <v>6836</v>
+      </c>
+      <c r="H133" t="n">
+        <v>6870</v>
+      </c>
+      <c r="I133" t="n">
+        <v>6755</v>
+      </c>
+      <c r="J133" t="n">
+        <v>6885</v>
+      </c>
+      <c r="K133" t="n">
+        <v>6912</v>
+      </c>
+      <c r="L133" t="n">
+        <v>6967</v>
+      </c>
+      <c r="M133" t="n">
+        <v>6876</v>
+      </c>
+      <c r="N133" t="n">
+        <v>5998</v>
+      </c>
+      <c r="O133" t="n">
+        <v>5611</v>
+      </c>
+      <c r="P133" t="n">
+        <v>6337</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>5788</v>
+      </c>
+      <c r="R133" t="n">
+        <v>5620</v>
+      </c>
+      <c r="S133" t="n">
+        <v>6209</v>
+      </c>
+      <c r="T133" t="n">
+        <v>6077</v>
+      </c>
+      <c r="U133" t="n">
+        <v>7518</v>
+      </c>
+      <c r="V133" t="n">
+        <v>6444</v>
+      </c>
       <c r="W133" t="n">
-        <v>15483</v>
+        <v>6098</v>
       </c>
       <c r="X133" t="n">
         <v>18957</v>
@@ -9238,14 +10130,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z133" t="n">
+        <v>2775</v>
+      </c>
       <c r="AA133" t="n">
-        <v>7006</v>
+        <v>5952</v>
       </c>
       <c r="AB133" t="n">
-        <v>16358</v>
+        <v>6682</v>
       </c>
       <c r="AC133" t="n">
-        <v>17556</v>
+        <v>7533</v>
       </c>
       <c r="AD133" t="n">
         <v>18354</v>
@@ -9272,8 +10167,62 @@
           <t>Detroit Marathon</t>
         </is>
       </c>
+      <c r="E134" t="n">
+        <v>2157</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2449</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2335</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2775</v>
+      </c>
+      <c r="I134" t="n">
+        <v>3514</v>
+      </c>
+      <c r="J134" t="n">
+        <v>3553</v>
+      </c>
+      <c r="K134" t="n">
+        <v>3880</v>
+      </c>
+      <c r="L134" t="n">
+        <v>3745</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3515</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3780</v>
+      </c>
+      <c r="O134" t="n">
+        <v>3227</v>
+      </c>
+      <c r="P134" t="n">
+        <v>3384</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>3708</v>
+      </c>
+      <c r="R134" t="n">
+        <v>4460</v>
+      </c>
+      <c r="S134" t="n">
+        <v>3993</v>
+      </c>
+      <c r="T134" t="n">
+        <v>3803</v>
+      </c>
+      <c r="U134" t="n">
+        <v>3217</v>
+      </c>
+      <c r="V134" t="n">
+        <v>3137</v>
+      </c>
       <c r="W134" t="n">
-        <v>17568</v>
+        <v>3067</v>
       </c>
       <c r="X134" t="n">
         <v>18806</v>
@@ -9283,17 +10232,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z134" t="n">
+        <v>1918</v>
+      </c>
       <c r="AA134" t="n">
-        <v>12659</v>
+        <v>2269</v>
       </c>
       <c r="AB134" t="n">
-        <v>16554</v>
+        <v>3078</v>
       </c>
       <c r="AC134" t="n">
-        <v>16526</v>
+        <v>3580</v>
       </c>
       <c r="AD134" t="n">
-        <v>17918</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="135">
@@ -9317,6 +10269,9 @@
           <t>Gasparilla Distance Classic</t>
         </is>
       </c>
+      <c r="U135" t="n">
+        <v>11944</v>
+      </c>
       <c r="W135" t="n">
         <v>26682</v>
       </c>
@@ -9447,8 +10402,62 @@
           <t>Richmond Marathon</t>
         </is>
       </c>
+      <c r="E138" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1901</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2560</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2783</v>
+      </c>
+      <c r="I138" t="n">
+        <v>3225</v>
+      </c>
+      <c r="J138" t="n">
+        <v>3537</v>
+      </c>
+      <c r="K138" t="n">
+        <v>2917</v>
+      </c>
+      <c r="L138" t="n">
+        <v>3686</v>
+      </c>
+      <c r="M138" t="n">
+        <v>3030</v>
+      </c>
+      <c r="N138" t="n">
+        <v>3821</v>
+      </c>
+      <c r="O138" t="n">
+        <v>3779</v>
+      </c>
+      <c r="P138" t="n">
+        <v>3800</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>4740</v>
+      </c>
+      <c r="R138" t="n">
+        <v>4842</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5117</v>
+      </c>
+      <c r="T138" t="n">
+        <v>4523</v>
+      </c>
+      <c r="U138" t="n">
+        <v>4060</v>
+      </c>
+      <c r="V138" t="n">
+        <v>4250</v>
+      </c>
       <c r="W138" t="n">
-        <v>14545</v>
+        <v>4000</v>
       </c>
       <c r="X138" t="n">
         <v>15382</v>
@@ -9458,17 +10467,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z138" t="n">
+        <v>3520</v>
+      </c>
       <c r="AA138" t="n">
-        <v>12358</v>
+        <v>3296</v>
       </c>
       <c r="AB138" t="n">
-        <v>14560</v>
+        <v>4079</v>
       </c>
       <c r="AC138" t="n">
-        <v>17495</v>
+        <v>5019</v>
       </c>
       <c r="AD138" t="n">
-        <v>17220</v>
+        <v>4939</v>
       </c>
     </row>
     <row r="139">
@@ -9632,6 +10644,9 @@
           <t>Gate River Run</t>
         </is>
       </c>
+      <c r="U142" t="n">
+        <v>14435</v>
+      </c>
       <c r="W142" t="n">
         <v>14113</v>
       </c>
@@ -9721,23 +10736,80 @@
           <t>Shamrock Marathon</t>
         </is>
       </c>
+      <c r="E144" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1553</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1167</v>
+      </c>
+      <c r="I144" t="n">
+        <v>1806</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1538</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1748</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1908</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2275</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2578</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2653</v>
+      </c>
+      <c r="P144" t="n">
+        <v>3162</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>3312</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2995</v>
+      </c>
+      <c r="S144" t="n">
+        <v>2780</v>
+      </c>
+      <c r="T144" t="n">
+        <v>2185</v>
+      </c>
+      <c r="U144" t="n">
+        <v>1841</v>
+      </c>
+      <c r="V144" t="n">
+        <v>1376</v>
+      </c>
       <c r="W144" t="n">
-        <v>18116</v>
+        <v>1435</v>
       </c>
       <c r="X144" t="n">
         <v>19965</v>
       </c>
+      <c r="Z144" t="n">
+        <v>339</v>
+      </c>
       <c r="AA144" t="n">
-        <v>17702</v>
+        <v>1255</v>
       </c>
       <c r="AB144" t="n">
-        <v>16305</v>
+        <v>1689</v>
       </c>
       <c r="AC144" t="n">
-        <v>13868</v>
+        <v>2005</v>
       </c>
       <c r="AD144" t="n">
-        <v>14301</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="145">
@@ -9806,8 +10878,62 @@
           <t>Columbus Marathon</t>
         </is>
       </c>
+      <c r="E146" t="n">
+        <v>3428</v>
+      </c>
+      <c r="F146" t="n">
+        <v>3061</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3343</v>
+      </c>
+      <c r="H146" t="n">
+        <v>3656</v>
+      </c>
+      <c r="I146" t="n">
+        <v>4311</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3771</v>
+      </c>
+      <c r="K146" t="n">
+        <v>3764</v>
+      </c>
+      <c r="L146" t="n">
+        <v>3992</v>
+      </c>
+      <c r="M146" t="n">
+        <v>3871</v>
+      </c>
+      <c r="N146" t="n">
+        <v>4123</v>
+      </c>
+      <c r="O146" t="n">
+        <v>4146</v>
+      </c>
+      <c r="P146" t="n">
+        <v>4746</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>5482</v>
+      </c>
+      <c r="R146" t="n">
+        <v>5523</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5461</v>
+      </c>
+      <c r="T146" t="n">
+        <v>4443</v>
+      </c>
+      <c r="U146" t="n">
+        <v>3850</v>
+      </c>
+      <c r="V146" t="n">
+        <v>3202</v>
+      </c>
       <c r="W146" t="n">
-        <v>12335</v>
+        <v>3214</v>
       </c>
       <c r="X146" t="n">
         <v>12530</v>
@@ -9817,17 +10943,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z146" t="n">
+        <v>1738</v>
+      </c>
       <c r="AA146" t="n">
-        <v>9124</v>
+        <v>2387</v>
       </c>
       <c r="AB146" t="n">
-        <v>10863</v>
+        <v>3006</v>
       </c>
       <c r="AC146" t="n">
-        <v>11681</v>
+        <v>3522</v>
       </c>
       <c r="AD146" t="n">
-        <v>13101</v>
+        <v>4122</v>
       </c>
     </row>
     <row r="147">
@@ -10171,6 +11300,63 @@
           <t>California International Marathon</t>
         </is>
       </c>
+      <c r="E154" t="n">
+        <v>2717</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2781</v>
+      </c>
+      <c r="G154" t="n">
+        <v>2619</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2943</v>
+      </c>
+      <c r="I154" t="n">
+        <v>2969</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3248</v>
+      </c>
+      <c r="K154" t="n">
+        <v>3820</v>
+      </c>
+      <c r="L154" t="n">
+        <v>4740</v>
+      </c>
+      <c r="M154" t="n">
+        <v>5193</v>
+      </c>
+      <c r="N154" t="n">
+        <v>5843</v>
+      </c>
+      <c r="O154" t="n">
+        <v>5876</v>
+      </c>
+      <c r="P154" t="n">
+        <v>5755</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>6208</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6238</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5779</v>
+      </c>
+      <c r="T154" t="n">
+        <v>5628</v>
+      </c>
+      <c r="U154" t="n">
+        <v>6171</v>
+      </c>
+      <c r="V154" t="n">
+        <v>7044</v>
+      </c>
+      <c r="W154" t="n">
+        <v>7831</v>
+      </c>
       <c r="X154" t="n">
         <v>11840</v>
       </c>
@@ -10179,17 +11365,20 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z154" t="n">
+        <v>7595</v>
+      </c>
       <c r="AA154" t="n">
-        <v>8372</v>
+        <v>8020</v>
       </c>
       <c r="AB154" t="n">
         <v>10165</v>
       </c>
       <c r="AC154" t="n">
-        <v>9125</v>
+        <v>8356</v>
       </c>
       <c r="AD154" t="n">
-        <v>9083</v>
+        <v>8181</v>
       </c>
     </row>
     <row r="155">
@@ -10327,13 +11516,73 @@
           <t>Haspa Marathon Hamburg</t>
         </is>
       </c>
+      <c r="G158" t="n">
+        <v>17028</v>
+      </c>
+      <c r="I158" t="n">
+        <v>15304</v>
+      </c>
+      <c r="J158" t="n">
+        <v>17535</v>
+      </c>
+      <c r="K158" t="n">
+        <v>31141</v>
+      </c>
+      <c r="L158" t="n">
+        <v>16486</v>
+      </c>
+      <c r="M158" t="n">
+        <v>15769</v>
+      </c>
+      <c r="N158" t="n">
+        <v>13942</v>
+      </c>
+      <c r="O158" t="n">
+        <v>14171</v>
+      </c>
+      <c r="P158" t="n">
+        <v>11188</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>10318</v>
+      </c>
+      <c r="R158" t="n">
+        <v>11450</v>
+      </c>
+      <c r="S158" t="n">
+        <v>12869</v>
+      </c>
+      <c r="T158" t="n">
+        <v>14767</v>
+      </c>
+      <c r="U158" t="n">
+        <v>12079</v>
+      </c>
+      <c r="V158" t="n">
+        <v>11933</v>
+      </c>
+      <c r="W158" t="n">
+        <v>10014</v>
+      </c>
       <c r="Y158" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="Z158" t="n">
+        <v>1977</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>6620</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>8632</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>11233</v>
+      </c>
       <c r="AD158" t="n">
-        <v>12923</v>
+        <v>11671</v>
       </c>
     </row>
     <row r="159">
@@ -10357,10 +11606,73 @@
           <t>Mainova Frankfurt Marathon</t>
         </is>
       </c>
+      <c r="G159" t="n">
+        <v>7248</v>
+      </c>
+      <c r="H159" t="n">
+        <v>7098</v>
+      </c>
+      <c r="I159" t="n">
+        <v>8284</v>
+      </c>
+      <c r="J159" t="n">
+        <v>8860</v>
+      </c>
+      <c r="K159" t="n">
+        <v>8904</v>
+      </c>
+      <c r="L159" t="n">
+        <v>9161</v>
+      </c>
+      <c r="M159" t="n">
+        <v>9462</v>
+      </c>
+      <c r="N159" t="n">
+        <v>9499</v>
+      </c>
+      <c r="O159" t="n">
+        <v>9554</v>
+      </c>
+      <c r="P159" t="n">
+        <v>12426</v>
+      </c>
+      <c r="R159" t="n">
+        <v>10999</v>
+      </c>
+      <c r="S159" t="n">
+        <v>11099</v>
+      </c>
+      <c r="T159" t="n">
+        <v>11165</v>
+      </c>
+      <c r="U159" t="n">
+        <v>11860</v>
+      </c>
+      <c r="V159" t="n">
+        <v>11168</v>
+      </c>
+      <c r="W159" t="n">
+        <v>10627</v>
+      </c>
+      <c r="X159" t="n">
+        <v>10552</v>
+      </c>
       <c r="Y159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA159" t="n">
+        <v>7941</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>9666</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>10253</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>12319</v>
       </c>
     </row>
     <row r="160">
@@ -10384,6 +11696,63 @@
           <t>Stockholm Marathon</t>
         </is>
       </c>
+      <c r="E160" t="n">
+        <v>9924</v>
+      </c>
+      <c r="F160" t="n">
+        <v>10170</v>
+      </c>
+      <c r="G160" t="n">
+        <v>10710</v>
+      </c>
+      <c r="H160" t="n">
+        <v>12140</v>
+      </c>
+      <c r="I160" t="n">
+        <v>12696</v>
+      </c>
+      <c r="J160" t="n">
+        <v>12700</v>
+      </c>
+      <c r="K160" t="n">
+        <v>12938</v>
+      </c>
+      <c r="L160" t="n">
+        <v>12353</v>
+      </c>
+      <c r="M160" t="n">
+        <v>13543</v>
+      </c>
+      <c r="N160" t="n">
+        <v>13721</v>
+      </c>
+      <c r="O160" t="n">
+        <v>14683</v>
+      </c>
+      <c r="P160" t="n">
+        <v>15465</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>14670</v>
+      </c>
+      <c r="R160" t="n">
+        <v>15651</v>
+      </c>
+      <c r="S160" t="n">
+        <v>16069</v>
+      </c>
+      <c r="T160" t="n">
+        <v>14809</v>
+      </c>
+      <c r="U160" t="n">
+        <v>12855</v>
+      </c>
+      <c r="V160" t="n">
+        <v>12570</v>
+      </c>
+      <c r="W160" t="n">
+        <v>14360</v>
+      </c>
       <c r="X160" t="n">
         <v>12349</v>
       </c>
@@ -10395,6 +11764,15 @@
       <c r="Z160" t="n">
         <v>6958</v>
       </c>
+      <c r="AA160" t="n">
+        <v>9076</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>12728</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>17044</v>
+      </c>
       <c r="AD160" t="n">
         <v>18839</v>
       </c>
@@ -10420,19 +11798,67 @@
           <t>Milano Marathon</t>
         </is>
       </c>
+      <c r="I161" t="n">
+        <v>4162</v>
+      </c>
+      <c r="J161" t="n">
+        <v>4178</v>
+      </c>
+      <c r="K161" t="n">
+        <v>2153</v>
+      </c>
+      <c r="L161" t="n">
+        <v>4470</v>
+      </c>
+      <c r="M161" t="n">
+        <v>4098</v>
+      </c>
+      <c r="O161" t="n">
+        <v>3435</v>
+      </c>
+      <c r="P161" t="n">
+        <v>3400</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>3975</v>
+      </c>
+      <c r="R161" t="n">
+        <v>3514</v>
+      </c>
+      <c r="S161" t="n">
+        <v>3556</v>
+      </c>
+      <c r="T161" t="n">
+        <v>4002</v>
+      </c>
+      <c r="U161" t="n">
+        <v>3719</v>
+      </c>
+      <c r="V161" t="n">
+        <v>5303</v>
+      </c>
+      <c r="W161" t="n">
+        <v>5556</v>
+      </c>
       <c r="Y161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z161" t="n">
+        <v>86</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>5196</v>
       </c>
       <c r="AB161" t="n">
         <v>5123</v>
       </c>
       <c r="AC161" t="n">
-        <v>8545</v>
+        <v>6920</v>
       </c>
       <c r="AD161" t="n">
-        <v>10250</v>
+        <v>8324</v>
       </c>
     </row>
     <row r="162">
@@ -10456,15 +11882,52 @@
           <t>Brighton Marathon</t>
         </is>
       </c>
+      <c r="O162" t="n">
+        <v>7411</v>
+      </c>
+      <c r="P162" t="n">
+        <v>7807</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>8937</v>
+      </c>
+      <c r="R162" t="n">
+        <v>9115</v>
+      </c>
+      <c r="S162" t="n">
+        <v>8710</v>
+      </c>
+      <c r="T162" t="n">
+        <v>9227</v>
+      </c>
+      <c r="U162" t="n">
+        <v>10721</v>
+      </c>
+      <c r="V162" t="n">
+        <v>12039</v>
+      </c>
+      <c r="W162" t="n">
+        <v>11385</v>
+      </c>
       <c r="Y162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z162" t="n">
+        <v>4106</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>8290</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>8476</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>11245</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>12562</v>
       </c>
     </row>
     <row r="163">
@@ -10577,6 +12040,54 @@
           <t>Gold Coast Marathon</t>
         </is>
       </c>
+      <c r="H166" t="n">
+        <v>1876</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1855</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1550</v>
+      </c>
+      <c r="K166" t="n">
+        <v>2237</v>
+      </c>
+      <c r="L166" t="n">
+        <v>2628</v>
+      </c>
+      <c r="M166" t="n">
+        <v>3657</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3716</v>
+      </c>
+      <c r="O166" t="n">
+        <v>4531</v>
+      </c>
+      <c r="P166" t="n">
+        <v>4554</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>5118</v>
+      </c>
+      <c r="R166" t="n">
+        <v>4829</v>
+      </c>
+      <c r="S166" t="n">
+        <v>4934</v>
+      </c>
+      <c r="T166" t="n">
+        <v>5282</v>
+      </c>
+      <c r="U166" t="n">
+        <v>5448</v>
+      </c>
+      <c r="V166" t="n">
+        <v>5209</v>
+      </c>
+      <c r="W166" t="n">
+        <v>5901</v>
+      </c>
       <c r="Y166" t="inlineStr">
         <is>
           <t>-</t>
@@ -10586,6 +12097,18 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA166" t="n">
+        <v>4057</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>5957</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>8656</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>12700</v>
       </c>
     </row>
     <row r="167">
@@ -10777,6 +12300,42 @@
           <t>Istanbul Marathon</t>
         </is>
       </c>
+      <c r="M170" t="n">
+        <v>667</v>
+      </c>
+      <c r="N170" t="n">
+        <v>918</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1273</v>
+      </c>
+      <c r="P170" t="n">
+        <v>1506</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>2331</v>
+      </c>
+      <c r="R170" t="n">
+        <v>2802</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3875</v>
+      </c>
+      <c r="T170" t="n">
+        <v>2771</v>
+      </c>
+      <c r="U170" t="n">
+        <v>1379</v>
+      </c>
+      <c r="V170" t="n">
+        <v>1703</v>
+      </c>
+      <c r="W170" t="n">
+        <v>2863</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2997</v>
+      </c>
       <c r="AA170" t="n">
         <v>3039</v>
       </c>
@@ -10811,16 +12370,73 @@
           <t>Athens Marathon</t>
         </is>
       </c>
+      <c r="G171" t="n">
+        <v>1779</v>
+      </c>
+      <c r="H171" t="n">
+        <v>2676</v>
+      </c>
+      <c r="I171" t="n">
+        <v>2868</v>
+      </c>
+      <c r="J171" t="n">
+        <v>2559</v>
+      </c>
+      <c r="L171" t="n">
+        <v>3438</v>
+      </c>
+      <c r="M171" t="n">
+        <v>3843</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3855</v>
+      </c>
+      <c r="O171" t="n">
+        <v>10371</v>
+      </c>
+      <c r="P171" t="n">
+        <v>6144</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>6470</v>
+      </c>
+      <c r="R171" t="n">
+        <v>8500</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10480</v>
+      </c>
+      <c r="T171" t="n">
+        <v>11886</v>
+      </c>
+      <c r="U171" t="n">
+        <v>13707</v>
+      </c>
+      <c r="V171" t="n">
+        <v>14743</v>
+      </c>
+      <c r="W171" t="n">
+        <v>15277</v>
+      </c>
       <c r="Y171" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="Z171" t="n">
+        <v>7540</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>12607</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>17073</v>
+      </c>
       <c r="AC171" t="n">
-        <v>19105</v>
+        <v>17029</v>
       </c>
       <c r="AD171" t="n">
-        <v>19105</v>
+        <v>18965</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4831,6 +4831,9 @@
           <t>Eurospin RomaOstia Half Marathon</t>
         </is>
       </c>
+      <c r="P23" t="n">
+        <v>9485</v>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>-</t>
@@ -4882,7 +4885,13 @@
         <v>17888</v>
       </c>
       <c r="O24" t="n">
-        <v>19670</v>
+        <v>19678</v>
+      </c>
+      <c r="P24" t="n">
+        <v>20250</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>23086</v>
       </c>
       <c r="R24" t="n">
         <v>22254</v>
@@ -4903,7 +4912,7 @@
         <v>25001</v>
       </c>
       <c r="X24" t="n">
-        <v>28471</v>
+        <v>28454</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -4913,11 +4922,14 @@
       <c r="Z24" t="n">
         <v>13290</v>
       </c>
+      <c r="AA24" t="n">
+        <v>22235</v>
+      </c>
       <c r="AB24" t="n">
-        <v>26104</v>
+        <v>26067</v>
       </c>
       <c r="AC24" t="n">
-        <v>30904</v>
+        <v>30886</v>
       </c>
       <c r="AD24" t="n">
         <v>34742</v>
@@ -7269,6 +7281,9 @@
       <c r="U77" t="n">
         <v>41615</v>
       </c>
+      <c r="V77" t="n">
+        <v>43656</v>
+      </c>
       <c r="W77" t="n">
         <v>43656</v>
       </c>
@@ -7304,6 +7319,9 @@
         <is>
           <t>Copenhagen Half Marathon</t>
         </is>
+      </c>
+      <c r="T78" t="n">
+        <v>20000</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6345,6 +6345,9 @@
           <t xml:space="preserve">Göteborgsvarvet </t>
         </is>
       </c>
+      <c r="H55" t="n">
+        <v>24600</v>
+      </c>
       <c r="M55" t="n">
         <v>45075</v>
       </c>
@@ -6366,6 +6369,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>30186</v>
       </c>
       <c r="AC55" t="n">
         <v>40765</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>11177</v>
+        <v>11093</v>
       </c>
       <c r="AC22" t="n">
-        <v>13346</v>
+        <v>13245</v>
       </c>
       <c r="AD22" t="n">
-        <v>17675</v>
+        <v>17850</v>
       </c>
       <c r="AE22" t="n">
         <v>15961</v>
@@ -5872,8 +5872,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AB44" t="n">
+        <v>17255</v>
+      </c>
       <c r="AC44" t="n">
-        <v>18869</v>
+        <v>18959</v>
       </c>
       <c r="AD44" t="n">
         <v>19968</v>
@@ -5905,6 +5908,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z45" t="n">
+        <v>7380</v>
+      </c>
       <c r="AB45" t="n">
         <v>15306</v>
       </c>
@@ -6142,6 +6148,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z51" t="n">
+        <v>3831</v>
+      </c>
       <c r="AB51" t="n">
         <v>7661</v>
       </c>
@@ -7782,6 +7791,15 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA87" t="n">
+        <v>8279</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>20097</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>22294</v>
+      </c>
       <c r="AD87" t="n">
         <v>24634</v>
       </c>
@@ -7905,8 +7923,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA89" t="n">
+        <v>8279</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>12976</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>18271</v>
+      </c>
       <c r="AD89" t="n">
-        <v>22354</v>
+        <v>22376</v>
       </c>
     </row>
     <row r="90">
@@ -8105,6 +8132,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA93" t="n">
+        <v>12073</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>15985</v>
+      </c>
       <c r="AD93" t="n">
         <v>16201</v>
       </c>
@@ -8362,6 +8395,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA101" t="n">
+        <v>3724</v>
+      </c>
       <c r="AB101" t="n">
         <v>4847</v>
       </c>
@@ -12156,6 +12192,15 @@
           <t>Dam tot Damloop</t>
         </is>
       </c>
+      <c r="U167" t="n">
+        <v>33856</v>
+      </c>
+      <c r="V167" t="n">
+        <v>33293</v>
+      </c>
+      <c r="X167" t="n">
+        <v>31079</v>
+      </c>
       <c r="Y167" t="inlineStr">
         <is>
           <t>-</t>
@@ -12165,6 +12210,12 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA167" t="n">
+        <v>24579</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>32377</v>
       </c>
       <c r="AD167" t="n">
         <v>37233</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5279,10 +5279,22 @@
           <t>NN CPC Loop Den Haag - Half Marathon</t>
         </is>
       </c>
+      <c r="W30" t="n">
+        <v>10528</v>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>7029</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9232</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>14607</v>
       </c>
       <c r="AD30" t="n">
         <v>19624</v>
@@ -6039,7 +6051,7 @@
         <v>13065</v>
       </c>
       <c r="W48" t="n">
-        <v>13978</v>
+        <v>13997</v>
       </c>
       <c r="X48" t="n">
         <v>14535</v>
@@ -6049,6 +6061,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z48" t="n">
+        <v>10866</v>
+      </c>
       <c r="AA48" t="n">
         <v>11722</v>
       </c>
@@ -9122,6 +9137,18 @@
         <is>
           <t>NN CPC Loop Den Haag - 10 KM Loop</t>
         </is>
+      </c>
+      <c r="W117" t="n">
+        <v>9797</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>5553</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>6847</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>8732</v>
       </c>
       <c r="AE117" t="n">
         <v>16283</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6718,6 +6718,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC63" t="n">
+        <v>7587</v>
+      </c>
       <c r="AD63" t="n">
         <v>12300</v>
       </c>
@@ -6748,6 +6751,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC64" t="n">
+        <v>8575</v>
+      </c>
       <c r="AD64" t="n">
         <v>10768</v>
       </c>
@@ -12324,7 +12330,7 @@
         <v>67894</v>
       </c>
       <c r="W168" t="n">
-        <v>67253</v>
+        <v>67121</v>
       </c>
       <c r="X168" t="n">
         <v>70517</v>
@@ -12345,7 +12351,7 @@
         </is>
       </c>
       <c r="AB168" t="n">
-        <v>68870</v>
+        <v>68865</v>
       </c>
       <c r="AC168" t="n">
         <v>77725</v>
@@ -12379,6 +12385,12 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AB169" t="n">
+        <v>9663</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>14754</v>
       </c>
     </row>
     <row r="170">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5848,11 +5848,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z43" t="n">
+        <v>13857</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>14184</v>
+      </c>
       <c r="AB43" t="n">
         <v>18576</v>
       </c>
       <c r="AC43" t="n">
-        <v>21893</v>
+        <v>23915</v>
       </c>
       <c r="AD43" t="n">
         <v>23949</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4603,10 +4603,10 @@
         <v>45387</v>
       </c>
       <c r="AC19" t="n">
-        <v>47856</v>
+        <v>47544</v>
       </c>
       <c r="AD19" t="n">
-        <v>47633</v>
+        <v>47903</v>
       </c>
       <c r="AE19" t="n">
         <v>49234</v>
@@ -4932,7 +4932,7 @@
         <v>30886</v>
       </c>
       <c r="AD24" t="n">
-        <v>34742</v>
+        <v>34734</v>
       </c>
     </row>
     <row r="25">
@@ -5679,10 +5679,10 @@
         <v>35757</v>
       </c>
       <c r="AB39" t="n">
-        <v>51234</v>
+        <v>50782</v>
       </c>
       <c r="AC39" t="n">
-        <v>54175</v>
+        <v>53899</v>
       </c>
       <c r="AD39" t="n">
         <v>55499</v>
@@ -6963,10 +6963,10 @@
         </is>
       </c>
       <c r="AB68" t="n">
-        <v>24629</v>
+        <v>24634</v>
       </c>
       <c r="AC68" t="n">
-        <v>29610</v>
+        <v>29615</v>
       </c>
       <c r="AD68" t="n">
         <v>34353</v>
@@ -7029,16 +7029,52 @@
           <t>Atlanta Journal-Constitution Peachtree Road Race</t>
         </is>
       </c>
+      <c r="N70" t="n">
+        <v>49638</v>
+      </c>
+      <c r="O70" t="n">
+        <v>50978</v>
+      </c>
+      <c r="P70" t="n">
+        <v>54708</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>58034</v>
+      </c>
+      <c r="R70" t="n">
+        <v>55861</v>
+      </c>
+      <c r="S70" t="n">
+        <v>57714</v>
+      </c>
+      <c r="T70" t="n">
+        <v>54812</v>
+      </c>
+      <c r="U70" t="n">
+        <v>57062</v>
+      </c>
+      <c r="V70" t="n">
+        <v>55263</v>
+      </c>
+      <c r="W70" t="n">
+        <v>54524</v>
+      </c>
       <c r="Y70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="Z70" t="n">
+        <v>24315</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>34841</v>
+      </c>
       <c r="AB70" t="n">
-        <v>41806</v>
+        <v>37601</v>
       </c>
       <c r="AC70" t="n">
-        <v>43339</v>
+        <v>43404</v>
       </c>
       <c r="AD70" t="n">
         <v>43654</v>
@@ -8127,10 +8163,10 @@
         <v>11065</v>
       </c>
       <c r="AC92" t="n">
-        <v>15270</v>
+        <v>16280</v>
       </c>
       <c r="AD92" t="n">
-        <v>16280</v>
+        <v>15279</v>
       </c>
     </row>
     <row r="93">
@@ -8352,13 +8388,13 @@
         </is>
       </c>
       <c r="AB99" t="n">
-        <v>13566</v>
+        <v>10984</v>
       </c>
       <c r="AC99" t="n">
-        <v>11150</v>
+        <v>11338</v>
       </c>
       <c r="AD99" t="n">
-        <v>11338</v>
+        <v>11274</v>
       </c>
     </row>
     <row r="100">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4603,10 +4603,10 @@
         <v>45387</v>
       </c>
       <c r="AC19" t="n">
-        <v>47544</v>
+        <v>47856</v>
       </c>
       <c r="AD19" t="n">
-        <v>47903</v>
+        <v>47633</v>
       </c>
       <c r="AE19" t="n">
         <v>49234</v>
@@ -5679,10 +5679,10 @@
         <v>35757</v>
       </c>
       <c r="AB39" t="n">
-        <v>50782</v>
+        <v>51234</v>
       </c>
       <c r="AC39" t="n">
-        <v>53899</v>
+        <v>54175</v>
       </c>
       <c r="AD39" t="n">
         <v>55499</v>
@@ -7071,7 +7071,7 @@
         <v>34841</v>
       </c>
       <c r="AB70" t="n">
-        <v>37601</v>
+        <v>41806</v>
       </c>
       <c r="AC70" t="n">
         <v>43404</v>
@@ -8163,10 +8163,10 @@
         <v>11065</v>
       </c>
       <c r="AC92" t="n">
+        <v>15270</v>
+      </c>
+      <c r="AD92" t="n">
         <v>16280</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>15279</v>
       </c>
     </row>
     <row r="93">
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="AB99" t="n">
-        <v>10984</v>
+        <v>13566</v>
       </c>
       <c r="AC99" t="n">
+        <v>11150</v>
+      </c>
+      <c r="AD99" t="n">
         <v>11338</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>11274</v>
       </c>
     </row>
     <row r="100">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6431,6 +6431,57 @@
           <t>BOLDERBoulder 10K</t>
         </is>
       </c>
+      <c r="G56" t="n">
+        <v>42238</v>
+      </c>
+      <c r="H56" t="n">
+        <v>44613</v>
+      </c>
+      <c r="I56" t="n">
+        <v>43771</v>
+      </c>
+      <c r="J56" t="n">
+        <v>42158</v>
+      </c>
+      <c r="K56" t="n">
+        <v>43387</v>
+      </c>
+      <c r="M56" t="n">
+        <v>47765</v>
+      </c>
+      <c r="N56" t="n">
+        <v>47865</v>
+      </c>
+      <c r="O56" t="n">
+        <v>48504</v>
+      </c>
+      <c r="P56" t="n">
+        <v>49246</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>46615</v>
+      </c>
+      <c r="R56" t="n">
+        <v>43477</v>
+      </c>
+      <c r="S56" t="n">
+        <v>45834</v>
+      </c>
+      <c r="T56" t="n">
+        <v>45336</v>
+      </c>
+      <c r="U56" t="n">
+        <v>44671</v>
+      </c>
+      <c r="V56" t="n">
+        <v>43912</v>
+      </c>
+      <c r="W56" t="n">
+        <v>44653</v>
+      </c>
+      <c r="X56" t="n">
+        <v>41059</v>
+      </c>
       <c r="Y56" t="inlineStr">
         <is>
           <t>-</t>
@@ -6440,6 +6491,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>28007</v>
       </c>
       <c r="AB56" t="n">
         <v>35639</v>
@@ -9223,9 +9277,54 @@
           <t>Broad Street Run</t>
         </is>
       </c>
+      <c r="G118" t="n">
+        <v>8684</v>
+      </c>
+      <c r="H118" t="n">
+        <v>9063</v>
+      </c>
+      <c r="I118" t="n">
+        <v>10684</v>
+      </c>
+      <c r="J118" t="n">
+        <v>12083</v>
+      </c>
+      <c r="K118" t="n">
+        <v>13610</v>
+      </c>
+      <c r="L118" t="n">
+        <v>15920</v>
+      </c>
+      <c r="M118" t="n">
+        <v>19192</v>
+      </c>
+      <c r="N118" t="n">
+        <v>23244</v>
+      </c>
+      <c r="O118" t="n">
+        <v>26264</v>
+      </c>
+      <c r="P118" t="n">
+        <v>25157</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>34066</v>
+      </c>
+      <c r="R118" t="n">
+        <v>31798</v>
+      </c>
+      <c r="S118" t="n">
+        <v>35176</v>
+      </c>
+      <c r="T118" t="n">
+        <v>35868</v>
+      </c>
       <c r="U118" t="n">
         <v>34237</v>
       </c>
+      <c r="V118" t="n">
+        <v>36968</v>
+      </c>
       <c r="W118" t="n">
         <v>36222</v>
       </c>
@@ -11114,6 +11213,54 @@
         <is>
           <t>Boilermaker Road Race</t>
         </is>
+      </c>
+      <c r="G147" t="n">
+        <v>9771</v>
+      </c>
+      <c r="H147" t="n">
+        <v>8829</v>
+      </c>
+      <c r="I147" t="n">
+        <v>9121</v>
+      </c>
+      <c r="J147" t="n">
+        <v>8430</v>
+      </c>
+      <c r="K147" t="n">
+        <v>9406</v>
+      </c>
+      <c r="L147" t="n">
+        <v>12341</v>
+      </c>
+      <c r="M147" t="n">
+        <v>11885</v>
+      </c>
+      <c r="N147" t="n">
+        <v>12848</v>
+      </c>
+      <c r="O147" t="n">
+        <v>14198</v>
+      </c>
+      <c r="P147" t="n">
+        <v>14261</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>14663</v>
+      </c>
+      <c r="R147" t="n">
+        <v>15150</v>
+      </c>
+      <c r="S147" t="n">
+        <v>16055</v>
+      </c>
+      <c r="T147" t="n">
+        <v>15665</v>
+      </c>
+      <c r="U147" t="n">
+        <v>15431</v>
+      </c>
+      <c r="V147" t="n">
+        <v>15831</v>
       </c>
       <c r="W147" t="n">
         <v>15752</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4956,10 +4956,70 @@
           <t>Cooper River Bridge Run</t>
         </is>
       </c>
+      <c r="G25" t="n">
+        <v>14337</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14602</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15184</v>
+      </c>
+      <c r="J25" t="n">
+        <v>18442</v>
+      </c>
+      <c r="K25" t="n">
+        <v>33278</v>
+      </c>
+      <c r="L25" t="n">
+        <v>28533</v>
+      </c>
+      <c r="M25" t="n">
+        <v>29253</v>
+      </c>
+      <c r="N25" t="n">
+        <v>31509</v>
+      </c>
+      <c r="O25" t="n">
+        <v>33068</v>
+      </c>
+      <c r="P25" t="n">
+        <v>34633</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>36753</v>
+      </c>
+      <c r="R25" t="n">
+        <v>31470</v>
+      </c>
+      <c r="S25" t="n">
+        <v>31849</v>
+      </c>
+      <c r="T25" t="n">
+        <v>27391</v>
+      </c>
+      <c r="U25" t="n">
+        <v>26840</v>
+      </c>
+      <c r="V25" t="n">
+        <v>32619</v>
+      </c>
+      <c r="W25" t="n">
+        <v>27461</v>
+      </c>
+      <c r="X25" t="n">
+        <v>29290</v>
+      </c>
       <c r="Y25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>11787</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>16081</v>
       </c>
       <c r="AB25" t="n">
         <v>22336</v>
@@ -11357,6 +11417,57 @@
           <t>Manchester Road Race</t>
         </is>
       </c>
+      <c r="F149" t="n">
+        <v>10571</v>
+      </c>
+      <c r="G149" t="n">
+        <v>9437</v>
+      </c>
+      <c r="H149" t="n">
+        <v>8678</v>
+      </c>
+      <c r="I149" t="n">
+        <v>8832</v>
+      </c>
+      <c r="J149" t="n">
+        <v>7182</v>
+      </c>
+      <c r="K149" t="n">
+        <v>8270</v>
+      </c>
+      <c r="L149" t="n">
+        <v>9483</v>
+      </c>
+      <c r="M149" t="n">
+        <v>10431</v>
+      </c>
+      <c r="N149" t="n">
+        <v>12054</v>
+      </c>
+      <c r="O149" t="n">
+        <v>13403</v>
+      </c>
+      <c r="P149" t="n">
+        <v>13470</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>13416</v>
+      </c>
+      <c r="R149" t="n">
+        <v>12879</v>
+      </c>
+      <c r="S149" t="n">
+        <v>11682</v>
+      </c>
+      <c r="T149" t="n">
+        <v>12463</v>
+      </c>
+      <c r="U149" t="n">
+        <v>11233</v>
+      </c>
+      <c r="V149" t="n">
+        <v>11282</v>
+      </c>
       <c r="W149" t="n">
         <v>9244</v>
       </c>
@@ -11378,6 +11489,9 @@
       </c>
       <c r="AB149" t="n">
         <v>9590</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>8385</v>
       </c>
       <c r="AD149" t="n">
         <v>11003</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10938,9 +10938,54 @@
           <t>Gate River Run</t>
         </is>
       </c>
+      <c r="G142" t="n">
+        <v>7412</v>
+      </c>
+      <c r="H142" t="n">
+        <v>7183</v>
+      </c>
+      <c r="I142" t="n">
+        <v>7546</v>
+      </c>
+      <c r="J142" t="n">
+        <v>7783</v>
+      </c>
+      <c r="K142" t="n">
+        <v>9015</v>
+      </c>
+      <c r="L142" t="n">
+        <v>11167</v>
+      </c>
+      <c r="M142" t="n">
+        <v>12087</v>
+      </c>
+      <c r="N142" t="n">
+        <v>9989</v>
+      </c>
+      <c r="O142" t="n">
+        <v>13342</v>
+      </c>
+      <c r="P142" t="n">
+        <v>14979</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>16357</v>
+      </c>
+      <c r="R142" t="n">
+        <v>15567</v>
+      </c>
+      <c r="S142" t="n">
+        <v>15514</v>
+      </c>
+      <c r="T142" t="n">
+        <v>14926</v>
+      </c>
       <c r="U142" t="n">
         <v>14435</v>
       </c>
+      <c r="V142" t="n">
+        <v>15620</v>
+      </c>
       <c r="W142" t="n">
         <v>14113</v>
       </c>
@@ -11567,6 +11612,54 @@
         <is>
           <t>Falmouth Road Race</t>
         </is>
+      </c>
+      <c r="G151" t="n">
+        <v>7568</v>
+      </c>
+      <c r="H151" t="n">
+        <v>8071</v>
+      </c>
+      <c r="I151" t="n">
+        <v>8161</v>
+      </c>
+      <c r="J151" t="n">
+        <v>7522</v>
+      </c>
+      <c r="K151" t="n">
+        <v>8241</v>
+      </c>
+      <c r="L151" t="n">
+        <v>8944</v>
+      </c>
+      <c r="M151" t="n">
+        <v>8728</v>
+      </c>
+      <c r="N151" t="n">
+        <v>8944</v>
+      </c>
+      <c r="O151" t="n">
+        <v>9738</v>
+      </c>
+      <c r="P151" t="n">
+        <v>10959</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>10592</v>
+      </c>
+      <c r="R151" t="n">
+        <v>10892</v>
+      </c>
+      <c r="S151" t="n">
+        <v>11075</v>
+      </c>
+      <c r="T151" t="n">
+        <v>10692</v>
+      </c>
+      <c r="U151" t="n">
+        <v>10557</v>
+      </c>
+      <c r="V151" t="n">
+        <v>11048</v>
       </c>
       <c r="W151" t="n">
         <v>11063</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -9537,8 +9537,26 @@
           <t>Lilac Bloomsday Run</t>
         </is>
       </c>
+      <c r="N120" t="n">
+        <v>47944</v>
+      </c>
+      <c r="O120" t="n">
+        <v>50566</v>
+      </c>
+      <c r="R120" t="n">
+        <v>44535</v>
+      </c>
+      <c r="S120" t="n">
+        <v>44581</v>
+      </c>
+      <c r="T120" t="n">
+        <v>42294</v>
+      </c>
       <c r="U120" t="n">
         <v>42206</v>
+      </c>
+      <c r="V120" t="n">
+        <v>28752</v>
       </c>
       <c r="W120" t="n">
         <v>38068</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10091,8 +10091,50 @@
           <t>Bay to Breakers</t>
         </is>
       </c>
+      <c r="G128" t="n">
+        <v>31351</v>
+      </c>
+      <c r="H128" t="n">
+        <v>24063</v>
+      </c>
+      <c r="I128" t="n">
+        <v>30571</v>
+      </c>
+      <c r="J128" t="n">
+        <v>30908</v>
+      </c>
+      <c r="K128" t="n">
+        <v>24561</v>
+      </c>
+      <c r="M128" t="n">
+        <v>22359</v>
+      </c>
+      <c r="N128" t="n">
+        <v>22149</v>
+      </c>
+      <c r="O128" t="n">
+        <v>24440</v>
+      </c>
+      <c r="P128" t="n">
+        <v>43891</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>23074</v>
+      </c>
+      <c r="R128" t="n">
+        <v>22468</v>
+      </c>
+      <c r="S128" t="n">
+        <v>28227</v>
+      </c>
+      <c r="T128" t="n">
+        <v>29962</v>
+      </c>
       <c r="U128" t="n">
         <v>28009</v>
+      </c>
+      <c r="V128" t="n">
+        <v>26726</v>
       </c>
       <c r="W128" t="n">
         <v>24572</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5501,6 +5501,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA34" t="n">
+        <v>6743</v>
+      </c>
       <c r="AB34" t="n">
         <v>10213</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6841,8 +6841,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA63" t="n">
+        <v>5394</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>6123</v>
+      </c>
       <c r="AC63" t="n">
-        <v>7587</v>
+        <v>9217</v>
       </c>
       <c r="AD63" t="n">
         <v>12300</v>
@@ -6874,8 +6880,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA64" t="n">
+        <v>5507</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>4713</v>
+      </c>
       <c r="AC64" t="n">
-        <v>8575</v>
+        <v>8940</v>
       </c>
       <c r="AD64" t="n">
         <v>10768</v>
@@ -7490,6 +7502,15 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA77" t="n">
+        <v>41066</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>43545</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>45889</v>
+      </c>
       <c r="AD77" t="n">
         <v>46258</v>
       </c>
@@ -12845,11 +12866,17 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA169" t="n">
+        <v>8174</v>
+      </c>
       <c r="AB169" t="n">
-        <v>9663</v>
+        <v>9745</v>
       </c>
       <c r="AC169" t="n">
-        <v>14754</v>
+        <v>15400</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>16320</v>
       </c>
     </row>
     <row r="170">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE171"/>
+  <dimension ref="A1:AE177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -6808,6 +6808,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA62" t="n">
+        <v>10863</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>12591</v>
+      </c>
       <c r="AC62" t="n">
         <v>15291</v>
       </c>
@@ -13037,6 +13043,237 @@
       </c>
       <c r="AD171" t="n">
         <v>18965</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>AJ Bell Great Birmingham Run</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA172" t="n">
+        <v>5671</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>5118</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>6554</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>7645</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Birmingham</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>AJ Bell Great Birmingham Run 10K</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA173" t="n">
+        <v>2942</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>3006</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>3788</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>AJ Bell Great Bristol Run 10K</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA174" t="n">
+        <v>4672</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>4688</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>7061</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>8486</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Great Scottish Run 10K</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA175" t="n">
+        <v>5202</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>6387</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>7570</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>8532</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>AJ Bell Great South Run</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA176" t="n">
+        <v>13062</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>14605</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>17488</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Gateshead</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>AJ Bell Great North 10K</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA177" t="n">
+        <v>2185</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>3620</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>4534</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>6962</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3951,6 +3951,16 @@
           <t>Aramco Houston Half Marathon</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AC4" t="n">
         <v>13715</v>
       </c>
@@ -3982,6 +3992,101 @@
           <t>10K Valencia Ibercaja by Kiprun</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>-</t>
@@ -4021,6 +4126,26 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AD6" t="n">
         <v>11453</v>
       </c>
@@ -4049,6 +4174,26 @@
           <t>Tata Mumbai Marathon</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="X7" t="n">
         <v>7803</v>
       </c>
@@ -4086,6 +4231,126 @@
           <t>10K Montmartre</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AE8" t="n">
         <v>10984</v>
       </c>
@@ -4205,6 +4470,116 @@
           <t>Riyadh Marathon</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AB10" t="n">
         <v>288</v>
       </c>
@@ -4269,6 +4644,31 @@
           <t>Mitja Marato Barcelona by Brooks</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V12" t="n">
         <v>15242</v>
       </c>
@@ -4318,6 +4718,81 @@
           <t>Cancer Research UK London Winter Run</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4429,6 +4904,51 @@
           <t>Rock 'n' Roll Running Series Las Vegas</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4468,6 +4988,121 @@
           <t>Burj2Burj Half Marathon</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AC16" t="n">
         <v>2942</v>
       </c>
@@ -4524,6 +5159,76 @@
           <t>Coelmo Napoli City Half Marathon</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AD18" t="n">
         <v>5732</v>
       </c>
@@ -4633,6 +5338,41 @@
           <t>Tokyo Marathon</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L20" t="n">
         <v>25102</v>
       </c>
@@ -5052,6 +5792,36 @@
           <t>United Airlines NYC Half</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="K26" t="n">
         <v>10302</v>
       </c>
@@ -5425,6 +6195,51 @@
           <t>Disney Princess Half Marathon</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
           <t>-</t>
@@ -5458,6 +6273,56 @@
           <t>Warsaw Half Marathon</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
           <t>-</t>
@@ -5535,6 +6400,21 @@
           <t>St. Jude Rock 'n' Roll Running Series Washington DC</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5598,6 +6478,56 @@
           <t>EDP Meia Maratona de Lisboa - Vodafone 10K</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y37" t="inlineStr">
         <is>
           <t>-</t>
@@ -5876,6 +6806,91 @@
           <t>NYCRUNS Brooklyn Experience Half Marathon</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y42" t="inlineStr">
         <is>
           <t>-</t>
@@ -5906,6 +6921,66 @@
           <t>Adidas Manchester Marathon</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
           <t>-</t>
@@ -5948,6 +7023,96 @@
           <t>London Landmarks Half Marathon</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5984,6 +7149,71 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr">
         <is>
           <t>-</t>
@@ -6197,6 +7427,21 @@
           <t>21K de Montréal</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y50" t="inlineStr">
         <is>
           <t>-</t>
@@ -6227,6 +7472,71 @@
           <t>Zurich Rock 'n' Roll Running Series Madrid</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
           <t>-</t>
@@ -6395,6 +7705,76 @@
           <t>Sanlam Cape Town Marathon</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6589,6 +7969,66 @@
           <t>NYRR RBC Brooklyn Half</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
           <t>-</t>
@@ -6619,6 +8059,106 @@
           <t>Hoka Runaway Sydney Half Marathon</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y58" t="inlineStr">
         <is>
           <t>-</t>
@@ -6803,6 +8343,21 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y62" t="inlineStr">
         <is>
           <t>-</t>
@@ -6842,6 +8397,76 @@
           <t>AJ Bell Great Manchester Run</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y63" t="inlineStr">
         <is>
           <t>-</t>
@@ -6881,6 +8506,11 @@
           <t>AJ Bell Great Bristol Run</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7021,6 +8651,91 @@
           <t>Bangsaen10</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y66" t="inlineStr">
         <is>
           <t>-</t>
@@ -7087,6 +8802,41 @@
           <t>Adidas 10K Paris</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y68" t="inlineStr">
         <is>
           <t>-</t>
@@ -7128,6 +8878,96 @@
           <t>Royal Run</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y69" t="inlineStr">
         <is>
           <t>-</t>
@@ -7266,6 +9106,51 @@
           <t>Saucony London 10K</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
           <t>-</t>
@@ -7302,6 +9187,66 @@
           <t>Asics Run Melbourne</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7542,6 +9487,81 @@
           <t>Copenhagen Half Marathon</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T78" t="n">
         <v>20000</v>
       </c>
@@ -7581,6 +9601,106 @@
           <t>Transurban Bridge to Brisbane</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y79" t="inlineStr">
         <is>
           <t>-</t>
@@ -7622,6 +9742,96 @@
           <t>The Big Half</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7652,6 +9862,46 @@
           <t>Vitality London 10,000</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y81" t="inlineStr">
         <is>
           <t>-</t>
@@ -7993,6 +10243,21 @@
           <t>Cardiff Half Marathon</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
           <t>-</t>
@@ -8125,6 +10390,41 @@
           <t>Manchester Half Marathon</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y89" t="inlineStr">
         <is>
           <t>-</t>
@@ -8164,6 +10464,76 @@
           <t>Wizz Air Rome Half Marathon by Brooks</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y90" t="inlineStr">
         <is>
           <t>-</t>
@@ -8298,6 +10668,76 @@
           <t>Run in Lyon</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y92" t="inlineStr">
         <is>
           <t>-</t>
@@ -8334,6 +10774,46 @@
           <t>Royal Parks Half Marathon</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y93" t="inlineStr">
         <is>
           <t>-</t>
@@ -8370,9 +10850,114 @@
           <t>Tokyo Legacy Half Marathon</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y94" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AD94" t="n">
@@ -8400,6 +10985,71 @@
           <t>TCS Mizuno Half Marathon</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y95" t="inlineStr">
         <is>
           <t>-</t>
@@ -8430,6 +11080,51 @@
           <t>Nike Melbourne Marathon Festival</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y96" t="inlineStr">
         <is>
           <t>-</t>
@@ -8460,6 +11155,31 @@
           <t>Vedanta Delhi Half Marathon</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y97" t="inlineStr">
         <is>
           <t>-</t>
@@ -8526,6 +11246,76 @@
           <t>Run in Lyon</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8562,6 +11352,101 @@
           <t>Half Marathon Munchen by Brooks</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y100" t="inlineStr">
         <is>
           <t>-</t>
@@ -8636,6 +11521,26 @@
           <t xml:space="preserve">Hyundai Meia Maratona </t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8713,6 +11618,126 @@
           <t>ASICS LDNX</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AD104" t="n">
         <v>4681</v>
       </c>
@@ -8872,6 +11897,91 @@
           <t>Bangsaen42 Chonburi Marathon</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y107" t="inlineStr">
         <is>
           <t>-</t>
@@ -9129,6 +12239,91 @@
           <t>Taipei Half Marathon</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y111" t="inlineStr">
         <is>
           <t>-</t>
@@ -9165,6 +12360,16 @@
           <t>Standard Chartered Singapore Half Marathon</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y112" t="inlineStr">
         <is>
           <t>-</t>
@@ -9195,6 +12400,91 @@
           <t>Bangsaen21</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y113" t="inlineStr">
         <is>
           <t>-</t>
@@ -9231,6 +12521,91 @@
           <t>Rock 'n' Roll Running Series Mexico City</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y114" t="inlineStr">
         <is>
           <t>-</t>
@@ -9261,6 +12636,16 @@
           <t>Standard Chartered Singapore Marathon</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9788,6 +13173,26 @@
           <t>Bank of America Shamrock Shuffle</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W123" t="n">
         <v>20892</v>
       </c>
@@ -9838,6 +13243,51 @@
           <t>Dick's Pittsburgh Marathon</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U124" t="n">
         <v>14132</v>
       </c>
@@ -10216,6 +13666,61 @@
           <t>Silicon Valley Turkey Trot</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W129" t="n">
         <v>15878</v>
       </c>
@@ -10358,6 +13863,21 @@
           <t>Miami Marathon</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U131" t="n">
         <v>14205</v>
       </c>
@@ -10741,6 +14261,11 @@
           <t>Oklahoma City Memorial Marathon</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W137" t="n">
         <v>15162</v>
       </c>
@@ -10938,6 +14463,16 @@
           <t>San Antonio Marathon</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W140" t="n">
         <v>18639</v>
       </c>
@@ -10983,6 +14518,31 @@
           <t>Hoag OC Marathon</t>
         </is>
       </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W141" t="n">
         <v>10707</v>
       </c>
@@ -11126,6 +14686,36 @@
           <t>Denver Colfax Marathon</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11262,6 +14852,46 @@
           <t>Indianapolis Monumental Marathon</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W145" t="n">
         <v>14992</v>
       </c>
@@ -11507,6 +15137,11 @@
           <t>Baltimore Running Festival</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W148" t="n">
         <v>17752</v>
       </c>
@@ -11801,6 +15436,41 @@
           <t>Eugene Marathon</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y152" t="inlineStr">
         <is>
           <t>-</t>
@@ -11981,6 +15651,31 @@
           <t>Fargo Marathon</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W155" t="n">
         <v>13981</v>
       </c>
@@ -12020,6 +15715,26 @@
           <t>Rock 'n' Roll Arizona Marathon</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="W156" t="n">
         <v>15908</v>
       </c>
@@ -12461,6 +16176,56 @@
           <t>Brighton Marathon</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O162" t="n">
         <v>7411</v>
       </c>
@@ -12589,6 +16354,61 @@
           <t>Osaka Marathon</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Z165" t="inlineStr">
         <is>
           <t>-</t>
@@ -12867,6 +16687,36 @@
           <t>Great Scottish Run</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13066,6 +16916,21 @@
           <t>AJ Bell Great Birmingham Run</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13105,6 +16970,21 @@
           <t>AJ Bell Great Birmingham Run 10K</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y173" t="inlineStr">
         <is>
           <t>-</t>
@@ -13144,6 +17024,21 @@
           <t>AJ Bell Great Bristol Run 10K</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13256,6 +17151,71 @@
       <c r="D177" t="inlineStr">
         <is>
           <t>AJ Bell Great North 10K</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4351,6 +4351,16 @@
           <t>x</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AE8" t="n">
         <v>10984</v>
       </c>
@@ -5103,6 +5113,11 @@
           <t>x</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="AC16" t="n">
         <v>2942</v>
       </c>
@@ -6079,6 +6094,16 @@
           <t>Movistar Madrid Medio Maraton</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
           <t>-</t>
@@ -6891,6 +6916,11 @@
           <t>x</t>
         </is>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y42" t="inlineStr">
         <is>
           <t>-</t>
@@ -8313,6 +8343,56 @@
           <t>Rock 'n' Roll Running Series San Diego</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y61" t="inlineStr">
         <is>
           <t>-</t>
@@ -8467,6 +8547,21 @@
           <t>x</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y63" t="inlineStr">
         <is>
           <t>-</t>
@@ -8837,6 +8932,56 @@
           <t>x</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y68" t="inlineStr">
         <is>
           <t>-</t>
@@ -10213,6 +10358,36 @@
           <t>Valencia Half Marathon Trinidad Alfonso Zurich</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y86" t="inlineStr">
         <is>
           <t>-</t>
@@ -10425,6 +10600,51 @@
           <t>x</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y89" t="inlineStr">
         <is>
           <t>-</t>
@@ -10534,9 +10754,54 @@
           <t>x</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y90" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AD90" t="n">
@@ -11541,6 +11806,21 @@
           <t>x</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y102" t="inlineStr">
         <is>
           <t>-</t>
@@ -16931,6 +17211,31 @@
           <t>x</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y172" t="inlineStr">
         <is>
           <t>-</t>
@@ -16985,9 +17290,99 @@
           <t>x</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y173" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="AA173" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8191,12 +8191,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>x</t>
         </is>
       </c>
       <c r="AD58" t="n">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>x</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8982,6 +8982,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="V68" t="n">
+        <v>15756</v>
+      </c>
+      <c r="W68" t="n">
+        <v>17525</v>
+      </c>
+      <c r="X68" t="n">
+        <v>18621</v>
+      </c>
       <c r="Y68" t="inlineStr">
         <is>
           <t>-</t>
@@ -8991,6 +9000,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA68" t="n">
+        <v>19327</v>
       </c>
       <c r="AB68" t="n">
         <v>24634</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6693,6 +6693,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z39" t="n">
+        <v>27114</v>
+      </c>
       <c r="AA39" t="n">
         <v>35757</v>
       </c>
@@ -11010,15 +11013,34 @@
           <t>x</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
+      <c r="R92" t="n">
+        <v>7566</v>
+      </c>
+      <c r="S92" t="n">
+        <v>9200</v>
+      </c>
+      <c r="T92" t="n">
+        <v>10165</v>
+      </c>
+      <c r="U92" t="n">
+        <v>11236</v>
+      </c>
+      <c r="V92" t="n">
+        <v>11174</v>
+      </c>
+      <c r="W92" t="n">
+        <v>10532</v>
+      </c>
+      <c r="X92" t="n">
+        <v>9498</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>5876</v>
       </c>
       <c r="AB92" t="n">
         <v>11065</v>
@@ -11588,15 +11610,34 @@
           <t>x</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
+      <c r="R99" t="n">
+        <v>8634</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10266</v>
+      </c>
+      <c r="T99" t="n">
+        <v>12110</v>
+      </c>
+      <c r="U99" t="n">
+        <v>13474</v>
+      </c>
+      <c r="V99" t="n">
+        <v>14547</v>
+      </c>
+      <c r="W99" t="n">
+        <v>14096</v>
+      </c>
+      <c r="X99" t="n">
+        <v>13126</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>7761</v>
       </c>
       <c r="AB99" t="n">
         <v>13566</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8570,6 +8570,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z63" t="n">
+        <v>2495</v>
+      </c>
       <c r="AA63" t="n">
         <v>5394</v>
       </c>
@@ -8614,6 +8617,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z64" t="n">
+        <v>5947</v>
+      </c>
       <c r="AA64" t="n">
         <v>5507</v>
       </c>
@@ -9613,6 +9619,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z77" t="n">
+        <v>49623</v>
+      </c>
       <c r="AA77" t="n">
         <v>41066</v>
       </c>
@@ -11118,6 +11127,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z93" t="n">
+        <v>15610</v>
+      </c>
       <c r="AA93" t="n">
         <v>12073</v>
       </c>
@@ -11354,6 +11366,18 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z95" t="n">
+        <v>10506</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>20398</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>21390</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>17662</v>
+      </c>
       <c r="AD95" t="n">
         <v>13341</v>
       </c>
@@ -13060,6 +13084,9 @@
       <c r="AC117" t="n">
         <v>8732</v>
       </c>
+      <c r="AD117" t="n">
+        <v>12862</v>
+      </c>
       <c r="AE117" t="n">
         <v>16283</v>
       </c>
@@ -16885,6 +16912,9 @@
       </c>
       <c r="AA167" t="n">
         <v>24579</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>39346</v>
       </c>
       <c r="AC167" t="n">
         <v>32377</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5552,6 +5552,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA22" t="n">
+        <v>8378</v>
+      </c>
       <c r="AB22" t="n">
         <v>11093</v>
       </c>
@@ -6558,6 +6561,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA37" t="n">
+        <v>9926</v>
+      </c>
       <c r="AB37" t="n">
         <v>11275</v>
       </c>
@@ -11907,6 +11913,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA102" t="n">
+        <v>5660</v>
       </c>
       <c r="AB102" t="n">
         <v>6567</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5542,15 +5542,16 @@
           <t>EDP Lisboa Meia Maratona</t>
         </is>
       </c>
+      <c r="W22" t="n">
+        <v>9191</v>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z22" t="n">
+        <v>5402</v>
       </c>
       <c r="AA22" t="n">
         <v>8378</v>
@@ -6561,6 +6562,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z37" t="n">
+        <v>5747</v>
+      </c>
       <c r="AA37" t="n">
         <v>9926</v>
       </c>
@@ -11830,10 +11834,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z101" t="n">
+        <v>1891</v>
       </c>
       <c r="AA101" t="n">
         <v>3724</v>
@@ -11909,10 +11911,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Z102" t="n">
+        <v>2387</v>
       </c>
       <c r="AA102" t="n">
         <v>5660</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -9453,10 +9453,67 @@
           <t>TCS Sydney Marathon presented by ASICS</t>
         </is>
       </c>
+      <c r="G74" t="n">
+        <v>1312</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1348</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1165</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1258</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1217</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1367</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1936</v>
+      </c>
+      <c r="N74" t="n">
+        <v>2464</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2820</v>
+      </c>
+      <c r="P74" t="n">
+        <v>3149</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2984</v>
+      </c>
+      <c r="R74" t="n">
+        <v>3389</v>
+      </c>
+      <c r="S74" t="n">
+        <v>3235</v>
+      </c>
+      <c r="T74" t="n">
+        <v>3273</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3477</v>
+      </c>
+      <c r="V74" t="n">
+        <v>3567</v>
+      </c>
+      <c r="W74" t="n">
+        <v>3808</v>
+      </c>
+      <c r="X74" t="n">
+        <v>4484</v>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA74" t="n">
+        <v>3453</v>
       </c>
       <c r="AB74" t="n">
         <v>13297</v>
@@ -9489,10 +9546,34 @@
           <t>Maratón de la Ciudad de México Telcel</t>
         </is>
       </c>
+      <c r="R75" t="n">
+        <v>8625</v>
+      </c>
+      <c r="S75" t="n">
+        <v>16323</v>
+      </c>
+      <c r="T75" t="n">
+        <v>18752</v>
+      </c>
+      <c r="U75" t="n">
+        <v>22753</v>
+      </c>
+      <c r="V75" t="n">
+        <v>23626</v>
+      </c>
+      <c r="W75" t="n">
+        <v>27255</v>
+      </c>
       <c r="Y75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>10046</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>15237</v>
       </c>
       <c r="AB75" t="n">
         <v>28364</v>
@@ -10117,10 +10198,49 @@
           <t>NN Maraton Warszawski</t>
         </is>
       </c>
+      <c r="L82" t="n">
+        <v>2119</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2640</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4061</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>6796</v>
+      </c>
+      <c r="R82" t="n">
+        <v>8509</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6674</v>
+      </c>
+      <c r="T82" t="n">
+        <v>6511</v>
+      </c>
+      <c r="U82" t="n">
+        <v>5921</v>
+      </c>
+      <c r="V82" t="n">
+        <v>5466</v>
+      </c>
+      <c r="W82" t="n">
+        <v>7529</v>
+      </c>
+      <c r="X82" t="n">
+        <v>4555</v>
+      </c>
       <c r="Y82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>2734</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>3699</v>
       </c>
       <c r="AB82" t="n">
         <v>5557</v>
@@ -11948,10 +12068,70 @@
           <t>TCS Toronto Waterfront Marathon</t>
         </is>
       </c>
+      <c r="E103" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1751</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1897</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1955</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1448</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1486</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1747</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1674</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1895</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1942</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1266</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>1740</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1641</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1504</v>
+      </c>
+      <c r="T103" t="n">
+        <v>1359</v>
+      </c>
+      <c r="U103" t="n">
+        <v>1496</v>
+      </c>
+      <c r="V103" t="n">
+        <v>1185</v>
+      </c>
+      <c r="W103" t="n">
+        <v>1365</v>
+      </c>
+      <c r="X103" t="n">
+        <v>1486</v>
+      </c>
       <c r="Y103" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA103" t="n">
+        <v>1633</v>
       </c>
       <c r="AB103" t="n">
         <v>4563</v>
@@ -13012,10 +13192,31 @@
           <t>x</t>
         </is>
       </c>
+      <c r="S115" t="n">
+        <v>10320</v>
+      </c>
+      <c r="T115" t="n">
+        <v>8972</v>
+      </c>
+      <c r="U115" t="n">
+        <v>8033</v>
+      </c>
+      <c r="V115" t="n">
+        <v>9386</v>
+      </c>
+      <c r="W115" t="n">
+        <v>9315</v>
+      </c>
       <c r="Y115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA115" t="n">
+        <v>5762</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>6719</v>
       </c>
       <c r="AC115" t="n">
         <v>8660</v>
@@ -14585,6 +14786,48 @@
           <t>St. Jude Memphis Marathon</t>
         </is>
       </c>
+      <c r="H136" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1292</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1531</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1534</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1963</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2219</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2459</v>
+      </c>
+      <c r="O136" t="n">
+        <v>2427</v>
+      </c>
+      <c r="P136" t="n">
+        <v>2364</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>2624</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2658</v>
+      </c>
+      <c r="T136" t="n">
+        <v>2510</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2504</v>
+      </c>
+      <c r="V136" t="n">
+        <v>2348</v>
+      </c>
       <c r="W136" t="n">
         <v>19406</v>
       </c>
@@ -14596,6 +14839,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z136" t="n">
+        <v>1499</v>
+      </c>
       <c r="AA136" t="n">
         <v>18944</v>
       </c>
@@ -16149,10 +16395,76 @@
           <t>Portland Marathon</t>
         </is>
       </c>
+      <c r="F157" t="n">
+        <v>8428</v>
+      </c>
+      <c r="G157" t="n">
+        <v>8039</v>
+      </c>
+      <c r="H157" t="n">
+        <v>7735</v>
+      </c>
+      <c r="I157" t="n">
+        <v>6804</v>
+      </c>
+      <c r="K157" t="n">
+        <v>8503</v>
+      </c>
+      <c r="L157" t="n">
+        <v>8734</v>
+      </c>
+      <c r="M157" t="n">
+        <v>9135</v>
+      </c>
+      <c r="N157" t="n">
+        <v>8093</v>
+      </c>
+      <c r="O157" t="n">
+        <v>10117</v>
+      </c>
+      <c r="P157" t="n">
+        <v>10969</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>8727</v>
+      </c>
+      <c r="R157" t="n">
+        <v>9393</v>
+      </c>
+      <c r="S157" t="n">
+        <v>8979</v>
+      </c>
+      <c r="T157" t="n">
+        <v>7874</v>
+      </c>
+      <c r="U157" t="n">
+        <v>6926</v>
+      </c>
+      <c r="V157" t="n">
+        <v>4445</v>
+      </c>
+      <c r="W157" t="n">
+        <v>2680</v>
+      </c>
+      <c r="X157" t="n">
+        <v>4965</v>
+      </c>
       <c r="Y157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z157" t="n">
+        <v>3404</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>5773</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>6041</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>7411</v>
       </c>
       <c r="AD157" t="n">
         <v>9838</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -13246,10 +13246,40 @@
           <t>Taipei Marathon</t>
         </is>
       </c>
+      <c r="Q116" t="n">
+        <v>4574</v>
+      </c>
+      <c r="R116" t="n">
+        <v>4897</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5318</v>
+      </c>
+      <c r="T116" t="n">
+        <v>4667</v>
+      </c>
+      <c r="U116" t="n">
+        <v>5560</v>
+      </c>
+      <c r="V116" t="n">
+        <v>5991</v>
+      </c>
+      <c r="W116" t="n">
+        <v>6272</v>
+      </c>
+      <c r="X116" t="n">
+        <v>6990</v>
+      </c>
       <c r="Y116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z116" t="n">
+        <v>6747</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>7840</v>
       </c>
       <c r="AB116" t="n">
         <v>8117</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4632,6 +4632,9 @@
       <c r="AD11" t="n">
         <v>22872</v>
       </c>
+      <c r="AE11" t="n">
+        <v>26621</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11949,6 +11952,27 @@
           <t>EDP Maratona de Lisboa</t>
         </is>
       </c>
+      <c r="J101" t="n">
+        <v>637</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1836</v>
+      </c>
+      <c r="S101" t="n">
+        <v>2863</v>
+      </c>
+      <c r="T101" t="n">
+        <v>3825</v>
+      </c>
+      <c r="U101" t="n">
+        <v>3540</v>
+      </c>
+      <c r="W101" t="n">
+        <v>3100</v>
+      </c>
+      <c r="X101" t="n">
+        <v>4695</v>
+      </c>
       <c r="Y101" t="inlineStr">
         <is>
           <t>-</t>
@@ -17247,6 +17271,9 @@
       </c>
       <c r="V167" t="n">
         <v>33293</v>
+      </c>
+      <c r="W167" t="n">
+        <v>33599</v>
       </c>
       <c r="X167" t="n">
         <v>31079</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE177"/>
+  <dimension ref="A1:AE181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -4624,6 +4624,9 @@
           <t>Standard Chartered Hong Kong Half Marathon</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>16370</v>
+      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>-</t>
@@ -18090,6 +18093,264 @@
       </c>
       <c r="AD177" t="n">
         <v>6962</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Standard Chartered KL Marathon</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD178" t="n">
+        <v>12146</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Standard Chartered KL Half Marathon</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD179" t="n">
+        <v>13035</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Standard Chartered KL 10K</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD180" t="n">
+        <v>10870</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Standard Chartered Hong Kong Marathon</t>
+        </is>
+      </c>
+      <c r="X181" t="n">
+        <v>18892</v>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE181" t="n">
+        <v>18575</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5441,6 +5441,11 @@
       <c r="Z20" t="n">
         <v>18272</v>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB20" t="n">
         <v>36560</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3918,7 +3918,17 @@
           <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4092,6 +4102,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB5" t="n">
         <v>9811</v>
       </c>
@@ -4146,6 +4161,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="Y6" t="n">
+        <v>12664</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10993</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12607</v>
+      </c>
       <c r="AD6" t="n">
         <v>11453</v>
       </c>
@@ -4632,6 +4656,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD11" t="n">
         <v>22872</v>
       </c>
@@ -4814,6 +4843,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB13" t="n">
         <v>13706</v>
       </c>
@@ -4970,6 +5004,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB15" t="n">
         <v>11865</v>
       </c>
@@ -6124,6 +6163,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD29" t="n">
         <v>20918</v>
       </c>
@@ -6157,6 +6201,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA30" t="n">
         <v>7029</v>
       </c>
@@ -6285,6 +6334,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD32" t="n">
         <v>15879</v>
       </c>
@@ -6363,10 +6417,24 @@
           <t>x</t>
         </is>
       </c>
+      <c r="V33" t="n">
+        <v>12190</v>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>7347</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10002</v>
       </c>
       <c r="AC33" t="n">
         <v>13422</v>
@@ -6460,6 +6528,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD35" t="n">
         <v>12363</v>
       </c>
@@ -6485,7 +6558,26 @@
           <t>GetPro Bath Half</t>
         </is>
       </c>
+      <c r="T36" t="n">
+        <v>12845</v>
+      </c>
+      <c r="U36" t="n">
+        <v>13915</v>
+      </c>
+      <c r="V36" t="n">
+        <v>13410</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6950,6 +7042,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD42" t="n">
         <v>24590</v>
       </c>
@@ -7172,6 +7269,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB44" t="n">
         <v>17255</v>
       </c>
@@ -7181,6 +7283,9 @@
       <c r="AD44" t="n">
         <v>19968</v>
       </c>
+      <c r="AE44" t="n">
+        <v>23383</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7307,7 +7412,20 @@
           <t>Statesman Capitol 10K</t>
         </is>
       </c>
+      <c r="W46" t="n">
+        <v>18751</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7348,6 +7466,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB47" t="n">
         <v>14985</v>
       </c>
@@ -7456,6 +7579,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD49" t="n">
         <v>12788</v>
       </c>
@@ -7501,6 +7629,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD50" t="n">
         <v>11795</v>
       </c>
@@ -7630,7 +7763,22 @@
           <t>St. Jude Rock 'n' Roll Series Nashville</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Y52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8083,7 +8231,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T57" t="n">
+        <v>26482</v>
+      </c>
+      <c r="X57" t="n">
+        <v>26803</v>
+      </c>
       <c r="Y57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8342,6 +8501,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD60" t="n">
         <v>17697</v>
       </c>
@@ -8422,6 +8586,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD61" t="n">
         <v>17222</v>
       </c>
@@ -8467,6 +8636,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA62" t="n">
         <v>10863</v>
       </c>
@@ -8866,6 +9040,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB66" t="n">
         <v>6035</v>
       </c>
@@ -8902,6 +9081,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD67" t="n">
         <v>40241</v>
       </c>
@@ -9160,6 +9344,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB69" t="n">
         <v>11329</v>
       </c>
@@ -9268,6 +9457,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD71" t="n">
         <v>21011</v>
       </c>
@@ -9343,6 +9537,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB72" t="n">
         <v>13368</v>
       </c>
@@ -9439,6 +9638,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD73" t="n">
         <v>11218</v>
       </c>
@@ -9523,6 +9727,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA74" t="n">
         <v>3453</v>
       </c>
@@ -9841,6 +10050,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB78" t="n">
         <v>24381</v>
       </c>
@@ -10108,6 +10322,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD80" t="n">
         <v>17223</v>
       </c>
@@ -10178,6 +10397,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB81" t="n">
         <v>12201</v>
       </c>
@@ -10295,6 +10519,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA83" t="n">
         <v>8329</v>
       </c>
@@ -10553,10 +10782,36 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T86" t="n">
+        <v>10884</v>
+      </c>
+      <c r="V86" t="n">
+        <v>12300</v>
+      </c>
+      <c r="W86" t="n">
+        <v>13827</v>
+      </c>
+      <c r="X86" t="n">
+        <v>15354</v>
+      </c>
       <c r="Y86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA86" t="n">
+        <v>17004</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>19420</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>24240</v>
       </c>
       <c r="AD86" t="n">
         <v>26060</v>
@@ -10603,6 +10858,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA87" t="n">
         <v>8279</v>
       </c>
@@ -10815,6 +11075,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z89" t="n">
+        <v>13844</v>
+      </c>
       <c r="AA89" t="n">
         <v>8279</v>
       </c>
@@ -11589,7 +11852,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T96" t="n">
+        <v>9599</v>
+      </c>
+      <c r="W96" t="n">
+        <v>9968</v>
+      </c>
       <c r="Y96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -11649,6 +11923,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD97" t="n">
         <v>11471</v>
       </c>
@@ -11679,6 +11958,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB98" t="n">
         <v>10690</v>
       </c>
@@ -11935,6 +12219,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD100" t="n">
         <v>10752</v>
       </c>
@@ -12162,6 +12451,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA103" t="n">
         <v>1633</v>
       </c>
@@ -12445,7 +12739,24 @@
           <t>Semi-Marathon de Boulogne-Billancourt</t>
         </is>
       </c>
+      <c r="U106" t="n">
+        <v>6483</v>
+      </c>
+      <c r="V106" t="n">
+        <v>7452</v>
+      </c>
+      <c r="W106" t="n">
+        <v>7897</v>
+      </c>
+      <c r="X106" t="n">
+        <v>8128</v>
+      </c>
       <c r="Y106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -12606,6 +12917,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB108" t="n">
         <v>31292</v>
       </c>
@@ -12907,6 +13223,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB111" t="n">
         <v>16689</v>
       </c>
@@ -12953,6 +13274,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD112" t="n">
         <v>14747</v>
       </c>
@@ -13068,6 +13394,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB113" t="n">
         <v>9126</v>
       </c>
@@ -13189,6 +13520,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD114" t="n">
         <v>10178</v>
       </c>
@@ -13244,6 +13580,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA115" t="n">
         <v>5762</v>
       </c>
@@ -13616,6 +13957,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA120" t="n">
         <v>21018</v>
       </c>
@@ -13934,6 +14280,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA124" t="n">
         <v>16750</v>
       </c>
@@ -14036,6 +14387,9 @@
       <c r="AA125" t="n">
         <v>6495</v>
       </c>
+      <c r="AB125" t="n">
+        <v>7791</v>
+      </c>
       <c r="AC125" t="n">
         <v>6787</v>
       </c>
@@ -14169,6 +14523,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA127" t="n">
         <v>8874</v>
       </c>
@@ -14364,6 +14723,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA129" t="n">
         <v>15076</v>
       </c>
@@ -14567,6 +14931,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA132" t="n">
         <v>12008</v>
       </c>
@@ -14954,6 +15323,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA137" t="n">
         <v>8470</v>
       </c>
@@ -15161,6 +15535,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA140" t="n">
         <v>17260</v>
       </c>
@@ -15231,6 +15610,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA141" t="n">
         <v>8425</v>
       </c>
@@ -15398,6 +15782,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA143" t="n">
         <v>9851</v>
       </c>
@@ -15580,6 +15969,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA145" t="n">
         <v>11520</v>
       </c>
@@ -15830,6 +16224,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA148" t="n">
         <v>10060</v>
       </c>
@@ -16148,7 +16547,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T152" t="n">
+        <v>1473</v>
+      </c>
       <c r="Y152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -16192,6 +16599,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA153" t="n">
         <v>13343</v>
       </c>
@@ -16364,6 +16776,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AC155" t="n">
         <v>9543</v>
       </c>
@@ -16423,6 +16840,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA156" t="n">
         <v>18272</v>
       </c>
@@ -16699,6 +17121,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA159" t="n">
         <v>7941</v>
       </c>
@@ -17065,6 +17492,21 @@
           <t>Beijing Marathon</t>
         </is>
       </c>
+      <c r="T164" t="n">
+        <v>26294</v>
+      </c>
+      <c r="U164" t="n">
+        <v>28957</v>
+      </c>
+      <c r="V164" t="n">
+        <v>28365</v>
+      </c>
+      <c r="W164" t="n">
+        <v>28235</v>
+      </c>
+      <c r="X164" t="n">
+        <v>29491</v>
+      </c>
       <c r="Y164" t="inlineStr">
         <is>
           <t>-</t>
@@ -17152,10 +17594,44 @@
           <t>x</t>
         </is>
       </c>
+      <c r="P165" t="n">
+        <v>26175</v>
+      </c>
+      <c r="T165" t="n">
+        <v>31529</v>
+      </c>
+      <c r="U165" t="n">
+        <v>29431</v>
+      </c>
+      <c r="V165" t="n">
+        <v>31315</v>
+      </c>
+      <c r="W165" t="n">
+        <v>29314</v>
+      </c>
+      <c r="X165" t="n">
+        <v>31594</v>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z165" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB165" t="n">
+        <v>24036</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>29128</v>
       </c>
       <c r="AD165" t="n">
         <v>26175</v>
@@ -17471,6 +17947,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA169" t="n">
         <v>8174</v>
       </c>
@@ -17710,6 +18191,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA172" t="n">
         <v>5671</v>
       </c>
@@ -17908,6 +18394,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA174" t="n">
         <v>4672</v>
       </c>
@@ -17947,6 +18438,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA175" t="n">
         <v>5202</v>
       </c>
@@ -17986,6 +18482,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z176" t="n">
+        <v>15567</v>
+      </c>
       <c r="AA176" t="n">
         <v>13062</v>
       </c>
@@ -18087,6 +18586,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AA177" t="n">
         <v>2185</v>
       </c>
@@ -18171,6 +18675,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD178" t="n">
         <v>12146</v>
       </c>
@@ -18246,6 +18755,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD179" t="n">
         <v>13035</v>
       </c>
@@ -18321,6 +18835,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD180" t="n">
         <v>10870</v>
       </c>
@@ -18350,6 +18869,11 @@
         <v>18892</v>
       </c>
       <c r="Y181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3879,6 +3879,9 @@
           <t>Medio Maraton de Sevilla</t>
         </is>
       </c>
+      <c r="V2" t="n">
+        <v>8001</v>
+      </c>
       <c r="Z2" t="inlineStr">
         <is>
           <t>-</t>
@@ -3918,6 +3921,18 @@
           <t>Walt Disney World Marathon Weekend</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>21991</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20243</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21495</v>
+      </c>
+      <c r="U3" t="n">
+        <v>21495</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>-</t>
@@ -3971,6 +3986,36 @@
           <t>x</t>
         </is>
       </c>
+      <c r="O4" t="n">
+        <v>9917</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9331</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9397</v>
+      </c>
+      <c r="R4" t="n">
+        <v>10074</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10498</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11653</v>
+      </c>
+      <c r="U4" t="n">
+        <v>11086</v>
+      </c>
+      <c r="V4" t="n">
+        <v>11398</v>
+      </c>
+      <c r="W4" t="n">
+        <v>11026</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6686</v>
+      </c>
       <c r="AC4" t="n">
         <v>13715</v>
       </c>
@@ -4218,9 +4263,17 @@
           <t>x</t>
         </is>
       </c>
+      <c r="W7" t="n">
+        <v>5382</v>
+      </c>
       <c r="X7" t="n">
         <v>7803</v>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AB7" t="n">
         <v>7238</v>
       </c>
@@ -4999,6 +5052,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="P15" t="n">
+        <v>33257</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25251</v>
+      </c>
+      <c r="T15" t="n">
+        <v>23100</v>
+      </c>
+      <c r="U15" t="n">
+        <v>22086</v>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
           <t>-</t>
@@ -5289,6 +5354,12 @@
           <t>x</t>
         </is>
       </c>
+      <c r="AA18" t="n">
+        <v>3917</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5200</v>
+      </c>
       <c r="AD18" t="n">
         <v>5732</v>
       </c>
@@ -5643,6 +5714,9 @@
       <c r="P23" t="n">
         <v>9485</v>
       </c>
+      <c r="R23" t="n">
+        <v>9683</v>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>-</t>
@@ -6158,6 +6232,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="P29" t="n">
+        <v>12260</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>13733</v>
+      </c>
+      <c r="R29" t="n">
+        <v>15943</v>
+      </c>
       <c r="Y29" t="inlineStr">
         <is>
           <t>-</t>
@@ -6329,6 +6412,9 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U32" t="n">
+        <v>18094</v>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
           <t>-</t>
@@ -6523,6 +6609,9 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U35" t="n">
+        <v>14498</v>
+      </c>
       <c r="Y35" t="inlineStr">
         <is>
           <t>-</t>
@@ -7461,6 +7550,24 @@
           <t>Ukrop's Monument Avenue 10K</t>
         </is>
       </c>
+      <c r="O47" t="n">
+        <v>30854</v>
+      </c>
+      <c r="P47" t="n">
+        <v>33364</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>33325</v>
+      </c>
+      <c r="R47" t="n">
+        <v>32239</v>
+      </c>
+      <c r="S47" t="n">
+        <v>27468</v>
+      </c>
+      <c r="T47" t="n">
+        <v>26472</v>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
           <t>-</t>
@@ -7773,6 +7880,24 @@
           <t>x</t>
         </is>
       </c>
+      <c r="P52" t="n">
+        <v>22015</v>
+      </c>
+      <c r="S52" t="n">
+        <v>23799</v>
+      </c>
+      <c r="T52" t="n">
+        <v>18331</v>
+      </c>
+      <c r="U52" t="n">
+        <v>18144</v>
+      </c>
+      <c r="W52" t="n">
+        <v>18820</v>
+      </c>
+      <c r="X52" t="n">
+        <v>17233</v>
+      </c>
       <c r="Y52" t="inlineStr">
         <is>
           <t>-</t>
@@ -7782,6 +7907,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>12359</v>
       </c>
       <c r="AD52" t="n">
         <v>10776</v>
@@ -8496,6 +8624,18 @@
           <t>IU Health 500 Festival Mini-Marathon</t>
         </is>
       </c>
+      <c r="P60" t="n">
+        <v>30659</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25524</v>
+      </c>
+      <c r="T60" t="n">
+        <v>22466</v>
+      </c>
+      <c r="U60" t="n">
+        <v>24768</v>
+      </c>
       <c r="Y60" t="inlineStr">
         <is>
           <t>-</t>
@@ -8581,6 +8721,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="P61" t="n">
+        <v>17194</v>
+      </c>
+      <c r="S61" t="n">
+        <v>16890</v>
+      </c>
+      <c r="T61" t="n">
+        <v>14153</v>
+      </c>
+      <c r="U61" t="n">
+        <v>16814</v>
+      </c>
       <c r="Y61" t="inlineStr">
         <is>
           <t>-</t>
@@ -9076,12 +9228,117 @@
           <t>Broløbet - The Bridge Run</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9462,6 +9719,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AC71" t="n">
+        <v>20534</v>
+      </c>
       <c r="AD71" t="n">
         <v>21011</v>
       </c>
@@ -10392,6 +10652,9 @@
           <t>x</t>
         </is>
       </c>
+      <c r="X81" t="n">
+        <v>19563</v>
+      </c>
       <c r="Y81" t="inlineStr">
         <is>
           <t>-</t>
@@ -10401,6 +10664,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA81" t="n">
+        <v>13500</v>
       </c>
       <c r="AB81" t="n">
         <v>12201</v>
@@ -13575,6 +13841,9 @@
       <c r="W115" t="n">
         <v>9315</v>
       </c>
+      <c r="X115" t="n">
+        <v>10169</v>
+      </c>
       <c r="Y115" t="inlineStr">
         <is>
           <t>-</t>
@@ -16547,9 +16816,36 @@
           <t>x</t>
         </is>
       </c>
+      <c r="O152" t="n">
+        <v>2333</v>
+      </c>
+      <c r="P152" t="n">
+        <v>2290</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>2345</v>
+      </c>
+      <c r="R152" t="n">
+        <v>2561</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1358</v>
+      </c>
       <c r="T152" t="n">
         <v>1473</v>
       </c>
+      <c r="U152" t="n">
+        <v>1674</v>
+      </c>
+      <c r="V152" t="n">
+        <v>1480</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1493</v>
+      </c>
+      <c r="X152" t="n">
+        <v>1314</v>
+      </c>
       <c r="Y152" t="inlineStr">
         <is>
           <t>-</t>
@@ -16559,6 +16855,12 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA152" t="n">
+        <v>2039</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>2088</v>
       </c>
       <c r="AC152" t="n">
         <v>8915</v>
@@ -18491,6 +18793,11 @@
       <c r="AB176" t="n">
         <v>14605</v>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AD176" t="n">
         <v>17488</v>
       </c>
@@ -18670,6 +18977,16 @@
           <t>x</t>
         </is>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y178" t="inlineStr">
         <is>
           <t>-</t>
@@ -18750,6 +19067,16 @@
           <t>x</t>
         </is>
       </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y179" t="inlineStr">
         <is>
           <t>-</t>
@@ -18830,6 +19157,16 @@
           <t>x</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y180" t="inlineStr">
         <is>
           <t>-</t>
@@ -18865,6 +19202,21 @@
           <t>Standard Chartered Hong Kong Marathon</t>
         </is>
       </c>
+      <c r="R181" t="n">
+        <v>6124</v>
+      </c>
+      <c r="S181" t="n">
+        <v>5604</v>
+      </c>
+      <c r="U181" t="n">
+        <v>12857</v>
+      </c>
+      <c r="V181" t="n">
+        <v>15028</v>
+      </c>
+      <c r="W181" t="n">
+        <v>15358</v>
+      </c>
       <c r="X181" t="n">
         <v>18892</v>
       </c>
@@ -18877,6 +19229,20 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB181" t="n">
+        <v>4975</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>11877</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>13375</v>
       </c>
       <c r="AE181" t="n">
         <v>18575</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4891,6 +4891,21 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T13" t="n">
+        <v>11472</v>
+      </c>
+      <c r="U13" t="n">
+        <v>12211</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13149</v>
+      </c>
+      <c r="W13" t="n">
+        <v>16449</v>
+      </c>
+      <c r="X13" t="n">
+        <v>18516</v>
+      </c>
       <c r="Y13" t="inlineStr">
         <is>
           <t>-</t>
@@ -4900,6 +4915,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>8707</v>
       </c>
       <c r="AB13" t="n">
         <v>13706</v>
@@ -6279,6 +6297,11 @@
       <c r="W30" t="n">
         <v>10528</v>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
           <t>-</t>
@@ -6550,6 +6573,15 @@
           <t>Generali Prague Half Marathon</t>
         </is>
       </c>
+      <c r="T34" t="n">
+        <v>9065</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9867</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9084</v>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
           <t>-</t>
@@ -6794,6 +6826,15 @@
           <t>TCS London Marathon</t>
         </is>
       </c>
+      <c r="L38" t="n">
+        <v>35667</v>
+      </c>
+      <c r="M38" t="n">
+        <v>34212</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35266</v>
+      </c>
       <c r="O38" t="n">
         <v>36549</v>
       </c>
@@ -6844,6 +6885,9 @@
       <c r="AD38" t="n">
         <v>56640</v>
       </c>
+      <c r="AE38" t="n">
+        <v>58000</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6932,6 +6976,18 @@
           <t>Vancouver Sun Run</t>
         </is>
       </c>
+      <c r="Q40" t="n">
+        <v>48904</v>
+      </c>
+      <c r="T40" t="n">
+        <v>39045</v>
+      </c>
+      <c r="V40" t="n">
+        <v>41924</v>
+      </c>
+      <c r="W40" t="n">
+        <v>41645</v>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
           <t>-</t>
@@ -6973,6 +7029,24 @@
           <t>Boston Marathon</t>
         </is>
       </c>
+      <c r="L41" t="n">
+        <v>20302</v>
+      </c>
+      <c r="M41" t="n">
+        <v>21963</v>
+      </c>
+      <c r="N41" t="n">
+        <v>22822</v>
+      </c>
+      <c r="O41" t="n">
+        <v>22721</v>
+      </c>
+      <c r="P41" t="n">
+        <v>23879</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>21554</v>
+      </c>
       <c r="R41" t="n">
         <v>17584</v>
       </c>
@@ -7221,6 +7295,21 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T43" t="n">
+        <v>7986</v>
+      </c>
+      <c r="U43" t="n">
+        <v>9411</v>
+      </c>
+      <c r="V43" t="n">
+        <v>8686</v>
+      </c>
+      <c r="W43" t="n">
+        <v>9460</v>
+      </c>
+      <c r="X43" t="n">
+        <v>18185</v>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
           <t>-</t>
@@ -7501,6 +7590,30 @@
           <t>Statesman Capitol 10K</t>
         </is>
       </c>
+      <c r="O46" t="n">
+        <v>20146</v>
+      </c>
+      <c r="P46" t="n">
+        <v>22932</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>22477</v>
+      </c>
+      <c r="R46" t="n">
+        <v>18382</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15959</v>
+      </c>
+      <c r="T46" t="n">
+        <v>18428</v>
+      </c>
+      <c r="U46" t="n">
+        <v>20527</v>
+      </c>
+      <c r="V46" t="n">
+        <v>21390</v>
+      </c>
       <c r="W46" t="n">
         <v>18751</v>
       </c>
@@ -7519,6 +7632,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA46" t="n">
+        <v>15256</v>
+      </c>
       <c r="AB46" t="n">
         <v>22059</v>
       </c>
@@ -9792,6 +9908,21 @@
           <t>x</t>
         </is>
       </c>
+      <c r="O72" t="n">
+        <v>5935</v>
+      </c>
+      <c r="P72" t="n">
+        <v>6521</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>20102</v>
+      </c>
+      <c r="R72" t="n">
+        <v>15801</v>
+      </c>
+      <c r="S72" t="n">
+        <v>14299</v>
+      </c>
       <c r="Y72" t="inlineStr">
         <is>
           <t>-</t>
@@ -10086,6 +10217,9 @@
           <t>BMW Berlin Marathon</t>
         </is>
       </c>
+      <c r="L76" t="n">
+        <v>32473</v>
+      </c>
       <c r="M76" t="n">
         <v>35783</v>
       </c>
@@ -10774,6 +10908,12 @@
           <t>Life Time Chicago Half Marathon &amp; 5K</t>
         </is>
       </c>
+      <c r="U83" t="n">
+        <v>8529</v>
+      </c>
+      <c r="V83" t="n">
+        <v>7943</v>
+      </c>
       <c r="W83" t="n">
         <v>13224</v>
       </c>
@@ -11721,6 +11861,9 @@
       <c r="Z92" t="n">
         <v>5876</v>
       </c>
+      <c r="AA92" t="n">
+        <v>11062</v>
+      </c>
       <c r="AB92" t="n">
         <v>11065</v>
       </c>
@@ -13956,6 +14099,21 @@
       </c>
       <c r="W117" t="n">
         <v>9797</v>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AA117" t="n">
         <v>5553</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="10K" sheetId="1" state="visible" r:id="rId1"/>
@@ -6885,9 +6885,6 @@
       <c r="AD38" t="n">
         <v>56640</v>
       </c>
-      <c r="AE38" t="n">
-        <v>58000</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7684,6 +7681,15 @@
       <c r="T47" t="n">
         <v>26472</v>
       </c>
+      <c r="V47" t="n">
+        <v>21954</v>
+      </c>
+      <c r="W47" t="n">
+        <v>21295</v>
+      </c>
+      <c r="X47" t="n">
+        <v>20167</v>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
           <t>-</t>
@@ -7693,6 +7699,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>12129</v>
       </c>
       <c r="AB47" t="n">
         <v>14985</v>
@@ -9933,6 +9942,9 @@
           <t>-</t>
         </is>
       </c>
+      <c r="AA72" t="n">
+        <v>7376</v>
+      </c>
       <c r="AB72" t="n">
         <v>13368</v>
       </c>
@@ -11934,6 +11946,9 @@
         <is>
           <t>x</t>
         </is>
+      </c>
+      <c r="X93" t="n">
+        <v>15867</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7806,6 +7806,12 @@
           <t>Vienna City Half Marathon</t>
         </is>
       </c>
+      <c r="V49" t="n">
+        <v>8031</v>
+      </c>
+      <c r="X49" t="n">
+        <v>7773</v>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
           <t>-</t>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE181"/>
+  <dimension ref="A1:AE182"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -19425,6 +19425,129 @@
       </c>
       <c r="AE181" t="n">
         <v>18575</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Standard Chartered Dubai Marathon</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M182" t="n">
+        <v>797</v>
+      </c>
+      <c r="N182" t="n">
+        <v>889</v>
+      </c>
+      <c r="O182" t="n">
+        <v>1314</v>
+      </c>
+      <c r="P182" t="n">
+        <v>1305</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>1576</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1899</v>
+      </c>
+      <c r="S182" t="n">
+        <v>2156</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1970</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2030</v>
+      </c>
+      <c r="V182" t="n">
+        <v>1914</v>
+      </c>
+      <c r="W182" t="n">
+        <v>1997</v>
+      </c>
+      <c r="X182" t="n">
+        <v>1824</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>1854</v>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB182" t="n">
+        <v>1448</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1458</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2687</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE182"/>
+  <dimension ref="A1:AE186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -19548,6 +19548,435 @@
       </c>
       <c r="AE182" t="n">
         <v>2687</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Marseille-Cassis AG2R La Mondiale</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R183" t="n">
+        <v>14481</v>
+      </c>
+      <c r="S183" t="n">
+        <v>14424</v>
+      </c>
+      <c r="U183" t="n">
+        <v>14228</v>
+      </c>
+      <c r="V183" t="n">
+        <v>16070</v>
+      </c>
+      <c r="W183" t="n">
+        <v>18755</v>
+      </c>
+      <c r="X183" t="n">
+        <v>18204</v>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z183" t="n">
+        <v>12656</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>18071</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>19183</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>19805</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>19402</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Harmonie Mutuelle 20km de Paris</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R184" t="n">
+        <v>22964</v>
+      </c>
+      <c r="S184" t="n">
+        <v>23878</v>
+      </c>
+      <c r="V184" t="n">
+        <v>25235</v>
+      </c>
+      <c r="W184" t="n">
+        <v>26281</v>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z184" t="n">
+        <v>9276</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>17713</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>22056</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>26470</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>28985</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Abalone Marathon de Nantes</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V185" t="n">
+        <v>2840</v>
+      </c>
+      <c r="W185" t="n">
+        <v>2969</v>
+      </c>
+      <c r="X185" t="n">
+        <v>3228</v>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA185" t="n">
+        <v>2955</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>2750</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>3468</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Harmonie Mutuelle Marathon 10-20K Tours</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z186" t="n">
+        <v>1603</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>2187</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>6512</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>7580</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>7778</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE186"/>
+  <dimension ref="A1:AE189"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -19977,6 +19977,347 @@
       </c>
       <c r="AD186" t="n">
         <v>7778</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Harmonie Mutuelle Toulouse Metropole Run Experience</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC187" t="n">
+        <v>10745</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>28695</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Marathon de Tours</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z188" t="n">
+        <v>691</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>1123</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>20km de Tours</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z189" t="n">
+        <v>1603</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>2187</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>2389</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>3115</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>3107</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE189"/>
+  <dimension ref="A1:AE191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -20318,6 +20318,243 @@
       </c>
       <c r="AD189" t="n">
         <v>3107</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Harmonie Mutuelle Toulouse Metropole Run Experience</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC190" t="n">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Harmonie Mutuelle Toulouse Metropole Run Experience</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -20099,7 +20099,7 @@
         <v>10745</v>
       </c>
       <c r="AD187" t="n">
-        <v>28695</v>
+        <v>15669</v>
       </c>
     </row>
     <row r="188">
@@ -20439,6 +20439,9 @@
       <c r="AC190" t="n">
         <v>3664</v>
       </c>
+      <c r="AD190" t="n">
+        <v>5031</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -20555,6 +20558,9 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="AD191" t="n">
+        <v>7995</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE191"/>
+  <dimension ref="A1:AE192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -20561,6 +20561,122 @@
       </c>
       <c r="AD191" t="n">
         <v>7995</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Run in Lyon</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K192" t="n">
+        <v>2779</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2442</v>
+      </c>
+      <c r="M192" t="n">
+        <v>2236</v>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O192" t="n">
+        <v>828</v>
+      </c>
+      <c r="P192" t="n">
+        <v>943</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>923</v>
+      </c>
+      <c r="R192" t="n">
+        <v>1334</v>
+      </c>
+      <c r="S192" t="n">
+        <v>1569</v>
+      </c>
+      <c r="T192" t="n">
+        <v>2065</v>
+      </c>
+      <c r="U192" t="n">
+        <v>2486</v>
+      </c>
+      <c r="V192" t="n">
+        <v>2497</v>
+      </c>
+      <c r="W192" t="n">
+        <v>2491</v>
+      </c>
+      <c r="X192" t="n">
+        <v>2551</v>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z192" t="n">
+        <v>1295</v>
+      </c>
+      <c r="AA192" t="n">
+        <v>1909</v>
+      </c>
+      <c r="AB192" t="n">
+        <v>2788</v>
+      </c>
+      <c r="AC192" t="n">
+        <v>3742</v>
+      </c>
+      <c r="AD192" t="n">
+        <v>5145</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -19885,7 +19885,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Harmonie Mutuelle Marathon 10-20K Tours</t>
+          <t>Harmonie Mutuelle 10km de Tours</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Marathon de Tours</t>
+          <t>Harmonie Mutuelle Marathon de Tours</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20km de Tours</t>
+          <t>Harmonie Mutuelle 20k de Tours</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE192"/>
+  <dimension ref="A1:AE195"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -20677,6 +20677,287 @@
       </c>
       <c r="AD192" t="n">
         <v>5145</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SEMI</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>S'MI Ouest-France Semi</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>3350</v>
+      </c>
+      <c r="R193" t="n">
+        <v>3713</v>
+      </c>
+      <c r="T193" t="n">
+        <v>3288</v>
+      </c>
+      <c r="U193" t="n">
+        <v>2928</v>
+      </c>
+      <c r="V193" t="n">
+        <v>2708</v>
+      </c>
+      <c r="W193" t="n">
+        <v>3294</v>
+      </c>
+      <c r="X193" t="n">
+        <v>3124</v>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA193" t="n">
+        <v>2495</v>
+      </c>
+      <c r="AB193" t="n">
+        <v>3630</v>
+      </c>
+      <c r="AC193" t="n">
+        <v>5630</v>
+      </c>
+      <c r="AD193" t="n">
+        <v>5264</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>10km CMB</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>5752</v>
+      </c>
+      <c r="T194" t="n">
+        <v>5711</v>
+      </c>
+      <c r="U194" t="n">
+        <v>5250</v>
+      </c>
+      <c r="V194" t="n">
+        <v>5127</v>
+      </c>
+      <c r="W194" t="n">
+        <v>5885</v>
+      </c>
+      <c r="X194" t="n">
+        <v>5673</v>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z194" t="n">
+        <v>3217</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>4608</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>5893</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>6544</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>8067</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AUTRE</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>5km Harmonie Mutuelle</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V195" t="n">
+        <v>652</v>
+      </c>
+      <c r="W195" t="n">
+        <v>846</v>
+      </c>
+      <c r="X195" t="n">
+        <v>846</v>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z195" t="n">
+        <v>472</v>
+      </c>
+      <c r="AA195" t="n">
+        <v>769</v>
+      </c>
+      <c r="AB195" t="n">
+        <v>1380</v>
+      </c>
+      <c r="AC195" t="n">
+        <v>2418</v>
+      </c>
+      <c r="AD195" t="n">
+        <v>4043</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5835,6 +5835,9 @@
       <c r="AD24" t="n">
         <v>34734</v>
       </c>
+      <c r="AE24" t="n">
+        <v>36587</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6134,6 +6137,9 @@
       <c r="AD27" t="n">
         <v>21893</v>
       </c>
+      <c r="AE27" t="n">
+        <v>30010</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6551,6 +6557,9 @@
       <c r="AD33" t="n">
         <v>14605</v>
       </c>
+      <c r="AE33" t="n">
+        <v>22562</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6604,6 +6613,9 @@
       <c r="AD34" t="n">
         <v>14144</v>
       </c>
+      <c r="AE34" t="n">
+        <v>15623</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16173,6 +16185,9 @@
       <c r="AD142" t="n">
         <v>15415</v>
       </c>
+      <c r="AE142" t="n">
+        <v>15243</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16343,6 +16358,9 @@
       </c>
       <c r="AD144" t="n">
         <v>1959</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2435</v>
       </c>
     </row>
     <row r="145">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6278,6 +6278,9 @@
       <c r="AD29" t="n">
         <v>20918</v>
       </c>
+      <c r="AE29" t="n">
+        <v>23392</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6922,6 +6922,9 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="P39" t="n">
+        <v>31133</v>
+      </c>
       <c r="Q39" t="n">
         <v>32981</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6922,6 +6922,9 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="O39" t="n">
+        <v>30939</v>
+      </c>
       <c r="P39" t="n">
         <v>31133</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6922,6 +6922,9 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="N39" t="n">
+        <v>30336</v>
+      </c>
       <c r="O39" t="n">
         <v>30939</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6922,6 +6922,9 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="M39" t="n">
+        <v>28656</v>
+      </c>
       <c r="N39" t="n">
         <v>30336</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6922,6 +6922,27 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>22318</v>
+      </c>
+      <c r="G39" t="n">
+        <v>16017</v>
+      </c>
+      <c r="H39" t="n">
+        <v>28997</v>
+      </c>
+      <c r="I39" t="n">
+        <v>29700</v>
+      </c>
+      <c r="J39" t="n">
+        <v>28857</v>
+      </c>
+      <c r="K39" t="n">
+        <v>30639</v>
+      </c>
+      <c r="L39" t="n">
+        <v>26926</v>
+      </c>
       <c r="M39" t="n">
         <v>28656</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6922,6 +6922,9 @@
           <t>Schneider Electric Marathon de Paris</t>
         </is>
       </c>
+      <c r="E39" t="n">
+        <v>27596</v>
+      </c>
       <c r="F39" t="n">
         <v>22318</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE195"/>
+  <dimension ref="A1:AE203"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -21015,6 +21015,215 @@
       </c>
       <c r="AD195" t="n">
         <v>4043</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Décembre</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Lidl S. Silvestre Cidade do Porto</t>
+        </is>
+      </c>
+      <c r="AB196" t="n">
+        <v>8809</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>11259</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>13313</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>TREK Singelloop Utrecht</t>
+        </is>
+      </c>
+      <c r="AD197" t="n">
+        <v>14380</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Barcelone</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Vueling Cursa Bombers de Barcelona</t>
+        </is>
+      </c>
+      <c r="AA198" t="n">
+        <v>11084</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ljubljana</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NLB Ljubljana Marathon 10K</t>
+        </is>
+      </c>
+      <c r="AD199" t="n">
+        <v>7382</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Breda</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>AMGEN Singelloop Breda 10km</t>
+        </is>
+      </c>
+      <c r="AD200" t="n">
+        <v>7609</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Saucony Run Shoreditch 10K</t>
+        </is>
+      </c>
+      <c r="AD201" t="n">
+        <v>7599</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Geneve</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Generali Geneve Marathon 10km</t>
+        </is>
+      </c>
+      <c r="AE202" t="n">
+        <v>5005</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Zurich Rock 'n' Roll Running Series Madrid 10K</t>
+        </is>
+      </c>
+      <c r="AC203" t="n">
+        <v>7207</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>7194</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10376,13 +10376,7 @@
       <c r="S77" t="n">
         <v>41615</v>
       </c>
-      <c r="U77" t="n">
-        <v>41615</v>
-      </c>
       <c r="V77" t="n">
-        <v>43656</v>
-      </c>
-      <c r="W77" t="n">
         <v>43656</v>
       </c>
       <c r="X77" t="n">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10376,8 +10376,14 @@
       <c r="S77" t="n">
         <v>41615</v>
       </c>
+      <c r="U77" t="n">
+        <v>41334</v>
+      </c>
       <c r="V77" t="n">
         <v>43656</v>
+      </c>
+      <c r="W77" t="n">
+        <v>43596</v>
       </c>
       <c r="X77" t="n">
         <v>43768</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8965,6 +8965,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U62" t="n">
+        <v>26057</v>
+      </c>
+      <c r="V62" t="n">
+        <v>17172</v>
+      </c>
+      <c r="W62" t="n">
+        <v>18700</v>
+      </c>
+      <c r="X62" t="n">
+        <v>18258</v>
+      </c>
       <c r="Y62" t="inlineStr">
         <is>
           <t>-</t>
@@ -9094,6 +9106,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="V63" t="n">
+        <v>5787</v>
+      </c>
+      <c r="W63" t="n">
+        <v>4811</v>
+      </c>
+      <c r="X63" t="n">
+        <v>4521</v>
+      </c>
       <c r="Y63" t="inlineStr">
         <is>
           <t>-</t>
@@ -9141,6 +9162,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U64" t="n">
+        <v>7088</v>
+      </c>
+      <c r="V64" t="n">
+        <v>7476</v>
+      </c>
+      <c r="W64" t="n">
+        <v>7030</v>
+      </c>
+      <c r="X64" t="n">
+        <v>6828</v>
+      </c>
       <c r="Y64" t="inlineStr">
         <is>
           <t>-</t>
@@ -10376,6 +10409,9 @@
       <c r="S77" t="n">
         <v>41615</v>
       </c>
+      <c r="T77" t="n">
+        <v>40906</v>
+      </c>
       <c r="U77" t="n">
         <v>41334</v>
       </c>
@@ -18480,6 +18516,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="T169" t="n">
+        <v>2719</v>
+      </c>
+      <c r="U169" t="n">
+        <v>3282</v>
+      </c>
+      <c r="V169" t="n">
+        <v>2968</v>
+      </c>
       <c r="Y169" t="inlineStr">
         <is>
           <t>-</t>
@@ -18724,6 +18769,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U172" t="n">
+        <v>13079</v>
+      </c>
+      <c r="V172" t="n">
+        <v>8885</v>
+      </c>
+      <c r="W172" t="n">
+        <v>7898</v>
+      </c>
+      <c r="X172" t="n">
+        <v>7867</v>
+      </c>
       <c r="Y172" t="inlineStr">
         <is>
           <t>-</t>
@@ -18927,6 +18984,18 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U174" t="n">
+        <v>9681</v>
+      </c>
+      <c r="V174" t="n">
+        <v>11189</v>
+      </c>
+      <c r="W174" t="n">
+        <v>10644</v>
+      </c>
+      <c r="X174" t="n">
+        <v>10170</v>
+      </c>
       <c r="Y174" t="inlineStr">
         <is>
           <t>-</t>
@@ -19014,6 +19083,18 @@
         <is>
           <t>AJ Bell Great South Run</t>
         </is>
+      </c>
+      <c r="U176" t="n">
+        <v>15642</v>
+      </c>
+      <c r="V176" t="n">
+        <v>16305</v>
+      </c>
+      <c r="W176" t="n">
+        <v>15840</v>
+      </c>
+      <c r="X176" t="n">
+        <v>15979</v>
       </c>
       <c r="Y176" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7002,6 +7002,9 @@
       <c r="AD39" t="n">
         <v>55499</v>
       </c>
+      <c r="AE39" t="n">
+        <v>57464</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3109,6 +3109,9 @@
       <c r="AB14" t="n">
         <v>55499</v>
       </c>
+      <c r="AC14" t="n">
+        <v>57464</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21669,6 +21672,9 @@
       <c r="AC4" t="n">
         <v>55499</v>
       </c>
+      <c r="AD4" t="n">
+        <v>57464</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="10K" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="21K" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="42K" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ALL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BIGGEST EVENTS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10K" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21K" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42K" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIGGEST EVENTS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -7841,6 +7841,9 @@
       <c r="AD48" t="n">
         <v>17867</v>
       </c>
+      <c r="AE48" t="n">
+        <v>15814</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6844,6 +6844,27 @@
           <t>TCS London Marathon</t>
         </is>
       </c>
+      <c r="E38" t="n">
+        <v>31698</v>
+      </c>
+      <c r="F38" t="n">
+        <v>30318</v>
+      </c>
+      <c r="G38" t="n">
+        <v>32950</v>
+      </c>
+      <c r="H38" t="n">
+        <v>32324</v>
+      </c>
+      <c r="I38" t="n">
+        <v>32012</v>
+      </c>
+      <c r="J38" t="n">
+        <v>35300</v>
+      </c>
+      <c r="K38" t="n">
+        <v>33250</v>
+      </c>
       <c r="L38" t="n">
         <v>35667</v>
       </c>
@@ -10346,6 +10367,27 @@
           <t>BMW Berlin Marathon</t>
         </is>
       </c>
+      <c r="E76" t="n">
+        <v>22879</v>
+      </c>
+      <c r="F76" t="n">
+        <v>25792</v>
+      </c>
+      <c r="G76" t="n">
+        <v>25286</v>
+      </c>
+      <c r="H76" t="n">
+        <v>30709</v>
+      </c>
+      <c r="I76" t="n">
+        <v>28023</v>
+      </c>
+      <c r="J76" t="n">
+        <v>30382</v>
+      </c>
+      <c r="K76" t="n">
+        <v>30190</v>
+      </c>
       <c r="L76" t="n">
         <v>32473</v>
       </c>
@@ -11114,11 +11156,23 @@
       <c r="E84" t="n">
         <v>27956</v>
       </c>
+      <c r="F84" t="n">
+        <v>28390</v>
+      </c>
+      <c r="G84" t="n">
+        <v>31093</v>
+      </c>
+      <c r="H84" t="n">
+        <v>32395</v>
+      </c>
       <c r="I84" t="n">
         <v>33125</v>
       </c>
       <c r="J84" t="n">
         <v>33125</v>
+      </c>
+      <c r="K84" t="n">
+        <v>33618</v>
       </c>
       <c r="L84" t="n">
         <v>25534</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5280,6 +5280,9 @@
           <t>Kagawa Marugame International Half Marathon</t>
         </is>
       </c>
+      <c r="Y17" t="n">
+        <v>943</v>
+      </c>
       <c r="AE17" t="n">
         <v>9638</v>
       </c>
@@ -18419,6 +18422,9 @@
         <is>
           <t>Dam tot Damloop</t>
         </is>
+      </c>
+      <c r="S167" t="n">
+        <v>36350</v>
       </c>
       <c r="U167" t="n">
         <v>33856</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -5586,9 +5586,6 @@
       <c r="AC20" t="n">
         <v>35443</v>
       </c>
-      <c r="AD20" t="n">
-        <v>36204</v>
-      </c>
       <c r="AE20" t="n">
         <v>37244</v>
       </c>
@@ -7082,9 +7079,6 @@
       <c r="AC40" t="n">
         <v>34990</v>
       </c>
-      <c r="AD40" t="n">
-        <v>39385</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10788,9 +10782,6 @@
       <c r="AC79" t="n">
         <v>22903</v>
       </c>
-      <c r="AD79" t="n">
-        <v>24703</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14928,9 +14919,6 @@
       <c r="AC124" t="n">
         <v>19748</v>
       </c>
-      <c r="AD124" t="n">
-        <v>21899</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15371,9 +15359,6 @@
       <c r="AC129" t="n">
         <v>17059</v>
       </c>
-      <c r="AD129" t="n">
-        <v>20019</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15681,9 +15666,6 @@
       <c r="AC133" t="n">
         <v>7533</v>
       </c>
-      <c r="AD133" t="n">
-        <v>18354</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -17236,9 +17218,6 @@
       <c r="AC152" t="n">
         <v>8915</v>
       </c>
-      <c r="AD152" t="n">
-        <v>10771</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -21694,9 +21673,6 @@
           <t>Singapore Marathon</t>
         </is>
       </c>
-      <c r="AD219" t="n">
-        <v>39901</v>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -21819,9 +21795,6 @@
           <t>Run in Lyon by Harmonie Mutuelle</t>
         </is>
       </c>
-      <c r="AD224" t="n">
-        <v>38475</v>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -22032,9 +22005,6 @@
           <t>Kuala Lampur Standard Chartered Marathon</t>
         </is>
       </c>
-      <c r="AD233" t="n">
-        <v>34860</v>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -22057,9 +22027,6 @@
           <t>Kuala Lampur Standard Chartered Marathon</t>
         </is>
       </c>
-      <c r="AD234" t="n">
-        <v>34860</v>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -22082,9 +22049,6 @@
           <t>Kuala Lampur Standard Chartered Marathon</t>
         </is>
       </c>
-      <c r="AD235" t="n">
-        <v>34860</v>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -22107,9 +22071,6 @@
           <t>Kuala Lampur Standard Chartered Marathon</t>
         </is>
       </c>
-      <c r="AD236" t="n">
-        <v>34860</v>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -22182,9 +22143,6 @@
           <t>Hot Chocolate Run</t>
         </is>
       </c>
-      <c r="AD239" t="n">
-        <v>33547</v>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -22207,9 +22165,6 @@
           <t>Hot Chocolate Run</t>
         </is>
       </c>
-      <c r="AD240" t="n">
-        <v>33547</v>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -22357,9 +22312,6 @@
           <t>ASML Marathon Eindhoven</t>
         </is>
       </c>
-      <c r="AD246" t="n">
-        <v>31749</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -22382,9 +22334,6 @@
           <t>Toulouse Metropole Run Experience</t>
         </is>
       </c>
-      <c r="AD247" t="n">
-        <v>31358</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -22432,9 +22381,6 @@
           <t>Run Rome Marathon</t>
         </is>
       </c>
-      <c r="AD249" t="n">
-        <v>29880</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -22457,9 +22403,6 @@
           <t>Run Rome Marathon</t>
         </is>
       </c>
-      <c r="AD250" t="n">
-        <v>29880</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -22632,9 +22575,6 @@
           <t>Wizz Air Milano Marathon</t>
         </is>
       </c>
-      <c r="AD257" t="n">
-        <v>29050</v>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -22657,9 +22597,6 @@
           <t>Wizz Air Milano Marathon</t>
         </is>
       </c>
-      <c r="AD258" t="n">
-        <v>29050</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -23012,9 +22949,6 @@
           <t>Walt Disney Marathon</t>
         </is>
       </c>
-      <c r="AD272" t="n">
-        <v>26167</v>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -23037,9 +22971,6 @@
           <t>Walt Disney Marathon</t>
         </is>
       </c>
-      <c r="AD273" t="n">
-        <v>26167</v>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -23062,9 +22993,6 @@
           <t>Walt Disney Marathon</t>
         </is>
       </c>
-      <c r="AD274" t="n">
-        <v>26167</v>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -23087,9 +23015,6 @@
           <t>Walt Disney Marathon</t>
         </is>
       </c>
-      <c r="AD275" t="n">
-        <v>26167</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -23462,9 +23387,6 @@
           <t>Generali Köln Marathon</t>
         </is>
       </c>
-      <c r="AD290" t="n">
-        <v>23935</v>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -23687,9 +23609,6 @@
           <t>Freshworks Chennai Marathon</t>
         </is>
       </c>
-      <c r="AD299" t="n">
-        <v>23346</v>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -23937,9 +23856,6 @@
           <t>Osterreichischer Frauenlauf</t>
         </is>
       </c>
-      <c r="AD309" t="n">
-        <v>22556</v>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -23962,9 +23878,6 @@
           <t>Osterreichischer Frauenlauf</t>
         </is>
       </c>
-      <c r="AD310" t="n">
-        <v>22556</v>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -24087,9 +24000,6 @@
           <t>Marathon International du Beaujolais</t>
         </is>
       </c>
-      <c r="AD315" t="n">
-        <v>22171</v>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -24412,9 +24322,6 @@
           <t>Semi &amp; 10km de Bordeaux</t>
         </is>
       </c>
-      <c r="AD328" t="n">
-        <v>21113</v>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -24437,9 +24344,6 @@
           <t>Semi &amp; 10km de Bordeaux</t>
         </is>
       </c>
-      <c r="AD329" t="n">
-        <v>21113</v>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -24462,9 +24366,6 @@
           <t>Madrid Medio Maraton</t>
         </is>
       </c>
-      <c r="AD330" t="n">
-        <v>20918</v>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -24487,9 +24388,6 @@
           <t>Sydney Half Marathon</t>
         </is>
       </c>
-      <c r="AD331" t="n">
-        <v>20531</v>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -24512,9 +24410,6 @@
           <t>Sydney Half Marathon</t>
         </is>
       </c>
-      <c r="AD332" t="n">
-        <v>20531</v>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -24562,9 +24457,6 @@
           <t>Adani Ahmedabad Marathon</t>
         </is>
       </c>
-      <c r="AD334" t="n">
-        <v>19920</v>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -24587,9 +24479,6 @@
           <t>Adani Ahmedabad Marathon</t>
         </is>
       </c>
-      <c r="AD335" t="n">
-        <v>19920</v>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -24612,9 +24501,6 @@
           <t>Adani Ahmedabad Marathon</t>
         </is>
       </c>
-      <c r="AD336" t="n">
-        <v>19920</v>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -24637,9 +24523,6 @@
           <t>Adani Ahmedabad Marathon</t>
         </is>
       </c>
-      <c r="AD337" t="n">
-        <v>19920</v>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -24892,9 +24775,6 @@
           <t>Rocky Run</t>
         </is>
       </c>
-      <c r="AD347" t="n">
-        <v>18841</v>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -24917,9 +24797,6 @@
           <t>Rocky Run</t>
         </is>
       </c>
-      <c r="AD348" t="n">
-        <v>18841</v>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -24942,9 +24819,6 @@
           <t>Rocky Run</t>
         </is>
       </c>
-      <c r="AD349" t="n">
-        <v>18841</v>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -24992,9 +24866,6 @@
           <t>20Km de Lausanne</t>
         </is>
       </c>
-      <c r="AD351" t="n">
-        <v>18754</v>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -25017,9 +24888,6 @@
           <t>20Km de Lausanne</t>
         </is>
       </c>
-      <c r="AD352" t="n">
-        <v>18754</v>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -25042,9 +24910,6 @@
           <t>20Km de Lausanne</t>
         </is>
       </c>
-      <c r="AD353" t="n">
-        <v>18754</v>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -25117,9 +24982,6 @@
           <t>Vedanta Delhi Half</t>
         </is>
       </c>
-      <c r="AD356" t="n">
-        <v>18590</v>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -25217,9 +25079,6 @@
           <t>ADAC Marathon de Hannover</t>
         </is>
       </c>
-      <c r="AD360" t="n">
-        <v>17587</v>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -25242,9 +25101,6 @@
           <t>ADAC Marathon de Hannover</t>
         </is>
       </c>
-      <c r="AD361" t="n">
-        <v>17587</v>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -25267,9 +25123,6 @@
           <t>ADAC Marathon de Hannover</t>
         </is>
       </c>
-      <c r="AD362" t="n">
-        <v>17587</v>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25392,9 +25245,6 @@
           <t>Rock'n'Roll San Diego Half Marathon</t>
         </is>
       </c>
-      <c r="AD367" t="n">
-        <v>17235</v>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -25417,9 +25267,6 @@
           <t>Rock'n'Roll San Diego Half Marathon</t>
         </is>
       </c>
-      <c r="AD368" t="n">
-        <v>17235</v>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -25442,9 +25289,6 @@
           <t>Rock'n'Roll San Diego Half Marathon</t>
         </is>
       </c>
-      <c r="AD369" t="n">
-        <v>17235</v>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -25467,9 +25311,6 @@
           <t>Reims Champagne Run</t>
         </is>
       </c>
-      <c r="AD370" t="n">
-        <v>17093</v>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -25492,9 +25333,6 @@
           <t>Reims Champagne Run</t>
         </is>
       </c>
-      <c r="AD371" t="n">
-        <v>17093</v>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -25517,9 +25355,6 @@
           <t>Reims Champagne Run</t>
         </is>
       </c>
-      <c r="AD372" t="n">
-        <v>17093</v>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -25542,9 +25377,6 @@
           <t>Reims Champagne Run</t>
         </is>
       </c>
-      <c r="AD373" t="n">
-        <v>17093</v>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -25567,9 +25399,6 @@
           <t>Surf City Marathon</t>
         </is>
       </c>
-      <c r="AD374" t="n">
-        <v>17068</v>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -25592,9 +25421,6 @@
           <t>Surf City Marathon</t>
         </is>
       </c>
-      <c r="AD375" t="n">
-        <v>17068</v>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -25617,9 +25443,6 @@
           <t>Surf City Marathon</t>
         </is>
       </c>
-      <c r="AD376" t="n">
-        <v>17068</v>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -25737,9 +25560,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD380" t="n">
-        <v>17052</v>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -25837,9 +25657,6 @@
           <t>Tout Rennes Court</t>
         </is>
       </c>
-      <c r="AD384" t="n">
-        <v>16936</v>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -26062,9 +25879,6 @@
           <t>Wizz Air Budapest Half marathon</t>
         </is>
       </c>
-      <c r="AD393" t="n">
-        <v>16781</v>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -26217,9 +26031,6 @@
           <t>Eva Air Marathon</t>
         </is>
       </c>
-      <c r="AD399" t="n">
-        <v>16360</v>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -26242,9 +26053,6 @@
           <t>Eva Air Marathon</t>
         </is>
       </c>
-      <c r="AD400" t="n">
-        <v>16360</v>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -26267,9 +26075,6 @@
           <t>Eva Air Marathon</t>
         </is>
       </c>
-      <c r="AD401" t="n">
-        <v>16360</v>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -26347,9 +26152,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD404" t="n">
-        <v>16144</v>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -26377,9 +26179,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD405" t="n">
-        <v>16144</v>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -26552,9 +26351,6 @@
           <t>Marathon International inDeauville</t>
         </is>
       </c>
-      <c r="AD412" t="n">
-        <v>16019</v>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -26577,9 +26373,6 @@
           <t>Carrera Ponle Freno Madrid</t>
         </is>
       </c>
-      <c r="AD413" t="n">
-        <v>15736</v>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -26602,9 +26395,6 @@
           <t>Carrera Ponle Freno Madrid</t>
         </is>
       </c>
-      <c r="AD414" t="n">
-        <v>15736</v>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -26627,9 +26417,6 @@
           <t>Maraton Lima 42K</t>
         </is>
       </c>
-      <c r="AD415" t="n">
-        <v>15687</v>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -26652,9 +26439,6 @@
           <t>Maraton Lima 42K</t>
         </is>
       </c>
-      <c r="AD416" t="n">
-        <v>15687</v>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -26677,9 +26461,6 @@
           <t>Maraton Lima 42K</t>
         </is>
       </c>
-      <c r="AD417" t="n">
-        <v>15687</v>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -26877,9 +26658,6 @@
           <t>Antwerp Marathon</t>
         </is>
       </c>
-      <c r="AD425" t="n">
-        <v>15424</v>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -27027,9 +26805,6 @@
           <t>Helsinki City run</t>
         </is>
       </c>
-      <c r="AD431" t="n">
-        <v>15009</v>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -27052,9 +26827,6 @@
           <t>Helsinki City run</t>
         </is>
       </c>
-      <c r="AD432" t="n">
-        <v>15009</v>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -27077,9 +26849,6 @@
           <t>Helsinki City run</t>
         </is>
       </c>
-      <c r="AD433" t="n">
-        <v>15009</v>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -27102,9 +26871,6 @@
           <t>Helsinki City run</t>
         </is>
       </c>
-      <c r="AD434" t="n">
-        <v>15009</v>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -27127,9 +26893,6 @@
           <t>Standard Chartered Hanoi Marathon - Heritage Race</t>
         </is>
       </c>
-      <c r="AD435" t="n">
-        <v>14940</v>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -27152,9 +26915,6 @@
           <t>Standard Chartered Hanoi Marathon - Heritage Race</t>
         </is>
       </c>
-      <c r="AD436" t="n">
-        <v>14940</v>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -27177,9 +26937,6 @@
           <t>Standard Chartered Hanoi Marathon - Heritage Race</t>
         </is>
       </c>
-      <c r="AD437" t="n">
-        <v>14940</v>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -27202,9 +26959,6 @@
           <t>Standard Chartered Hanoi Marathon - Heritage Race</t>
         </is>
       </c>
-      <c r="AD438" t="n">
-        <v>14940</v>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -27227,9 +26981,6 @@
           <t>Doha Running Festival</t>
         </is>
       </c>
-      <c r="AD439" t="n">
-        <v>14894</v>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -27252,9 +27003,6 @@
           <t>Doha Running Festival</t>
         </is>
       </c>
-      <c r="AD440" t="n">
-        <v>14894</v>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -27277,9 +27025,6 @@
           <t>Doha Running Festival</t>
         </is>
       </c>
-      <c r="AD441" t="n">
-        <v>14894</v>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -27302,9 +27047,6 @@
           <t>Doha Running Festival</t>
         </is>
       </c>
-      <c r="AD442" t="n">
-        <v>14894</v>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -27452,9 +27194,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD447" t="n">
-        <v>14894</v>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -27477,9 +27216,6 @@
           <t>Rock'n'Roll Las Vegas</t>
         </is>
       </c>
-      <c r="AD448" t="n">
-        <v>14694</v>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -27502,9 +27238,6 @@
           <t>Rock'n'Roll Las Vegas</t>
         </is>
       </c>
-      <c r="AD449" t="n">
-        <v>14694</v>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -27527,9 +27260,6 @@
           <t>Rock'n'Roll Las Vegas</t>
         </is>
       </c>
-      <c r="AD450" t="n">
-        <v>14694</v>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -27677,9 +27407,6 @@
           <t>Allianz Jean Bouin</t>
         </is>
       </c>
-      <c r="AD456" t="n">
-        <v>13808</v>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -27702,9 +27429,6 @@
           <t>Allianz Jean Bouin</t>
         </is>
       </c>
-      <c r="AD457" t="n">
-        <v>13808</v>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -27827,9 +27551,6 @@
           <t>Marathon de la Liberté - Normandy Running Festival</t>
         </is>
       </c>
-      <c r="AD462" t="n">
-        <v>13798</v>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -27952,9 +27673,6 @@
           <t>Swedbank Tallinna maraton</t>
         </is>
       </c>
-      <c r="AD467" t="n">
-        <v>13764</v>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -28027,9 +27745,6 @@
           <t>Running Loire Valley</t>
         </is>
       </c>
-      <c r="AD470" t="n">
-        <v>13603</v>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -28052,9 +27767,6 @@
           <t>Running Loire Valley</t>
         </is>
       </c>
-      <c r="AD471" t="n">
-        <v>13603</v>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -28077,9 +27789,6 @@
           <t>Running Loire Valley</t>
         </is>
       </c>
-      <c r="AD472" t="n">
-        <v>13603</v>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -28352,9 +28061,6 @@
           <t>Marathon Vert</t>
         </is>
       </c>
-      <c r="AD483" t="n">
-        <v>13524</v>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -28402,9 +28108,6 @@
           <t>Marathon Vert</t>
         </is>
       </c>
-      <c r="AD485" t="n">
-        <v>13524</v>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -28477,9 +28180,6 @@
           <t>Mezza Maratona d'Italia - Memorial Enzo Ferrari</t>
         </is>
       </c>
-      <c r="AD488" t="n">
-        <v>13456</v>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -28502,9 +28202,6 @@
           <t>Mezza Maratona d'Italia - Memorial Enzo Ferrari</t>
         </is>
       </c>
-      <c r="AD489" t="n">
-        <v>13456</v>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -28527,9 +28224,6 @@
           <t>Mezza Maratona d'Italia - Memorial Enzo Ferrari</t>
         </is>
       </c>
-      <c r="AD490" t="n">
-        <v>13456</v>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -28552,9 +28246,6 @@
           <t>Media Maraton de Lima</t>
         </is>
       </c>
-      <c r="AD491" t="n">
-        <v>13423</v>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -28577,9 +28268,6 @@
           <t>Media Maraton de Lima</t>
         </is>
       </c>
-      <c r="AD492" t="n">
-        <v>13423</v>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -28602,9 +28290,6 @@
           <t>Enschede Marathon</t>
         </is>
       </c>
-      <c r="AD493" t="n">
-        <v>13415</v>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -28627,9 +28312,6 @@
           <t>Enschede Marathon</t>
         </is>
       </c>
-      <c r="AD494" t="n">
-        <v>13415</v>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -28652,9 +28334,6 @@
           <t>Enschede Marathon</t>
         </is>
       </c>
-      <c r="AD495" t="n">
-        <v>13415</v>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -28677,9 +28356,6 @@
           <t>Enschede Marathon</t>
         </is>
       </c>
-      <c r="AD496" t="n">
-        <v>13415</v>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -28792,9 +28468,6 @@
           <t>Almaty Marathon</t>
         </is>
       </c>
-      <c r="AD500" t="n">
-        <v>13280</v>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -28817,9 +28490,6 @@
           <t>Almaty Marathon</t>
         </is>
       </c>
-      <c r="AD501" t="n">
-        <v>13280</v>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -28842,9 +28512,6 @@
           <t>Almaty Marathon</t>
         </is>
       </c>
-      <c r="AD502" t="n">
-        <v>13280</v>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -28967,9 +28634,6 @@
           <t>Marathon de Biarritz</t>
         </is>
       </c>
-      <c r="AD507" t="n">
-        <v>13150</v>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -28992,9 +28656,6 @@
           <t>Marathon de Biarritz</t>
         </is>
       </c>
-      <c r="AD508" t="n">
-        <v>13150</v>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -29017,9 +28678,6 @@
           <t>Marathon de Biarritz</t>
         </is>
       </c>
-      <c r="AD509" t="n">
-        <v>13150</v>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -29042,9 +28700,6 @@
           <t>Rock'n'Roll Nashville</t>
         </is>
       </c>
-      <c r="AD510" t="n">
-        <v>13098</v>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -29067,9 +28722,6 @@
           <t>Rock'n'Roll Nashville</t>
         </is>
       </c>
-      <c r="AD511" t="n">
-        <v>13098</v>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -29092,9 +28744,6 @@
           <t>Rock'n'Roll Nashville</t>
         </is>
       </c>
-      <c r="AD512" t="n">
-        <v>13098</v>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -29117,9 +28766,6 @@
           <t>Rock'n'Roll Nashville</t>
         </is>
       </c>
-      <c r="AD513" t="n">
-        <v>13098</v>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -29192,9 +28838,6 @@
           <t>Vedanta Pink City Half</t>
         </is>
       </c>
-      <c r="AD516" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -29217,9 +28860,6 @@
           <t>Vedanta Pink City Half</t>
         </is>
       </c>
-      <c r="AD517" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -29242,9 +28882,6 @@
           <t>Vedanta Pink City Half</t>
         </is>
       </c>
-      <c r="AD518" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -29267,9 +28904,6 @@
           <t>SK Jodhpur Marathon</t>
         </is>
       </c>
-      <c r="AD519" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -29292,9 +28926,6 @@
           <t>SK Jodhpur Marathon</t>
         </is>
       </c>
-      <c r="AD520" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -29317,9 +28948,6 @@
           <t>JBG Kolkata Marathon</t>
         </is>
       </c>
-      <c r="AD521" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -29342,9 +28970,6 @@
           <t>JBG Kolkata Marathon</t>
         </is>
       </c>
-      <c r="AD522" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -29367,9 +28992,6 @@
           <t>JBG Kolkata Marathon</t>
         </is>
       </c>
-      <c r="AD523" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -29417,9 +29039,6 @@
           <t>Konya Half Marathon</t>
         </is>
       </c>
-      <c r="AD525" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -29442,9 +29061,6 @@
           <t>Konya Half Marathon</t>
         </is>
       </c>
-      <c r="AD526" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -29467,9 +29083,6 @@
           <t>Konya Half Marathon</t>
         </is>
       </c>
-      <c r="AD527" t="n">
-        <v>12450</v>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -29567,9 +29180,6 @@
           <t>Marathon de La Rochelle Serge Vigot</t>
         </is>
       </c>
-      <c r="AD531" t="n">
-        <v>12316</v>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -29667,9 +29277,6 @@
           <t>Royal Victoria Marathon</t>
         </is>
       </c>
-      <c r="AD535" t="n">
-        <v>12174</v>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -29692,9 +29299,6 @@
           <t>Royal Victoria Marathon</t>
         </is>
       </c>
-      <c r="AD536" t="n">
-        <v>12174</v>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -29717,9 +29321,6 @@
           <t>Royal Victoria Marathon</t>
         </is>
       </c>
-      <c r="AD537" t="n">
-        <v>12174</v>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -29767,9 +29368,6 @@
           <t>SportScheck RUN Munchen</t>
         </is>
       </c>
-      <c r="AD539" t="n">
-        <v>12080</v>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -29792,9 +29390,6 @@
           <t>SportScheck RUN Munchen</t>
         </is>
       </c>
-      <c r="AD540" t="n">
-        <v>12080</v>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -29817,9 +29412,6 @@
           <t>SportScheck RUN Munchen</t>
         </is>
       </c>
-      <c r="AD541" t="n">
-        <v>12080</v>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -29842,9 +29434,6 @@
           <t>Singapore Compression Run</t>
         </is>
       </c>
-      <c r="AD542" t="n">
-        <v>11969</v>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -29867,9 +29456,6 @@
           <t>Singapore Compression Run</t>
         </is>
       </c>
-      <c r="AD543" t="n">
-        <v>11969</v>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -29892,9 +29478,6 @@
           <t>Singapore Compression Run</t>
         </is>
       </c>
-      <c r="AD544" t="n">
-        <v>11969</v>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -30017,9 +29600,6 @@
           <t>Dresden Marathon</t>
         </is>
       </c>
-      <c r="AD549" t="n">
-        <v>11963</v>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -30042,9 +29622,6 @@
           <t>Sunshine coast Marathon Festival</t>
         </is>
       </c>
-      <c r="AD550" t="n">
-        <v>11834</v>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -30067,9 +29644,6 @@
           <t>Sunshine coast Marathon Festival</t>
         </is>
       </c>
-      <c r="AD551" t="n">
-        <v>11834</v>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -30092,9 +29666,6 @@
           <t>Sunshine coast Marathon Festival</t>
         </is>
       </c>
-      <c r="AD552" t="n">
-        <v>11834</v>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -30192,9 +29763,6 @@
           <t>Adidas Runners city night</t>
         </is>
       </c>
-      <c r="AD556" t="n">
-        <v>11736</v>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -30217,9 +29785,6 @@
           <t>Adidas Runners city night</t>
         </is>
       </c>
-      <c r="AD557" t="n">
-        <v>11736</v>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -30242,9 +29807,6 @@
           <t>Maratona Di Ravenna</t>
         </is>
       </c>
-      <c r="AD558" t="n">
-        <v>11734</v>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -30267,9 +29829,6 @@
           <t>Maratona Di Ravenna</t>
         </is>
       </c>
-      <c r="AD559" t="n">
-        <v>11734</v>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -30292,9 +29851,6 @@
           <t>Maratona Di Ravenna</t>
         </is>
       </c>
-      <c r="AD560" t="n">
-        <v>11734</v>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -30317,9 +29873,6 @@
           <t>Perth running festival</t>
         </is>
       </c>
-      <c r="AD561" t="n">
-        <v>11727</v>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -30342,9 +29895,6 @@
           <t>Perth running festival</t>
         </is>
       </c>
-      <c r="AD562" t="n">
-        <v>11727</v>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -30367,9 +29917,6 @@
           <t>Perth running festival</t>
         </is>
       </c>
-      <c r="AD563" t="n">
-        <v>11727</v>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -30442,9 +29989,6 @@
           <t>Halong Bay Heritage Marathon</t>
         </is>
       </c>
-      <c r="AD566" t="n">
-        <v>11620</v>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -30467,9 +30011,6 @@
           <t>Halong Bay Heritage Marathon</t>
         </is>
       </c>
-      <c r="AD567" t="n">
-        <v>11620</v>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -30492,9 +30033,6 @@
           <t>Halong Bay Heritage Marathon</t>
         </is>
       </c>
-      <c r="AD568" t="n">
-        <v>11620</v>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -30517,9 +30055,6 @@
           <t>Halong Bay Heritage Marathon</t>
         </is>
       </c>
-      <c r="AD569" t="n">
-        <v>11620</v>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -30542,9 +30077,6 @@
           <t>Deutsche Post Marathon Bonn</t>
         </is>
       </c>
-      <c r="AD570" t="n">
-        <v>11463</v>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -30567,9 +30099,6 @@
           <t>Deutsche Post Marathon Bonn</t>
         </is>
       </c>
-      <c r="AD571" t="n">
-        <v>11463</v>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -30592,9 +30121,6 @@
           <t>Deutsche Post Marathon Bonn</t>
         </is>
       </c>
-      <c r="AD572" t="n">
-        <v>11463</v>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -30717,9 +30243,6 @@
           <t>Sao Silvestre do Porto</t>
         </is>
       </c>
-      <c r="AD577" t="n">
-        <v>11372</v>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -30742,9 +30265,6 @@
           <t>Sao Silvestre do Porto</t>
         </is>
       </c>
-      <c r="AD578" t="n">
-        <v>11372</v>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -30842,9 +30362,6 @@
           <t>Indian Army Day Half Marathon</t>
         </is>
       </c>
-      <c r="AD582" t="n">
-        <v>11205</v>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -30867,9 +30384,6 @@
           <t>Indian Army Day Half Marathon</t>
         </is>
       </c>
-      <c r="AD583" t="n">
-        <v>11205</v>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -30892,9 +30406,6 @@
           <t>Indian Army Day Half Marathon</t>
         </is>
       </c>
-      <c r="AD584" t="n">
-        <v>11205</v>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -30917,9 +30428,6 @@
           <t>Marathon international de Marrakech</t>
         </is>
       </c>
-      <c r="AD585" t="n">
-        <v>11164</v>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -30942,9 +30450,6 @@
           <t>Marathon international de Marrakech</t>
         </is>
       </c>
-      <c r="AD586" t="n">
-        <v>11164</v>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -31067,9 +30572,6 @@
           <t>Brooks Marathon du Lac d’Annecy</t>
         </is>
       </c>
-      <c r="AD591" t="n">
-        <v>11020</v>
-      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -31092,9 +30594,6 @@
           <t>Brooks Marathon du Lac d’Annecy</t>
         </is>
       </c>
-      <c r="AD592" t="n">
-        <v>11020</v>
-      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -31117,9 +30616,6 @@
           <t>Brooks Marathon du Lac d’Annecy</t>
         </is>
       </c>
-      <c r="AD593" t="n">
-        <v>11020</v>
-      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -31142,9 +30638,6 @@
           <t>Brooks Marathon du Lac d’Annecy</t>
         </is>
       </c>
-      <c r="AD594" t="n">
-        <v>11020</v>
-      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -31167,9 +30660,6 @@
           <t>Shamrock Run</t>
         </is>
       </c>
-      <c r="AD595" t="n">
-        <v>10929</v>
-      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -31192,9 +30682,6 @@
           <t>Shamrock Run</t>
         </is>
       </c>
-      <c r="AD596" t="n">
-        <v>10929</v>
-      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -31242,9 +30729,6 @@
           <t>Cursa dels Nassos</t>
         </is>
       </c>
-      <c r="AD598" t="n">
-        <v>10918</v>
-      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -31267,9 +30751,6 @@
           <t>Cursa dels Nassos</t>
         </is>
       </c>
-      <c r="AD599" t="n">
-        <v>10918</v>
-      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -31292,9 +30773,6 @@
           <t>Seine-Marathon 76</t>
         </is>
       </c>
-      <c r="AD600" t="n">
-        <v>10909</v>
-      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -31317,9 +30795,6 @@
           <t>Seine-Marathon 76</t>
         </is>
       </c>
-      <c r="AD601" t="n">
-        <v>10909</v>
-      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -31342,9 +30817,6 @@
           <t>Seine-Marathon 76</t>
         </is>
       </c>
-      <c r="AD602" t="n">
-        <v>10909</v>
-      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -31367,9 +30839,6 @@
           <t>Seine-Marathon 76</t>
         </is>
       </c>
-      <c r="AD603" t="n">
-        <v>10909</v>
-      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -31392,9 +30861,6 @@
           <t>Seine-Marathon 76</t>
         </is>
       </c>
-      <c r="AD604" t="n">
-        <v>10909</v>
-      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -31442,9 +30908,6 @@
           <t>New Delhi Marathon</t>
         </is>
       </c>
-      <c r="AD606" t="n">
-        <v>10825</v>
-      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -31467,9 +30930,6 @@
           <t>New Delhi Marathon</t>
         </is>
       </c>
-      <c r="AD607" t="n">
-        <v>10825</v>
-      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -31492,9 +30952,6 @@
           <t>New Delhi Marathon</t>
         </is>
       </c>
-      <c r="AD608" t="n">
-        <v>10825</v>
-      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -31517,9 +30974,6 @@
           <t>New Delhi Marathon</t>
         </is>
       </c>
-      <c r="AD609" t="n">
-        <v>10825</v>
-      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -31542,9 +30996,6 @@
           <t>Sapporo Half Marathon</t>
         </is>
       </c>
-      <c r="AD610" t="n">
-        <v>10790</v>
-      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -31567,9 +31018,6 @@
           <t>Sapporo Half Marathon</t>
         </is>
       </c>
-      <c r="AD611" t="n">
-        <v>10790</v>
-      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -31592,9 +31040,6 @@
           <t>Sapporo Half Marathon</t>
         </is>
       </c>
-      <c r="AD612" t="n">
-        <v>10790</v>
-      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -31717,9 +31162,6 @@
           <t>Great Bristol Run</t>
         </is>
       </c>
-      <c r="AD617" t="n">
-        <v>10770</v>
-      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -31747,9 +31189,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD618" t="n">
-        <v>10631</v>
-      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -31777,9 +31216,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD619" t="n">
-        <v>10631</v>
-      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -31807,9 +31243,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD620" t="n">
-        <v>10631</v>
-      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -32157,9 +31590,6 @@
           <t>Montpellier Run Festival</t>
         </is>
       </c>
-      <c r="AD634" t="n">
-        <v>10313</v>
-      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -32182,9 +31612,6 @@
           <t>Montpellier Run Festival</t>
         </is>
       </c>
-      <c r="AD635" t="n">
-        <v>10313</v>
-      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -32257,9 +31684,6 @@
           <t>Denver Marathon</t>
         </is>
       </c>
-      <c r="AD638" t="n">
-        <v>10234</v>
-      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -32382,9 +31806,6 @@
           <t>La Grande Course RATP du Grand Paris</t>
         </is>
       </c>
-      <c r="AD643" t="n">
-        <v>10118</v>
-      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -32407,9 +31828,6 @@
           <t>ACSE - Les courses de Strasbourg Eurométropole</t>
         </is>
       </c>
-      <c r="AD644" t="n">
-        <v>10097</v>
-      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -32432,9 +31850,6 @@
           <t>ACSE - Les courses de Strasbourg Eurométropole</t>
         </is>
       </c>
-      <c r="AD645" t="n">
-        <v>10097</v>
-      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -32457,9 +31872,6 @@
           <t>ACSE - Les courses de Strasbourg Eurométropole</t>
         </is>
       </c>
-      <c r="AD646" t="n">
-        <v>10097</v>
-      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -32482,9 +31894,6 @@
           <t>ACSE - Les courses de Strasbourg Eurométropole</t>
         </is>
       </c>
-      <c r="AD647" t="n">
-        <v>10097</v>
-      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -32507,9 +31916,6 @@
           <t>Greifenseelauf</t>
         </is>
       </c>
-      <c r="AD648" t="n">
-        <v>9972</v>
-      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -32532,9 +31938,6 @@
           <t>Greifenseelauf</t>
         </is>
       </c>
-      <c r="AD649" t="n">
-        <v>9972</v>
-      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -32582,9 +31985,6 @@
           <t>Bruges marathon</t>
         </is>
       </c>
-      <c r="AD651" t="n">
-        <v>9962</v>
-      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -32607,9 +32007,6 @@
           <t>Bruges marathon</t>
         </is>
       </c>
-      <c r="AD652" t="n">
-        <v>9962</v>
-      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -32632,9 +32029,6 @@
           <t>Union Bank of India Thane Half Marathon</t>
         </is>
       </c>
-      <c r="AD653" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -32657,9 +32051,6 @@
           <t>Union Bank of India Thane Half Marathon</t>
         </is>
       </c>
-      <c r="AD654" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -32707,9 +32098,6 @@
           <t>Tay Ho Half Marathon</t>
         </is>
       </c>
-      <c r="AD656" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -32732,9 +32120,6 @@
           <t>Tay Ho Half Marathon</t>
         </is>
       </c>
-      <c r="AD657" t="n">
-        <v>9960</v>
-      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -32857,9 +32242,6 @@
           <t>Midnight sun Marathon</t>
         </is>
       </c>
-      <c r="AD662" t="n">
-        <v>9659</v>
-      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -32882,9 +32264,6 @@
           <t>Midnight sun Marathon</t>
         </is>
       </c>
-      <c r="AD663" t="n">
-        <v>9659</v>
-      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -33022,9 +32401,6 @@
           <t>Vilniaus Maratonas</t>
         </is>
       </c>
-      <c r="AD668" t="n">
-        <v>9365</v>
-      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -33047,9 +32423,6 @@
           <t>Vilniaus Maratonas</t>
         </is>
       </c>
-      <c r="AD669" t="n">
-        <v>9365</v>
-      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -33072,9 +32445,6 @@
           <t>Vilniaus Maratonas</t>
         </is>
       </c>
-      <c r="AD670" t="n">
-        <v>9365</v>
-      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -33097,9 +32467,6 @@
           <t>Vilniaus Maratonas</t>
         </is>
       </c>
-      <c r="AD671" t="n">
-        <v>9365</v>
-      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -33147,9 +32514,6 @@
           <t>Love Run</t>
         </is>
       </c>
-      <c r="AD673" t="n">
-        <v>9130</v>
-      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -33197,9 +32561,6 @@
           <t>Maraton Murcia Costa Calida</t>
         </is>
       </c>
-      <c r="AD675" t="n">
-        <v>9093</v>
-      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -33222,9 +32583,6 @@
           <t>Maraton Murcia Costa Calida</t>
         </is>
       </c>
-      <c r="AD676" t="n">
-        <v>9093</v>
-      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -33247,9 +32605,6 @@
           <t>Gutenberg Halbmarathon Mainz</t>
         </is>
       </c>
-      <c r="AD677" t="n">
-        <v>9082</v>
-      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -33272,9 +32627,6 @@
           <t>Gutenberg Halbmarathon Mainz</t>
         </is>
       </c>
-      <c r="AD678" t="n">
-        <v>9082</v>
-      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -33297,9 +32649,6 @@
           <t>Tjejmilen</t>
         </is>
       </c>
-      <c r="AD679" t="n">
-        <v>9073</v>
-      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -33377,9 +32726,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD682" t="n">
-        <v>8997</v>
-      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -33407,9 +32753,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD683" t="n">
-        <v>8997</v>
-      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -33437,9 +32780,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD684" t="n">
-        <v>8997</v>
-      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -33462,9 +32802,6 @@
           <t>Trondheim Marathon</t>
         </is>
       </c>
-      <c r="AD685" t="n">
-        <v>8980</v>
-      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -33487,9 +32824,6 @@
           <t>Trondheim Marathon</t>
         </is>
       </c>
-      <c r="AD686" t="n">
-        <v>8980</v>
-      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -33512,9 +32846,6 @@
           <t>San Sebastian Marathon</t>
         </is>
       </c>
-      <c r="AD687" t="n">
-        <v>8872</v>
-      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -33537,9 +32868,6 @@
           <t>San Sebastian Marathon</t>
         </is>
       </c>
-      <c r="AD688" t="n">
-        <v>8872</v>
-      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -33562,9 +32890,6 @@
           <t>Graz Marathon</t>
         </is>
       </c>
-      <c r="AD689" t="n">
-        <v>8786</v>
-      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -33587,9 +32912,6 @@
           <t>Graz Marathon</t>
         </is>
       </c>
-      <c r="AD690" t="n">
-        <v>8786</v>
-      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -33612,9 +32934,6 @@
           <t>Graz Marathon</t>
         </is>
       </c>
-      <c r="AD691" t="n">
-        <v>8786</v>
-      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -33637,9 +32956,6 @@
           <t>Graz Marathon</t>
         </is>
       </c>
-      <c r="AD692" t="n">
-        <v>8786</v>
-      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -33662,9 +32978,6 @@
           <t>Graz Marathon</t>
         </is>
       </c>
-      <c r="AD693" t="n">
-        <v>8786</v>
-      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -33687,9 +33000,6 @@
           <t>Rock'n'Roll Arizona</t>
         </is>
       </c>
-      <c r="AD694" t="n">
-        <v>8767</v>
-      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -33712,9 +33022,6 @@
           <t>Rock'n'Roll Arizona</t>
         </is>
       </c>
-      <c r="AD695" t="n">
-        <v>8767</v>
-      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -33737,9 +33044,6 @@
           <t>Rock'n'Roll Arizona</t>
         </is>
       </c>
-      <c r="AD696" t="n">
-        <v>8767</v>
-      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -33762,9 +33066,6 @@
           <t>Ho Chi Minh city marathon</t>
         </is>
       </c>
-      <c r="AD697" t="n">
-        <v>8696</v>
-      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -33787,9 +33088,6 @@
           <t>Ho Chi Minh city marathon</t>
         </is>
       </c>
-      <c r="AD698" t="n">
-        <v>8696</v>
-      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -33812,9 +33110,6 @@
           <t>Ho Chi Minh city marathon</t>
         </is>
       </c>
-      <c r="AD699" t="n">
-        <v>8696</v>
-      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -33962,9 +33257,6 @@
           <t>Bergen City Marathon</t>
         </is>
       </c>
-      <c r="AD705" t="n">
-        <v>8619</v>
-      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -33987,9 +33279,6 @@
           <t>Bergen City Marathon</t>
         </is>
       </c>
-      <c r="AD706" t="n">
-        <v>8619</v>
-      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -34012,9 +33301,6 @@
           <t>Bergen City Marathon</t>
         </is>
       </c>
-      <c r="AD707" t="n">
-        <v>8619</v>
-      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -34037,9 +33323,6 @@
           <t>Generali Maraton Malaga</t>
         </is>
       </c>
-      <c r="AD708" t="n">
-        <v>8534</v>
-      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -34062,9 +33345,6 @@
           <t>Generali Maraton Malaga</t>
         </is>
       </c>
-      <c r="AD709" t="n">
-        <v>8534</v>
-      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -34112,9 +33392,6 @@
           <t>Linz Donau Marathon</t>
         </is>
       </c>
-      <c r="AD711" t="n">
-        <v>8488</v>
-      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -34137,9 +33414,6 @@
           <t>Linz Donau Marathon</t>
         </is>
       </c>
-      <c r="AD712" t="n">
-        <v>8488</v>
-      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -34162,9 +33436,6 @@
           <t>Linz Donau Marathon</t>
         </is>
       </c>
-      <c r="AD713" t="n">
-        <v>8488</v>
-      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -34187,9 +33458,6 @@
           <t>Linz Donau Marathon</t>
         </is>
       </c>
-      <c r="AD714" t="n">
-        <v>8488</v>
-      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -34212,9 +33480,6 @@
           <t>Linz Donau Marathon</t>
         </is>
       </c>
-      <c r="AD715" t="n">
-        <v>8488</v>
-      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -34237,9 +33502,6 @@
           <t>Uniper Marathon de Düsseldorf</t>
         </is>
       </c>
-      <c r="AD716" t="n">
-        <v>8451</v>
-      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -34262,9 +33524,6 @@
           <t>Uniper Marathon de Düsseldorf</t>
         </is>
       </c>
-      <c r="AD717" t="n">
-        <v>8451</v>
-      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -34337,9 +33596,6 @@
           <t>Karnataka State Police Run</t>
         </is>
       </c>
-      <c r="AD720" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -34362,9 +33618,6 @@
           <t>Karnataka State Police Run</t>
         </is>
       </c>
-      <c r="AD721" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -34392,9 +33645,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD722" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -34422,9 +33672,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD723" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -34452,9 +33699,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD724" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -34482,9 +33726,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD725" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -34512,9 +33753,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD726" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -34537,9 +33775,6 @@
           <t>Global 10K New Delhi</t>
         </is>
       </c>
-      <c r="AD727" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -34562,9 +33797,6 @@
           <t>Global 10K New Delhi</t>
         </is>
       </c>
-      <c r="AD728" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -34587,9 +33819,6 @@
           <t>Sharqiyah International Race</t>
         </is>
       </c>
-      <c r="AD729" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -34612,9 +33841,6 @@
           <t>Sharqiyah International Race</t>
         </is>
       </c>
-      <c r="AD730" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -34637,9 +33863,6 @@
           <t>Sharqiyah International Race</t>
         </is>
       </c>
-      <c r="AD731" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -34662,9 +33885,6 @@
           <t>Almaty Half Marathon</t>
         </is>
       </c>
-      <c r="AD732" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -34687,9 +33907,6 @@
           <t>Almaty Half Marathon</t>
         </is>
       </c>
-      <c r="AD733" t="n">
-        <v>8300</v>
-      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -34712,9 +33929,6 @@
           <t>Brisbane marathon festival</t>
         </is>
       </c>
-      <c r="AD734" t="n">
-        <v>8299</v>
-      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -34737,9 +33951,6 @@
           <t>Brisbane marathon festival</t>
         </is>
       </c>
-      <c r="AD735" t="n">
-        <v>8299</v>
-      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -34762,9 +33973,6 @@
           <t>Brisbane marathon festival</t>
         </is>
       </c>
-      <c r="AD736" t="n">
-        <v>8299</v>
-      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -34787,9 +33995,6 @@
           <t>Brisbane marathon festival</t>
         </is>
       </c>
-      <c r="AD737" t="n">
-        <v>8299</v>
-      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -34837,9 +34042,6 @@
           <t>Leipzig Marathon</t>
         </is>
       </c>
-      <c r="AD739" t="n">
-        <v>8069</v>
-      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -34862,9 +34064,6 @@
           <t>Leipzig Marathon</t>
         </is>
       </c>
-      <c r="AD740" t="n">
-        <v>8069</v>
-      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -34887,9 +34086,6 @@
           <t>Leipzig Marathon</t>
         </is>
       </c>
-      <c r="AD741" t="n">
-        <v>8069</v>
-      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -34987,9 +34183,6 @@
           <t>Pyramids Half Marathon</t>
         </is>
       </c>
-      <c r="AD745" t="n">
-        <v>7871</v>
-      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -35012,9 +34205,6 @@
           <t>Pyramids Half Marathon</t>
         </is>
       </c>
-      <c r="AD746" t="n">
-        <v>7871</v>
-      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -35037,9 +34227,6 @@
           <t>Pyramids Half Marathon</t>
         </is>
       </c>
-      <c r="AD747" t="n">
-        <v>7871</v>
-      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -35137,9 +34324,6 @@
           <t>Auffahrtslauf St.Gallen</t>
         </is>
       </c>
-      <c r="AD751" t="n">
-        <v>7800</v>
-      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -35162,9 +34346,6 @@
           <t>Auffahrtslauf St.Gallen</t>
         </is>
       </c>
-      <c r="AD752" t="n">
-        <v>7800</v>
-      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -35187,9 +34368,6 @@
           <t>Auffahrtslauf St.Gallen</t>
         </is>
       </c>
-      <c r="AD753" t="n">
-        <v>7800</v>
-      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -35212,9 +34390,6 @@
           <t>Baloise Namur Marathon</t>
         </is>
       </c>
-      <c r="AD754" t="n">
-        <v>7764</v>
-      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -35237,9 +34412,6 @@
           <t>Baloise Namur Marathon</t>
         </is>
       </c>
-      <c r="AD755" t="n">
-        <v>7764</v>
-      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -35262,9 +34434,6 @@
           <t>Baloise Namur Marathon</t>
         </is>
       </c>
-      <c r="AD756" t="n">
-        <v>7764</v>
-      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -35287,9 +34456,6 @@
           <t>Rock'n'Roll San Jose</t>
         </is>
       </c>
-      <c r="AD757" t="n">
-        <v>7724</v>
-      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -35312,9 +34478,6 @@
           <t>Rock'n'Roll San Jose</t>
         </is>
       </c>
-      <c r="AD758" t="n">
-        <v>7724</v>
-      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -35337,9 +34500,6 @@
           <t>Rock'n'Roll San Jose</t>
         </is>
       </c>
-      <c r="AD759" t="n">
-        <v>7724</v>
-      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -35362,9 +34522,6 @@
           <t>Montepio Meia Maratona Cascais</t>
         </is>
       </c>
-      <c r="AD760" t="n">
-        <v>7720</v>
-      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -35387,9 +34544,6 @@
           <t>Montepio Meia Maratona Cascais</t>
         </is>
       </c>
-      <c r="AD761" t="n">
-        <v>7720</v>
-      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -35412,9 +34566,6 @@
           <t>Montepio Meia Maratona Cascais</t>
         </is>
       </c>
-      <c r="AD762" t="n">
-        <v>7720</v>
-      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -35437,9 +34588,6 @@
           <t>Maratona do Porto</t>
         </is>
       </c>
-      <c r="AD763" t="n">
-        <v>7700</v>
-      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -35462,9 +34610,6 @@
           <t>Maratona do Porto</t>
         </is>
       </c>
-      <c r="AD764" t="n">
-        <v>7700</v>
-      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -35512,9 +34657,6 @@
           <t>Wizz Air Sofia Marathon</t>
         </is>
       </c>
-      <c r="AD766" t="n">
-        <v>7655</v>
-      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -35537,9 +34679,6 @@
           <t>Wizz Air Sofia Marathon</t>
         </is>
       </c>
-      <c r="AD767" t="n">
-        <v>7655</v>
-      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -35562,9 +34701,6 @@
           <t>Wizz Air Sofia Marathon</t>
         </is>
       </c>
-      <c r="AD768" t="n">
-        <v>7655</v>
-      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -35587,9 +34723,6 @@
           <t>Wizz Air Sofia Marathon</t>
         </is>
       </c>
-      <c r="AD769" t="n">
-        <v>7655</v>
-      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -35687,9 +34820,6 @@
           <t>Route du Louvre</t>
         </is>
       </c>
-      <c r="AD773" t="n">
-        <v>7597</v>
-      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -35737,9 +34867,6 @@
           <t>Can Tho Marathon Heritage Race</t>
         </is>
       </c>
-      <c r="AD775" t="n">
-        <v>7442</v>
-      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -35762,9 +34889,6 @@
           <t>Can Tho Marathon Heritage Race</t>
         </is>
       </c>
-      <c r="AD776" t="n">
-        <v>7442</v>
-      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -35787,9 +34911,6 @@
           <t>Can Tho Marathon Heritage Race</t>
         </is>
       </c>
-      <c r="AD777" t="n">
-        <v>7442</v>
-      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -35812,9 +34933,6 @@
           <t>Can Tho Marathon Heritage Race</t>
         </is>
       </c>
-      <c r="AD778" t="n">
-        <v>7442</v>
-      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -35862,9 +34980,6 @@
           <t>Euro Marathon Metz</t>
         </is>
       </c>
-      <c r="AD780" t="n">
-        <v>7440</v>
-      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -35887,9 +35002,6 @@
           <t>Euro Marathon Metz</t>
         </is>
       </c>
-      <c r="AD781" t="n">
-        <v>7440</v>
-      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -35912,9 +35024,6 @@
           <t>Bengaluru Marathon</t>
         </is>
       </c>
-      <c r="AD782" t="n">
-        <v>7426</v>
-      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -35937,9 +35046,6 @@
           <t>Bengaluru Marathon</t>
         </is>
       </c>
-      <c r="AD783" t="n">
-        <v>7426</v>
-      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -35962,9 +35068,6 @@
           <t>Bengaluru Marathon</t>
         </is>
       </c>
-      <c r="AD784" t="n">
-        <v>7426</v>
-      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -35987,9 +35090,6 @@
           <t>Bengaluru Marathon</t>
         </is>
       </c>
-      <c r="AD785" t="n">
-        <v>7426</v>
-      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -36037,9 +35137,6 @@
           <t>Bangkok Marathon</t>
         </is>
       </c>
-      <c r="AD787" t="n">
-        <v>7355</v>
-      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -36062,9 +35159,6 @@
           <t>Bangkok Marathon</t>
         </is>
       </c>
-      <c r="AD788" t="n">
-        <v>7355</v>
-      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -36087,9 +35181,6 @@
           <t>Rock'n'Roll Manila</t>
         </is>
       </c>
-      <c r="AD789" t="n">
-        <v>7312</v>
-      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -36112,9 +35203,6 @@
           <t>Rock'n'Roll Manila</t>
         </is>
       </c>
-      <c r="AD790" t="n">
-        <v>7312</v>
-      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -36137,9 +35225,6 @@
           <t>Rock'n'Roll Manila</t>
         </is>
       </c>
-      <c r="AD791" t="n">
-        <v>7312</v>
-      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -36162,9 +35247,6 @@
           <t>Rock'n'Roll Manila</t>
         </is>
       </c>
-      <c r="AD792" t="n">
-        <v>7312</v>
-      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -36187,9 +35269,6 @@
           <t>Estra Firenze Marathon</t>
         </is>
       </c>
-      <c r="AD793" t="n">
-        <v>7287</v>
-      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -36212,9 +35291,6 @@
           <t>Estra Firenze Marathon</t>
         </is>
       </c>
-      <c r="AD794" t="n">
-        <v>7287</v>
-      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -36237,9 +35313,6 @@
           <t>Estra Firenze Marathon</t>
         </is>
       </c>
-      <c r="AD795" t="n">
-        <v>7287</v>
-      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -36262,9 +35335,6 @@
           <t>Marathon de la Loire</t>
         </is>
       </c>
-      <c r="AD796" t="n">
-        <v>7283</v>
-      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -36287,9 +35357,6 @@
           <t>Marathon de la Loire</t>
         </is>
       </c>
-      <c r="AD797" t="n">
-        <v>7283</v>
-      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -36312,9 +35379,6 @@
           <t>Marathon de la Loire</t>
         </is>
       </c>
-      <c r="AD798" t="n">
-        <v>7283</v>
-      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -36337,9 +35401,6 @@
           <t>Quebec City Marathon</t>
         </is>
       </c>
-      <c r="AD799" t="n">
-        <v>7260</v>
-      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -36362,9 +35423,6 @@
           <t>Quebec City Marathon</t>
         </is>
       </c>
-      <c r="AD800" t="n">
-        <v>7260</v>
-      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -36387,9 +35445,6 @@
           <t>Quebec City Marathon</t>
         </is>
       </c>
-      <c r="AD801" t="n">
-        <v>7260</v>
-      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -36412,9 +35467,6 @@
           <t>Quebec City Marathon</t>
         </is>
       </c>
-      <c r="AD802" t="n">
-        <v>7260</v>
-      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -36487,9 +35539,6 @@
           <t>Bratislava Marathon</t>
         </is>
       </c>
-      <c r="AD805" t="n">
-        <v>7255</v>
-      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -36512,9 +35561,6 @@
           <t>Les foulées de Vincennes</t>
         </is>
       </c>
-      <c r="AD806" t="n">
-        <v>7202</v>
-      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -36537,9 +35583,6 @@
           <t>Les foulées de Vincennes</t>
         </is>
       </c>
-      <c r="AD807" t="n">
-        <v>7202</v>
-      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -36562,9 +35605,6 @@
           <t>Les foulées de Vincennes</t>
         </is>
       </c>
-      <c r="AD808" t="n">
-        <v>7202</v>
-      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -36587,9 +35627,6 @@
           <t>Palma Marathon Mallorca</t>
         </is>
       </c>
-      <c r="AD809" t="n">
-        <v>7153</v>
-      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -36612,9 +35649,6 @@
           <t>Palma Marathon Mallorca</t>
         </is>
       </c>
-      <c r="AD810" t="n">
-        <v>7153</v>
-      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -36637,9 +35671,6 @@
           <t>Palma Marathon Mallorca</t>
         </is>
       </c>
-      <c r="AD811" t="n">
-        <v>7153</v>
-      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -36662,9 +35693,6 @@
           <t>Marathon Bière Flandre Festival</t>
         </is>
       </c>
-      <c r="AD812" t="n">
-        <v>7146</v>
-      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -36687,9 +35715,6 @@
           <t>Marathon Bière Flandre Festival</t>
         </is>
       </c>
-      <c r="AD813" t="n">
-        <v>7146</v>
-      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -36712,9 +35737,6 @@
           <t>Marathon Bière Flandre Festival</t>
         </is>
       </c>
-      <c r="AD814" t="n">
-        <v>7146</v>
-      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -36737,9 +35759,6 @@
           <t>Newport Marathon</t>
         </is>
       </c>
-      <c r="AD815" t="n">
-        <v>7076</v>
-      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -36762,9 +35781,6 @@
           <t>Newport Marathon</t>
         </is>
       </c>
-      <c r="AD816" t="n">
-        <v>7076</v>
-      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -36787,9 +35803,6 @@
           <t>Newport Marathon</t>
         </is>
       </c>
-      <c r="AD817" t="n">
-        <v>7076</v>
-      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -36837,9 +35850,6 @@
           <t>Louisiana Marathon</t>
         </is>
       </c>
-      <c r="AD819" t="n">
-        <v>7065</v>
-      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -36862,9 +35872,6 @@
           <t>Louisiana Marathon</t>
         </is>
       </c>
-      <c r="AD820" t="n">
-        <v>7065</v>
-      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -36887,9 +35894,6 @@
           <t>Louisiana Marathon</t>
         </is>
       </c>
-      <c r="AD821" t="n">
-        <v>7065</v>
-      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -36912,9 +35916,6 @@
           <t>Louisiana Marathon</t>
         </is>
       </c>
-      <c r="AD822" t="n">
-        <v>7065</v>
-      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -37062,9 +36063,6 @@
           <t>Milano21</t>
         </is>
       </c>
-      <c r="AD828" t="n">
-        <v>6804</v>
-      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -37087,9 +36085,6 @@
           <t>Milano21</t>
         </is>
       </c>
-      <c r="AD829" t="n">
-        <v>6804</v>
-      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -37162,9 +36157,6 @@
           <t>Maraton de Mendoza</t>
         </is>
       </c>
-      <c r="AD832" t="n">
-        <v>6680</v>
-      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -37187,9 +36179,6 @@
           <t>Maraton de Mendoza</t>
         </is>
       </c>
-      <c r="AD833" t="n">
-        <v>6680</v>
-      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -37212,9 +36201,6 @@
           <t>Maraton de Mendoza</t>
         </is>
       </c>
-      <c r="AD834" t="n">
-        <v>6680</v>
-      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -37262,9 +36248,6 @@
           <t>Chennai Navy Half Marathon</t>
         </is>
       </c>
-      <c r="AD836" t="n">
-        <v>6640</v>
-      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -37287,9 +36270,6 @@
           <t>Chennai Navy Half Marathon</t>
         </is>
       </c>
-      <c r="AD837" t="n">
-        <v>6640</v>
-      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -37312,9 +36292,6 @@
           <t>Chennai Navy Half Marathon</t>
         </is>
       </c>
-      <c r="AD838" t="n">
-        <v>6640</v>
-      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -37437,9 +36414,6 @@
           <t>Southampton Marathon festival</t>
         </is>
       </c>
-      <c r="AD843" t="n">
-        <v>6579</v>
-      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -37462,9 +36436,6 @@
           <t>Southampton Marathon festival</t>
         </is>
       </c>
-      <c r="AD844" t="n">
-        <v>6579</v>
-      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -37487,9 +36458,6 @@
           <t>Southampton Marathon festival</t>
         </is>
       </c>
-      <c r="AD845" t="n">
-        <v>6579</v>
-      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -37512,9 +36480,6 @@
           <t>Southampton Marathon festival</t>
         </is>
       </c>
-      <c r="AD846" t="n">
-        <v>6579</v>
-      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -37542,9 +36507,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD847" t="n">
-        <v>6552</v>
-      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -37647,9 +36609,6 @@
           <t>Schweizer Frauenlauf Bern</t>
         </is>
       </c>
-      <c r="AD851" t="n">
-        <v>6497</v>
-      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -37672,9 +36631,6 @@
           <t>Schweizer Frauenlauf Bern</t>
         </is>
       </c>
-      <c r="AD852" t="n">
-        <v>6497</v>
-      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -37698,7 +36654,7 @@
         </is>
       </c>
       <c r="AD853" t="n">
-        <v>6488</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="854">
@@ -37723,7 +36679,7 @@
         </is>
       </c>
       <c r="AD854" t="n">
-        <v>6488</v>
+        <v>5137</v>
       </c>
     </row>
     <row r="855">
@@ -37747,9 +36703,6 @@
           <t>Rock'n' Roll Mexico City</t>
         </is>
       </c>
-      <c r="AD855" t="n">
-        <v>6427</v>
-      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -37772,9 +36725,6 @@
           <t>Rock'n' Roll Mexico City</t>
         </is>
       </c>
-      <c r="AD856" t="n">
-        <v>6427</v>
-      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -37797,9 +36747,6 @@
           <t>Baxters Marathon du Loch Ness</t>
         </is>
       </c>
-      <c r="AD857" t="n">
-        <v>6372</v>
-      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -37822,9 +36769,6 @@
           <t>Baxters Marathon du Loch Ness</t>
         </is>
       </c>
-      <c r="AD858" t="n">
-        <v>6372</v>
-      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -37847,9 +36791,6 @@
           <t>Baxters Marathon du Loch Ness</t>
         </is>
       </c>
-      <c r="AD859" t="n">
-        <v>6372</v>
-      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -37872,9 +36813,6 @@
           <t>Les voies royales de Saint Denis</t>
         </is>
       </c>
-      <c r="AD860" t="n">
-        <v>6363</v>
-      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -37897,9 +36835,6 @@
           <t>Les voies royales de Saint Denis</t>
         </is>
       </c>
-      <c r="AD861" t="n">
-        <v>6363</v>
-      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -37922,9 +36857,6 @@
           <t>Les voies royales de Saint Denis</t>
         </is>
       </c>
-      <c r="AD862" t="n">
-        <v>6363</v>
-      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -37947,9 +36879,6 @@
           <t>Les voies royales de Saint Denis</t>
         </is>
       </c>
-      <c r="AD863" t="n">
-        <v>6363</v>
-      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -37972,9 +36901,6 @@
           <t>Les voies royales de Saint Denis</t>
         </is>
       </c>
-      <c r="AD864" t="n">
-        <v>6363</v>
-      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -37997,9 +36923,6 @@
           <t>Bjorn Borg Helsinki Marathon</t>
         </is>
       </c>
-      <c r="AD865" t="n">
-        <v>6337</v>
-      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -38022,9 +36945,6 @@
           <t>Bjorn Borg Helsinki Marathon</t>
         </is>
       </c>
-      <c r="AD866" t="n">
-        <v>6337</v>
-      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -38047,9 +36967,6 @@
           <t>Bjorn Borg Helsinki Marathon</t>
         </is>
       </c>
-      <c r="AD867" t="n">
-        <v>6337</v>
-      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -38072,9 +36989,6 @@
           <t>Bjorn Borg Helsinki Marathon</t>
         </is>
       </c>
-      <c r="AD868" t="n">
-        <v>6337</v>
-      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -38097,9 +37011,6 @@
           <t>SportScheck Run Nuremberg</t>
         </is>
       </c>
-      <c r="AD869" t="n">
-        <v>6335</v>
-      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -38122,9 +37033,6 @@
           <t>SportScheck Run Nuremberg</t>
         </is>
       </c>
-      <c r="AD870" t="n">
-        <v>6335</v>
-      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -38197,9 +37105,6 @@
           <t>Media Maraton internacional aguas de alicante</t>
         </is>
       </c>
-      <c r="AD873" t="n">
-        <v>6247</v>
-      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -38222,9 +37127,6 @@
           <t>Media Maraton internacional aguas de alicante</t>
         </is>
       </c>
-      <c r="AD874" t="n">
-        <v>6247</v>
-      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -38247,9 +37149,6 @@
           <t>Casablanca Marathon</t>
         </is>
       </c>
-      <c r="AD875" t="n">
-        <v>6218</v>
-      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -38272,9 +37171,6 @@
           <t>Casablanca Marathon</t>
         </is>
       </c>
-      <c r="AD876" t="n">
-        <v>6218</v>
-      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -38297,9 +37193,6 @@
           <t>Casablanca Marathon</t>
         </is>
       </c>
-      <c r="AD877" t="n">
-        <v>6218</v>
-      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -38322,9 +37215,6 @@
           <t>Running Festival in Mozart City</t>
         </is>
       </c>
-      <c r="AD878" t="n">
-        <v>6215</v>
-      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -38347,9 +37237,6 @@
           <t>Running Festival in Mozart City</t>
         </is>
       </c>
-      <c r="AD879" t="n">
-        <v>6215</v>
-      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -38372,9 +37259,6 @@
           <t>Running Festival in Mozart City</t>
         </is>
       </c>
-      <c r="AD880" t="n">
-        <v>6215</v>
-      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -38397,9 +37281,6 @@
           <t>Running Festival in Mozart City</t>
         </is>
       </c>
-      <c r="AD881" t="n">
-        <v>6215</v>
-      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -38422,9 +37303,6 @@
           <t>Running Festival in Mozart City</t>
         </is>
       </c>
-      <c r="AD882" t="n">
-        <v>6215</v>
-      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -38447,9 +37325,6 @@
           <t>Santa Monica Classic</t>
         </is>
       </c>
-      <c r="AD883" t="n">
-        <v>6188</v>
-      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -38472,9 +37347,6 @@
           <t>Santa Monica Classic</t>
         </is>
       </c>
-      <c r="AD884" t="n">
-        <v>6188</v>
-      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -38497,9 +37369,6 @@
           <t>Golden Gate</t>
         </is>
       </c>
-      <c r="AD885" t="n">
-        <v>6182</v>
-      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -38522,9 +37391,6 @@
           <t>Golden Gate</t>
         </is>
       </c>
-      <c r="AD886" t="n">
-        <v>6182</v>
-      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -38597,9 +37463,6 @@
           <t>Les foulées Valenciennoises</t>
         </is>
       </c>
-      <c r="AD889" t="n">
-        <v>6178</v>
-      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -38622,9 +37485,6 @@
           <t>SportScheck Run Hannovre</t>
         </is>
       </c>
-      <c r="AD890" t="n">
-        <v>6160</v>
-      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -38647,9 +37507,6 @@
           <t>SportScheck Run Hannovre</t>
         </is>
       </c>
-      <c r="AD891" t="n">
-        <v>6160</v>
-      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -38672,9 +37529,6 @@
           <t>Marathon des vins de la côte chalonnaise</t>
         </is>
       </c>
-      <c r="AD892" t="n">
-        <v>6141</v>
-      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -38697,9 +37551,6 @@
           <t>Marathon des vins de la côte chalonnaise</t>
         </is>
       </c>
-      <c r="AD893" t="n">
-        <v>6141</v>
-      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -38722,9 +37573,6 @@
           <t>Marathon des vins de la côte chalonnaise</t>
         </is>
       </c>
-      <c r="AD894" t="n">
-        <v>6141</v>
-      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -38797,9 +37645,6 @@
           <t>KPMG Lentermarathon</t>
         </is>
       </c>
-      <c r="AD897" t="n">
-        <v>6032</v>
-      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -38822,9 +37667,6 @@
           <t>KPMG Lentermarathon</t>
         </is>
       </c>
-      <c r="AD898" t="n">
-        <v>6032</v>
-      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -38847,9 +37689,6 @@
           <t>KPMG Lentermarathon</t>
         </is>
       </c>
-      <c r="AD899" t="n">
-        <v>6032</v>
-      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -38872,9 +37711,6 @@
           <t>KPMG Lentermarathon</t>
         </is>
       </c>
-      <c r="AD900" t="n">
-        <v>6032</v>
-      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -39091,9 +37927,6 @@
           <t>Sydney Harbour 10K</t>
         </is>
       </c>
-      <c r="AD909" t="n">
-        <v>5859</v>
-      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -39116,9 +37949,6 @@
           <t>Sydney Harbour 10K</t>
         </is>
       </c>
-      <c r="AD910" t="n">
-        <v>5859</v>
-      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -39141,9 +37971,6 @@
           <t>Torino city marathon</t>
         </is>
       </c>
-      <c r="AD911" t="n">
-        <v>5843</v>
-      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -39166,9 +37993,6 @@
           <t>Torino city marathon</t>
         </is>
       </c>
-      <c r="AD912" t="n">
-        <v>5843</v>
-      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -39191,9 +38015,6 @@
           <t>Torino city marathon</t>
         </is>
       </c>
-      <c r="AD913" t="n">
-        <v>5843</v>
-      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -39216,9 +38037,6 @@
           <t>Hallwilerseelauf</t>
         </is>
       </c>
-      <c r="AD914" t="n">
-        <v>5817</v>
-      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -39241,9 +38059,6 @@
           <t>Hallwilerseelauf</t>
         </is>
       </c>
-      <c r="AD915" t="n">
-        <v>5817</v>
-      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -39266,9 +38081,6 @@
           <t>Hallwilerseelauf</t>
         </is>
       </c>
-      <c r="AD916" t="n">
-        <v>5817</v>
-      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -39291,9 +38103,6 @@
           <t>Hallwilerseelauf</t>
         </is>
       </c>
-      <c r="AD917" t="n">
-        <v>5817</v>
-      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -39341,9 +38150,6 @@
           <t>Neapolis marathon</t>
         </is>
       </c>
-      <c r="AD919" t="n">
-        <v>5708</v>
-      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -39366,9 +38172,6 @@
           <t>Neapolis marathon</t>
         </is>
       </c>
-      <c r="AD920" t="n">
-        <v>5708</v>
-      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -39391,9 +38194,6 @@
           <t>Neapolis marathon</t>
         </is>
       </c>
-      <c r="AD921" t="n">
-        <v>5708</v>
-      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -39416,9 +38216,6 @@
           <t>Semi du Grand Nancy</t>
         </is>
       </c>
-      <c r="AD922" t="n">
-        <v>5665</v>
-      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -39441,9 +38238,6 @@
           <t>Semi du Grand Nancy</t>
         </is>
       </c>
-      <c r="AD923" t="n">
-        <v>5665</v>
-      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -39466,9 +38260,6 @@
           <t>Semi du Grand Nancy</t>
         </is>
       </c>
-      <c r="AD924" t="n">
-        <v>5665</v>
-      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -39566,9 +38357,6 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
-      <c r="AD928" t="n">
-        <v>5646</v>
-      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -39591,9 +38379,6 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
-      <c r="AD929" t="n">
-        <v>5646</v>
-      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -39616,9 +38401,6 @@
           <t>Mattoni Running Festival Olomouc</t>
         </is>
       </c>
-      <c r="AD930" t="n">
-        <v>5590</v>
-      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -39641,9 +38423,6 @@
           <t>Mattoni Running Festival Olomouc</t>
         </is>
       </c>
-      <c r="AD931" t="n">
-        <v>5590</v>
-      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -39666,9 +38445,6 @@
           <t>Belgrade Marathon</t>
         </is>
       </c>
-      <c r="AD932" t="n">
-        <v>5521</v>
-      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -39691,9 +38467,6 @@
           <t>Belgrade Marathon</t>
         </is>
       </c>
-      <c r="AD933" t="n">
-        <v>5521</v>
-      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -39716,9 +38489,6 @@
           <t>Belgrade Marathon</t>
         </is>
       </c>
-      <c r="AD934" t="n">
-        <v>5521</v>
-      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -39741,9 +38511,6 @@
           <t>Wizz Air Napoca Marathon</t>
         </is>
       </c>
-      <c r="AD935" t="n">
-        <v>5504</v>
-      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -39766,9 +38533,6 @@
           <t>Wizz Air Napoca Marathon</t>
         </is>
       </c>
-      <c r="AD936" t="n">
-        <v>5504</v>
-      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -39791,9 +38555,6 @@
           <t>Wizz Air Napoca Marathon</t>
         </is>
       </c>
-      <c r="AD937" t="n">
-        <v>5504</v>
-      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -39916,9 +38677,6 @@
           <t>Maraton Lodz</t>
         </is>
       </c>
-      <c r="AD942" t="n">
-        <v>5395</v>
-      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -39941,9 +38699,6 @@
           <t>Maraton Lodz</t>
         </is>
       </c>
-      <c r="AD943" t="n">
-        <v>5395</v>
-      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -39966,9 +38721,6 @@
           <t>Maratona Monumental Brasilia</t>
         </is>
       </c>
-      <c r="AD944" t="n">
-        <v>5375</v>
-      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -39991,9 +38743,6 @@
           <t>Maratona Monumental Brasilia</t>
         </is>
       </c>
-      <c r="AD945" t="n">
-        <v>5375</v>
-      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -40016,9 +38765,6 @@
           <t>Maratona Monumental Brasilia</t>
         </is>
       </c>
-      <c r="AD946" t="n">
-        <v>5375</v>
-      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -40041,9 +38787,6 @@
           <t>Maratona Monumental Brasilia</t>
         </is>
       </c>
-      <c r="AD947" t="n">
-        <v>5375</v>
-      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -40096,9 +38839,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD949" t="n">
-        <v>5300</v>
-      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -40126,9 +38866,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD950" t="n">
-        <v>5300</v>
-      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -40151,9 +38888,6 @@
           <t>Bruells Ekiden</t>
         </is>
       </c>
-      <c r="AD951" t="n">
-        <v>5226</v>
-      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -40176,9 +38910,6 @@
           <t>Bruells Ekiden</t>
         </is>
       </c>
-      <c r="AD952" t="n">
-        <v>5226</v>
-      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -40226,9 +38957,6 @@
           <t>Münster Marathon</t>
         </is>
       </c>
-      <c r="AD954" t="n">
-        <v>5097</v>
-      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -40251,9 +38979,6 @@
           <t>Münster Marathon</t>
         </is>
       </c>
-      <c r="AD955" t="n">
-        <v>5097</v>
-      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -40276,9 +39001,6 @@
           <t>Münster Marathon</t>
         </is>
       </c>
-      <c r="AD956" t="n">
-        <v>5097</v>
-      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -40376,9 +39098,6 @@
           <t>Marathon de la mer</t>
         </is>
       </c>
-      <c r="AD960" t="n">
-        <v>5085</v>
-      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -40401,9 +39120,6 @@
           <t>Christchurch marathon</t>
         </is>
       </c>
-      <c r="AD961" t="n">
-        <v>5034</v>
-      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -40426,9 +39142,6 @@
           <t>Christchurch marathon</t>
         </is>
       </c>
-      <c r="AD962" t="n">
-        <v>5034</v>
-      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -40451,9 +39164,6 @@
           <t>Christchurch marathon</t>
         </is>
       </c>
-      <c r="AD963" t="n">
-        <v>5034</v>
-      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -40476,9 +39186,6 @@
           <t>SKF Goa River Marathon</t>
         </is>
       </c>
-      <c r="AD964" t="n">
-        <v>4980</v>
-      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -40501,9 +39208,6 @@
           <t>SKF Goa River Marathon</t>
         </is>
       </c>
-      <c r="AD965" t="n">
-        <v>4980</v>
-      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -40526,9 +39230,6 @@
           <t>SKF Goa River Marathon</t>
         </is>
       </c>
-      <c r="AD966" t="n">
-        <v>4980</v>
-      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -40551,9 +39252,6 @@
           <t>SKF Goa River Marathon</t>
         </is>
       </c>
-      <c r="AD967" t="n">
-        <v>4980</v>
-      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -40576,9 +39274,6 @@
           <t>SKF Goa River Marathon</t>
         </is>
       </c>
-      <c r="AD968" t="n">
-        <v>4980</v>
-      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -40626,9 +39321,6 @@
           <t>Bengaluru half Marathon</t>
         </is>
       </c>
-      <c r="AD970" t="n">
-        <v>4897</v>
-      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -40651,9 +39343,6 @@
           <t>Bengaluru half Marathon</t>
         </is>
       </c>
-      <c r="AD971" t="n">
-        <v>4897</v>
-      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -40676,9 +39365,6 @@
           <t>Bengaluru half Marathon</t>
         </is>
       </c>
-      <c r="AD972" t="n">
-        <v>4897</v>
-      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -40701,9 +39387,6 @@
           <t>Chester marathon</t>
         </is>
       </c>
-      <c r="AD973" t="n">
-        <v>4880</v>
-      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -40726,9 +39409,6 @@
           <t>Chester marathon</t>
         </is>
       </c>
-      <c r="AD974" t="n">
-        <v>4880</v>
-      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -40751,9 +39431,6 @@
           <t>Chester marathon</t>
         </is>
       </c>
-      <c r="AD975" t="n">
-        <v>4880</v>
-      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -40776,9 +39453,6 @@
           <t>Maraton Leon</t>
         </is>
       </c>
-      <c r="AD976" t="n">
-        <v>4879</v>
-      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -40801,9 +39475,6 @@
           <t>Maraton Leon</t>
         </is>
       </c>
-      <c r="AD977" t="n">
-        <v>4879</v>
-      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -40826,9 +39497,6 @@
           <t>Maraton Leon</t>
         </is>
       </c>
-      <c r="AD978" t="n">
-        <v>4879</v>
-      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -40851,9 +39519,6 @@
           <t>Cracovia Maraton</t>
         </is>
       </c>
-      <c r="AD979" t="n">
-        <v>4833</v>
-      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -40876,9 +39541,6 @@
           <t>Cracovia Maraton</t>
         </is>
       </c>
-      <c r="AD980" t="n">
-        <v>4833</v>
-      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -40926,9 +39588,6 @@
           <t>Kerzerslauf</t>
         </is>
       </c>
-      <c r="AD982" t="n">
-        <v>4824</v>
-      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -40951,9 +39610,6 @@
           <t>Kerzerslauf</t>
         </is>
       </c>
-      <c r="AD983" t="n">
-        <v>4824</v>
-      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
@@ -41001,9 +39657,6 @@
           <t>Maratona Internacional de Sao Paulo</t>
         </is>
       </c>
-      <c r="AD985" t="n">
-        <v>4824</v>
-      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -41026,9 +39679,6 @@
           <t>Maratona Internacional de Sao Paulo</t>
         </is>
       </c>
-      <c r="AD986" t="n">
-        <v>4824</v>
-      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -41051,9 +39701,6 @@
           <t>Maratona Internacional de Sao Paulo</t>
         </is>
       </c>
-      <c r="AD987" t="n">
-        <v>4824</v>
-      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -41076,9 +39723,6 @@
           <t>Maratona Internacional de Sao Paulo</t>
         </is>
       </c>
-      <c r="AD988" t="n">
-        <v>4824</v>
-      </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
@@ -41126,9 +39770,6 @@
           <t>Marathon du vignoble d’Alsace</t>
         </is>
       </c>
-      <c r="AD990" t="n">
-        <v>4773</v>
-      </c>
     </row>
     <row r="991">
       <c r="A991" t="inlineStr">
@@ -41151,9 +39792,6 @@
           <t>Marathon du vignoble d’Alsace</t>
         </is>
       </c>
-      <c r="AD991" t="n">
-        <v>4773</v>
-      </c>
     </row>
     <row r="992">
       <c r="A992" t="inlineStr">
@@ -41176,9 +39814,6 @@
           <t>Marathon du vignoble d’Alsace</t>
         </is>
       </c>
-      <c r="AD992" t="n">
-        <v>4773</v>
-      </c>
     </row>
     <row r="993">
       <c r="A993" t="inlineStr">
@@ -41201,9 +39836,6 @@
           <t>Media Elche</t>
         </is>
       </c>
-      <c r="AD993" t="n">
-        <v>4769</v>
-      </c>
     </row>
     <row r="994">
       <c r="A994" t="inlineStr">
@@ -41226,9 +39858,6 @@
           <t>Media Elche</t>
         </is>
       </c>
-      <c r="AD994" t="n">
-        <v>4769</v>
-      </c>
     </row>
     <row r="995">
       <c r="A995" t="inlineStr">
@@ -41251,9 +39880,6 @@
           <t>3-Länder-Marathon</t>
         </is>
       </c>
-      <c r="AD995" t="n">
-        <v>4724</v>
-      </c>
     </row>
     <row r="996">
       <c r="A996" t="inlineStr">
@@ -41276,9 +39902,6 @@
           <t>3-Länder-Marathon</t>
         </is>
       </c>
-      <c r="AD996" t="n">
-        <v>4724</v>
-      </c>
     </row>
     <row r="997">
       <c r="A997" t="inlineStr">
@@ -41301,9 +39924,6 @@
           <t>3-Länder-Marathon</t>
         </is>
       </c>
-      <c r="AD997" t="n">
-        <v>4724</v>
-      </c>
     </row>
     <row r="998">
       <c r="A998" t="inlineStr">
@@ -41326,9 +39946,6 @@
           <t>3-Länder-Marathon</t>
         </is>
       </c>
-      <c r="AD998" t="n">
-        <v>4724</v>
-      </c>
     </row>
     <row r="999">
       <c r="A999" t="inlineStr">
@@ -41351,9 +39968,6 @@
           <t>S25</t>
         </is>
       </c>
-      <c r="AD999" t="n">
-        <v>4700</v>
-      </c>
     </row>
     <row r="1000">
       <c r="A1000" t="inlineStr">
@@ -41376,9 +39990,6 @@
           <t>S25</t>
         </is>
       </c>
-      <c r="AD1000" t="n">
-        <v>4700</v>
-      </c>
     </row>
     <row r="1001">
       <c r="A1001" t="inlineStr">
@@ -41401,9 +40012,6 @@
           <t>S25</t>
         </is>
       </c>
-      <c r="AD1001" t="n">
-        <v>4700</v>
-      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
@@ -41451,9 +40059,6 @@
           <t>EVL Halbmarathon Leverkusen</t>
         </is>
       </c>
-      <c r="AD1003" t="n">
-        <v>4648</v>
-      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -41476,9 +40081,6 @@
           <t>EVL Halbmarathon Leverkusen</t>
         </is>
       </c>
-      <c r="AD1004" t="n">
-        <v>4648</v>
-      </c>
     </row>
     <row r="1005">
       <c r="A1005" t="inlineStr">
@@ -41501,9 +40103,6 @@
           <t>EVL Halbmarathon Leverkusen</t>
         </is>
       </c>
-      <c r="AD1005" t="n">
-        <v>4648</v>
-      </c>
     </row>
     <row r="1006">
       <c r="A1006" t="inlineStr">
@@ -41551,9 +40150,6 @@
           <t>Bengaluru 10K Challenge</t>
         </is>
       </c>
-      <c r="AD1007" t="n">
-        <v>4630</v>
-      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -41681,9 +40277,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1012" t="n">
-        <v>4520</v>
-      </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
@@ -41711,9 +40304,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1013" t="n">
-        <v>4520</v>
-      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -41741,9 +40331,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1014" t="n">
-        <v>4520</v>
-      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -41766,9 +40353,6 @@
           <t>Pro Potsdam Schlösserlauf</t>
         </is>
       </c>
-      <c r="AD1015" t="n">
-        <v>4520</v>
-      </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -41791,9 +40375,6 @@
           <t>Pro Potsdam Schlösserlauf</t>
         </is>
       </c>
-      <c r="AD1016" t="n">
-        <v>4520</v>
-      </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -41821,9 +40402,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1017" t="n">
-        <v>4497</v>
-      </c>
     </row>
     <row r="1018">
       <c r="A1018" t="inlineStr">
@@ -41851,9 +40429,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1018" t="n">
-        <v>4497</v>
-      </c>
     </row>
     <row r="1019">
       <c r="A1019" t="inlineStr">
@@ -41881,9 +40456,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1019" t="n">
-        <v>4497</v>
-      </c>
     </row>
     <row r="1020">
       <c r="A1020" t="inlineStr">
@@ -41911,9 +40483,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1020" t="n">
-        <v>4497</v>
-      </c>
     </row>
     <row r="1021">
       <c r="A1021" t="inlineStr">
@@ -41961,9 +40530,6 @@
           <t>Semi-Marathon de la Vente des Vins</t>
         </is>
       </c>
-      <c r="AD1022" t="n">
-        <v>4456</v>
-      </c>
     </row>
     <row r="1023">
       <c r="A1023" t="inlineStr">
@@ -41986,9 +40552,6 @@
           <t>Semi-Marathon de la Vente des Vins</t>
         </is>
       </c>
-      <c r="AD1023" t="n">
-        <v>4456</v>
-      </c>
     </row>
     <row r="1024">
       <c r="A1024" t="inlineStr">
@@ -42011,9 +40574,6 @@
           <t>Limassol Marathon</t>
         </is>
       </c>
-      <c r="AD1024" t="n">
-        <v>4424</v>
-      </c>
     </row>
     <row r="1025">
       <c r="A1025" t="inlineStr">
@@ -42036,9 +40596,6 @@
           <t>Limassol Marathon</t>
         </is>
       </c>
-      <c r="AD1025" t="n">
-        <v>4424</v>
-      </c>
     </row>
     <row r="1026">
       <c r="A1026" t="inlineStr">
@@ -42061,9 +40618,6 @@
           <t>Limassol Marathon</t>
         </is>
       </c>
-      <c r="AD1026" t="n">
-        <v>4424</v>
-      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -42086,9 +40640,6 @@
           <t>Limassol Marathon</t>
         </is>
       </c>
-      <c r="AD1027" t="n">
-        <v>4424</v>
-      </c>
     </row>
     <row r="1028">
       <c r="A1028" t="inlineStr">
@@ -42141,9 +40692,6 @@
           <t>Sparkassen Metropolmarathon</t>
         </is>
       </c>
-      <c r="AD1029" t="n">
-        <v>4384</v>
-      </c>
     </row>
     <row r="1030">
       <c r="A1030" t="inlineStr">
@@ -42166,9 +40714,6 @@
           <t>Sparkassen Metropolmarathon</t>
         </is>
       </c>
-      <c r="AD1030" t="n">
-        <v>4384</v>
-      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -42191,9 +40736,6 @@
           <t>Sparkassen Metropolmarathon</t>
         </is>
       </c>
-      <c r="AD1031" t="n">
-        <v>4384</v>
-      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -42216,9 +40758,6 @@
           <t>Würzburg marathon</t>
         </is>
       </c>
-      <c r="AD1032" t="n">
-        <v>4378</v>
-      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -42241,9 +40780,6 @@
           <t>Würzburg marathon</t>
         </is>
       </c>
-      <c r="AD1033" t="n">
-        <v>4378</v>
-      </c>
     </row>
     <row r="1034">
       <c r="A1034" t="inlineStr">
@@ -42266,9 +40802,6 @@
           <t>Würzburg marathon</t>
         </is>
       </c>
-      <c r="AD1034" t="n">
-        <v>4378</v>
-      </c>
     </row>
     <row r="1035">
       <c r="A1035" t="inlineStr">
@@ -42296,9 +40829,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1035" t="n">
-        <v>4369</v>
-      </c>
     </row>
     <row r="1036">
       <c r="A1036" t="inlineStr">
@@ -42326,9 +40856,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1036" t="n">
-        <v>4369</v>
-      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -42356,9 +40883,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1037" t="n">
-        <v>4369</v>
-      </c>
     </row>
     <row r="1038">
       <c r="A1038" t="inlineStr">
@@ -42381,9 +40905,6 @@
           <t>Province de Liège semi marathon</t>
         </is>
       </c>
-      <c r="AD1038" t="n">
-        <v>4357</v>
-      </c>
     </row>
     <row r="1039">
       <c r="A1039" t="inlineStr">
@@ -42406,9 +40927,6 @@
           <t>Province de Liège semi marathon</t>
         </is>
       </c>
-      <c r="AD1039" t="n">
-        <v>4357</v>
-      </c>
     </row>
     <row r="1040">
       <c r="A1040" t="inlineStr">
@@ -42431,9 +40949,6 @@
           <t>Province de Liège semi marathon</t>
         </is>
       </c>
-      <c r="AD1040" t="n">
-        <v>4357</v>
-      </c>
     </row>
     <row r="1041">
       <c r="A1041" t="inlineStr">
@@ -42486,9 +41001,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1042" t="n">
-        <v>4324</v>
-      </c>
     </row>
     <row r="1043">
       <c r="A1043" t="inlineStr">
@@ -42516,9 +41028,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1043" t="n">
-        <v>4324</v>
-      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -42546,9 +41055,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1044" t="n">
-        <v>4284</v>
-      </c>
     </row>
     <row r="1045">
       <c r="A1045" t="inlineStr">
@@ -42576,9 +41082,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1045" t="n">
-        <v>4284</v>
-      </c>
     </row>
     <row r="1046">
       <c r="A1046" t="inlineStr">
@@ -42606,9 +41109,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1046" t="n">
-        <v>4284</v>
-      </c>
     </row>
     <row r="1047">
       <c r="A1047" t="inlineStr">
@@ -42661,9 +41161,6 @@
           <t>Rotorua Marathon</t>
         </is>
       </c>
-      <c r="AD1048" t="n">
-        <v>4214</v>
-      </c>
     </row>
     <row r="1049">
       <c r="A1049" t="inlineStr">
@@ -42686,9 +41183,6 @@
           <t>Rotorua Marathon</t>
         </is>
       </c>
-      <c r="AD1049" t="n">
-        <v>4214</v>
-      </c>
     </row>
     <row r="1050">
       <c r="A1050" t="inlineStr">
@@ -42711,9 +41205,6 @@
           <t>Rotorua Marathon</t>
         </is>
       </c>
-      <c r="AD1050" t="n">
-        <v>4214</v>
-      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -42736,9 +41227,6 @@
           <t>Rotorua Marathon</t>
         </is>
       </c>
-      <c r="AD1051" t="n">
-        <v>4214</v>
-      </c>
     </row>
     <row r="1052">
       <c r="A1052" t="inlineStr">
@@ -42761,9 +41249,6 @@
           <t>Stramilano</t>
         </is>
       </c>
-      <c r="AD1052" t="n">
-        <v>4201</v>
-      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -42786,9 +41271,6 @@
           <t>Stramilano</t>
         </is>
       </c>
-      <c r="AD1053" t="n">
-        <v>4201</v>
-      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -42811,9 +41293,6 @@
           <t>Stramilano</t>
         </is>
       </c>
-      <c r="AD1054" t="n">
-        <v>4201</v>
-      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -42941,9 +41420,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1059" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -42971,9 +41447,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1060" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1061">
       <c r="A1061" t="inlineStr">
@@ -43001,9 +41474,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1061" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
@@ -43026,9 +41496,6 @@
           <t>Lotus Juhu Half Marathon</t>
         </is>
       </c>
-      <c r="AD1062" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1063">
       <c r="A1063" t="inlineStr">
@@ -43051,9 +41518,6 @@
           <t>Lotus Juhu Half Marathon</t>
         </is>
       </c>
-      <c r="AD1063" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1064">
       <c r="A1064" t="inlineStr">
@@ -43076,9 +41540,6 @@
           <t>Niveus Mangalore Marathon</t>
         </is>
       </c>
-      <c r="AD1064" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1065">
       <c r="A1065" t="inlineStr">
@@ -43101,9 +41562,6 @@
           <t>Niveus Mangalore Marathon</t>
         </is>
       </c>
-      <c r="AD1065" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -43126,9 +41584,6 @@
           <t>Niveus Mangalore Marathon</t>
         </is>
       </c>
-      <c r="AD1066" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1067">
       <c r="A1067" t="inlineStr">
@@ -43151,9 +41606,6 @@
           <t>Niveus Mangalore Marathon</t>
         </is>
       </c>
-      <c r="AD1067" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1068">
       <c r="A1068" t="inlineStr">
@@ -43176,9 +41628,6 @@
           <t>Rome 15K</t>
         </is>
       </c>
-      <c r="AD1068" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1069">
       <c r="A1069" t="inlineStr">
@@ -43226,9 +41675,6 @@
           <t>Hyderabad 10K</t>
         </is>
       </c>
-      <c r="AD1070" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1071">
       <c r="A1071" t="inlineStr">
@@ -43251,9 +41697,6 @@
           <t>Hyderabad 10K</t>
         </is>
       </c>
-      <c r="AD1071" t="n">
-        <v>4150</v>
-      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
@@ -43301,9 +41744,6 @@
           <t>Half Marathon Delhi</t>
         </is>
       </c>
-      <c r="AD1073" t="n">
-        <v>4076</v>
-      </c>
     </row>
     <row r="1074">
       <c r="A1074" t="inlineStr">
@@ -43326,9 +41766,6 @@
           <t>Half Marathon Delhi</t>
         </is>
       </c>
-      <c r="AD1074" t="n">
-        <v>4076</v>
-      </c>
     </row>
     <row r="1075">
       <c r="A1075" t="inlineStr">
@@ -43351,9 +41788,6 @@
           <t>Half Marathon Delhi</t>
         </is>
       </c>
-      <c r="AD1075" t="n">
-        <v>4076</v>
-      </c>
     </row>
     <row r="1076">
       <c r="A1076" t="inlineStr">
@@ -43376,9 +41810,6 @@
           <t>Napa To Sonama</t>
         </is>
       </c>
-      <c r="AD1076" t="n">
-        <v>4060</v>
-      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -43401,9 +41832,6 @@
           <t>Napa To Sonama</t>
         </is>
       </c>
-      <c r="AD1077" t="n">
-        <v>4060</v>
-      </c>
     </row>
     <row r="1078">
       <c r="A1078" t="inlineStr">
@@ -43426,9 +41854,6 @@
           <t>Foulées d’Orléans</t>
         </is>
       </c>
-      <c r="AD1078" t="n">
-        <v>4056</v>
-      </c>
     </row>
     <row r="1079">
       <c r="A1079" t="inlineStr">
@@ -43451,9 +41876,6 @@
           <t>Foulées d’Orléans</t>
         </is>
       </c>
-      <c r="AD1079" t="n">
-        <v>4056</v>
-      </c>
     </row>
     <row r="1080">
       <c r="A1080" t="inlineStr">
@@ -43476,9 +41898,6 @@
           <t>Foulées d’Orléans</t>
         </is>
       </c>
-      <c r="AD1080" t="n">
-        <v>4056</v>
-      </c>
     </row>
     <row r="1081">
       <c r="A1081" t="inlineStr">
@@ -43531,9 +41950,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1082" t="n">
-        <v>4012</v>
-      </c>
     </row>
     <row r="1083">
       <c r="A1083" t="inlineStr">
@@ -43561,9 +41977,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1083" t="n">
-        <v>4012</v>
-      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
@@ -43591,9 +42004,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1084" t="n">
-        <v>4012</v>
-      </c>
     </row>
     <row r="1085">
       <c r="A1085" t="inlineStr">
@@ -43621,9 +42031,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1085" t="n">
-        <v>4012</v>
-      </c>
     </row>
     <row r="1086">
       <c r="A1086" t="inlineStr">
@@ -43646,9 +42053,6 @@
           <t>Corrida de Santo Antonio</t>
         </is>
       </c>
-      <c r="AD1086" t="n">
-        <v>3983</v>
-      </c>
     </row>
     <row r="1087">
       <c r="A1087" t="inlineStr">
@@ -43756,9 +42160,6 @@
           <t>Maratona di Palermo</t>
         </is>
       </c>
-      <c r="AD1090" t="n">
-        <v>3832</v>
-      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -43781,9 +42182,6 @@
           <t>Maratona di Palermo</t>
         </is>
       </c>
-      <c r="AD1091" t="n">
-        <v>3832</v>
-      </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
@@ -43806,9 +42204,6 @@
           <t>Half Marathon Garda Trentino</t>
         </is>
       </c>
-      <c r="AD1092" t="n">
-        <v>3776</v>
-      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -43831,9 +42226,6 @@
           <t>Half Marathon Garda Trentino</t>
         </is>
       </c>
-      <c r="AD1093" t="n">
-        <v>3776</v>
-      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -43856,9 +42248,6 @@
           <t>Half Marathon Garda Trentino</t>
         </is>
       </c>
-      <c r="AD1094" t="n">
-        <v>3776</v>
-      </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -43881,9 +42270,6 @@
           <t>Nieuwpoort Marathon</t>
         </is>
       </c>
-      <c r="AD1095" t="n">
-        <v>3759</v>
-      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -43906,9 +42292,6 @@
           <t>Nieuwpoort Marathon</t>
         </is>
       </c>
-      <c r="AD1096" t="n">
-        <v>3759</v>
-      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -43931,9 +42314,6 @@
           <t>Nieuwpoort Marathon</t>
         </is>
       </c>
-      <c r="AD1097" t="n">
-        <v>3759</v>
-      </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
@@ -43956,9 +42336,6 @@
           <t>Nieuwpoort Marathon</t>
         </is>
       </c>
-      <c r="AD1098" t="n">
-        <v>3759</v>
-      </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
@@ -43981,9 +42358,6 @@
           <t>Bergamo21</t>
         </is>
       </c>
-      <c r="AD1099" t="n">
-        <v>3737</v>
-      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -44006,9 +42380,6 @@
           <t>Bergamo21</t>
         </is>
       </c>
-      <c r="AD1100" t="n">
-        <v>3737</v>
-      </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
@@ -44081,9 +42452,6 @@
           <t>Marathon Comar Tunis-Carthage</t>
         </is>
       </c>
-      <c r="AD1103" t="n">
-        <v>3710</v>
-      </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -44106,9 +42474,6 @@
           <t>Marathon Comar Tunis-Carthage</t>
         </is>
       </c>
-      <c r="AD1104" t="n">
-        <v>3710</v>
-      </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
@@ -44131,9 +42496,6 @@
           <t>Marathon Comar Tunis-Carthage</t>
         </is>
       </c>
-      <c r="AD1105" t="n">
-        <v>3710</v>
-      </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
@@ -44156,9 +42518,6 @@
           <t>Poseidon Athens Half Marathon</t>
         </is>
       </c>
-      <c r="AD1106" t="n">
-        <v>3680</v>
-      </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
@@ -44181,9 +42540,6 @@
           <t>Poseidon Athens Half Marathon</t>
         </is>
       </c>
-      <c r="AD1107" t="n">
-        <v>3680</v>
-      </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
@@ -44206,9 +42562,6 @@
           <t>Poseidon Athens Half Marathon</t>
         </is>
       </c>
-      <c r="AD1108" t="n">
-        <v>3680</v>
-      </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
@@ -44231,9 +42584,6 @@
           <t>Phuket marathon</t>
         </is>
       </c>
-      <c r="AD1109" t="n">
-        <v>3677</v>
-      </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
@@ -44256,9 +42606,6 @@
           <t>Phuket marathon</t>
         </is>
       </c>
-      <c r="AD1110" t="n">
-        <v>3677</v>
-      </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
@@ -44281,9 +42628,6 @@
           <t>Phuket marathon</t>
         </is>
       </c>
-      <c r="AD1111" t="n">
-        <v>3677</v>
-      </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
@@ -44306,9 +42650,6 @@
           <t>Phuket marathon</t>
         </is>
       </c>
-      <c r="AD1112" t="n">
-        <v>3677</v>
-      </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
@@ -44356,9 +42697,6 @@
           <t>les Boucles dunkerquoises</t>
         </is>
       </c>
-      <c r="AD1114" t="n">
-        <v>3601</v>
-      </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
@@ -44381,9 +42719,6 @@
           <t>les Boucles dunkerquoises</t>
         </is>
       </c>
-      <c r="AD1115" t="n">
-        <v>3601</v>
-      </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
@@ -44406,9 +42741,6 @@
           <t>les Boucles dunkerquoises</t>
         </is>
       </c>
-      <c r="AD1116" t="n">
-        <v>3601</v>
-      </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
@@ -44431,9 +42763,6 @@
           <t>Monaco Run</t>
         </is>
       </c>
-      <c r="AD1117" t="n">
-        <v>3561</v>
-      </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
@@ -44456,9 +42785,6 @@
           <t>Monaco Run</t>
         </is>
       </c>
-      <c r="AD1118" t="n">
-        <v>3561</v>
-      </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
@@ -44481,9 +42807,6 @@
           <t>Monaco Run</t>
         </is>
       </c>
-      <c r="AD1119" t="n">
-        <v>3561</v>
-      </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
@@ -44506,9 +42829,6 @@
           <t>Savannah Southern Half</t>
         </is>
       </c>
-      <c r="AD1120" t="n">
-        <v>3503</v>
-      </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
@@ -44531,9 +42851,6 @@
           <t>Savannah Southern Half</t>
         </is>
       </c>
-      <c r="AD1121" t="n">
-        <v>3503</v>
-      </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
@@ -44556,9 +42873,6 @@
           <t>Mezza di Genova</t>
         </is>
       </c>
-      <c r="AD1122" t="n">
-        <v>3497</v>
-      </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
@@ -44581,9 +42895,6 @@
           <t>Mezza di Genova</t>
         </is>
       </c>
-      <c r="AD1123" t="n">
-        <v>3497</v>
-      </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
@@ -44631,9 +42942,6 @@
           <t>Waterfront Half Marathon</t>
         </is>
       </c>
-      <c r="AD1125" t="n">
-        <v>3440</v>
-      </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
@@ -44656,9 +42964,6 @@
           <t>Waterfront Half Marathon</t>
         </is>
       </c>
-      <c r="AD1126" t="n">
-        <v>3440</v>
-      </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
@@ -44681,9 +42986,6 @@
           <t>Waterfront Half Marathon</t>
         </is>
       </c>
-      <c r="AD1127" t="n">
-        <v>3440</v>
-      </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
@@ -44706,9 +43008,6 @@
           <t>Marathon Golfe de Saint-Tropez</t>
         </is>
       </c>
-      <c r="AD1128" t="n">
-        <v>3420</v>
-      </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
@@ -44731,9 +43030,6 @@
           <t>Marathon Golfe de Saint-Tropez</t>
         </is>
       </c>
-      <c r="AD1129" t="n">
-        <v>3420</v>
-      </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
@@ -44756,9 +43052,6 @@
           <t>Marathon Golfe de Saint-Tropez</t>
         </is>
       </c>
-      <c r="AD1130" t="n">
-        <v>3420</v>
-      </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
@@ -44781,9 +43074,6 @@
           <t>Mysuru Marathon</t>
         </is>
       </c>
-      <c r="AD1131" t="n">
-        <v>3417</v>
-      </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
@@ -44806,9 +43096,6 @@
           <t>Mysuru Marathon</t>
         </is>
       </c>
-      <c r="AD1132" t="n">
-        <v>3417</v>
-      </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
@@ -44831,9 +43118,6 @@
           <t>Mysuru Marathon</t>
         </is>
       </c>
-      <c r="AD1133" t="n">
-        <v>3417</v>
-      </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
@@ -44856,9 +43140,6 @@
           <t>Mysuru Marathon</t>
         </is>
       </c>
-      <c r="AD1134" t="n">
-        <v>3417</v>
-      </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
@@ -44881,9 +43162,6 @@
           <t>Monza21</t>
         </is>
       </c>
-      <c r="AD1135" t="n">
-        <v>3409</v>
-      </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
@@ -44906,9 +43184,6 @@
           <t>Monza21</t>
         </is>
       </c>
-      <c r="AD1136" t="n">
-        <v>3409</v>
-      </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
@@ -44981,9 +43256,6 @@
           <t>Mattoni Running Festival Usti Nad Labem</t>
         </is>
       </c>
-      <c r="AD1139" t="n">
-        <v>3378</v>
-      </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
@@ -45006,9 +43278,6 @@
           <t>Mattoni Running Festival Usti Nad Labem</t>
         </is>
       </c>
-      <c r="AD1140" t="n">
-        <v>3378</v>
-      </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
@@ -45031,9 +43300,6 @@
           <t>Waterford Viking Marathon</t>
         </is>
       </c>
-      <c r="AD1141" t="n">
-        <v>3378</v>
-      </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
@@ -45056,9 +43322,6 @@
           <t>Waterford Viking Marathon</t>
         </is>
       </c>
-      <c r="AD1142" t="n">
-        <v>3378</v>
-      </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
@@ -45081,9 +43344,6 @@
           <t>Waterford Viking Marathon</t>
         </is>
       </c>
-      <c r="AD1143" t="n">
-        <v>3378</v>
-      </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
@@ -45106,9 +43366,6 @@
           <t>Mattoni Running Festival Ceské Budejovice</t>
         </is>
       </c>
-      <c r="AD1144" t="n">
-        <v>3356</v>
-      </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
@@ -45131,9 +43388,6 @@
           <t>Mattoni Running Festival Ceské Budejovice</t>
         </is>
       </c>
-      <c r="AD1145" t="n">
-        <v>3356</v>
-      </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
@@ -45156,9 +43410,6 @@
           <t>Mattoni Running Festival Ceské Budejovice</t>
         </is>
       </c>
-      <c r="AD1146" t="n">
-        <v>3356</v>
-      </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
@@ -45181,9 +43432,6 @@
           <t>IIT Bombay Half Marathon</t>
         </is>
       </c>
-      <c r="AD1147" t="n">
-        <v>3320</v>
-      </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
@@ -45206,9 +43454,6 @@
           <t>IIT Bombay Half Marathon</t>
         </is>
       </c>
-      <c r="AD1148" t="n">
-        <v>3320</v>
-      </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
@@ -45231,9 +43476,6 @@
           <t>IIT Bombay Half Marathon</t>
         </is>
       </c>
-      <c r="AD1149" t="n">
-        <v>3320</v>
-      </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
@@ -45281,9 +43523,6 @@
           <t>Brescia art marathon</t>
         </is>
       </c>
-      <c r="AD1151" t="n">
-        <v>3285</v>
-      </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
@@ -45306,9 +43545,6 @@
           <t>Brescia art marathon</t>
         </is>
       </c>
-      <c r="AD1152" t="n">
-        <v>3285</v>
-      </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
@@ -45331,9 +43567,6 @@
           <t>Brescia art marathon</t>
         </is>
       </c>
-      <c r="AD1153" t="n">
-        <v>3285</v>
-      </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
@@ -45356,9 +43589,6 @@
           <t>Wellington Marathon</t>
         </is>
       </c>
-      <c r="AD1154" t="n">
-        <v>3268</v>
-      </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
@@ -45381,9 +43611,6 @@
           <t>Wellington Marathon</t>
         </is>
       </c>
-      <c r="AD1155" t="n">
-        <v>3268</v>
-      </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
@@ -45406,9 +43633,6 @@
           <t>Wellington Marathon</t>
         </is>
       </c>
-      <c r="AD1156" t="n">
-        <v>3268</v>
-      </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
@@ -45431,9 +43655,6 @@
           <t>Half marathon Firenze</t>
         </is>
       </c>
-      <c r="AD1157" t="n">
-        <v>3206</v>
-      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -45481,9 +43702,6 @@
           <t>Besox Halve Van Oostende</t>
         </is>
       </c>
-      <c r="AD1159" t="n">
-        <v>3133</v>
-      </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -45506,9 +43724,6 @@
           <t>Besox Halve Van Oostende</t>
         </is>
       </c>
-      <c r="AD1160" t="n">
-        <v>3133</v>
-      </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
@@ -45531,9 +43746,6 @@
           <t>Medio Maraton Almeria</t>
         </is>
       </c>
-      <c r="AD1161" t="n">
-        <v>3111</v>
-      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -45556,9 +43768,6 @@
           <t>Medio Maraton Almeria</t>
         </is>
       </c>
-      <c r="AD1162" t="n">
-        <v>3111</v>
-      </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
@@ -45606,9 +43815,6 @@
           <t>Wiesbaden Marathon</t>
         </is>
       </c>
-      <c r="AD1164" t="n">
-        <v>3038</v>
-      </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
@@ -45631,9 +43837,6 @@
           <t>Wiesbaden Marathon</t>
         </is>
       </c>
-      <c r="AD1165" t="n">
-        <v>3038</v>
-      </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
@@ -45656,9 +43859,6 @@
           <t>Wiesbaden Marathon</t>
         </is>
       </c>
-      <c r="AD1166" t="n">
-        <v>3038</v>
-      </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
@@ -45681,9 +43881,6 @@
           <t>Wiesbaden Marathon</t>
         </is>
       </c>
-      <c r="AD1167" t="n">
-        <v>3038</v>
-      </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
@@ -45706,9 +43903,6 @@
           <t>Salto 15K Donostia San Sebastian</t>
         </is>
       </c>
-      <c r="AD1168" t="n">
-        <v>3018</v>
-      </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
@@ -45781,9 +43975,6 @@
           <t>Decathlon Night Run Budapest</t>
         </is>
       </c>
-      <c r="AD1171" t="n">
-        <v>2984</v>
-      </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
@@ -45806,9 +43997,6 @@
           <t>Decathlon Night Run Budapest</t>
         </is>
       </c>
-      <c r="AD1172" t="n">
-        <v>2984</v>
-      </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
@@ -45831,9 +44019,6 @@
           <t>Decathlon Night Run Budapest</t>
         </is>
       </c>
-      <c r="AD1173" t="n">
-        <v>2984</v>
-      </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
@@ -45856,9 +44041,6 @@
           <t>Zagreb Marathon</t>
         </is>
       </c>
-      <c r="AD1174" t="n">
-        <v>2970</v>
-      </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
@@ -45881,9 +44063,6 @@
           <t>Zagreb Marathon</t>
         </is>
       </c>
-      <c r="AD1175" t="n">
-        <v>2970</v>
-      </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
@@ -45906,9 +44085,6 @@
           <t>Zagreb Marathon</t>
         </is>
       </c>
-      <c r="AD1176" t="n">
-        <v>2970</v>
-      </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
@@ -45931,9 +44107,6 @@
           <t>Gurugram Half Marathon</t>
         </is>
       </c>
-      <c r="AD1177" t="n">
-        <v>2939</v>
-      </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
@@ -45956,9 +44129,6 @@
           <t>Gurugram Half Marathon</t>
         </is>
       </c>
-      <c r="AD1178" t="n">
-        <v>2939</v>
-      </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
@@ -45981,9 +44151,6 @@
           <t>Gurugram Half Marathon</t>
         </is>
       </c>
-      <c r="AD1179" t="n">
-        <v>2939</v>
-      </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
@@ -46056,9 +44223,6 @@
           <t>Foulées du Populaire</t>
         </is>
       </c>
-      <c r="AD1182" t="n">
-        <v>2890</v>
-      </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
@@ -46081,9 +44245,6 @@
           <t>Foulées du Populaire</t>
         </is>
       </c>
-      <c r="AD1183" t="n">
-        <v>2890</v>
-      </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
@@ -46181,9 +44342,6 @@
           <t>Cairns Marathon Festival</t>
         </is>
       </c>
-      <c r="AD1187" t="n">
-        <v>2803</v>
-      </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
@@ -46206,9 +44364,6 @@
           <t>Cairns Marathon Festival</t>
         </is>
       </c>
-      <c r="AD1188" t="n">
-        <v>2803</v>
-      </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
@@ -46231,9 +44386,6 @@
           <t>Cairns Marathon Festival</t>
         </is>
       </c>
-      <c r="AD1189" t="n">
-        <v>2803</v>
-      </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
@@ -46256,9 +44408,6 @@
           <t>Cairns Marathon Festival</t>
         </is>
       </c>
-      <c r="AD1190" t="n">
-        <v>2803</v>
-      </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
@@ -46281,9 +44430,6 @@
           <t>Winter Run Istanbul</t>
         </is>
       </c>
-      <c r="AD1191" t="n">
-        <v>2788</v>
-      </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
@@ -46306,9 +44452,6 @@
           <t>Winter Run Istanbul</t>
         </is>
       </c>
-      <c r="AD1192" t="n">
-        <v>2788</v>
-      </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
@@ -46356,9 +44499,6 @@
           <t>Marathon Poitiers-Futuroscope</t>
         </is>
       </c>
-      <c r="AD1194" t="n">
-        <v>2779</v>
-      </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
@@ -46406,9 +44546,6 @@
           <t>Marathon Poitiers-Futuroscope</t>
         </is>
       </c>
-      <c r="AD1196" t="n">
-        <v>2779</v>
-      </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
@@ -46431,9 +44568,6 @@
           <t>Marathon Poitiers-Futuroscope</t>
         </is>
       </c>
-      <c r="AD1197" t="n">
-        <v>2779</v>
-      </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
@@ -46456,9 +44590,6 @@
           <t>Marathon Poitiers-Futuroscope</t>
         </is>
       </c>
-      <c r="AD1198" t="n">
-        <v>2779</v>
-      </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
@@ -46556,9 +44687,6 @@
           <t>Bijlmer run</t>
         </is>
       </c>
-      <c r="AD1202" t="n">
-        <v>2699</v>
-      </c>
     </row>
     <row r="1203">
       <c r="A1203" t="inlineStr">
@@ -46581,9 +44709,6 @@
           <t>Bijlmer run</t>
         </is>
       </c>
-      <c r="AD1203" t="n">
-        <v>2699</v>
-      </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
@@ -46606,9 +44731,6 @@
           <t>Bijlmer run</t>
         </is>
       </c>
-      <c r="AD1204" t="n">
-        <v>2699</v>
-      </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
@@ -46631,9 +44753,6 @@
           <t>Media Maraton Bucaramanga</t>
         </is>
       </c>
-      <c r="AD1205" t="n">
-        <v>2695</v>
-      </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
@@ -46656,9 +44775,6 @@
           <t>Media Maraton Bucaramanga</t>
         </is>
       </c>
-      <c r="AD1206" t="n">
-        <v>2695</v>
-      </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
@@ -46681,9 +44797,6 @@
           <t>Media Maraton Bucaramanga</t>
         </is>
       </c>
-      <c r="AD1207" t="n">
-        <v>2695</v>
-      </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
@@ -46806,9 +44919,6 @@
           <t>Maratona di Pisa</t>
         </is>
       </c>
-      <c r="AD1212" t="n">
-        <v>2655</v>
-      </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
@@ -46831,9 +44941,6 @@
           <t>Maratona di Pisa</t>
         </is>
       </c>
-      <c r="AD1213" t="n">
-        <v>2655</v>
-      </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
@@ -46856,9 +44963,6 @@
           <t>Split Marathon</t>
         </is>
       </c>
-      <c r="AD1214" t="n">
-        <v>2645</v>
-      </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
@@ -46881,9 +44985,6 @@
           <t>Split Marathon</t>
         </is>
       </c>
-      <c r="AD1215" t="n">
-        <v>2645</v>
-      </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
@@ -46906,9 +45007,6 @@
           <t>Split Marathon</t>
         </is>
       </c>
-      <c r="AD1216" t="n">
-        <v>2645</v>
-      </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
@@ -46931,9 +45029,6 @@
           <t>Inverness Half Marathon</t>
         </is>
       </c>
-      <c r="AD1217" t="n">
-        <v>2564</v>
-      </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
@@ -46956,9 +45051,6 @@
           <t>Inverness Half Marathon</t>
         </is>
       </c>
-      <c r="AD1218" t="n">
-        <v>2564</v>
-      </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
@@ -47091,9 +45183,6 @@
           <t>Demi-Marathon de Mont-Tremblant</t>
         </is>
       </c>
-      <c r="AD1223" t="n">
-        <v>2506</v>
-      </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
@@ -47116,9 +45205,6 @@
           <t>Demi-Marathon de Mont-Tremblant</t>
         </is>
       </c>
-      <c r="AD1224" t="n">
-        <v>2506</v>
-      </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
@@ -47141,9 +45227,6 @@
           <t>Demi-Marathon de Mont-Tremblant</t>
         </is>
       </c>
-      <c r="AD1225" t="n">
-        <v>2506</v>
-      </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
@@ -47166,9 +45249,6 @@
           <t>Lauf Für Mehir Zeit</t>
         </is>
       </c>
-      <c r="AD1226" t="n">
-        <v>2505</v>
-      </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
@@ -47191,9 +45271,6 @@
           <t>Lauf Für Mehir Zeit</t>
         </is>
       </c>
-      <c r="AD1227" t="n">
-        <v>2505</v>
-      </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
@@ -47216,9 +45293,6 @@
           <t>Lauf Für Mehir Zeit</t>
         </is>
       </c>
-      <c r="AD1228" t="n">
-        <v>2505</v>
-      </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
@@ -47241,9 +45315,6 @@
           <t>Lucknow Marathon</t>
         </is>
       </c>
-      <c r="AD1229" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
@@ -47266,9 +45337,6 @@
           <t>Lucknow Marathon</t>
         </is>
       </c>
-      <c r="AD1230" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
@@ -47291,9 +45359,6 @@
           <t>Lucknow Marathon</t>
         </is>
       </c>
-      <c r="AD1231" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
@@ -47316,9 +45381,6 @@
           <t>Run Malibu</t>
         </is>
       </c>
-      <c r="AD1232" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
@@ -47341,9 +45403,6 @@
           <t>Run Malibu</t>
         </is>
       </c>
-      <c r="AD1233" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
@@ -47426,9 +45485,6 @@
           <t>Federal Bank Pune Marathon</t>
         </is>
       </c>
-      <c r="AD1236" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
@@ -47451,9 +45507,6 @@
           <t>Federal Bank Pune Marathon</t>
         </is>
       </c>
-      <c r="AD1237" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
@@ -47476,9 +45529,6 @@
           <t>Federal Bank Pune Marathon</t>
         </is>
       </c>
-      <c r="AD1238" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
@@ -47501,9 +45551,6 @@
           <t>Federal Bank Pune Marathon</t>
         </is>
       </c>
-      <c r="AD1239" t="n">
-        <v>2490</v>
-      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
@@ -47551,9 +45598,6 @@
           <t>La mezza di Torino</t>
         </is>
       </c>
-      <c r="AD1241" t="n">
-        <v>2422</v>
-      </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -47576,9 +45620,6 @@
           <t>La mezza di Torino</t>
         </is>
       </c>
-      <c r="AD1242" t="n">
-        <v>2422</v>
-      </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
@@ -47601,9 +45642,6 @@
           <t>KLM Curacao Marathon</t>
         </is>
       </c>
-      <c r="AD1243" t="n">
-        <v>2386</v>
-      </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
@@ -47626,9 +45664,6 @@
           <t>KLM Curacao Marathon</t>
         </is>
       </c>
-      <c r="AD1244" t="n">
-        <v>2386</v>
-      </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
@@ -47651,9 +45686,6 @@
           <t>KLM Curacao Marathon</t>
         </is>
       </c>
-      <c r="AD1245" t="n">
-        <v>2386</v>
-      </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
@@ -47676,9 +45708,6 @@
           <t>KLM Curacao Marathon</t>
         </is>
       </c>
-      <c r="AD1246" t="n">
-        <v>2386</v>
-      </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
@@ -47776,9 +45805,6 @@
           <t>Kolkata Full Marathon</t>
         </is>
       </c>
-      <c r="AD1250" t="n">
-        <v>2377</v>
-      </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
@@ -47826,9 +45852,6 @@
           <t>Conegliano Valdobbiadene Prosecco Running festival</t>
         </is>
       </c>
-      <c r="AD1252" t="n">
-        <v>2361</v>
-      </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
@@ -47851,9 +45874,6 @@
           <t>Conegliano Valdobbiadene Prosecco Running festival</t>
         </is>
       </c>
-      <c r="AD1253" t="n">
-        <v>2361</v>
-      </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
@@ -47876,9 +45896,6 @@
           <t>Conegliano Valdobbiadene Prosecco Running festival</t>
         </is>
       </c>
-      <c r="AD1254" t="n">
-        <v>2361</v>
-      </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
@@ -47981,9 +45998,6 @@
           <t>Rock'n'Roll Taipei</t>
         </is>
       </c>
-      <c r="AD1258" t="n">
-        <v>2305</v>
-      </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
@@ -48006,9 +46020,6 @@
           <t>Rock'n'Roll Taipei</t>
         </is>
       </c>
-      <c r="AD1259" t="n">
-        <v>2305</v>
-      </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
@@ -48061,9 +46072,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1261" t="n">
-        <v>2232</v>
-      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
@@ -48091,9 +46099,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1262" t="n">
-        <v>2232</v>
-      </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
@@ -48116,9 +46121,6 @@
           <t>Runkara International Half Marathon</t>
         </is>
       </c>
-      <c r="AD1263" t="n">
-        <v>2204</v>
-      </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
@@ -48141,9 +46143,6 @@
           <t>Runkara International Half Marathon</t>
         </is>
       </c>
-      <c r="AD1264" t="n">
-        <v>2204</v>
-      </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
@@ -48166,9 +46165,6 @@
           <t>Runkara International Half Marathon</t>
         </is>
       </c>
-      <c r="AD1265" t="n">
-        <v>2204</v>
-      </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -48191,9 +46187,6 @@
           <t>Bucharest international half marathon</t>
         </is>
       </c>
-      <c r="AD1266" t="n">
-        <v>2122</v>
-      </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
@@ -48216,9 +46209,6 @@
           <t>Bucharest international half marathon</t>
         </is>
       </c>
-      <c r="AD1267" t="n">
-        <v>2122</v>
-      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
@@ -48266,9 +46256,6 @@
           <t>La route du vin</t>
         </is>
       </c>
-      <c r="AD1269" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
@@ -48291,9 +46278,6 @@
           <t>La route du vin</t>
         </is>
       </c>
-      <c r="AD1270" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
@@ -48316,9 +46300,6 @@
           <t>La route du vin</t>
         </is>
       </c>
-      <c r="AD1271" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -48346,9 +46327,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1272" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
@@ -48376,9 +46354,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1273" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -48406,9 +46381,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1274" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
@@ -48436,9 +46408,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1275" t="n">
-        <v>2075</v>
-      </c>
     </row>
     <row r="1276">
       <c r="A1276" t="inlineStr">
@@ -48491,9 +46460,6 @@
           <t>Newcastle-Gateshead Marathon</t>
         </is>
       </c>
-      <c r="AD1277" t="n">
-        <v>2036</v>
-      </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
@@ -48516,9 +46482,6 @@
           <t>Newcastle-Gateshead Marathon</t>
         </is>
       </c>
-      <c r="AD1278" t="n">
-        <v>2036</v>
-      </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
@@ -48541,9 +46504,6 @@
           <t>Newcastle-Gateshead Marathon</t>
         </is>
       </c>
-      <c r="AD1279" t="n">
-        <v>2036</v>
-      </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
@@ -48566,9 +46526,6 @@
           <t>SportScheck Run Köln</t>
         </is>
       </c>
-      <c r="AD1280" t="n">
-        <v>2017</v>
-      </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
@@ -48591,9 +46548,6 @@
           <t>SportScheck Run Köln</t>
         </is>
       </c>
-      <c r="AD1281" t="n">
-        <v>2017</v>
-      </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
@@ -48616,9 +46570,6 @@
           <t>Halbmaratho Altötting</t>
         </is>
       </c>
-      <c r="AD1282" t="n">
-        <v>2012</v>
-      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -48666,9 +46617,6 @@
           <t>Media Maraton Bidasoa</t>
         </is>
       </c>
-      <c r="AD1284" t="n">
-        <v>1991</v>
-      </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
@@ -48691,9 +46639,6 @@
           <t>Media Maraton Bidasoa</t>
         </is>
       </c>
-      <c r="AD1285" t="n">
-        <v>1991</v>
-      </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
@@ -48791,9 +46736,6 @@
           <t>Havana marathon</t>
         </is>
       </c>
-      <c r="AD1289" t="n">
-        <v>1954</v>
-      </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
@@ -48816,9 +46758,6 @@
           <t>Havana marathon</t>
         </is>
       </c>
-      <c r="AD1290" t="n">
-        <v>1954</v>
-      </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
@@ -48841,9 +46780,6 @@
           <t>Havana marathon</t>
         </is>
       </c>
-      <c r="AD1291" t="n">
-        <v>1954</v>
-      </c>
     </row>
     <row r="1292">
       <c r="A1292" t="inlineStr">
@@ -48866,9 +46802,6 @@
           <t>Havana marathon</t>
         </is>
       </c>
-      <c r="AD1292" t="n">
-        <v>1954</v>
-      </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
@@ -48891,9 +46824,6 @@
           <t>Coventry Half marathon</t>
         </is>
       </c>
-      <c r="AD1293" t="n">
-        <v>1936</v>
-      </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
@@ -48916,9 +46846,6 @@
           <t>Coventry Half marathon</t>
         </is>
       </c>
-      <c r="AD1294" t="n">
-        <v>1936</v>
-      </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
@@ -48941,9 +46868,6 @@
           <t>Marathon di Parma</t>
         </is>
       </c>
-      <c r="AD1295" t="n">
-        <v>1909</v>
-      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
@@ -48966,9 +46890,6 @@
           <t>Marathon di Parma</t>
         </is>
       </c>
-      <c r="AD1296" t="n">
-        <v>1909</v>
-      </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
@@ -48991,9 +46912,6 @@
           <t>Marathon di Parma</t>
         </is>
       </c>
-      <c r="AD1297" t="n">
-        <v>1909</v>
-      </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
@@ -49041,9 +46959,6 @@
           <t>Hyderabad Hitec Marathon</t>
         </is>
       </c>
-      <c r="AD1299" t="n">
-        <v>1879</v>
-      </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
@@ -49116,9 +47031,6 @@
           <t>Hyderabad Hitec Marathon</t>
         </is>
       </c>
-      <c r="AD1302" t="n">
-        <v>1879</v>
-      </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
@@ -49141,9 +47053,6 @@
           <t>Energa Gdansk Marathon</t>
         </is>
       </c>
-      <c r="AD1303" t="n">
-        <v>1855</v>
-      </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
@@ -49166,9 +47075,6 @@
           <t>Energa Gdansk Marathon</t>
         </is>
       </c>
-      <c r="AD1304" t="n">
-        <v>1855</v>
-      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
@@ -49246,9 +47152,6 @@
           <t>Salzkotten Marathon</t>
         </is>
       </c>
-      <c r="AD1307" t="n">
-        <v>1813</v>
-      </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
@@ -49271,9 +47174,6 @@
           <t>Salzkotten Marathon</t>
         </is>
       </c>
-      <c r="AD1308" t="n">
-        <v>1813</v>
-      </c>
     </row>
     <row r="1309">
       <c r="A1309" t="inlineStr">
@@ -49296,9 +47196,6 @@
           <t>Salzkotten Marathon</t>
         </is>
       </c>
-      <c r="AD1309" t="n">
-        <v>1813</v>
-      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
@@ -49321,9 +47218,6 @@
           <t>Salzkotten Marathon</t>
         </is>
       </c>
-      <c r="AD1310" t="n">
-        <v>1813</v>
-      </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
@@ -49421,9 +47315,6 @@
           <t>Bajaj Pune Marathon</t>
         </is>
       </c>
-      <c r="AD1314" t="n">
-        <v>1803</v>
-      </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
@@ -49446,9 +47337,6 @@
           <t>Leiden Marathon</t>
         </is>
       </c>
-      <c r="AD1315" t="n">
-        <v>1775</v>
-      </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
@@ -49471,9 +47359,6 @@
           <t>Leiden Marathon</t>
         </is>
       </c>
-      <c r="AD1316" t="n">
-        <v>1775</v>
-      </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
@@ -49496,9 +47381,6 @@
           <t>Fulda Marathon</t>
         </is>
       </c>
-      <c r="AD1317" t="n">
-        <v>1766</v>
-      </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
@@ -49521,9 +47403,6 @@
           <t>Fulda Marathon</t>
         </is>
       </c>
-      <c r="AD1318" t="n">
-        <v>1766</v>
-      </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
@@ -49546,9 +47425,6 @@
           <t>Fulda Marathon</t>
         </is>
       </c>
-      <c r="AD1319" t="n">
-        <v>1766</v>
-      </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
@@ -49571,9 +47447,6 @@
           <t>Victoria Park Half marathon</t>
         </is>
       </c>
-      <c r="AD1320" t="n">
-        <v>1746</v>
-      </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
@@ -49596,9 +47469,6 @@
           <t>Victoria Park Half marathon</t>
         </is>
       </c>
-      <c r="AD1321" t="n">
-        <v>1746</v>
-      </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
@@ -49621,9 +47491,6 @@
           <t>Victoria Park Half marathon</t>
         </is>
       </c>
-      <c r="AD1322" t="n">
-        <v>1746</v>
-      </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
@@ -49646,9 +47513,6 @@
           <t>White marble marathon</t>
         </is>
       </c>
-      <c r="AD1323" t="n">
-        <v>1742</v>
-      </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
@@ -49671,9 +47535,6 @@
           <t>White marble marathon</t>
         </is>
       </c>
-      <c r="AD1324" t="n">
-        <v>1742</v>
-      </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
@@ -49721,9 +47582,6 @@
           <t>Trento Running Festival</t>
         </is>
       </c>
-      <c r="AD1326" t="n">
-        <v>1740</v>
-      </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
@@ -49746,9 +47604,6 @@
           <t>Trento Running Festival</t>
         </is>
       </c>
-      <c r="AD1327" t="n">
-        <v>1740</v>
-      </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
@@ -49776,9 +47631,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1328" t="n">
-        <v>1734</v>
-      </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
@@ -49806,9 +47658,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1329" t="n">
-        <v>1734</v>
-      </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
@@ -49911,9 +47760,6 @@
           <t>Zagreb21 Spring Half Marathon</t>
         </is>
       </c>
-      <c r="AD1333" t="n">
-        <v>1734</v>
-      </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
@@ -49936,9 +47782,6 @@
           <t>1/2 Maraton de la Mujer</t>
         </is>
       </c>
-      <c r="AD1334" t="n">
-        <v>1716</v>
-      </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
@@ -49961,9 +47804,6 @@
           <t>1/2 Maraton de la Mujer</t>
         </is>
       </c>
-      <c r="AD1335" t="n">
-        <v>1716</v>
-      </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
@@ -49986,9 +47826,6 @@
           <t>1/2 Maraton de la Mujer</t>
         </is>
       </c>
-      <c r="AD1336" t="n">
-        <v>1716</v>
-      </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
@@ -50011,9 +47848,6 @@
           <t>Sudstroum escher kulturlaf</t>
         </is>
       </c>
-      <c r="AD1337" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
@@ -50036,9 +47870,6 @@
           <t>Sudstroum escher kulturlaf</t>
         </is>
       </c>
-      <c r="AD1338" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
@@ -50061,9 +47892,6 @@
           <t>Sudstroum escher kulturlaf</t>
         </is>
       </c>
-      <c r="AD1339" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
@@ -50086,9 +47914,6 @@
           <t>Sudstroum escher kulturlaf</t>
         </is>
       </c>
-      <c r="AD1340" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
@@ -50111,9 +47936,6 @@
           <t>J.P Morgan City Jogging</t>
         </is>
       </c>
-      <c r="AD1341" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
@@ -50161,9 +47983,6 @@
           <t>Bodhgaya Marathon</t>
         </is>
       </c>
-      <c r="AD1343" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
@@ -50186,9 +48005,6 @@
           <t>Bodhgaya Marathon</t>
         </is>
       </c>
-      <c r="AD1344" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
@@ -50211,9 +48027,6 @@
           <t>Bodhgaya Marathon</t>
         </is>
       </c>
-      <c r="AD1345" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
@@ -50236,9 +48049,6 @@
           <t>Bodhgaya Marathon</t>
         </is>
       </c>
-      <c r="AD1346" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
@@ -50261,9 +48071,6 @@
           <t>Lucknow Half</t>
         </is>
       </c>
-      <c r="AD1347" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
@@ -50286,9 +48093,6 @@
           <t>Lucknow Half</t>
         </is>
       </c>
-      <c r="AD1348" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
@@ -50311,9 +48115,6 @@
           <t>Lucknow Half</t>
         </is>
       </c>
-      <c r="AD1349" t="n">
-        <v>1660</v>
-      </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
@@ -50336,9 +48137,6 @@
           <t>RunForLife</t>
         </is>
       </c>
-      <c r="AD1350" t="n">
-        <v>1639</v>
-      </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
@@ -50361,9 +48159,6 @@
           <t>RunForLife</t>
         </is>
       </c>
-      <c r="AD1351" t="n">
-        <v>1639</v>
-      </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
@@ -50386,9 +48181,6 @@
           <t>RunForLife</t>
         </is>
       </c>
-      <c r="AD1352" t="n">
-        <v>1639</v>
-      </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
@@ -50466,9 +48258,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1355" t="n">
-        <v>1600</v>
-      </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
@@ -50496,9 +48285,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1356" t="n">
-        <v>1600</v>
-      </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
@@ -50526,9 +48312,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1357" t="n">
-        <v>1600</v>
-      </c>
     </row>
     <row r="1358">
       <c r="A1358" t="inlineStr">
@@ -50556,9 +48339,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1358" t="n">
-        <v>1600</v>
-      </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
@@ -50636,9 +48416,6 @@
           <t>marathon halb marathon rostocker</t>
         </is>
       </c>
-      <c r="AD1361" t="n">
-        <v>1529</v>
-      </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
@@ -50661,9 +48438,6 @@
           <t>marathon halb marathon rostocker</t>
         </is>
       </c>
-      <c r="AD1362" t="n">
-        <v>1529</v>
-      </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
@@ -50711,9 +48485,6 @@
           <t>Parma Mezza maratona</t>
         </is>
       </c>
-      <c r="AD1364" t="n">
-        <v>1501</v>
-      </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
@@ -50736,9 +48507,6 @@
           <t>Parma Mezza maratona</t>
         </is>
       </c>
-      <c r="AD1365" t="n">
-        <v>1501</v>
-      </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
@@ -50761,9 +48529,6 @@
           <t>Med marathon</t>
         </is>
       </c>
-      <c r="AD1366" t="n">
-        <v>1494</v>
-      </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
@@ -50786,9 +48551,6 @@
           <t>Med marathon</t>
         </is>
       </c>
-      <c r="AD1367" t="n">
-        <v>1494</v>
-      </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
@@ -50836,9 +48598,6 @@
           <t>Comacchio Half Marathon</t>
         </is>
       </c>
-      <c r="AD1369" t="n">
-        <v>1453</v>
-      </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
@@ -50861,9 +48620,6 @@
           <t>Comacchio Half Marathon</t>
         </is>
       </c>
-      <c r="AD1370" t="n">
-        <v>1453</v>
-      </c>
     </row>
     <row r="1371">
       <c r="A1371" t="inlineStr">
@@ -50916,9 +48672,6 @@
           <t>Great Welsh Marathon</t>
         </is>
       </c>
-      <c r="AD1372" t="n">
-        <v>1424</v>
-      </c>
     </row>
     <row r="1373">
       <c r="A1373" t="inlineStr">
@@ -50941,9 +48694,6 @@
           <t>Great Welsh Marathon</t>
         </is>
       </c>
-      <c r="AD1373" t="n">
-        <v>1424</v>
-      </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
@@ -50966,9 +48716,6 @@
           <t>Great Welsh Marathon</t>
         </is>
       </c>
-      <c r="AD1374" t="n">
-        <v>1424</v>
-      </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
@@ -51016,9 +48763,6 @@
           <t>Media Marton Ciudad de Huelva</t>
         </is>
       </c>
-      <c r="AD1376" t="n">
-        <v>1408</v>
-      </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
@@ -51041,9 +48785,6 @@
           <t>Media Marton Ciudad de Huelva</t>
         </is>
       </c>
-      <c r="AD1377" t="n">
-        <v>1408</v>
-      </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
@@ -51066,9 +48807,6 @@
           <t>15K Formentera Sunset Run</t>
         </is>
       </c>
-      <c r="AD1378" t="n">
-        <v>1404</v>
-      </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
@@ -51216,9 +48954,6 @@
           <t>Binter Night Run Zaragoza</t>
         </is>
       </c>
-      <c r="AD1384" t="n">
-        <v>1384</v>
-      </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
@@ -51246,9 +48981,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1385" t="n">
-        <v>1368</v>
-      </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
@@ -51276,9 +49008,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1386" t="n">
-        <v>1368</v>
-      </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
@@ -51306,9 +49035,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1387" t="n">
-        <v>1368</v>
-      </c>
     </row>
     <row r="1388">
       <c r="A1388" t="inlineStr">
@@ -51431,9 +49157,6 @@
           <t>Run Festival Tossa de Mar</t>
         </is>
       </c>
-      <c r="AD1392" t="n">
-        <v>1338</v>
-      </c>
     </row>
     <row r="1393">
       <c r="A1393" t="inlineStr">
@@ -51456,9 +49179,6 @@
           <t>Run Festival Tossa de Mar</t>
         </is>
       </c>
-      <c r="AD1393" t="n">
-        <v>1338</v>
-      </c>
     </row>
     <row r="1394">
       <c r="A1394" t="inlineStr">
@@ -51481,9 +49201,6 @@
           <t>Run Festival Tossa de Mar</t>
         </is>
       </c>
-      <c r="AD1394" t="n">
-        <v>1338</v>
-      </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
@@ -51571,9 +49288,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1397" t="n">
-        <v>1328</v>
-      </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
@@ -51601,9 +49315,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1398" t="n">
-        <v>1328</v>
-      </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
@@ -51626,9 +49337,6 @@
           <t>Trieste21</t>
         </is>
       </c>
-      <c r="AD1399" t="n">
-        <v>1312</v>
-      </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
@@ -51651,9 +49359,6 @@
           <t>Trieste21</t>
         </is>
       </c>
-      <c r="AD1400" t="n">
-        <v>1312</v>
-      </c>
     </row>
     <row r="1401">
       <c r="A1401" t="inlineStr">
@@ -51676,9 +49381,6 @@
           <t>UST Trivandrum Marathon</t>
         </is>
       </c>
-      <c r="AD1401" t="n">
-        <v>1298</v>
-      </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
@@ -51701,9 +49403,6 @@
           <t>UST Trivandrum Marathon</t>
         </is>
       </c>
-      <c r="AD1402" t="n">
-        <v>1298</v>
-      </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
@@ -51726,9 +49425,6 @@
           <t>UST Trivandrum Marathon</t>
         </is>
       </c>
-      <c r="AD1403" t="n">
-        <v>1298</v>
-      </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
@@ -51751,9 +49447,6 @@
           <t>UST Trivandrum Marathon</t>
         </is>
       </c>
-      <c r="AD1404" t="n">
-        <v>1298</v>
-      </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
@@ -51776,9 +49469,6 @@
           <t>Rewe Women's Run</t>
         </is>
       </c>
-      <c r="AD1405" t="n">
-        <v>1296</v>
-      </c>
     </row>
     <row r="1406">
       <c r="A1406" t="inlineStr">
@@ -51801,9 +49491,6 @@
           <t>Rewe Women's Run</t>
         </is>
       </c>
-      <c r="AD1406" t="n">
-        <v>1296</v>
-      </c>
     </row>
     <row r="1407">
       <c r="A1407" t="inlineStr">
@@ -51826,9 +49513,6 @@
           <t>Media Maraton Pamplona</t>
         </is>
       </c>
-      <c r="AD1407" t="n">
-        <v>1292</v>
-      </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
@@ -51851,9 +49535,6 @@
           <t>Media Maraton Pamplona</t>
         </is>
       </c>
-      <c r="AD1408" t="n">
-        <v>1292</v>
-      </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
@@ -51876,9 +49557,6 @@
           <t>Marato Vies Verdes</t>
         </is>
       </c>
-      <c r="AD1409" t="n">
-        <v>1290</v>
-      </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
@@ -51901,9 +49579,6 @@
           <t>Marato Vies Verdes</t>
         </is>
       </c>
-      <c r="AD1410" t="n">
-        <v>1290</v>
-      </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
@@ -51926,9 +49601,6 @@
           <t>Marato Vies Verdes</t>
         </is>
       </c>
-      <c r="AD1411" t="n">
-        <v>1290</v>
-      </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
@@ -52006,9 +49678,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1414" t="n">
-        <v>1267</v>
-      </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
@@ -52036,9 +49705,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1415" t="n">
-        <v>1267</v>
-      </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
@@ -52066,9 +49732,6 @@
           <t>★</t>
         </is>
       </c>
-      <c r="AD1416" t="n">
-        <v>1267</v>
-      </c>
     </row>
     <row r="1417">
       <c r="A1417" t="inlineStr">
@@ -52116,9 +49779,6 @@
           <t>Norske Fjell Marathon</t>
         </is>
       </c>
-      <c r="AD1418" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
@@ -52141,9 +49801,6 @@
           <t>Norske Fjell Marathon</t>
         </is>
       </c>
-      <c r="AD1419" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
@@ -52166,9 +49823,6 @@
           <t>Norske Fjell Marathon</t>
         </is>
       </c>
-      <c r="AD1420" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1421">
       <c r="A1421" t="inlineStr">
@@ -52191,9 +49845,6 @@
           <t>Hindustan Marathon</t>
         </is>
       </c>
-      <c r="AD1421" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1422">
       <c r="A1422" t="inlineStr">
@@ -52216,9 +49867,6 @@
           <t>Hindustan Marathon</t>
         </is>
       </c>
-      <c r="AD1422" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1423">
       <c r="A1423" t="inlineStr">
@@ -52241,9 +49889,6 @@
           <t>Hindustan Marathon</t>
         </is>
       </c>
-      <c r="AD1423" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1424">
       <c r="A1424" t="inlineStr">
@@ -52266,9 +49911,6 @@
           <t>Run Bournemouth</t>
         </is>
       </c>
-      <c r="AD1424" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
@@ -52291,9 +49933,6 @@
           <t>Run Bournemouth</t>
         </is>
       </c>
-      <c r="AD1425" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
@@ -52316,9 +49955,6 @@
           <t>Run Bournemouth</t>
         </is>
       </c>
-      <c r="AD1426" t="n">
-        <v>1245</v>
-      </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
@@ -52401,9 +50037,6 @@
           <t>Corrida de Noël</t>
         </is>
       </c>
-      <c r="AD1429" t="n">
-        <v>1228</v>
-      </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
@@ -52426,9 +50059,6 @@
           <t>Corrida de Noël</t>
         </is>
       </c>
-      <c r="AD1430" t="n">
-        <v>1228</v>
-      </c>
     </row>
     <row r="1431">
       <c r="A1431" t="inlineStr">
@@ -52451,9 +50081,6 @@
           <t>Corrida de Noël</t>
         </is>
       </c>
-      <c r="AD1431" t="n">
-        <v>1228</v>
-      </c>
     </row>
     <row r="1432">
       <c r="A1432" t="inlineStr">
@@ -52476,9 +50103,6 @@
           <t>Marathon de Funchal</t>
         </is>
       </c>
-      <c r="AD1432" t="n">
-        <v>1192</v>
-      </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
@@ -52501,9 +50125,6 @@
           <t>Marathon de Funchal</t>
         </is>
       </c>
-      <c r="AD1433" t="n">
-        <v>1192</v>
-      </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
@@ -52601,9 +50222,6 @@
           <t>Dosti Thane Half Marathon</t>
         </is>
       </c>
-      <c r="AD1437" t="n">
-        <v>1184</v>
-      </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
@@ -52626,9 +50244,6 @@
           <t>Dosti Thane Half Marathon</t>
         </is>
       </c>
-      <c r="AD1438" t="n">
-        <v>1184</v>
-      </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
@@ -52651,9 +50266,6 @@
           <t>Palermo international half marathon</t>
         </is>
       </c>
-      <c r="AD1439" t="n">
-        <v>1128</v>
-      </c>
     </row>
     <row r="1440">
       <c r="A1440" t="inlineStr">
@@ -52676,9 +50288,6 @@
           <t>Palermo international half marathon</t>
         </is>
       </c>
-      <c r="AD1440" t="n">
-        <v>1128</v>
-      </c>
     </row>
     <row r="1441">
       <c r="A1441" t="inlineStr">
@@ -52701,9 +50310,6 @@
           <t>Palermo international half marathon</t>
         </is>
       </c>
-      <c r="AD1441" t="n">
-        <v>1128</v>
-      </c>
     </row>
     <row r="1442">
       <c r="A1442" t="inlineStr">
@@ -52726,9 +50332,6 @@
           <t>BrighTEN Marina Run</t>
         </is>
       </c>
-      <c r="AD1442" t="n">
-        <v>1125</v>
-      </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
@@ -52751,9 +50354,6 @@
           <t>BrighTEN Marina Run</t>
         </is>
       </c>
-      <c r="AD1443" t="n">
-        <v>1125</v>
-      </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
@@ -52776,9 +50376,6 @@
           <t>BrighTEN Marina Run</t>
         </is>
       </c>
-      <c r="AD1444" t="n">
-        <v>1125</v>
-      </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
@@ -52801,9 +50398,6 @@
           <t>Bodensee Marathon</t>
         </is>
       </c>
-      <c r="AD1445" t="n">
-        <v>1090</v>
-      </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
@@ -52826,9 +50420,6 @@
           <t>Bodensee Marathon</t>
         </is>
       </c>
-      <c r="AD1446" t="n">
-        <v>1090</v>
-      </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
@@ -52851,9 +50442,6 @@
           <t>Bodensee Marathon</t>
         </is>
       </c>
-      <c r="AD1447" t="n">
-        <v>1090</v>
-      </c>
     </row>
     <row r="1448">
       <c r="A1448" t="inlineStr">
@@ -52876,9 +50464,6 @@
           <t>Meia maratona de Braga</t>
         </is>
       </c>
-      <c r="AD1448" t="n">
-        <v>1057</v>
-      </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
@@ -52901,9 +50486,6 @@
           <t>Meia maratona de Braga</t>
         </is>
       </c>
-      <c r="AD1449" t="n">
-        <v>1057</v>
-      </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
@@ -52926,9 +50508,6 @@
           <t>Renascenca Fatima Half Marathon</t>
         </is>
       </c>
-      <c r="AD1450" t="n">
-        <v>1047</v>
-      </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
@@ -52951,9 +50530,6 @@
           <t>Renascenca Fatima Half Marathon</t>
         </is>
       </c>
-      <c r="AD1451" t="n">
-        <v>1047</v>
-      </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
@@ -52976,9 +50552,6 @@
           <t>Maastricht Marathon</t>
         </is>
       </c>
-      <c r="AD1452" t="n">
-        <v>1026</v>
-      </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
@@ -53001,9 +50574,6 @@
           <t>Maastricht Marathon</t>
         </is>
       </c>
-      <c r="AD1453" t="n">
-        <v>1026</v>
-      </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
@@ -53026,9 +50596,6 @@
           <t>Maastricht Marathon</t>
         </is>
       </c>
-      <c r="AD1454" t="n">
-        <v>1026</v>
-      </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
@@ -53051,9 +50618,6 @@
           <t>Maastricht Marathon</t>
         </is>
       </c>
-      <c r="AD1455" t="n">
-        <v>1026</v>
-      </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
@@ -53076,9 +50640,6 @@
           <t>Bibione half marathon</t>
         </is>
       </c>
-      <c r="AD1456" t="n">
-        <v>1012</v>
-      </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
@@ -53101,9 +50662,6 @@
           <t>Bibione half marathon</t>
         </is>
       </c>
-      <c r="AD1457" t="n">
-        <v>1012</v>
-      </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
@@ -53201,9 +50759,6 @@
           <t>Bahrain Night Half Marathon</t>
         </is>
       </c>
-      <c r="AD1461" t="n">
-        <v>830</v>
-      </c>
     </row>
     <row r="1462">
       <c r="A1462" t="inlineStr">
@@ -53226,9 +50781,6 @@
           <t>Bahrain Night Half Marathon</t>
         </is>
       </c>
-      <c r="AD1462" t="n">
-        <v>830</v>
-      </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
@@ -53376,9 +50928,6 @@
           <t>CrediMax Grand Prix</t>
         </is>
       </c>
-      <c r="AD1468" t="n">
-        <v>507</v>
-      </c>
     </row>
     <row r="1469">
       <c r="A1469" t="inlineStr">
@@ -53401,9 +50950,6 @@
           <t>CrediMax Grand Prix</t>
         </is>
       </c>
-      <c r="AD1469" t="n">
-        <v>507</v>
-      </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
@@ -53426,9 +50972,6 @@
           <t>Saaletal Marathon</t>
         </is>
       </c>
-      <c r="AD1470" t="n">
-        <v>496</v>
-      </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
@@ -53451,9 +50994,6 @@
           <t>Saaletal Marathon</t>
         </is>
       </c>
-      <c r="AD1471" t="n">
-        <v>496</v>
-      </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
@@ -53476,9 +51016,6 @@
           <t>Saaletal Marathon</t>
         </is>
       </c>
-      <c r="AD1472" t="n">
-        <v>496</v>
-      </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
@@ -53501,9 +51038,6 @@
           <t>Saaletal Marathon</t>
         </is>
       </c>
-      <c r="AD1473" t="n">
-        <v>496</v>
-      </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
@@ -53576,9 +51110,6 @@
           <t>Hunsrück Marathon</t>
         </is>
       </c>
-      <c r="AD1476" t="n">
-        <v>426</v>
-      </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
@@ -53601,9 +51132,6 @@
           <t>Hunsrück Marathon</t>
         </is>
       </c>
-      <c r="AD1477" t="n">
-        <v>426</v>
-      </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
@@ -53626,9 +51154,6 @@
           <t>Hunsrück Marathon</t>
         </is>
       </c>
-      <c r="AD1478" t="n">
-        <v>426</v>
-      </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
@@ -53651,9 +51176,6 @@
           <t>Indore Marathon</t>
         </is>
       </c>
-      <c r="AD1479" t="n">
-        <v>415</v>
-      </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
@@ -53676,9 +51198,6 @@
           <t>Indore Marathon</t>
         </is>
       </c>
-      <c r="AD1480" t="n">
-        <v>415</v>
-      </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
@@ -53701,9 +51220,6 @@
           <t>Indore Marathon</t>
         </is>
       </c>
-      <c r="AD1481" t="n">
-        <v>415</v>
-      </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
@@ -53751,9 +51267,6 @@
           <t>Peak Lake Garda 42</t>
         </is>
       </c>
-      <c r="AD1483" t="n">
-        <v>329</v>
-      </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
@@ -53775,9 +51288,6 @@
         <is>
           <t>Peak Lake Garda 42</t>
         </is>
-      </c>
-      <c r="AD1484" t="n">
-        <v>329</v>
       </c>
     </row>
     <row r="1485">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -21010,6 +21010,9 @@
           <t>Generali Geneve Marathon 10km</t>
         </is>
       </c>
+      <c r="AD199" t="n">
+        <v>4215</v>
+      </c>
       <c r="AE199" t="n">
         <v>5005</v>
       </c>
@@ -27587,6 +27590,9 @@
           <t>Dresden Marathon</t>
         </is>
       </c>
+      <c r="AD475" t="n">
+        <v>2084</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -27609,6 +27615,9 @@
           <t>Dresden Marathon</t>
         </is>
       </c>
+      <c r="AD476" t="n">
+        <v>6168</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -27653,6 +27662,9 @@
           <t>Dresden Marathon</t>
         </is>
       </c>
+      <c r="AD478" t="n">
+        <v>1111</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -30615,6 +30627,9 @@
           <t>★</t>
         </is>
       </c>
+      <c r="AD606" t="n">
+        <v>9510</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -30642,6 +30657,9 @@
           <t>★</t>
         </is>
       </c>
+      <c r="AD607" t="n">
+        <v>5729</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -32503,6 +32521,9 @@
           <t>Route du Louvre</t>
         </is>
       </c>
+      <c r="AD689" t="n">
+        <v>3600</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -32525,6 +32546,9 @@
           <t>Route du Louvre</t>
         </is>
       </c>
+      <c r="AD690" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -32682,6 +32706,9 @@
           <t>Euro Marathon Metz</t>
         </is>
       </c>
+      <c r="AD697" t="n">
+        <v>2200</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -34412,6 +34439,9 @@
           <t>Maraton de Zaragoza</t>
         </is>
       </c>
+      <c r="AD773" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -34434,6 +34464,9 @@
           <t>Maraton de Zaragoza</t>
         </is>
       </c>
+      <c r="AD774" t="n">
+        <v>5137</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -35094,6 +35127,9 @@
           <t>Les foulées Valenciennoises</t>
         </is>
       </c>
+      <c r="AD804" t="n">
+        <v>4400</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -35926,6 +35962,9 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
+      <c r="AD841" t="n">
+        <v>1620</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -35948,6 +35987,9 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
+      <c r="AD842" t="n">
+        <v>3240</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -35970,6 +36012,9 @@
           <t>Marathon des Grands Crus</t>
         </is>
       </c>
+      <c r="AD843" t="n">
+        <v>3240</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -36646,6 +36691,9 @@
           <t>Marathon de la mer</t>
         </is>
       </c>
+      <c r="AD873" t="n">
+        <v>1700</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -36668,6 +36716,9 @@
           <t>Marathon de la mer</t>
         </is>
       </c>
+      <c r="AD874" t="n">
+        <v>2400</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -37733,6 +37784,9 @@
           <t>Bengaluru 10K Challenge</t>
         </is>
       </c>
+      <c r="AD922" t="n">
+        <v>4630</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -43146,6 +43200,9 @@
           <t>Kolkata Full Marathon</t>
         </is>
       </c>
+      <c r="AD1157" t="n">
+        <v>304</v>
+      </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
@@ -43168,6 +43225,9 @@
           <t>Kolkata Full Marathon</t>
         </is>
       </c>
+      <c r="AD1158" t="n">
+        <v>604</v>
+      </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
@@ -43190,6 +43250,9 @@
           <t>Kolkata Full Marathon</t>
         </is>
       </c>
+      <c r="AD1159" t="n">
+        <v>1469</v>
+      </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
@@ -44323,6 +44386,9 @@
           <t>Hyderabad Hitec Marathon</t>
         </is>
       </c>
+      <c r="AD1208" t="n">
+        <v>797</v>
+      </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
@@ -44345,6 +44411,9 @@
           <t>Hyderabad Hitec Marathon</t>
         </is>
       </c>
+      <c r="AD1209" t="n">
+        <v>1082</v>
+      </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
@@ -47472,6 +47541,9 @@
           <t>Dosti Thane Half Marathon</t>
         </is>
       </c>
+      <c r="AD1343" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="1344">
       <c r="A1344" t="inlineStr">
@@ -47493,6 +47565,9 @@
         <is>
           <t>Dosti Thane Half Marathon</t>
         </is>
+      </c>
+      <c r="AD1344" t="n">
+        <v>896</v>
       </c>
     </row>
     <row r="1345">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -10487,9 +10487,6 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T77" t="n">
-        <v>20000</v>
-      </c>
       <c r="Y77" t="inlineStr">
         <is>
           <t>-</t>
@@ -10850,9 +10847,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AA80" t="n">
-        <v>13500</v>
-      </c>
       <c r="AB80" t="n">
         <v>12201</v>
       </c>
@@ -15611,9 +15605,6 @@
       <c r="V135" t="n">
         <v>4250</v>
       </c>
-      <c r="W135" t="n">
-        <v>4000</v>
-      </c>
       <c r="X135" t="n">
         <v>15382</v>
       </c>
@@ -18346,9 +18337,6 @@
       </c>
       <c r="Q168" t="n">
         <v>6470</v>
-      </c>
-      <c r="R168" t="n">
-        <v>8500</v>
       </c>
       <c r="S168" t="n">
         <v>10480</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -21189,6 +21189,38 @@
           <t>20KM de Bruxelles</t>
         </is>
       </c>
+      <c r="R207" t="n">
+        <v>37127</v>
+      </c>
+      <c r="S207" t="n">
+        <v>40370</v>
+      </c>
+      <c r="T207" t="n">
+        <v>40785</v>
+      </c>
+      <c r="U207" t="n">
+        <v>39418</v>
+      </c>
+      <c r="V207" t="n">
+        <v>36588</v>
+      </c>
+      <c r="W207" t="n">
+        <v>36899</v>
+      </c>
+      <c r="X207" t="n">
+        <v>33923</v>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z207" t="n">
+        <v>18889</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>29549</v>
+      </c>
       <c r="AB207" t="n">
         <v>36692</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -20683,7 +20683,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>AUTRE</t>
+          <t>5KM</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -8344,7 +8344,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Göteborg (Suède)</t>
+          <t>Göteborg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -21125,7 +21125,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>10KM</t>
+          <t>AUTRE</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -37819,6 +37819,9 @@
           <t>15Km de Woluwe</t>
         </is>
       </c>
+      <c r="AC922" t="n">
+        <v>3109</v>
+      </c>
       <c r="AD922" t="n">
         <v>4581</v>
       </c>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6117,6 +6117,9 @@
       <c r="W27" t="n">
         <v>11743</v>
       </c>
+      <c r="X27" t="n">
+        <v>8877</v>
+      </c>
       <c r="Y27" t="inlineStr">
         <is>
           <t>-</t>
@@ -17257,6 +17260,9 @@
       <c r="W155" t="n">
         <v>10014</v>
       </c>
+      <c r="X155" t="n">
+        <v>10079</v>
+      </c>
       <c r="Y155" t="inlineStr">
         <is>
           <t>-</t>
@@ -21133,6 +21139,34 @@
           <t>Course de l'escalade</t>
         </is>
       </c>
+      <c r="T205" t="n">
+        <v>38957</v>
+      </c>
+      <c r="U205" t="n">
+        <v>40566</v>
+      </c>
+      <c r="V205" t="n">
+        <v>46844</v>
+      </c>
+      <c r="W205" t="n">
+        <v>41221</v>
+      </c>
+      <c r="X205" t="n">
+        <v>40051</v>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA205" t="n">
+        <v>52588</v>
+      </c>
       <c r="AB205" t="n">
         <v>46765</v>
       </c>
@@ -24881,6 +24915,18 @@
         <is>
           <t>Antwerp Marathon</t>
         </is>
+      </c>
+      <c r="X358" t="n">
+        <v>2686</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>1056</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>2802</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>3744</v>
       </c>
       <c r="AD358" t="n">
         <v>1313</v>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4764,9 +4764,15 @@
           <t>x</t>
         </is>
       </c>
+      <c r="U12" t="n">
+        <v>16511</v>
+      </c>
       <c r="V12" t="n">
         <v>15242</v>
       </c>
+      <c r="W12" t="n">
+        <v>17855</v>
+      </c>
       <c r="X12" t="n">
         <v>16410</v>
       </c>
@@ -7062,6 +7068,9 @@
       </c>
       <c r="W40" t="n">
         <v>41645</v>
+      </c>
+      <c r="X40" t="n">
+        <v>43300</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4764,15 +4764,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="U12" t="n">
-        <v>16511</v>
-      </c>
       <c r="V12" t="n">
         <v>15242</v>
       </c>
-      <c r="W12" t="n">
-        <v>17855</v>
-      </c>
       <c r="X12" t="n">
         <v>16410</v>
       </c>
@@ -7068,9 +7062,6 @@
       </c>
       <c r="W40" t="n">
         <v>41645</v>
-      </c>
-      <c r="X40" t="n">
-        <v>43300</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -9824,6 +9824,9 @@
       <c r="AD69" t="n">
         <v>43654</v>
       </c>
+      <c r="AE69" t="n">
+        <v>43337</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6924,6 +6924,9 @@
       <c r="AD38" t="n">
         <v>56640</v>
       </c>
+      <c r="AE38" t="n">
+        <v>59830</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8222,6 +8225,9 @@
       <c r="AD53" t="n">
         <v>9286</v>
       </c>
+      <c r="AE53" t="n">
+        <v>8645</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9340,6 +9346,9 @@
       <c r="AD65" t="n">
         <v>7656</v>
       </c>
+      <c r="AE65" t="n">
+        <v>9041</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17694,6 +17703,9 @@
       </c>
       <c r="AD158" t="n">
         <v>11671</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>15550</v>
       </c>
     </row>
     <row r="159">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7163,6 +7163,9 @@
       <c r="AD41" t="n">
         <v>28506</v>
       </c>
+      <c r="AE41" t="n">
+        <v>29034</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7405,6 +7408,9 @@
       <c r="AD43" t="n">
         <v>23949</v>
       </c>
+      <c r="AE43" t="n">
+        <v>27977</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8060,6 +8066,9 @@
       <c r="AD51" t="n">
         <v>11464</v>
       </c>
+      <c r="AE51" t="n">
+        <v>12896</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -15965,6 +15974,9 @@
       <c r="AD137" t="n">
         <v>17278</v>
       </c>
+      <c r="AE137" t="n">
+        <v>2527</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17988,6 +18000,9 @@
       <c r="AD161" t="n">
         <v>8324</v>
       </c>
+      <c r="AE161" t="n">
+        <v>11948</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -19936,6 +19951,9 @@
       <c r="AD183" t="n">
         <v>3729</v>
       </c>
+      <c r="AE183" t="n">
+        <v>5602</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -29400,6 +29418,9 @@
       <c r="AD541" t="n">
         <v>11020</v>
       </c>
+      <c r="AE541" t="n">
+        <v>5232</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -30276,6 +30297,9 @@
       </c>
       <c r="AD578" t="n">
         <v>10313</v>
+      </c>
+      <c r="AE578" t="n">
+        <v>1115</v>
       </c>
     </row>
     <row r="579">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -6380,6 +6380,9 @@
       <c r="AD31" t="n">
         <v>19112</v>
       </c>
+      <c r="AE31" t="n">
+        <v>16805</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -18196,6 +18199,9 @@
       <c r="AD164" t="n">
         <v>26175</v>
       </c>
+      <c r="AE164" t="n">
+        <v>30683</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -22339,6 +22345,9 @@
       <c r="AD246" t="n">
         <v>27390</v>
       </c>
+      <c r="AE246" t="n">
+        <v>24088</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -22364,6 +22373,9 @@
       <c r="AD247" t="n">
         <v>27390</v>
       </c>
+      <c r="AE247" t="n">
+        <v>8498</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25196,6 +25208,9 @@
           <t>★</t>
         </is>
       </c>
+      <c r="AE363" t="n">
+        <v>14049</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -25727,6 +25742,9 @@
       <c r="AD385" t="n">
         <v>15421</v>
       </c>
+      <c r="AE385" t="n">
+        <v>16526</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -27546,6 +27564,9 @@
           <t>Marathon de Biarritz</t>
         </is>
       </c>
+      <c r="AE460" t="n">
+        <v>1933</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -41697,6 +41718,9 @@
           <t>Marathon Golfe de Saint-Tropez</t>
         </is>
       </c>
+      <c r="AE1071" t="n">
+        <v>1568</v>
+      </c>
     </row>
     <row r="1072">
       <c r="A1072" t="inlineStr">
@@ -58543,6 +58567,9 @@
         <is>
           <t>Marathon des deux rives</t>
         </is>
+      </c>
+      <c r="AE1813" t="n">
+        <v>482</v>
       </c>
     </row>
     <row r="1814">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3750,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1962"/>
+  <dimension ref="A1:AE1963"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -5586,6 +5586,9 @@
       <c r="AC20" t="n">
         <v>35443</v>
       </c>
+      <c r="AD20" t="n">
+        <v>36204</v>
+      </c>
       <c r="AE20" t="n">
         <v>37244</v>
       </c>
@@ -61851,6 +61854,31 @@
         <is>
           <t>Canberra Times Marathon Festival</t>
         </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>Xiamen</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>MARATHON</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>C&amp;D Xiamen Marathon</t>
+        </is>
+      </c>
+      <c r="AE1963" t="n">
+        <v>30581</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -3750,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1963"/>
+  <dimension ref="A1:AE1964"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="18.21875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -61879,6 +61879,31 @@
       </c>
       <c r="AE1963" t="n">
         <v>30581</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>Février</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>10KM</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>Standard Chartered Hong Kong Marathon</t>
+        </is>
+      </c>
+      <c r="AE1964" t="n">
+        <v>28635</v>
       </c>
     </row>
   </sheetData>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -4721,7 +4721,7 @@
         <v>22872</v>
       </c>
       <c r="AE11" t="n">
-        <v>26621</v>
+        <v>22475</v>
       </c>
     </row>
     <row r="12">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26298,7 +26298,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SEMI</t>
+          <t>10KM</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -30214,7 +30214,7 @@
         <v>10393</v>
       </c>
       <c r="AE573" t="n">
-        <v>10393</v>
+        <v>12153</v>
       </c>
     </row>
     <row r="574">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -22204,6 +22204,9 @@
       <c r="AD240" t="n">
         <v>28858</v>
       </c>
+      <c r="AE240" t="n">
+        <v>14687</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -7661,6 +7661,9 @@
       <c r="AD45" t="n">
         <v>19850</v>
       </c>
+      <c r="AE45" t="n">
+        <v>19817</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26341,6 +26341,9 @@
           <t>Allianz Jean Bouin</t>
         </is>
       </c>
+      <c r="AE409" t="n">
+        <v>11240</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -26341,7 +26341,7 @@
           <t>Allianz Jean Bouin</t>
         </is>
       </c>
-      <c r="AE409" t="n">
+      <c r="AD409" t="n">
         <v>11240</v>
       </c>
     </row>

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1884" yWindow="1884" windowWidth="17280" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10K" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21K" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42K" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIGGEST EVENTS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="10K" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="21K" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="42K" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ALL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BIGGEST EVENTS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -18750,6 +18750,9 @@
       <c r="AD170" t="n">
         <v>7645</v>
       </c>
+      <c r="AE170" t="n">
+        <v>19256</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">

--- a/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
+++ b/Suivi_Finishers_Monde_10k_-_21k_-_42k_HISTORIQUE.xlsx
@@ -9213,6 +9213,9 @@
       <c r="AD63" t="n">
         <v>12300</v>
       </c>
+      <c r="AE63" t="n">
+        <v>31340</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
